--- a/domain-investing/domain-portfolio-tracker.xlsx
+++ b/domain-investing/domain-portfolio-tracker.xlsx
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="683">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="761">
   <si>
     <t xml:space="preserve">Domain Investing — Rubric &amp; Portfolio Tracker</t>
   </si>
@@ -1674,6 +1674,240 @@
   </si>
   <si>
     <t xml:space="preserve">[B3/Control] CONTROL — same. Included so you can see the model reject it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticcommerce.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Agents transacting is the biggest live commercial problem in the space. Closest in kind to the $150k sale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticpayments.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Stripe and Coinbase are both shipping machine-to-machine payment rails.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticsecurity.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Autonomy creates the attack surface; a named 2026 problem after the ChatGPT agent hack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticfinance.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Vertical compound, high-value buyer pool.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticworkflows.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Orchestration is the layer where Cognition and AnySphere are valued in the billions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticsystems.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Broad and institutional. Reads like a consultancy or a platform.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticcloud.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Infrastructure framing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticdata.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Short, clean, obvious enterprise buyer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticcore.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] 'Core' is on the reported 2026 investor keyword list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticlabs.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] 'Labs' is likewise on that list, and reads as a company name.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticnetwork.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Fits the A2A interoperability story.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticsearch.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Perplexity at $9B makes this a live category.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentichealth.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Vertical compound into the highest-value sector there is.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticretail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Vertical compound, clear buyer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticenterprise.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Enterprise framing, slightly long.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agenticinfrastructure.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Agentic+] Precise but 21 characters. Length is the weakness.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentprotocol.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Protocol] The generic term above MCP/A2A/ACP. Strong if any of them converge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentgateway.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Protocol] Gateways are where agent traffic gets controlled and billed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentrouter.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Protocol] Same layer, shorter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentbroker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Protocol] Brokering between agents — the A2A middle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentdirectory.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Protocol] Agent discovery is genuinely unsolved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentinterop.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Protocol] Exact word the standards bodies use. 'Interop' is jargon-y spoken.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contextprotocol.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Protocol] Adjacent to Anthropic's Model Context Protocol. Open standard, not a brand — but check before relying on the association.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentcommerce.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Payments] Non-'agentic' variant of the top pick; likely gone, worth testing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentwallet.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Payments] An agent needs somewhere to hold funds. Concrete and short.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentcheckout.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Payments] The merchant side of the same problem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">machinepayments.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Payments] M2M framing — survives even if 'agent' falls out of fashion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autonomouspayments.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Payments] Precise, and the longest name here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentspend.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Payments] Spend management for agents. Reads like a real SaaS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentsecurity.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Security] Plainest statement of the category.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentguard.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Security] Product-shaped and brandable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentfirewall.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Security] Borrowed metaphor that enterprise buyers already understand.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentsandbox.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Security] Sandboxing is how you actually contain an agent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentpermissions.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Security] The authorisation half of agent identity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentconsent.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/Security] Narrower, more legal-flavoured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentmemory.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/AgentOps] Memory is the hardest unsolved piece of agent design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentevals.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/AgentOps] Evaluation is a real budget line. 'Evals' is insider but universal in the field.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agentobservability.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/AgentOps] Exact enterprise term, punishingly long.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contextengineering.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[B4/AgentOps] Has largely replaced 'prompt engineering' as the serious term.</t>
   </si>
   <si>
     <t xml:space="preserve">Closeout Screener — expired names at $5-$11</t>
@@ -2704,10 +2938,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2794,6 +3024,10 @@
     </xf>
     <xf numFmtId="173" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="174" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -12895,8 +13129,8 @@
       <c r="I113" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J113" s="47"/>
-      <c r="K113" s="48"/>
+      <c r="J113" s="27"/>
+      <c r="K113" s="28"/>
       <c r="L113" s="26"/>
       <c r="M113" s="39" t="n">
         <f aca="false">IF($B113="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B113,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -12975,8 +13209,8 @@
       <c r="I114" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J114" s="47"/>
-      <c r="K114" s="48"/>
+      <c r="J114" s="27"/>
+      <c r="K114" s="28"/>
       <c r="L114" s="26"/>
       <c r="M114" s="39" t="n">
         <f aca="false">IF($B114="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B114,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13055,8 +13289,8 @@
       <c r="I115" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J115" s="47"/>
-      <c r="K115" s="48"/>
+      <c r="J115" s="27"/>
+      <c r="K115" s="28"/>
       <c r="L115" s="26"/>
       <c r="M115" s="39" t="n">
         <f aca="false">IF($B115="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B115,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13135,8 +13369,8 @@
       <c r="I116" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J116" s="47"/>
-      <c r="K116" s="48"/>
+      <c r="J116" s="27"/>
+      <c r="K116" s="28"/>
       <c r="L116" s="26"/>
       <c r="M116" s="39" t="n">
         <f aca="false">IF($B116="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B116,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13215,8 +13449,8 @@
       <c r="I117" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J117" s="47"/>
-      <c r="K117" s="48"/>
+      <c r="J117" s="27"/>
+      <c r="K117" s="28"/>
       <c r="L117" s="26"/>
       <c r="M117" s="39" t="n">
         <f aca="false">IF($B117="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B117,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13295,8 +13529,8 @@
       <c r="I118" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J118" s="47"/>
-      <c r="K118" s="48"/>
+      <c r="J118" s="27"/>
+      <c r="K118" s="28"/>
       <c r="L118" s="26"/>
       <c r="M118" s="39" t="n">
         <f aca="false">IF($B118="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B118,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13375,8 +13609,8 @@
       <c r="I119" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J119" s="47"/>
-      <c r="K119" s="48"/>
+      <c r="J119" s="27"/>
+      <c r="K119" s="28"/>
       <c r="L119" s="26"/>
       <c r="M119" s="39" t="n">
         <f aca="false">IF($B119="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B119,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13455,8 +13689,8 @@
       <c r="I120" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J120" s="47"/>
-      <c r="K120" s="48"/>
+      <c r="J120" s="27"/>
+      <c r="K120" s="28"/>
       <c r="L120" s="26"/>
       <c r="M120" s="39" t="n">
         <f aca="false">IF($B120="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B120,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13535,8 +13769,8 @@
       <c r="I121" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J121" s="47"/>
-      <c r="K121" s="48"/>
+      <c r="J121" s="27"/>
+      <c r="K121" s="28"/>
       <c r="L121" s="26"/>
       <c r="M121" s="39" t="n">
         <f aca="false">IF($B121="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B121,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13615,8 +13849,8 @@
       <c r="I122" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J122" s="47"/>
-      <c r="K122" s="48"/>
+      <c r="J122" s="27"/>
+      <c r="K122" s="28"/>
       <c r="L122" s="26"/>
       <c r="M122" s="39" t="n">
         <f aca="false">IF($B122="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B122,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13695,8 +13929,8 @@
       <c r="I123" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J123" s="47"/>
-      <c r="K123" s="48"/>
+      <c r="J123" s="27"/>
+      <c r="K123" s="28"/>
       <c r="L123" s="26"/>
       <c r="M123" s="39" t="n">
         <f aca="false">IF($B123="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B123,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13775,8 +14009,8 @@
       <c r="I124" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J124" s="47"/>
-      <c r="K124" s="48"/>
+      <c r="J124" s="27"/>
+      <c r="K124" s="28"/>
       <c r="L124" s="26"/>
       <c r="M124" s="39" t="n">
         <f aca="false">IF($B124="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B124,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13855,8 +14089,8 @@
       <c r="I125" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J125" s="47"/>
-      <c r="K125" s="48"/>
+      <c r="J125" s="27"/>
+      <c r="K125" s="28"/>
       <c r="L125" s="26"/>
       <c r="M125" s="39" t="n">
         <f aca="false">IF($B125="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B125,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -13935,8 +14169,8 @@
       <c r="I126" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J126" s="47"/>
-      <c r="K126" s="48"/>
+      <c r="J126" s="27"/>
+      <c r="K126" s="28"/>
       <c r="L126" s="26"/>
       <c r="M126" s="39" t="n">
         <f aca="false">IF($B126="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B126,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14015,8 +14249,8 @@
       <c r="I127" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J127" s="47"/>
-      <c r="K127" s="48"/>
+      <c r="J127" s="27"/>
+      <c r="K127" s="28"/>
       <c r="L127" s="26"/>
       <c r="M127" s="39" t="n">
         <f aca="false">IF($B127="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B127,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14095,8 +14329,8 @@
       <c r="I128" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J128" s="47"/>
-      <c r="K128" s="48"/>
+      <c r="J128" s="27"/>
+      <c r="K128" s="28"/>
       <c r="L128" s="26"/>
       <c r="M128" s="39" t="n">
         <f aca="false">IF($B128="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B128,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14175,8 +14409,8 @@
       <c r="I129" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J129" s="47"/>
-      <c r="K129" s="48"/>
+      <c r="J129" s="27"/>
+      <c r="K129" s="28"/>
       <c r="L129" s="26"/>
       <c r="M129" s="39" t="n">
         <f aca="false">IF($B129="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B129,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14255,8 +14489,8 @@
       <c r="I130" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J130" s="47"/>
-      <c r="K130" s="48"/>
+      <c r="J130" s="27"/>
+      <c r="K130" s="28"/>
       <c r="L130" s="26"/>
       <c r="M130" s="39" t="n">
         <f aca="false">IF($B130="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B130,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14335,8 +14569,8 @@
       <c r="I131" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J131" s="47"/>
-      <c r="K131" s="48"/>
+      <c r="J131" s="27"/>
+      <c r="K131" s="28"/>
       <c r="L131" s="26"/>
       <c r="M131" s="39" t="n">
         <f aca="false">IF($B131="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B131,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14415,8 +14649,8 @@
       <c r="I132" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J132" s="47"/>
-      <c r="K132" s="48"/>
+      <c r="J132" s="27"/>
+      <c r="K132" s="28"/>
       <c r="L132" s="26"/>
       <c r="M132" s="39" t="n">
         <f aca="false">IF($B132="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B132,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14495,8 +14729,8 @@
       <c r="I133" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J133" s="47"/>
-      <c r="K133" s="48"/>
+      <c r="J133" s="27"/>
+      <c r="K133" s="28"/>
       <c r="L133" s="26"/>
       <c r="M133" s="39" t="n">
         <f aca="false">IF($B133="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B133,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14575,8 +14809,8 @@
       <c r="I134" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J134" s="47"/>
-      <c r="K134" s="48"/>
+      <c r="J134" s="27"/>
+      <c r="K134" s="28"/>
       <c r="L134" s="26"/>
       <c r="M134" s="39" t="n">
         <f aca="false">IF($B134="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B134,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14655,8 +14889,8 @@
       <c r="I135" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J135" s="47"/>
-      <c r="K135" s="48"/>
+      <c r="J135" s="27"/>
+      <c r="K135" s="28"/>
       <c r="L135" s="26"/>
       <c r="M135" s="39" t="n">
         <f aca="false">IF($B135="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B135,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14735,8 +14969,8 @@
       <c r="I136" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J136" s="47"/>
-      <c r="K136" s="48"/>
+      <c r="J136" s="27"/>
+      <c r="K136" s="28"/>
       <c r="L136" s="26"/>
       <c r="M136" s="39" t="n">
         <f aca="false">IF($B136="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B136,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14815,8 +15049,8 @@
       <c r="I137" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J137" s="47"/>
-      <c r="K137" s="48"/>
+      <c r="J137" s="27"/>
+      <c r="K137" s="28"/>
       <c r="L137" s="26"/>
       <c r="M137" s="39" t="n">
         <f aca="false">IF($B137="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B137,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14895,8 +15129,8 @@
       <c r="I138" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J138" s="47"/>
-      <c r="K138" s="48"/>
+      <c r="J138" s="27"/>
+      <c r="K138" s="28"/>
       <c r="L138" s="26"/>
       <c r="M138" s="39" t="n">
         <f aca="false">IF($B138="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B138,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -14975,8 +15209,8 @@
       <c r="I139" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J139" s="47"/>
-      <c r="K139" s="48"/>
+      <c r="J139" s="27"/>
+      <c r="K139" s="28"/>
       <c r="L139" s="26"/>
       <c r="M139" s="39" t="n">
         <f aca="false">IF($B139="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B139,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15055,8 +15289,8 @@
       <c r="I140" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J140" s="47"/>
-      <c r="K140" s="48"/>
+      <c r="J140" s="27"/>
+      <c r="K140" s="28"/>
       <c r="L140" s="26"/>
       <c r="M140" s="39" t="n">
         <f aca="false">IF($B140="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B140,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15135,8 +15369,8 @@
       <c r="I141" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J141" s="47"/>
-      <c r="K141" s="48"/>
+      <c r="J141" s="27"/>
+      <c r="K141" s="28"/>
       <c r="L141" s="26"/>
       <c r="M141" s="39" t="n">
         <f aca="false">IF($B141="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B141,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15215,8 +15449,8 @@
       <c r="I142" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J142" s="47"/>
-      <c r="K142" s="48"/>
+      <c r="J142" s="27"/>
+      <c r="K142" s="28"/>
       <c r="L142" s="26"/>
       <c r="M142" s="39" t="n">
         <f aca="false">IF($B142="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B142,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15295,8 +15529,8 @@
       <c r="I143" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J143" s="47"/>
-      <c r="K143" s="48"/>
+      <c r="J143" s="27"/>
+      <c r="K143" s="28"/>
       <c r="L143" s="26"/>
       <c r="M143" s="39" t="n">
         <f aca="false">IF($B143="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B143,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15375,8 +15609,8 @@
       <c r="I144" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J144" s="47"/>
-      <c r="K144" s="48"/>
+      <c r="J144" s="27"/>
+      <c r="K144" s="28"/>
       <c r="L144" s="26"/>
       <c r="M144" s="39" t="n">
         <f aca="false">IF($B144="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B144,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15455,8 +15689,8 @@
       <c r="I145" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J145" s="47"/>
-      <c r="K145" s="48"/>
+      <c r="J145" s="27"/>
+      <c r="K145" s="28"/>
       <c r="L145" s="26"/>
       <c r="M145" s="39" t="n">
         <f aca="false">IF($B145="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B145,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15535,8 +15769,8 @@
       <c r="I146" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J146" s="47"/>
-      <c r="K146" s="48"/>
+      <c r="J146" s="27"/>
+      <c r="K146" s="28"/>
       <c r="L146" s="26"/>
       <c r="M146" s="39" t="n">
         <f aca="false">IF($B146="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B146,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15615,8 +15849,8 @@
       <c r="I147" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J147" s="47"/>
-      <c r="K147" s="48"/>
+      <c r="J147" s="27"/>
+      <c r="K147" s="28"/>
       <c r="L147" s="26"/>
       <c r="M147" s="39" t="n">
         <f aca="false">IF($B147="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B147,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15695,8 +15929,8 @@
       <c r="I148" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J148" s="47"/>
-      <c r="K148" s="48"/>
+      <c r="J148" s="27"/>
+      <c r="K148" s="28"/>
       <c r="L148" s="26"/>
       <c r="M148" s="39" t="n">
         <f aca="false">IF($B148="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B148,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15775,8 +16009,8 @@
       <c r="I149" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J149" s="47"/>
-      <c r="K149" s="48"/>
+      <c r="J149" s="27"/>
+      <c r="K149" s="28"/>
       <c r="L149" s="26"/>
       <c r="M149" s="39" t="n">
         <f aca="false">IF($B149="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B149,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15855,8 +16089,8 @@
       <c r="I150" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J150" s="47"/>
-      <c r="K150" s="48"/>
+      <c r="J150" s="27"/>
+      <c r="K150" s="28"/>
       <c r="L150" s="26"/>
       <c r="M150" s="39" t="n">
         <f aca="false">IF($B150="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B150,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -15935,8 +16169,8 @@
       <c r="I151" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J151" s="47"/>
-      <c r="K151" s="48"/>
+      <c r="J151" s="27"/>
+      <c r="K151" s="28"/>
       <c r="L151" s="26"/>
       <c r="M151" s="39" t="n">
         <f aca="false">IF($B151="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B151,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16015,8 +16249,8 @@
       <c r="I152" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J152" s="47"/>
-      <c r="K152" s="48"/>
+      <c r="J152" s="27"/>
+      <c r="K152" s="28"/>
       <c r="L152" s="26"/>
       <c r="M152" s="39" t="n">
         <f aca="false">IF($B152="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B152,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16095,8 +16329,8 @@
       <c r="I153" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J153" s="47"/>
-      <c r="K153" s="48"/>
+      <c r="J153" s="27"/>
+      <c r="K153" s="28"/>
       <c r="L153" s="26"/>
       <c r="M153" s="39" t="n">
         <f aca="false">IF($B153="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B153,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16175,8 +16409,8 @@
       <c r="I154" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J154" s="47"/>
-      <c r="K154" s="48"/>
+      <c r="J154" s="27"/>
+      <c r="K154" s="28"/>
       <c r="L154" s="26"/>
       <c r="M154" s="39" t="n">
         <f aca="false">IF($B154="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B154,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16255,8 +16489,8 @@
       <c r="I155" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J155" s="47"/>
-      <c r="K155" s="48"/>
+      <c r="J155" s="27"/>
+      <c r="K155" s="28"/>
       <c r="L155" s="26"/>
       <c r="M155" s="39" t="n">
         <f aca="false">IF($B155="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B155,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16335,8 +16569,8 @@
       <c r="I156" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="J156" s="47"/>
-      <c r="K156" s="48"/>
+      <c r="J156" s="27"/>
+      <c r="K156" s="28"/>
       <c r="L156" s="26"/>
       <c r="M156" s="39" t="n">
         <f aca="false">IF($B156="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B156,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16415,8 +16649,8 @@
       <c r="I157" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J157" s="47"/>
-      <c r="K157" s="48"/>
+      <c r="J157" s="27"/>
+      <c r="K157" s="28"/>
       <c r="L157" s="26"/>
       <c r="M157" s="39" t="n">
         <f aca="false">IF($B157="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B157,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16495,8 +16729,8 @@
       <c r="I158" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J158" s="47"/>
-      <c r="K158" s="48"/>
+      <c r="J158" s="27"/>
+      <c r="K158" s="28"/>
       <c r="L158" s="26"/>
       <c r="M158" s="39" t="n">
         <f aca="false">IF($B158="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B158,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16575,8 +16809,8 @@
       <c r="I159" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J159" s="47"/>
-      <c r="K159" s="48"/>
+      <c r="J159" s="27"/>
+      <c r="K159" s="28"/>
       <c r="L159" s="26"/>
       <c r="M159" s="39" t="n">
         <f aca="false">IF($B159="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B159,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16655,8 +16889,8 @@
       <c r="I160" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J160" s="47"/>
-      <c r="K160" s="48"/>
+      <c r="J160" s="27"/>
+      <c r="K160" s="28"/>
       <c r="L160" s="26"/>
       <c r="M160" s="39" t="n">
         <f aca="false">IF($B160="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B160,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16735,8 +16969,8 @@
       <c r="I161" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J161" s="47"/>
-      <c r="K161" s="48"/>
+      <c r="J161" s="27"/>
+      <c r="K161" s="28"/>
       <c r="L161" s="26"/>
       <c r="M161" s="39" t="n">
         <f aca="false">IF($B161="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B161,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16815,8 +17049,8 @@
       <c r="I162" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J162" s="47"/>
-      <c r="K162" s="48"/>
+      <c r="J162" s="27"/>
+      <c r="K162" s="28"/>
       <c r="L162" s="26"/>
       <c r="M162" s="39" t="n">
         <f aca="false">IF($B162="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B162,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16895,8 +17129,8 @@
       <c r="I163" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J163" s="47"/>
-      <c r="K163" s="48"/>
+      <c r="J163" s="27"/>
+      <c r="K163" s="28"/>
       <c r="L163" s="26"/>
       <c r="M163" s="39" t="n">
         <f aca="false">IF($B163="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B163,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -16975,8 +17209,8 @@
       <c r="I164" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J164" s="47"/>
-      <c r="K164" s="48"/>
+      <c r="J164" s="27"/>
+      <c r="K164" s="28"/>
       <c r="L164" s="26"/>
       <c r="M164" s="39" t="n">
         <f aca="false">IF($B164="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B164,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17055,8 +17289,8 @@
       <c r="I165" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J165" s="47"/>
-      <c r="K165" s="48"/>
+      <c r="J165" s="27"/>
+      <c r="K165" s="28"/>
       <c r="L165" s="26"/>
       <c r="M165" s="39" t="n">
         <f aca="false">IF($B165="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B165,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17106,47 +17340,61 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="49"/>
+      <c r="A166" s="23" t="s">
+        <v>497</v>
+      </c>
       <c r="B166" s="37" t="str">
         <f aca="false">IF($A166="","",IF(ISERROR(FIND(".",$A166)),"",LOWER(MID($A166,FIND(CHAR(1),SUBSTITUTE($A166,".",CHAR(1),LEN($A166)-LEN(SUBSTITUTE($A166,".",""))))+1,LEN($A166)))))</f>
-        <v/>
-      </c>
-      <c r="C166" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C166" s="38" t="n">
         <f aca="false">IF($B166="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B166,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D166" s="26"/>
-      <c r="E166" s="26"/>
-      <c r="F166" s="26"/>
-      <c r="G166" s="26"/>
-      <c r="H166" s="26"/>
-      <c r="I166" s="26"/>
-      <c r="J166" s="27"/>
-      <c r="K166" s="28"/>
-      <c r="L166" s="49"/>
-      <c r="M166" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D166" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E166" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F166" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G166" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H166" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I166" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J166" s="47"/>
+      <c r="K166" s="48"/>
+      <c r="L166" s="26"/>
+      <c r="M166" s="39" t="n">
         <f aca="false">IF($B166="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B166,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N166" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N166" s="40" t="n">
         <f aca="false">IF(OR($A166="",$C166=""),"",$C166*Rubric!$B$5+$D166*Rubric!$B$6+$E166*Rubric!$B$7+$F166*Rubric!$B$8+$G166*Rubric!$B$9)</f>
-        <v/>
+        <v>4.84</v>
       </c>
       <c r="O166" s="41" t="str">
         <f aca="false">IF($A166="","",IF(OR(UPPER($H166)="Y",UPPER($I166)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P166" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P166" s="42" t="n">
         <f aca="false">IF($N166="","",Assumptions!$B$6*MAX(0.05,($N166/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q166" s="42" t="str">
+        <v>0.0322666666666667</v>
+      </c>
+      <c r="Q166" s="42" t="n">
         <f aca="false">IF($P166="","",1-(1-$P166)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R166" s="43" t="str">
+        <v>0.15125251114852</v>
+      </c>
+      <c r="R166" s="43" t="n">
         <f aca="false">IF($M166="","",$M166*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S166" s="43" t="str">
         <f aca="false">IF(OR($J166="",$Q166="",$Q166=0),"",($J166+$R166)/($Q166*(1-Assumptions!$B$4)))</f>
@@ -17162,53 +17410,71 @@
       </c>
       <c r="V166" s="41" t="str">
         <f aca="false">IF($A166="","",IF($O166="FAIL","REJECT",IF($J166="","NEEDS PRICE",IF(OR($K166="",$L166=""),"NEEDS VALUATION",IF($T166&gt;=Assumptions!$B$13,"BUY",IF($T166&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W166" s="26"/>
-      <c r="X166" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W166" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X166" s="36" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="49"/>
+      <c r="A167" s="23" t="s">
+        <v>499</v>
+      </c>
       <c r="B167" s="37" t="str">
         <f aca="false">IF($A167="","",IF(ISERROR(FIND(".",$A167)),"",LOWER(MID($A167,FIND(CHAR(1),SUBSTITUTE($A167,".",CHAR(1),LEN($A167)-LEN(SUBSTITUTE($A167,".",""))))+1,LEN($A167)))))</f>
-        <v/>
-      </c>
-      <c r="C167" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C167" s="38" t="n">
         <f aca="false">IF($B167="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B167,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
-      <c r="F167" s="26"/>
-      <c r="G167" s="26"/>
-      <c r="H167" s="26"/>
-      <c r="I167" s="26"/>
-      <c r="J167" s="27"/>
-      <c r="K167" s="28"/>
-      <c r="L167" s="49"/>
-      <c r="M167" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D167" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E167" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F167" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G167" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H167" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I167" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J167" s="47"/>
+      <c r="K167" s="48"/>
+      <c r="L167" s="26"/>
+      <c r="M167" s="39" t="n">
         <f aca="false">IF($B167="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B167,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N167" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N167" s="40" t="n">
         <f aca="false">IF(OR($A167="",$C167=""),"",$C167*Rubric!$B$5+$D167*Rubric!$B$6+$E167*Rubric!$B$7+$F167*Rubric!$B$8+$G167*Rubric!$B$9)</f>
-        <v/>
+        <v>4.84</v>
       </c>
       <c r="O167" s="41" t="str">
         <f aca="false">IF($A167="","",IF(OR(UPPER($H167)="Y",UPPER($I167)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P167" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P167" s="42" t="n">
         <f aca="false">IF($N167="","",Assumptions!$B$6*MAX(0.05,($N167/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q167" s="42" t="str">
+        <v>0.0322666666666667</v>
+      </c>
+      <c r="Q167" s="42" t="n">
         <f aca="false">IF($P167="","",1-(1-$P167)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R167" s="43" t="str">
+        <v>0.15125251114852</v>
+      </c>
+      <c r="R167" s="43" t="n">
         <f aca="false">IF($M167="","",$M167*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S167" s="43" t="str">
         <f aca="false">IF(OR($J167="",$Q167="",$Q167=0),"",($J167+$R167)/($Q167*(1-Assumptions!$B$4)))</f>
@@ -17224,53 +17490,71 @@
       </c>
       <c r="V167" s="41" t="str">
         <f aca="false">IF($A167="","",IF($O167="FAIL","REJECT",IF($J167="","NEEDS PRICE",IF(OR($K167="",$L167=""),"NEEDS VALUATION",IF($T167&gt;=Assumptions!$B$13,"BUY",IF($T167&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W167" s="26"/>
-      <c r="X167" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W167" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X167" s="36" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="49"/>
+      <c r="A168" s="23" t="s">
+        <v>501</v>
+      </c>
       <c r="B168" s="37" t="str">
         <f aca="false">IF($A168="","",IF(ISERROR(FIND(".",$A168)),"",LOWER(MID($A168,FIND(CHAR(1),SUBSTITUTE($A168,".",CHAR(1),LEN($A168)-LEN(SUBSTITUTE($A168,".",""))))+1,LEN($A168)))))</f>
-        <v/>
-      </c>
-      <c r="C168" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C168" s="38" t="n">
         <f aca="false">IF($B168="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B168,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D168" s="26"/>
-      <c r="E168" s="26"/>
-      <c r="F168" s="26"/>
-      <c r="G168" s="26"/>
-      <c r="H168" s="26"/>
-      <c r="I168" s="26"/>
-      <c r="J168" s="27"/>
-      <c r="K168" s="28"/>
-      <c r="L168" s="49"/>
-      <c r="M168" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D168" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E168" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F168" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G168" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H168" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I168" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J168" s="47"/>
+      <c r="K168" s="48"/>
+      <c r="L168" s="26"/>
+      <c r="M168" s="39" t="n">
         <f aca="false">IF($B168="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B168,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N168" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N168" s="40" t="n">
         <f aca="false">IF(OR($A168="",$C168=""),"",$C168*Rubric!$B$5+$D168*Rubric!$B$6+$E168*Rubric!$B$7+$F168*Rubric!$B$8+$G168*Rubric!$B$9)</f>
-        <v/>
+        <v>4.84</v>
       </c>
       <c r="O168" s="41" t="str">
         <f aca="false">IF($A168="","",IF(OR(UPPER($H168)="Y",UPPER($I168)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P168" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P168" s="42" t="n">
         <f aca="false">IF($N168="","",Assumptions!$B$6*MAX(0.05,($N168/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q168" s="42" t="str">
+        <v>0.0322666666666667</v>
+      </c>
+      <c r="Q168" s="42" t="n">
         <f aca="false">IF($P168="","",1-(1-$P168)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R168" s="43" t="str">
+        <v>0.15125251114852</v>
+      </c>
+      <c r="R168" s="43" t="n">
         <f aca="false">IF($M168="","",$M168*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S168" s="43" t="str">
         <f aca="false">IF(OR($J168="",$Q168="",$Q168=0),"",($J168+$R168)/($Q168*(1-Assumptions!$B$4)))</f>
@@ -17286,53 +17570,71 @@
       </c>
       <c r="V168" s="41" t="str">
         <f aca="false">IF($A168="","",IF($O168="FAIL","REJECT",IF($J168="","NEEDS PRICE",IF(OR($K168="",$L168=""),"NEEDS VALUATION",IF($T168&gt;=Assumptions!$B$13,"BUY",IF($T168&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W168" s="26"/>
-      <c r="X168" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W168" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X168" s="36" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="49"/>
+      <c r="A169" s="23" t="s">
+        <v>503</v>
+      </c>
       <c r="B169" s="37" t="str">
         <f aca="false">IF($A169="","",IF(ISERROR(FIND(".",$A169)),"",LOWER(MID($A169,FIND(CHAR(1),SUBSTITUTE($A169,".",CHAR(1),LEN($A169)-LEN(SUBSTITUTE($A169,".",""))))+1,LEN($A169)))))</f>
-        <v/>
-      </c>
-      <c r="C169" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C169" s="38" t="n">
         <f aca="false">IF($B169="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B169,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D169" s="26"/>
-      <c r="E169" s="26"/>
-      <c r="F169" s="26"/>
-      <c r="G169" s="26"/>
-      <c r="H169" s="26"/>
-      <c r="I169" s="26"/>
-      <c r="J169" s="27"/>
-      <c r="K169" s="28"/>
-      <c r="L169" s="49"/>
-      <c r="M169" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D169" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E169" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F169" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G169" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H169" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I169" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J169" s="47"/>
+      <c r="K169" s="48"/>
+      <c r="L169" s="26"/>
+      <c r="M169" s="39" t="n">
         <f aca="false">IF($B169="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B169,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N169" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N169" s="40" t="n">
         <f aca="false">IF(OR($A169="",$C169=""),"",$C169*Rubric!$B$5+$D169*Rubric!$B$6+$E169*Rubric!$B$7+$F169*Rubric!$B$8+$G169*Rubric!$B$9)</f>
-        <v/>
+        <v>4.62</v>
       </c>
       <c r="O169" s="41" t="str">
         <f aca="false">IF($A169="","",IF(OR(UPPER($H169)="Y",UPPER($I169)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P169" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P169" s="42" t="n">
         <f aca="false">IF($N169="","",Assumptions!$B$6*MAX(0.05,($N169/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q169" s="42" t="str">
+        <v>0.0308</v>
+      </c>
+      <c r="Q169" s="42" t="n">
         <f aca="false">IF($P169="","",1-(1-$P169)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R169" s="43" t="str">
+        <v>0.144801309248222</v>
+      </c>
+      <c r="R169" s="43" t="n">
         <f aca="false">IF($M169="","",$M169*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S169" s="43" t="str">
         <f aca="false">IF(OR($J169="",$Q169="",$Q169=0),"",($J169+$R169)/($Q169*(1-Assumptions!$B$4)))</f>
@@ -17348,53 +17650,71 @@
       </c>
       <c r="V169" s="41" t="str">
         <f aca="false">IF($A169="","",IF($O169="FAIL","REJECT",IF($J169="","NEEDS PRICE",IF(OR($K169="",$L169=""),"NEEDS VALUATION",IF($T169&gt;=Assumptions!$B$13,"BUY",IF($T169&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W169" s="26"/>
-      <c r="X169" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W169" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X169" s="36" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="49"/>
+      <c r="A170" s="23" t="s">
+        <v>505</v>
+      </c>
       <c r="B170" s="37" t="str">
         <f aca="false">IF($A170="","",IF(ISERROR(FIND(".",$A170)),"",LOWER(MID($A170,FIND(CHAR(1),SUBSTITUTE($A170,".",CHAR(1),LEN($A170)-LEN(SUBSTITUTE($A170,".",""))))+1,LEN($A170)))))</f>
-        <v/>
-      </c>
-      <c r="C170" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C170" s="38" t="n">
         <f aca="false">IF($B170="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B170,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D170" s="26"/>
-      <c r="E170" s="26"/>
-      <c r="F170" s="26"/>
-      <c r="G170" s="26"/>
-      <c r="H170" s="26"/>
-      <c r="I170" s="26"/>
-      <c r="J170" s="27"/>
-      <c r="K170" s="28"/>
-      <c r="L170" s="49"/>
-      <c r="M170" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D170" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E170" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F170" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G170" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H170" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I170" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J170" s="47"/>
+      <c r="K170" s="48"/>
+      <c r="L170" s="26"/>
+      <c r="M170" s="39" t="n">
         <f aca="false">IF($B170="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B170,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N170" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N170" s="40" t="n">
         <f aca="false">IF(OR($A170="",$C170=""),"",$C170*Rubric!$B$5+$D170*Rubric!$B$6+$E170*Rubric!$B$7+$F170*Rubric!$B$8+$G170*Rubric!$B$9)</f>
-        <v/>
+        <v>4.46</v>
       </c>
       <c r="O170" s="41" t="str">
         <f aca="false">IF($A170="","",IF(OR(UPPER($H170)="Y",UPPER($I170)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P170" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P170" s="42" t="n">
         <f aca="false">IF($N170="","",Assumptions!$B$6*MAX(0.05,($N170/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q170" s="42" t="str">
+        <v>0.0297333333333333</v>
+      </c>
+      <c r="Q170" s="42" t="n">
         <f aca="false">IF($P170="","",1-(1-$P170)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R170" s="43" t="str">
+        <v>0.140084934696309</v>
+      </c>
+      <c r="R170" s="43" t="n">
         <f aca="false">IF($M170="","",$M170*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S170" s="43" t="str">
         <f aca="false">IF(OR($J170="",$Q170="",$Q170=0),"",($J170+$R170)/($Q170*(1-Assumptions!$B$4)))</f>
@@ -17410,53 +17730,71 @@
       </c>
       <c r="V170" s="41" t="str">
         <f aca="false">IF($A170="","",IF($O170="FAIL","REJECT",IF($J170="","NEEDS PRICE",IF(OR($K170="",$L170=""),"NEEDS VALUATION",IF($T170&gt;=Assumptions!$B$13,"BUY",IF($T170&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W170" s="26"/>
-      <c r="X170" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W170" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X170" s="36" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="49"/>
+      <c r="A171" s="23" t="s">
+        <v>507</v>
+      </c>
       <c r="B171" s="37" t="str">
         <f aca="false">IF($A171="","",IF(ISERROR(FIND(".",$A171)),"",LOWER(MID($A171,FIND(CHAR(1),SUBSTITUTE($A171,".",CHAR(1),LEN($A171)-LEN(SUBSTITUTE($A171,".",""))))+1,LEN($A171)))))</f>
-        <v/>
-      </c>
-      <c r="C171" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C171" s="38" t="n">
         <f aca="false">IF($B171="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B171,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D171" s="26"/>
-      <c r="E171" s="26"/>
-      <c r="F171" s="26"/>
-      <c r="G171" s="26"/>
-      <c r="H171" s="26"/>
-      <c r="I171" s="26"/>
-      <c r="J171" s="27"/>
-      <c r="K171" s="28"/>
-      <c r="L171" s="49"/>
-      <c r="M171" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D171" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E171" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F171" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G171" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H171" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I171" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J171" s="47"/>
+      <c r="K171" s="48"/>
+      <c r="L171" s="26"/>
+      <c r="M171" s="39" t="n">
         <f aca="false">IF($B171="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B171,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N171" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N171" s="40" t="n">
         <f aca="false">IF(OR($A171="",$C171=""),"",$C171*Rubric!$B$5+$D171*Rubric!$B$6+$E171*Rubric!$B$7+$F171*Rubric!$B$8+$G171*Rubric!$B$9)</f>
-        <v/>
+        <v>4.32</v>
       </c>
       <c r="O171" s="41" t="str">
         <f aca="false">IF($A171="","",IF(OR(UPPER($H171)="Y",UPPER($I171)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P171" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P171" s="42" t="n">
         <f aca="false">IF($N171="","",Assumptions!$B$6*MAX(0.05,($N171/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q171" s="42" t="str">
+        <v>0.0288</v>
+      </c>
+      <c r="Q171" s="42" t="n">
         <f aca="false">IF($P171="","",1-(1-$P171)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R171" s="43" t="str">
+        <v>0.135941058679989</v>
+      </c>
+      <c r="R171" s="43" t="n">
         <f aca="false">IF($M171="","",$M171*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S171" s="43" t="str">
         <f aca="false">IF(OR($J171="",$Q171="",$Q171=0),"",($J171+$R171)/($Q171*(1-Assumptions!$B$4)))</f>
@@ -17472,53 +17810,71 @@
       </c>
       <c r="V171" s="41" t="str">
         <f aca="false">IF($A171="","",IF($O171="FAIL","REJECT",IF($J171="","NEEDS PRICE",IF(OR($K171="",$L171=""),"NEEDS VALUATION",IF($T171&gt;=Assumptions!$B$13,"BUY",IF($T171&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W171" s="26"/>
-      <c r="X171" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W171" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X171" s="36" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="49"/>
+      <c r="A172" s="23" t="s">
+        <v>509</v>
+      </c>
       <c r="B172" s="37" t="str">
         <f aca="false">IF($A172="","",IF(ISERROR(FIND(".",$A172)),"",LOWER(MID($A172,FIND(CHAR(1),SUBSTITUTE($A172,".",CHAR(1),LEN($A172)-LEN(SUBSTITUTE($A172,".",""))))+1,LEN($A172)))))</f>
-        <v/>
-      </c>
-      <c r="C172" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C172" s="38" t="n">
         <f aca="false">IF($B172="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B172,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D172" s="26"/>
-      <c r="E172" s="26"/>
-      <c r="F172" s="26"/>
-      <c r="G172" s="26"/>
-      <c r="H172" s="26"/>
-      <c r="I172" s="26"/>
-      <c r="J172" s="27"/>
-      <c r="K172" s="28"/>
-      <c r="L172" s="49"/>
-      <c r="M172" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D172" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E172" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F172" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G172" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H172" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I172" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J172" s="47"/>
+      <c r="K172" s="48"/>
+      <c r="L172" s="26"/>
+      <c r="M172" s="39" t="n">
         <f aca="false">IF($B172="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B172,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N172" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N172" s="40" t="n">
         <f aca="false">IF(OR($A172="",$C172=""),"",$C172*Rubric!$B$5+$D172*Rubric!$B$6+$E172*Rubric!$B$7+$F172*Rubric!$B$8+$G172*Rubric!$B$9)</f>
-        <v/>
+        <v>4.32</v>
       </c>
       <c r="O172" s="41" t="str">
         <f aca="false">IF($A172="","",IF(OR(UPPER($H172)="Y",UPPER($I172)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P172" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P172" s="42" t="n">
         <f aca="false">IF($N172="","",Assumptions!$B$6*MAX(0.05,($N172/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q172" s="42" t="str">
+        <v>0.0288</v>
+      </c>
+      <c r="Q172" s="42" t="n">
         <f aca="false">IF($P172="","",1-(1-$P172)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R172" s="43" t="str">
+        <v>0.135941058679989</v>
+      </c>
+      <c r="R172" s="43" t="n">
         <f aca="false">IF($M172="","",$M172*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S172" s="43" t="str">
         <f aca="false">IF(OR($J172="",$Q172="",$Q172=0),"",($J172+$R172)/($Q172*(1-Assumptions!$B$4)))</f>
@@ -17534,53 +17890,71 @@
       </c>
       <c r="V172" s="41" t="str">
         <f aca="false">IF($A172="","",IF($O172="FAIL","REJECT",IF($J172="","NEEDS PRICE",IF(OR($K172="",$L172=""),"NEEDS VALUATION",IF($T172&gt;=Assumptions!$B$13,"BUY",IF($T172&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W172" s="26"/>
-      <c r="X172" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W172" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X172" s="36" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="49"/>
+      <c r="A173" s="23" t="s">
+        <v>511</v>
+      </c>
       <c r="B173" s="37" t="str">
         <f aca="false">IF($A173="","",IF(ISERROR(FIND(".",$A173)),"",LOWER(MID($A173,FIND(CHAR(1),SUBSTITUTE($A173,".",CHAR(1),LEN($A173)-LEN(SUBSTITUTE($A173,".",""))))+1,LEN($A173)))))</f>
-        <v/>
-      </c>
-      <c r="C173" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C173" s="38" t="n">
         <f aca="false">IF($B173="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B173,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D173" s="26"/>
-      <c r="E173" s="26"/>
-      <c r="F173" s="26"/>
-      <c r="G173" s="26"/>
-      <c r="H173" s="26"/>
-      <c r="I173" s="26"/>
-      <c r="J173" s="27"/>
-      <c r="K173" s="28"/>
-      <c r="L173" s="49"/>
-      <c r="M173" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D173" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E173" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F173" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G173" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H173" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I173" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J173" s="47"/>
+      <c r="K173" s="48"/>
+      <c r="L173" s="26"/>
+      <c r="M173" s="39" t="n">
         <f aca="false">IF($B173="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B173,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N173" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N173" s="40" t="n">
         <f aca="false">IF(OR($A173="",$C173=""),"",$C173*Rubric!$B$5+$D173*Rubric!$B$6+$E173*Rubric!$B$7+$F173*Rubric!$B$8+$G173*Rubric!$B$9)</f>
-        <v/>
+        <v>4.48</v>
       </c>
       <c r="O173" s="41" t="str">
         <f aca="false">IF($A173="","",IF(OR(UPPER($H173)="Y",UPPER($I173)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P173" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P173" s="42" t="n">
         <f aca="false">IF($N173="","",Assumptions!$B$6*MAX(0.05,($N173/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q173" s="42" t="str">
+        <v>0.0298666666666667</v>
+      </c>
+      <c r="Q173" s="42" t="n">
         <f aca="false">IF($P173="","",1-(1-$P173)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R173" s="43" t="str">
+        <v>0.140675616818051</v>
+      </c>
+      <c r="R173" s="43" t="n">
         <f aca="false">IF($M173="","",$M173*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S173" s="43" t="str">
         <f aca="false">IF(OR($J173="",$Q173="",$Q173=0),"",($J173+$R173)/($Q173*(1-Assumptions!$B$4)))</f>
@@ -17596,53 +17970,71 @@
       </c>
       <c r="V173" s="41" t="str">
         <f aca="false">IF($A173="","",IF($O173="FAIL","REJECT",IF($J173="","NEEDS PRICE",IF(OR($K173="",$L173=""),"NEEDS VALUATION",IF($T173&gt;=Assumptions!$B$13,"BUY",IF($T173&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W173" s="26"/>
-      <c r="X173" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W173" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X173" s="36" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="49"/>
+      <c r="A174" s="23" t="s">
+        <v>513</v>
+      </c>
       <c r="B174" s="37" t="str">
         <f aca="false">IF($A174="","",IF(ISERROR(FIND(".",$A174)),"",LOWER(MID($A174,FIND(CHAR(1),SUBSTITUTE($A174,".",CHAR(1),LEN($A174)-LEN(SUBSTITUTE($A174,".",""))))+1,LEN($A174)))))</f>
-        <v/>
-      </c>
-      <c r="C174" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C174" s="38" t="n">
         <f aca="false">IF($B174="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B174,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D174" s="26"/>
-      <c r="E174" s="26"/>
-      <c r="F174" s="26"/>
-      <c r="G174" s="26"/>
-      <c r="H174" s="26"/>
-      <c r="I174" s="26"/>
-      <c r="J174" s="27"/>
-      <c r="K174" s="28"/>
-      <c r="L174" s="49"/>
-      <c r="M174" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D174" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E174" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F174" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G174" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H174" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I174" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J174" s="47"/>
+      <c r="K174" s="48"/>
+      <c r="L174" s="26"/>
+      <c r="M174" s="39" t="n">
         <f aca="false">IF($B174="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B174,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N174" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N174" s="40" t="n">
         <f aca="false">IF(OR($A174="",$C174=""),"",$C174*Rubric!$B$5+$D174*Rubric!$B$6+$E174*Rubric!$B$7+$F174*Rubric!$B$8+$G174*Rubric!$B$9)</f>
-        <v/>
+        <v>4.48</v>
       </c>
       <c r="O174" s="41" t="str">
         <f aca="false">IF($A174="","",IF(OR(UPPER($H174)="Y",UPPER($I174)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P174" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P174" s="42" t="n">
         <f aca="false">IF($N174="","",Assumptions!$B$6*MAX(0.05,($N174/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q174" s="42" t="str">
+        <v>0.0298666666666667</v>
+      </c>
+      <c r="Q174" s="42" t="n">
         <f aca="false">IF($P174="","",1-(1-$P174)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R174" s="43" t="str">
+        <v>0.140675616818051</v>
+      </c>
+      <c r="R174" s="43" t="n">
         <f aca="false">IF($M174="","",$M174*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S174" s="43" t="str">
         <f aca="false">IF(OR($J174="",$Q174="",$Q174=0),"",($J174+$R174)/($Q174*(1-Assumptions!$B$4)))</f>
@@ -17658,53 +18050,71 @@
       </c>
       <c r="V174" s="41" t="str">
         <f aca="false">IF($A174="","",IF($O174="FAIL","REJECT",IF($J174="","NEEDS PRICE",IF(OR($K174="",$L174=""),"NEEDS VALUATION",IF($T174&gt;=Assumptions!$B$13,"BUY",IF($T174&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W174" s="26"/>
-      <c r="X174" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W174" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X174" s="36" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="49"/>
+      <c r="A175" s="23" t="s">
+        <v>515</v>
+      </c>
       <c r="B175" s="37" t="str">
         <f aca="false">IF($A175="","",IF(ISERROR(FIND(".",$A175)),"",LOWER(MID($A175,FIND(CHAR(1),SUBSTITUTE($A175,".",CHAR(1),LEN($A175)-LEN(SUBSTITUTE($A175,".",""))))+1,LEN($A175)))))</f>
-        <v/>
-      </c>
-      <c r="C175" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C175" s="38" t="n">
         <f aca="false">IF($B175="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B175,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D175" s="26"/>
-      <c r="E175" s="26"/>
-      <c r="F175" s="26"/>
-      <c r="G175" s="26"/>
-      <c r="H175" s="26"/>
-      <c r="I175" s="26"/>
-      <c r="J175" s="27"/>
-      <c r="K175" s="28"/>
-      <c r="L175" s="49"/>
-      <c r="M175" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D175" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E175" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F175" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G175" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H175" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I175" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J175" s="47"/>
+      <c r="K175" s="48"/>
+      <c r="L175" s="26"/>
+      <c r="M175" s="39" t="n">
         <f aca="false">IF($B175="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B175,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N175" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N175" s="40" t="n">
         <f aca="false">IF(OR($A175="",$C175=""),"",$C175*Rubric!$B$5+$D175*Rubric!$B$6+$E175*Rubric!$B$7+$F175*Rubric!$B$8+$G175*Rubric!$B$9)</f>
-        <v/>
+        <v>4.48</v>
       </c>
       <c r="O175" s="41" t="str">
         <f aca="false">IF($A175="","",IF(OR(UPPER($H175)="Y",UPPER($I175)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P175" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P175" s="42" t="n">
         <f aca="false">IF($N175="","",Assumptions!$B$6*MAX(0.05,($N175/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q175" s="42" t="str">
+        <v>0.0298666666666667</v>
+      </c>
+      <c r="Q175" s="42" t="n">
         <f aca="false">IF($P175="","",1-(1-$P175)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R175" s="43" t="str">
+        <v>0.140675616818051</v>
+      </c>
+      <c r="R175" s="43" t="n">
         <f aca="false">IF($M175="","",$M175*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S175" s="43" t="str">
         <f aca="false">IF(OR($J175="",$Q175="",$Q175=0),"",($J175+$R175)/($Q175*(1-Assumptions!$B$4)))</f>
@@ -17720,53 +18130,71 @@
       </c>
       <c r="V175" s="41" t="str">
         <f aca="false">IF($A175="","",IF($O175="FAIL","REJECT",IF($J175="","NEEDS PRICE",IF(OR($K175="",$L175=""),"NEEDS VALUATION",IF($T175&gt;=Assumptions!$B$13,"BUY",IF($T175&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W175" s="26"/>
-      <c r="X175" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W175" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X175" s="36" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="49"/>
+      <c r="A176" s="23" t="s">
+        <v>517</v>
+      </c>
       <c r="B176" s="37" t="str">
         <f aca="false">IF($A176="","",IF(ISERROR(FIND(".",$A176)),"",LOWER(MID($A176,FIND(CHAR(1),SUBSTITUTE($A176,".",CHAR(1),LEN($A176)-LEN(SUBSTITUTE($A176,".",""))))+1,LEN($A176)))))</f>
-        <v/>
-      </c>
-      <c r="C176" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C176" s="38" t="n">
         <f aca="false">IF($B176="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B176,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D176" s="26"/>
-      <c r="E176" s="26"/>
-      <c r="F176" s="26"/>
-      <c r="G176" s="26"/>
-      <c r="H176" s="26"/>
-      <c r="I176" s="26"/>
-      <c r="J176" s="27"/>
-      <c r="K176" s="28"/>
-      <c r="L176" s="49"/>
-      <c r="M176" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D176" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E176" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F176" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G176" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H176" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I176" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J176" s="47"/>
+      <c r="K176" s="48"/>
+      <c r="L176" s="26"/>
+      <c r="M176" s="39" t="n">
         <f aca="false">IF($B176="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B176,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N176" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N176" s="40" t="n">
         <f aca="false">IF(OR($A176="",$C176=""),"",$C176*Rubric!$B$5+$D176*Rubric!$B$6+$E176*Rubric!$B$7+$F176*Rubric!$B$8+$G176*Rubric!$B$9)</f>
-        <v/>
+        <v>4.32</v>
       </c>
       <c r="O176" s="41" t="str">
         <f aca="false">IF($A176="","",IF(OR(UPPER($H176)="Y",UPPER($I176)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P176" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P176" s="42" t="n">
         <f aca="false">IF($N176="","",Assumptions!$B$6*MAX(0.05,($N176/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q176" s="42" t="str">
+        <v>0.0288</v>
+      </c>
+      <c r="Q176" s="42" t="n">
         <f aca="false">IF($P176="","",1-(1-$P176)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R176" s="43" t="str">
+        <v>0.135941058679989</v>
+      </c>
+      <c r="R176" s="43" t="n">
         <f aca="false">IF($M176="","",$M176*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S176" s="43" t="str">
         <f aca="false">IF(OR($J176="",$Q176="",$Q176=0),"",($J176+$R176)/($Q176*(1-Assumptions!$B$4)))</f>
@@ -17782,53 +18210,71 @@
       </c>
       <c r="V176" s="41" t="str">
         <f aca="false">IF($A176="","",IF($O176="FAIL","REJECT",IF($J176="","NEEDS PRICE",IF(OR($K176="",$L176=""),"NEEDS VALUATION",IF($T176&gt;=Assumptions!$B$13,"BUY",IF($T176&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W176" s="26"/>
-      <c r="X176" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W176" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X176" s="36" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="49"/>
+      <c r="A177" s="23" t="s">
+        <v>519</v>
+      </c>
       <c r="B177" s="37" t="str">
         <f aca="false">IF($A177="","",IF(ISERROR(FIND(".",$A177)),"",LOWER(MID($A177,FIND(CHAR(1),SUBSTITUTE($A177,".",CHAR(1),LEN($A177)-LEN(SUBSTITUTE($A177,".",""))))+1,LEN($A177)))))</f>
-        <v/>
-      </c>
-      <c r="C177" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C177" s="38" t="n">
         <f aca="false">IF($B177="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B177,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D177" s="26"/>
-      <c r="E177" s="26"/>
-      <c r="F177" s="26"/>
-      <c r="G177" s="26"/>
-      <c r="H177" s="26"/>
-      <c r="I177" s="26"/>
-      <c r="J177" s="27"/>
-      <c r="K177" s="28"/>
-      <c r="L177" s="49"/>
-      <c r="M177" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D177" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E177" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F177" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G177" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H177" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I177" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J177" s="47"/>
+      <c r="K177" s="48"/>
+      <c r="L177" s="26"/>
+      <c r="M177" s="39" t="n">
         <f aca="false">IF($B177="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B177,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N177" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N177" s="40" t="n">
         <f aca="false">IF(OR($A177="",$C177=""),"",$C177*Rubric!$B$5+$D177*Rubric!$B$6+$E177*Rubric!$B$7+$F177*Rubric!$B$8+$G177*Rubric!$B$9)</f>
-        <v/>
+        <v>4.32</v>
       </c>
       <c r="O177" s="41" t="str">
         <f aca="false">IF($A177="","",IF(OR(UPPER($H177)="Y",UPPER($I177)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P177" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P177" s="42" t="n">
         <f aca="false">IF($N177="","",Assumptions!$B$6*MAX(0.05,($N177/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q177" s="42" t="str">
+        <v>0.0288</v>
+      </c>
+      <c r="Q177" s="42" t="n">
         <f aca="false">IF($P177="","",1-(1-$P177)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R177" s="43" t="str">
+        <v>0.135941058679989</v>
+      </c>
+      <c r="R177" s="43" t="n">
         <f aca="false">IF($M177="","",$M177*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S177" s="43" t="str">
         <f aca="false">IF(OR($J177="",$Q177="",$Q177=0),"",($J177+$R177)/($Q177*(1-Assumptions!$B$4)))</f>
@@ -17844,53 +18290,71 @@
       </c>
       <c r="V177" s="41" t="str">
         <f aca="false">IF($A177="","",IF($O177="FAIL","REJECT",IF($J177="","NEEDS PRICE",IF(OR($K177="",$L177=""),"NEEDS VALUATION",IF($T177&gt;=Assumptions!$B$13,"BUY",IF($T177&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W177" s="26"/>
-      <c r="X177" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W177" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X177" s="36" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="49"/>
+      <c r="A178" s="23" t="s">
+        <v>521</v>
+      </c>
       <c r="B178" s="37" t="str">
         <f aca="false">IF($A178="","",IF(ISERROR(FIND(".",$A178)),"",LOWER(MID($A178,FIND(CHAR(1),SUBSTITUTE($A178,".",CHAR(1),LEN($A178)-LEN(SUBSTITUTE($A178,".",""))))+1,LEN($A178)))))</f>
-        <v/>
-      </c>
-      <c r="C178" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C178" s="38" t="n">
         <f aca="false">IF($B178="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B178,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D178" s="26"/>
-      <c r="E178" s="26"/>
-      <c r="F178" s="26"/>
-      <c r="G178" s="26"/>
-      <c r="H178" s="26"/>
-      <c r="I178" s="26"/>
-      <c r="J178" s="27"/>
-      <c r="K178" s="28"/>
-      <c r="L178" s="49"/>
-      <c r="M178" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D178" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E178" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F178" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G178" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H178" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I178" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J178" s="47"/>
+      <c r="K178" s="48"/>
+      <c r="L178" s="26"/>
+      <c r="M178" s="39" t="n">
         <f aca="false">IF($B178="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B178,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N178" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N178" s="40" t="n">
         <f aca="false">IF(OR($A178="",$C178=""),"",$C178*Rubric!$B$5+$D178*Rubric!$B$6+$E178*Rubric!$B$7+$F178*Rubric!$B$8+$G178*Rubric!$B$9)</f>
-        <v/>
+        <v>4.32</v>
       </c>
       <c r="O178" s="41" t="str">
         <f aca="false">IF($A178="","",IF(OR(UPPER($H178)="Y",UPPER($I178)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P178" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P178" s="42" t="n">
         <f aca="false">IF($N178="","",Assumptions!$B$6*MAX(0.05,($N178/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q178" s="42" t="str">
+        <v>0.0288</v>
+      </c>
+      <c r="Q178" s="42" t="n">
         <f aca="false">IF($P178="","",1-(1-$P178)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R178" s="43" t="str">
+        <v>0.135941058679989</v>
+      </c>
+      <c r="R178" s="43" t="n">
         <f aca="false">IF($M178="","",$M178*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S178" s="43" t="str">
         <f aca="false">IF(OR($J178="",$Q178="",$Q178=0),"",($J178+$R178)/($Q178*(1-Assumptions!$B$4)))</f>
@@ -17906,53 +18370,71 @@
       </c>
       <c r="V178" s="41" t="str">
         <f aca="false">IF($A178="","",IF($O178="FAIL","REJECT",IF($J178="","NEEDS PRICE",IF(OR($K178="",$L178=""),"NEEDS VALUATION",IF($T178&gt;=Assumptions!$B$13,"BUY",IF($T178&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W178" s="26"/>
-      <c r="X178" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W178" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X178" s="36" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="49"/>
+      <c r="A179" s="23" t="s">
+        <v>523</v>
+      </c>
       <c r="B179" s="37" t="str">
         <f aca="false">IF($A179="","",IF(ISERROR(FIND(".",$A179)),"",LOWER(MID($A179,FIND(CHAR(1),SUBSTITUTE($A179,".",CHAR(1),LEN($A179)-LEN(SUBSTITUTE($A179,".",""))))+1,LEN($A179)))))</f>
-        <v/>
-      </c>
-      <c r="C179" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C179" s="38" t="n">
         <f aca="false">IF($B179="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B179,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D179" s="26"/>
-      <c r="E179" s="26"/>
-      <c r="F179" s="26"/>
-      <c r="G179" s="26"/>
-      <c r="H179" s="26"/>
-      <c r="I179" s="26"/>
-      <c r="J179" s="27"/>
-      <c r="K179" s="28"/>
-      <c r="L179" s="49"/>
-      <c r="M179" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D179" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E179" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F179" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G179" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H179" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I179" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J179" s="47"/>
+      <c r="K179" s="48"/>
+      <c r="L179" s="26"/>
+      <c r="M179" s="39" t="n">
         <f aca="false">IF($B179="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B179,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N179" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N179" s="40" t="n">
         <f aca="false">IF(OR($A179="",$C179=""),"",$C179*Rubric!$B$5+$D179*Rubric!$B$6+$E179*Rubric!$B$7+$F179*Rubric!$B$8+$G179*Rubric!$B$9)</f>
-        <v/>
+        <v>4.32</v>
       </c>
       <c r="O179" s="41" t="str">
         <f aca="false">IF($A179="","",IF(OR(UPPER($H179)="Y",UPPER($I179)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P179" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P179" s="42" t="n">
         <f aca="false">IF($N179="","",Assumptions!$B$6*MAX(0.05,($N179/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q179" s="42" t="str">
+        <v>0.0288</v>
+      </c>
+      <c r="Q179" s="42" t="n">
         <f aca="false">IF($P179="","",1-(1-$P179)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R179" s="43" t="str">
+        <v>0.135941058679989</v>
+      </c>
+      <c r="R179" s="43" t="n">
         <f aca="false">IF($M179="","",$M179*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S179" s="43" t="str">
         <f aca="false">IF(OR($J179="",$Q179="",$Q179=0),"",($J179+$R179)/($Q179*(1-Assumptions!$B$4)))</f>
@@ -17968,53 +18450,71 @@
       </c>
       <c r="V179" s="41" t="str">
         <f aca="false">IF($A179="","",IF($O179="FAIL","REJECT",IF($J179="","NEEDS PRICE",IF(OR($K179="",$L179=""),"NEEDS VALUATION",IF($T179&gt;=Assumptions!$B$13,"BUY",IF($T179&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W179" s="26"/>
-      <c r="X179" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W179" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X179" s="36" t="s">
+        <v>524</v>
+      </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="49"/>
+      <c r="A180" s="23" t="s">
+        <v>525</v>
+      </c>
       <c r="B180" s="37" t="str">
         <f aca="false">IF($A180="","",IF(ISERROR(FIND(".",$A180)),"",LOWER(MID($A180,FIND(CHAR(1),SUBSTITUTE($A180,".",CHAR(1),LEN($A180)-LEN(SUBSTITUTE($A180,".",""))))+1,LEN($A180)))))</f>
-        <v/>
-      </c>
-      <c r="C180" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C180" s="38" t="n">
         <f aca="false">IF($B180="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B180,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D180" s="26"/>
-      <c r="E180" s="26"/>
-      <c r="F180" s="26"/>
-      <c r="G180" s="26"/>
-      <c r="H180" s="26"/>
-      <c r="I180" s="26"/>
-      <c r="J180" s="27"/>
-      <c r="K180" s="28"/>
-      <c r="L180" s="49"/>
-      <c r="M180" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D180" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E180" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F180" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G180" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H180" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I180" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J180" s="47"/>
+      <c r="K180" s="48"/>
+      <c r="L180" s="26"/>
+      <c r="M180" s="39" t="n">
         <f aca="false">IF($B180="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B180,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N180" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N180" s="40" t="n">
         <f aca="false">IF(OR($A180="",$C180=""),"",$C180*Rubric!$B$5+$D180*Rubric!$B$6+$E180*Rubric!$B$7+$F180*Rubric!$B$8+$G180*Rubric!$B$9)</f>
-        <v/>
+        <v>4.06</v>
       </c>
       <c r="O180" s="41" t="str">
         <f aca="false">IF($A180="","",IF(OR(UPPER($H180)="Y",UPPER($I180)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P180" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P180" s="42" t="n">
         <f aca="false">IF($N180="","",Assumptions!$B$6*MAX(0.05,($N180/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q180" s="42" t="str">
+        <v>0.0270666666666667</v>
+      </c>
+      <c r="Q180" s="42" t="n">
         <f aca="false">IF($P180="","",1-(1-$P180)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R180" s="43" t="str">
+        <v>0.128202911472423</v>
+      </c>
+      <c r="R180" s="43" t="n">
         <f aca="false">IF($M180="","",$M180*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S180" s="43" t="str">
         <f aca="false">IF(OR($J180="",$Q180="",$Q180=0),"",($J180+$R180)/($Q180*(1-Assumptions!$B$4)))</f>
@@ -18030,53 +18530,71 @@
       </c>
       <c r="V180" s="41" t="str">
         <f aca="false">IF($A180="","",IF($O180="FAIL","REJECT",IF($J180="","NEEDS PRICE",IF(OR($K180="",$L180=""),"NEEDS VALUATION",IF($T180&gt;=Assumptions!$B$13,"BUY",IF($T180&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W180" s="26"/>
-      <c r="X180" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W180" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X180" s="36" t="s">
+        <v>526</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="49"/>
+      <c r="A181" s="23" t="s">
+        <v>527</v>
+      </c>
       <c r="B181" s="37" t="str">
         <f aca="false">IF($A181="","",IF(ISERROR(FIND(".",$A181)),"",LOWER(MID($A181,FIND(CHAR(1),SUBSTITUTE($A181,".",CHAR(1),LEN($A181)-LEN(SUBSTITUTE($A181,".",""))))+1,LEN($A181)))))</f>
-        <v/>
-      </c>
-      <c r="C181" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C181" s="38" t="n">
         <f aca="false">IF($B181="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B181,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D181" s="26"/>
-      <c r="E181" s="26"/>
-      <c r="F181" s="26"/>
-      <c r="G181" s="26"/>
-      <c r="H181" s="26"/>
-      <c r="I181" s="26"/>
-      <c r="J181" s="27"/>
-      <c r="K181" s="28"/>
-      <c r="L181" s="49"/>
-      <c r="M181" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D181" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E181" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F181" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H181" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I181" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J181" s="47"/>
+      <c r="K181" s="48"/>
+      <c r="L181" s="26"/>
+      <c r="M181" s="39" t="n">
         <f aca="false">IF($B181="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B181,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N181" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N181" s="40" t="n">
         <f aca="false">IF(OR($A181="",$C181=""),"",$C181*Rubric!$B$5+$D181*Rubric!$B$6+$E181*Rubric!$B$7+$F181*Rubric!$B$8+$G181*Rubric!$B$9)</f>
-        <v/>
+        <v>3.9</v>
       </c>
       <c r="O181" s="41" t="str">
         <f aca="false">IF($A181="","",IF(OR(UPPER($H181)="Y",UPPER($I181)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P181" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P181" s="42" t="n">
         <f aca="false">IF($N181="","",Assumptions!$B$6*MAX(0.05,($N181/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q181" s="42" t="str">
+        <v>0.026</v>
+      </c>
+      <c r="Q181" s="42" t="n">
         <f aca="false">IF($P181="","",1-(1-$P181)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R181" s="43" t="str">
+        <v>0.123413487001376</v>
+      </c>
+      <c r="R181" s="43" t="n">
         <f aca="false">IF($M181="","",$M181*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S181" s="43" t="str">
         <f aca="false">IF(OR($J181="",$Q181="",$Q181=0),"",($J181+$R181)/($Q181*(1-Assumptions!$B$4)))</f>
@@ -18092,53 +18610,71 @@
       </c>
       <c r="V181" s="41" t="str">
         <f aca="false">IF($A181="","",IF($O181="FAIL","REJECT",IF($J181="","NEEDS PRICE",IF(OR($K181="",$L181=""),"NEEDS VALUATION",IF($T181&gt;=Assumptions!$B$13,"BUY",IF($T181&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W181" s="26"/>
-      <c r="X181" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W181" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X181" s="36" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="49"/>
+      <c r="A182" s="23" t="s">
+        <v>529</v>
+      </c>
       <c r="B182" s="37" t="str">
         <f aca="false">IF($A182="","",IF(ISERROR(FIND(".",$A182)),"",LOWER(MID($A182,FIND(CHAR(1),SUBSTITUTE($A182,".",CHAR(1),LEN($A182)-LEN(SUBSTITUTE($A182,".",""))))+1,LEN($A182)))))</f>
-        <v/>
-      </c>
-      <c r="C182" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C182" s="38" t="n">
         <f aca="false">IF($B182="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B182,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D182" s="26"/>
-      <c r="E182" s="26"/>
-      <c r="F182" s="26"/>
-      <c r="G182" s="26"/>
-      <c r="H182" s="26"/>
-      <c r="I182" s="26"/>
-      <c r="J182" s="27"/>
-      <c r="K182" s="28"/>
-      <c r="L182" s="49"/>
-      <c r="M182" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D182" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E182" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F182" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G182" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H182" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I182" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J182" s="47"/>
+      <c r="K182" s="48"/>
+      <c r="L182" s="26"/>
+      <c r="M182" s="39" t="n">
         <f aca="false">IF($B182="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B182,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N182" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N182" s="40" t="n">
         <f aca="false">IF(OR($A182="",$C182=""),"",$C182*Rubric!$B$5+$D182*Rubric!$B$6+$E182*Rubric!$B$7+$F182*Rubric!$B$8+$G182*Rubric!$B$9)</f>
-        <v/>
+        <v>4.4</v>
       </c>
       <c r="O182" s="41" t="str">
         <f aca="false">IF($A182="","",IF(OR(UPPER($H182)="Y",UPPER($I182)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P182" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P182" s="42" t="n">
         <f aca="false">IF($N182="","",Assumptions!$B$6*MAX(0.05,($N182/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q182" s="42" t="str">
+        <v>0.0293333333333333</v>
+      </c>
+      <c r="Q182" s="42" t="n">
         <f aca="false">IF($P182="","",1-(1-$P182)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R182" s="43" t="str">
+        <v>0.138310939153412</v>
+      </c>
+      <c r="R182" s="43" t="n">
         <f aca="false">IF($M182="","",$M182*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S182" s="43" t="str">
         <f aca="false">IF(OR($J182="",$Q182="",$Q182=0),"",($J182+$R182)/($Q182*(1-Assumptions!$B$4)))</f>
@@ -18154,53 +18690,71 @@
       </c>
       <c r="V182" s="41" t="str">
         <f aca="false">IF($A182="","",IF($O182="FAIL","REJECT",IF($J182="","NEEDS PRICE",IF(OR($K182="",$L182=""),"NEEDS VALUATION",IF($T182&gt;=Assumptions!$B$13,"BUY",IF($T182&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W182" s="26"/>
-      <c r="X182" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W182" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X182" s="36" t="s">
+        <v>530</v>
+      </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="49"/>
+      <c r="A183" s="23" t="s">
+        <v>531</v>
+      </c>
       <c r="B183" s="37" t="str">
         <f aca="false">IF($A183="","",IF(ISERROR(FIND(".",$A183)),"",LOWER(MID($A183,FIND(CHAR(1),SUBSTITUTE($A183,".",CHAR(1),LEN($A183)-LEN(SUBSTITUTE($A183,".",""))))+1,LEN($A183)))))</f>
-        <v/>
-      </c>
-      <c r="C183" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C183" s="38" t="n">
         <f aca="false">IF($B183="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B183,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D183" s="26"/>
-      <c r="E183" s="26"/>
-      <c r="F183" s="26"/>
-      <c r="G183" s="26"/>
-      <c r="H183" s="26"/>
-      <c r="I183" s="26"/>
-      <c r="J183" s="27"/>
-      <c r="K183" s="28"/>
-      <c r="L183" s="49"/>
-      <c r="M183" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D183" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E183" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F183" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G183" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H183" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I183" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J183" s="47"/>
+      <c r="K183" s="48"/>
+      <c r="L183" s="26"/>
+      <c r="M183" s="39" t="n">
         <f aca="false">IF($B183="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B183,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N183" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N183" s="40" t="n">
         <f aca="false">IF(OR($A183="",$C183=""),"",$C183*Rubric!$B$5+$D183*Rubric!$B$6+$E183*Rubric!$B$7+$F183*Rubric!$B$8+$G183*Rubric!$B$9)</f>
-        <v/>
+        <v>4.4</v>
       </c>
       <c r="O183" s="41" t="str">
         <f aca="false">IF($A183="","",IF(OR(UPPER($H183)="Y",UPPER($I183)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P183" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P183" s="42" t="n">
         <f aca="false">IF($N183="","",Assumptions!$B$6*MAX(0.05,($N183/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q183" s="42" t="str">
+        <v>0.0293333333333333</v>
+      </c>
+      <c r="Q183" s="42" t="n">
         <f aca="false">IF($P183="","",1-(1-$P183)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R183" s="43" t="str">
+        <v>0.138310939153412</v>
+      </c>
+      <c r="R183" s="43" t="n">
         <f aca="false">IF($M183="","",$M183*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S183" s="43" t="str">
         <f aca="false">IF(OR($J183="",$Q183="",$Q183=0),"",($J183+$R183)/($Q183*(1-Assumptions!$B$4)))</f>
@@ -18216,53 +18770,71 @@
       </c>
       <c r="V183" s="41" t="str">
         <f aca="false">IF($A183="","",IF($O183="FAIL","REJECT",IF($J183="","NEEDS PRICE",IF(OR($K183="",$L183=""),"NEEDS VALUATION",IF($T183&gt;=Assumptions!$B$13,"BUY",IF($T183&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W183" s="26"/>
-      <c r="X183" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W183" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X183" s="36" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="49"/>
+      <c r="A184" s="23" t="s">
+        <v>533</v>
+      </c>
       <c r="B184" s="37" t="str">
         <f aca="false">IF($A184="","",IF(ISERROR(FIND(".",$A184)),"",LOWER(MID($A184,FIND(CHAR(1),SUBSTITUTE($A184,".",CHAR(1),LEN($A184)-LEN(SUBSTITUTE($A184,".",""))))+1,LEN($A184)))))</f>
-        <v/>
-      </c>
-      <c r="C184" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C184" s="38" t="n">
         <f aca="false">IF($B184="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B184,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
-      <c r="F184" s="26"/>
-      <c r="G184" s="26"/>
-      <c r="H184" s="26"/>
-      <c r="I184" s="26"/>
-      <c r="J184" s="27"/>
-      <c r="K184" s="28"/>
-      <c r="L184" s="49"/>
-      <c r="M184" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D184" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E184" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F184" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G184" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H184" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I184" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J184" s="47"/>
+      <c r="K184" s="48"/>
+      <c r="L184" s="26"/>
+      <c r="M184" s="39" t="n">
         <f aca="false">IF($B184="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B184,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N184" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N184" s="40" t="n">
         <f aca="false">IF(OR($A184="",$C184=""),"",$C184*Rubric!$B$5+$D184*Rubric!$B$6+$E184*Rubric!$B$7+$F184*Rubric!$B$8+$G184*Rubric!$B$9)</f>
-        <v/>
+        <v>4.26</v>
       </c>
       <c r="O184" s="41" t="str">
         <f aca="false">IF($A184="","",IF(OR(UPPER($H184)="Y",UPPER($I184)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P184" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P184" s="42" t="n">
         <f aca="false">IF($N184="","",Assumptions!$B$6*MAX(0.05,($N184/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q184" s="42" t="str">
+        <v>0.0284</v>
+      </c>
+      <c r="Q184" s="42" t="n">
         <f aca="false">IF($P184="","",1-(1-$P184)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R184" s="43" t="str">
+        <v>0.13416022882014</v>
+      </c>
+      <c r="R184" s="43" t="n">
         <f aca="false">IF($M184="","",$M184*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S184" s="43" t="str">
         <f aca="false">IF(OR($J184="",$Q184="",$Q184=0),"",($J184+$R184)/($Q184*(1-Assumptions!$B$4)))</f>
@@ -18278,53 +18850,71 @@
       </c>
       <c r="V184" s="41" t="str">
         <f aca="false">IF($A184="","",IF($O184="FAIL","REJECT",IF($J184="","NEEDS PRICE",IF(OR($K184="",$L184=""),"NEEDS VALUATION",IF($T184&gt;=Assumptions!$B$13,"BUY",IF($T184&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W184" s="26"/>
-      <c r="X184" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W184" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X184" s="36" t="s">
+        <v>534</v>
+      </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="49"/>
+      <c r="A185" s="23" t="s">
+        <v>535</v>
+      </c>
       <c r="B185" s="37" t="str">
         <f aca="false">IF($A185="","",IF(ISERROR(FIND(".",$A185)),"",LOWER(MID($A185,FIND(CHAR(1),SUBSTITUTE($A185,".",CHAR(1),LEN($A185)-LEN(SUBSTITUTE($A185,".",""))))+1,LEN($A185)))))</f>
-        <v/>
-      </c>
-      <c r="C185" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C185" s="38" t="n">
         <f aca="false">IF($B185="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B185,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D185" s="26"/>
-      <c r="E185" s="26"/>
-      <c r="F185" s="26"/>
-      <c r="G185" s="26"/>
-      <c r="H185" s="26"/>
-      <c r="I185" s="26"/>
-      <c r="J185" s="27"/>
-      <c r="K185" s="28"/>
-      <c r="L185" s="49"/>
-      <c r="M185" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D185" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E185" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F185" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G185" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H185" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I185" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J185" s="47"/>
+      <c r="K185" s="48"/>
+      <c r="L185" s="26"/>
+      <c r="M185" s="39" t="n">
         <f aca="false">IF($B185="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B185,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N185" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N185" s="40" t="n">
         <f aca="false">IF(OR($A185="",$C185=""),"",$C185*Rubric!$B$5+$D185*Rubric!$B$6+$E185*Rubric!$B$7+$F185*Rubric!$B$8+$G185*Rubric!$B$9)</f>
-        <v/>
+        <v>4.26</v>
       </c>
       <c r="O185" s="41" t="str">
         <f aca="false">IF($A185="","",IF(OR(UPPER($H185)="Y",UPPER($I185)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P185" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P185" s="42" t="n">
         <f aca="false">IF($N185="","",Assumptions!$B$6*MAX(0.05,($N185/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q185" s="42" t="str">
+        <v>0.0284</v>
+      </c>
+      <c r="Q185" s="42" t="n">
         <f aca="false">IF($P185="","",1-(1-$P185)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R185" s="43" t="str">
+        <v>0.13416022882014</v>
+      </c>
+      <c r="R185" s="43" t="n">
         <f aca="false">IF($M185="","",$M185*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S185" s="43" t="str">
         <f aca="false">IF(OR($J185="",$Q185="",$Q185=0),"",($J185+$R185)/($Q185*(1-Assumptions!$B$4)))</f>
@@ -18340,53 +18930,71 @@
       </c>
       <c r="V185" s="41" t="str">
         <f aca="false">IF($A185="","",IF($O185="FAIL","REJECT",IF($J185="","NEEDS PRICE",IF(OR($K185="",$L185=""),"NEEDS VALUATION",IF($T185&gt;=Assumptions!$B$13,"BUY",IF($T185&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W185" s="26"/>
-      <c r="X185" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W185" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X185" s="36" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="49"/>
+      <c r="A186" s="23" t="s">
+        <v>537</v>
+      </c>
       <c r="B186" s="37" t="str">
         <f aca="false">IF($A186="","",IF(ISERROR(FIND(".",$A186)),"",LOWER(MID($A186,FIND(CHAR(1),SUBSTITUTE($A186,".",CHAR(1),LEN($A186)-LEN(SUBSTITUTE($A186,".",""))))+1,LEN($A186)))))</f>
-        <v/>
-      </c>
-      <c r="C186" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C186" s="38" t="n">
         <f aca="false">IF($B186="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B186,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D186" s="26"/>
-      <c r="E186" s="26"/>
-      <c r="F186" s="26"/>
-      <c r="G186" s="26"/>
-      <c r="H186" s="26"/>
-      <c r="I186" s="26"/>
-      <c r="J186" s="27"/>
-      <c r="K186" s="28"/>
-      <c r="L186" s="49"/>
-      <c r="M186" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D186" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E186" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F186" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G186" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H186" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I186" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J186" s="47"/>
+      <c r="K186" s="48"/>
+      <c r="L186" s="26"/>
+      <c r="M186" s="39" t="n">
         <f aca="false">IF($B186="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B186,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N186" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N186" s="40" t="n">
         <f aca="false">IF(OR($A186="",$C186=""),"",$C186*Rubric!$B$5+$D186*Rubric!$B$6+$E186*Rubric!$B$7+$F186*Rubric!$B$8+$G186*Rubric!$B$9)</f>
-        <v/>
+        <v>4.1</v>
       </c>
       <c r="O186" s="41" t="str">
         <f aca="false">IF($A186="","",IF(OR(UPPER($H186)="Y",UPPER($I186)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P186" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P186" s="42" t="n">
         <f aca="false">IF($N186="","",Assumptions!$B$6*MAX(0.05,($N186/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q186" s="42" t="str">
+        <v>0.0273333333333333</v>
+      </c>
+      <c r="Q186" s="42" t="n">
         <f aca="false">IF($P186="","",1-(1-$P186)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R186" s="43" t="str">
+        <v>0.129396990307648</v>
+      </c>
+      <c r="R186" s="43" t="n">
         <f aca="false">IF($M186="","",$M186*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S186" s="43" t="str">
         <f aca="false">IF(OR($J186="",$Q186="",$Q186=0),"",($J186+$R186)/($Q186*(1-Assumptions!$B$4)))</f>
@@ -18402,53 +19010,71 @@
       </c>
       <c r="V186" s="41" t="str">
         <f aca="false">IF($A186="","",IF($O186="FAIL","REJECT",IF($J186="","NEEDS PRICE",IF(OR($K186="",$L186=""),"NEEDS VALUATION",IF($T186&gt;=Assumptions!$B$13,"BUY",IF($T186&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W186" s="26"/>
-      <c r="X186" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W186" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X186" s="36" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="49"/>
+      <c r="A187" s="23" t="s">
+        <v>539</v>
+      </c>
       <c r="B187" s="37" t="str">
         <f aca="false">IF($A187="","",IF(ISERROR(FIND(".",$A187)),"",LOWER(MID($A187,FIND(CHAR(1),SUBSTITUTE($A187,".",CHAR(1),LEN($A187)-LEN(SUBSTITUTE($A187,".",""))))+1,LEN($A187)))))</f>
-        <v/>
-      </c>
-      <c r="C187" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C187" s="38" t="n">
         <f aca="false">IF($B187="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B187,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D187" s="26"/>
-      <c r="E187" s="26"/>
-      <c r="F187" s="26"/>
-      <c r="G187" s="26"/>
-      <c r="H187" s="26"/>
-      <c r="I187" s="26"/>
-      <c r="J187" s="27"/>
-      <c r="K187" s="28"/>
-      <c r="L187" s="49"/>
-      <c r="M187" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D187" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E187" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F187" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G187" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H187" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I187" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J187" s="47"/>
+      <c r="K187" s="48"/>
+      <c r="L187" s="26"/>
+      <c r="M187" s="39" t="n">
         <f aca="false">IF($B187="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B187,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N187" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N187" s="40" t="n">
         <f aca="false">IF(OR($A187="",$C187=""),"",$C187*Rubric!$B$5+$D187*Rubric!$B$6+$E187*Rubric!$B$7+$F187*Rubric!$B$8+$G187*Rubric!$B$9)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="O187" s="41" t="str">
         <f aca="false">IF($A187="","",IF(OR(UPPER($H187)="Y",UPPER($I187)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P187" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P187" s="42" t="n">
         <f aca="false">IF($N187="","",Assumptions!$B$6*MAX(0.05,($N187/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q187" s="42" t="str">
+        <v>0.0266666666666667</v>
+      </c>
+      <c r="Q187" s="42" t="n">
         <f aca="false">IF($P187="","",1-(1-$P187)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R187" s="43" t="str">
+        <v>0.126409336941564</v>
+      </c>
+      <c r="R187" s="43" t="n">
         <f aca="false">IF($M187="","",$M187*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S187" s="43" t="str">
         <f aca="false">IF(OR($J187="",$Q187="",$Q187=0),"",($J187+$R187)/($Q187*(1-Assumptions!$B$4)))</f>
@@ -18464,53 +19090,71 @@
       </c>
       <c r="V187" s="41" t="str">
         <f aca="false">IF($A187="","",IF($O187="FAIL","REJECT",IF($J187="","NEEDS PRICE",IF(OR($K187="",$L187=""),"NEEDS VALUATION",IF($T187&gt;=Assumptions!$B$13,"BUY",IF($T187&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W187" s="26"/>
-      <c r="X187" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W187" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X187" s="36" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="49"/>
+      <c r="A188" s="23" t="s">
+        <v>541</v>
+      </c>
       <c r="B188" s="37" t="str">
         <f aca="false">IF($A188="","",IF(ISERROR(FIND(".",$A188)),"",LOWER(MID($A188,FIND(CHAR(1),SUBSTITUTE($A188,".",CHAR(1),LEN($A188)-LEN(SUBSTITUTE($A188,".",""))))+1,LEN($A188)))))</f>
-        <v/>
-      </c>
-      <c r="C188" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C188" s="38" t="n">
         <f aca="false">IF($B188="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B188,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D188" s="26"/>
-      <c r="E188" s="26"/>
-      <c r="F188" s="26"/>
-      <c r="G188" s="26"/>
-      <c r="H188" s="26"/>
-      <c r="I188" s="26"/>
-      <c r="J188" s="27"/>
-      <c r="K188" s="28"/>
-      <c r="L188" s="49"/>
-      <c r="M188" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D188" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F188" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G188" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H188" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I188" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J188" s="47"/>
+      <c r="K188" s="48"/>
+      <c r="L188" s="26"/>
+      <c r="M188" s="39" t="n">
         <f aca="false">IF($B188="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B188,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N188" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N188" s="40" t="n">
         <f aca="false">IF(OR($A188="",$C188=""),"",$C188*Rubric!$B$5+$D188*Rubric!$B$6+$E188*Rubric!$B$7+$F188*Rubric!$B$8+$G188*Rubric!$B$9)</f>
-        <v/>
+        <v>3.84</v>
       </c>
       <c r="O188" s="41" t="str">
         <f aca="false">IF($A188="","",IF(OR(UPPER($H188)="Y",UPPER($I188)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P188" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P188" s="42" t="n">
         <f aca="false">IF($N188="","",Assumptions!$B$6*MAX(0.05,($N188/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q188" s="42" t="str">
+        <v>0.0256</v>
+      </c>
+      <c r="Q188" s="42" t="n">
         <f aca="false">IF($P188="","",1-(1-$P188)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R188" s="43" t="str">
+        <v>0.121612035671468</v>
+      </c>
+      <c r="R188" s="43" t="n">
         <f aca="false">IF($M188="","",$M188*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S188" s="43" t="str">
         <f aca="false">IF(OR($J188="",$Q188="",$Q188=0),"",($J188+$R188)/($Q188*(1-Assumptions!$B$4)))</f>
@@ -18526,53 +19170,71 @@
       </c>
       <c r="V188" s="41" t="str">
         <f aca="false">IF($A188="","",IF($O188="FAIL","REJECT",IF($J188="","NEEDS PRICE",IF(OR($K188="",$L188=""),"NEEDS VALUATION",IF($T188&gt;=Assumptions!$B$13,"BUY",IF($T188&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W188" s="26"/>
-      <c r="X188" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W188" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X188" s="36" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="49"/>
+      <c r="A189" s="23" t="s">
+        <v>543</v>
+      </c>
       <c r="B189" s="37" t="str">
         <f aca="false">IF($A189="","",IF(ISERROR(FIND(".",$A189)),"",LOWER(MID($A189,FIND(CHAR(1),SUBSTITUTE($A189,".",CHAR(1),LEN($A189)-LEN(SUBSTITUTE($A189,".",""))))+1,LEN($A189)))))</f>
-        <v/>
-      </c>
-      <c r="C189" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C189" s="38" t="n">
         <f aca="false">IF($B189="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B189,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D189" s="26"/>
-      <c r="E189" s="26"/>
-      <c r="F189" s="26"/>
-      <c r="G189" s="26"/>
-      <c r="H189" s="26"/>
-      <c r="I189" s="26"/>
-      <c r="J189" s="27"/>
-      <c r="K189" s="28"/>
-      <c r="L189" s="49"/>
-      <c r="M189" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D189" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E189" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F189" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G189" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H189" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I189" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J189" s="47"/>
+      <c r="K189" s="48"/>
+      <c r="L189" s="26"/>
+      <c r="M189" s="39" t="n">
         <f aca="false">IF($B189="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B189,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N189" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N189" s="40" t="n">
         <f aca="false">IF(OR($A189="",$C189=""),"",$C189*Rubric!$B$5+$D189*Rubric!$B$6+$E189*Rubric!$B$7+$F189*Rubric!$B$8+$G189*Rubric!$B$9)</f>
-        <v/>
+        <v>4.62</v>
       </c>
       <c r="O189" s="41" t="str">
         <f aca="false">IF($A189="","",IF(OR(UPPER($H189)="Y",UPPER($I189)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P189" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P189" s="42" t="n">
         <f aca="false">IF($N189="","",Assumptions!$B$6*MAX(0.05,($N189/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q189" s="42" t="str">
+        <v>0.0308</v>
+      </c>
+      <c r="Q189" s="42" t="n">
         <f aca="false">IF($P189="","",1-(1-$P189)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R189" s="43" t="str">
+        <v>0.144801309248222</v>
+      </c>
+      <c r="R189" s="43" t="n">
         <f aca="false">IF($M189="","",$M189*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S189" s="43" t="str">
         <f aca="false">IF(OR($J189="",$Q189="",$Q189=0),"",($J189+$R189)/($Q189*(1-Assumptions!$B$4)))</f>
@@ -18588,53 +19250,71 @@
       </c>
       <c r="V189" s="41" t="str">
         <f aca="false">IF($A189="","",IF($O189="FAIL","REJECT",IF($J189="","NEEDS PRICE",IF(OR($K189="",$L189=""),"NEEDS VALUATION",IF($T189&gt;=Assumptions!$B$13,"BUY",IF($T189&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W189" s="26"/>
-      <c r="X189" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W189" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X189" s="36" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="49"/>
+      <c r="A190" s="23" t="s">
+        <v>545</v>
+      </c>
       <c r="B190" s="37" t="str">
         <f aca="false">IF($A190="","",IF(ISERROR(FIND(".",$A190)),"",LOWER(MID($A190,FIND(CHAR(1),SUBSTITUTE($A190,".",CHAR(1),LEN($A190)-LEN(SUBSTITUTE($A190,".",""))))+1,LEN($A190)))))</f>
-        <v/>
-      </c>
-      <c r="C190" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C190" s="38" t="n">
         <f aca="false">IF($B190="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B190,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D190" s="26"/>
-      <c r="E190" s="26"/>
-      <c r="F190" s="26"/>
-      <c r="G190" s="26"/>
-      <c r="H190" s="26"/>
-      <c r="I190" s="26"/>
-      <c r="J190" s="27"/>
-      <c r="K190" s="28"/>
-      <c r="L190" s="49"/>
-      <c r="M190" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D190" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E190" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F190" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G190" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H190" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I190" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J190" s="47"/>
+      <c r="K190" s="48"/>
+      <c r="L190" s="26"/>
+      <c r="M190" s="39" t="n">
         <f aca="false">IF($B190="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B190,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N190" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N190" s="40" t="n">
         <f aca="false">IF(OR($A190="",$C190=""),"",$C190*Rubric!$B$5+$D190*Rubric!$B$6+$E190*Rubric!$B$7+$F190*Rubric!$B$8+$G190*Rubric!$B$9)</f>
-        <v/>
+        <v>4.56</v>
       </c>
       <c r="O190" s="41" t="str">
         <f aca="false">IF($A190="","",IF(OR(UPPER($H190)="Y",UPPER($I190)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P190" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P190" s="42" t="n">
         <f aca="false">IF($N190="","",Assumptions!$B$6*MAX(0.05,($N190/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q190" s="42" t="str">
+        <v>0.0304</v>
+      </c>
+      <c r="Q190" s="42" t="n">
         <f aca="false">IF($P190="","",1-(1-$P190)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R190" s="43" t="str">
+        <v>0.143035100245252</v>
+      </c>
+      <c r="R190" s="43" t="n">
         <f aca="false">IF($M190="","",$M190*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S190" s="43" t="str">
         <f aca="false">IF(OR($J190="",$Q190="",$Q190=0),"",($J190+$R190)/($Q190*(1-Assumptions!$B$4)))</f>
@@ -18650,53 +19330,71 @@
       </c>
       <c r="V190" s="41" t="str">
         <f aca="false">IF($A190="","",IF($O190="FAIL","REJECT",IF($J190="","NEEDS PRICE",IF(OR($K190="",$L190=""),"NEEDS VALUATION",IF($T190&gt;=Assumptions!$B$13,"BUY",IF($T190&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W190" s="26"/>
-      <c r="X190" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W190" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X190" s="36" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="49"/>
+      <c r="A191" s="23" t="s">
+        <v>547</v>
+      </c>
       <c r="B191" s="37" t="str">
         <f aca="false">IF($A191="","",IF(ISERROR(FIND(".",$A191)),"",LOWER(MID($A191,FIND(CHAR(1),SUBSTITUTE($A191,".",CHAR(1),LEN($A191)-LEN(SUBSTITUTE($A191,".",""))))+1,LEN($A191)))))</f>
-        <v/>
-      </c>
-      <c r="C191" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C191" s="38" t="n">
         <f aca="false">IF($B191="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B191,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D191" s="26"/>
-      <c r="E191" s="26"/>
-      <c r="F191" s="26"/>
-      <c r="G191" s="26"/>
-      <c r="H191" s="26"/>
-      <c r="I191" s="26"/>
-      <c r="J191" s="27"/>
-      <c r="K191" s="28"/>
-      <c r="L191" s="49"/>
-      <c r="M191" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D191" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E191" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F191" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G191" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H191" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I191" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J191" s="47"/>
+      <c r="K191" s="48"/>
+      <c r="L191" s="26"/>
+      <c r="M191" s="39" t="n">
         <f aca="false">IF($B191="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B191,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N191" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N191" s="40" t="n">
         <f aca="false">IF(OR($A191="",$C191=""),"",$C191*Rubric!$B$5+$D191*Rubric!$B$6+$E191*Rubric!$B$7+$F191*Rubric!$B$8+$G191*Rubric!$B$9)</f>
-        <v/>
+        <v>4.1</v>
       </c>
       <c r="O191" s="41" t="str">
         <f aca="false">IF($A191="","",IF(OR(UPPER($H191)="Y",UPPER($I191)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P191" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P191" s="42" t="n">
         <f aca="false">IF($N191="","",Assumptions!$B$6*MAX(0.05,($N191/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q191" s="42" t="str">
+        <v>0.0273333333333333</v>
+      </c>
+      <c r="Q191" s="42" t="n">
         <f aca="false">IF($P191="","",1-(1-$P191)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R191" s="43" t="str">
+        <v>0.129396990307648</v>
+      </c>
+      <c r="R191" s="43" t="n">
         <f aca="false">IF($M191="","",$M191*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S191" s="43" t="str">
         <f aca="false">IF(OR($J191="",$Q191="",$Q191=0),"",($J191+$R191)/($Q191*(1-Assumptions!$B$4)))</f>
@@ -18712,53 +19410,71 @@
       </c>
       <c r="V191" s="41" t="str">
         <f aca="false">IF($A191="","",IF($O191="FAIL","REJECT",IF($J191="","NEEDS PRICE",IF(OR($K191="",$L191=""),"NEEDS VALUATION",IF($T191&gt;=Assumptions!$B$13,"BUY",IF($T191&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W191" s="26"/>
-      <c r="X191" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W191" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X191" s="36" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="49"/>
+      <c r="A192" s="23" t="s">
+        <v>549</v>
+      </c>
       <c r="B192" s="37" t="str">
         <f aca="false">IF($A192="","",IF(ISERROR(FIND(".",$A192)),"",LOWER(MID($A192,FIND(CHAR(1),SUBSTITUTE($A192,".",CHAR(1),LEN($A192)-LEN(SUBSTITUTE($A192,".",""))))+1,LEN($A192)))))</f>
-        <v/>
-      </c>
-      <c r="C192" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C192" s="38" t="n">
         <f aca="false">IF($B192="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B192,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D192" s="26"/>
-      <c r="E192" s="26"/>
-      <c r="F192" s="26"/>
-      <c r="G192" s="26"/>
-      <c r="H192" s="26"/>
-      <c r="I192" s="26"/>
-      <c r="J192" s="27"/>
-      <c r="K192" s="28"/>
-      <c r="L192" s="49"/>
-      <c r="M192" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D192" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E192" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F192" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G192" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H192" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I192" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J192" s="47"/>
+      <c r="K192" s="48"/>
+      <c r="L192" s="26"/>
+      <c r="M192" s="39" t="n">
         <f aca="false">IF($B192="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B192,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N192" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N192" s="40" t="n">
         <f aca="false">IF(OR($A192="",$C192=""),"",$C192*Rubric!$B$5+$D192*Rubric!$B$6+$E192*Rubric!$B$7+$F192*Rubric!$B$8+$G192*Rubric!$B$9)</f>
-        <v/>
+        <v>4.1</v>
       </c>
       <c r="O192" s="41" t="str">
         <f aca="false">IF($A192="","",IF(OR(UPPER($H192)="Y",UPPER($I192)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P192" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P192" s="42" t="n">
         <f aca="false">IF($N192="","",Assumptions!$B$6*MAX(0.05,($N192/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q192" s="42" t="str">
+        <v>0.0273333333333333</v>
+      </c>
+      <c r="Q192" s="42" t="n">
         <f aca="false">IF($P192="","",1-(1-$P192)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R192" s="43" t="str">
+        <v>0.129396990307648</v>
+      </c>
+      <c r="R192" s="43" t="n">
         <f aca="false">IF($M192="","",$M192*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S192" s="43" t="str">
         <f aca="false">IF(OR($J192="",$Q192="",$Q192=0),"",($J192+$R192)/($Q192*(1-Assumptions!$B$4)))</f>
@@ -18774,53 +19490,71 @@
       </c>
       <c r="V192" s="41" t="str">
         <f aca="false">IF($A192="","",IF($O192="FAIL","REJECT",IF($J192="","NEEDS PRICE",IF(OR($K192="",$L192=""),"NEEDS VALUATION",IF($T192&gt;=Assumptions!$B$13,"BUY",IF($T192&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W192" s="26"/>
-      <c r="X192" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W192" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X192" s="36" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="49"/>
+      <c r="A193" s="23" t="s">
+        <v>551</v>
+      </c>
       <c r="B193" s="37" t="str">
         <f aca="false">IF($A193="","",IF(ISERROR(FIND(".",$A193)),"",LOWER(MID($A193,FIND(CHAR(1),SUBSTITUTE($A193,".",CHAR(1),LEN($A193)-LEN(SUBSTITUTE($A193,".",""))))+1,LEN($A193)))))</f>
-        <v/>
-      </c>
-      <c r="C193" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C193" s="38" t="n">
         <f aca="false">IF($B193="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B193,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D193" s="26"/>
-      <c r="E193" s="26"/>
-      <c r="F193" s="26"/>
-      <c r="G193" s="26"/>
-      <c r="H193" s="26"/>
-      <c r="I193" s="26"/>
-      <c r="J193" s="27"/>
-      <c r="K193" s="28"/>
-      <c r="L193" s="49"/>
-      <c r="M193" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D193" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E193" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F193" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H193" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I193" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J193" s="47"/>
+      <c r="K193" s="48"/>
+      <c r="L193" s="26"/>
+      <c r="M193" s="39" t="n">
         <f aca="false">IF($B193="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B193,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N193" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N193" s="40" t="n">
         <f aca="false">IF(OR($A193="",$C193=""),"",$C193*Rubric!$B$5+$D193*Rubric!$B$6+$E193*Rubric!$B$7+$F193*Rubric!$B$8+$G193*Rubric!$B$9)</f>
-        <v/>
+        <v>3.68</v>
       </c>
       <c r="O193" s="41" t="str">
         <f aca="false">IF($A193="","",IF(OR(UPPER($H193)="Y",UPPER($I193)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P193" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P193" s="42" t="n">
         <f aca="false">IF($N193="","",Assumptions!$B$6*MAX(0.05,($N193/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q193" s="42" t="str">
+        <v>0.0245333333333333</v>
+      </c>
+      <c r="Q193" s="42" t="n">
         <f aca="false">IF($P193="","",1-(1-$P193)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R193" s="43" t="str">
+        <v>0.116793682102402</v>
+      </c>
+      <c r="R193" s="43" t="n">
         <f aca="false">IF($M193="","",$M193*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S193" s="43" t="str">
         <f aca="false">IF(OR($J193="",$Q193="",$Q193=0),"",($J193+$R193)/($Q193*(1-Assumptions!$B$4)))</f>
@@ -18836,53 +19570,71 @@
       </c>
       <c r="V193" s="41" t="str">
         <f aca="false">IF($A193="","",IF($O193="FAIL","REJECT",IF($J193="","NEEDS PRICE",IF(OR($K193="",$L193=""),"NEEDS VALUATION",IF($T193&gt;=Assumptions!$B$13,"BUY",IF($T193&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W193" s="26"/>
-      <c r="X193" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W193" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X193" s="36" t="s">
+        <v>552</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="49"/>
+      <c r="A194" s="23" t="s">
+        <v>553</v>
+      </c>
       <c r="B194" s="37" t="str">
         <f aca="false">IF($A194="","",IF(ISERROR(FIND(".",$A194)),"",LOWER(MID($A194,FIND(CHAR(1),SUBSTITUTE($A194,".",CHAR(1),LEN($A194)-LEN(SUBSTITUTE($A194,".",""))))+1,LEN($A194)))))</f>
-        <v/>
-      </c>
-      <c r="C194" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C194" s="38" t="n">
         <f aca="false">IF($B194="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B194,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D194" s="26"/>
-      <c r="E194" s="26"/>
-      <c r="F194" s="26"/>
-      <c r="G194" s="26"/>
-      <c r="H194" s="26"/>
-      <c r="I194" s="26"/>
-      <c r="J194" s="27"/>
-      <c r="K194" s="28"/>
-      <c r="L194" s="49"/>
-      <c r="M194" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D194" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E194" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F194" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G194" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H194" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I194" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J194" s="47"/>
+      <c r="K194" s="48"/>
+      <c r="L194" s="26"/>
+      <c r="M194" s="39" t="n">
         <f aca="false">IF($B194="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B194,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N194" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N194" s="40" t="n">
         <f aca="false">IF(OR($A194="",$C194=""),"",$C194*Rubric!$B$5+$D194*Rubric!$B$6+$E194*Rubric!$B$7+$F194*Rubric!$B$8+$G194*Rubric!$B$9)</f>
-        <v/>
+        <v>4.26</v>
       </c>
       <c r="O194" s="41" t="str">
         <f aca="false">IF($A194="","",IF(OR(UPPER($H194)="Y",UPPER($I194)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P194" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P194" s="42" t="n">
         <f aca="false">IF($N194="","",Assumptions!$B$6*MAX(0.05,($N194/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q194" s="42" t="str">
+        <v>0.0284</v>
+      </c>
+      <c r="Q194" s="42" t="n">
         <f aca="false">IF($P194="","",1-(1-$P194)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R194" s="43" t="str">
+        <v>0.13416022882014</v>
+      </c>
+      <c r="R194" s="43" t="n">
         <f aca="false">IF($M194="","",$M194*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S194" s="43" t="str">
         <f aca="false">IF(OR($J194="",$Q194="",$Q194=0),"",($J194+$R194)/($Q194*(1-Assumptions!$B$4)))</f>
@@ -18898,53 +19650,71 @@
       </c>
       <c r="V194" s="41" t="str">
         <f aca="false">IF($A194="","",IF($O194="FAIL","REJECT",IF($J194="","NEEDS PRICE",IF(OR($K194="",$L194=""),"NEEDS VALUATION",IF($T194&gt;=Assumptions!$B$13,"BUY",IF($T194&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W194" s="26"/>
-      <c r="X194" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W194" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X194" s="36" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="49"/>
+      <c r="A195" s="23" t="s">
+        <v>555</v>
+      </c>
       <c r="B195" s="37" t="str">
         <f aca="false">IF($A195="","",IF(ISERROR(FIND(".",$A195)),"",LOWER(MID($A195,FIND(CHAR(1),SUBSTITUTE($A195,".",CHAR(1),LEN($A195)-LEN(SUBSTITUTE($A195,".",""))))+1,LEN($A195)))))</f>
-        <v/>
-      </c>
-      <c r="C195" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C195" s="38" t="n">
         <f aca="false">IF($B195="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B195,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D195" s="26"/>
-      <c r="E195" s="26"/>
-      <c r="F195" s="26"/>
-      <c r="G195" s="26"/>
-      <c r="H195" s="26"/>
-      <c r="I195" s="26"/>
-      <c r="J195" s="27"/>
-      <c r="K195" s="28"/>
-      <c r="L195" s="49"/>
-      <c r="M195" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D195" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E195" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F195" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G195" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H195" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I195" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J195" s="47"/>
+      <c r="K195" s="48"/>
+      <c r="L195" s="26"/>
+      <c r="M195" s="39" t="n">
         <f aca="false">IF($B195="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B195,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N195" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N195" s="40" t="n">
         <f aca="false">IF(OR($A195="",$C195=""),"",$C195*Rubric!$B$5+$D195*Rubric!$B$6+$E195*Rubric!$B$7+$F195*Rubric!$B$8+$G195*Rubric!$B$9)</f>
-        <v/>
+        <v>4.62</v>
       </c>
       <c r="O195" s="41" t="str">
         <f aca="false">IF($A195="","",IF(OR(UPPER($H195)="Y",UPPER($I195)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P195" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P195" s="42" t="n">
         <f aca="false">IF($N195="","",Assumptions!$B$6*MAX(0.05,($N195/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q195" s="42" t="str">
+        <v>0.0308</v>
+      </c>
+      <c r="Q195" s="42" t="n">
         <f aca="false">IF($P195="","",1-(1-$P195)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R195" s="43" t="str">
+        <v>0.144801309248222</v>
+      </c>
+      <c r="R195" s="43" t="n">
         <f aca="false">IF($M195="","",$M195*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S195" s="43" t="str">
         <f aca="false">IF(OR($J195="",$Q195="",$Q195=0),"",($J195+$R195)/($Q195*(1-Assumptions!$B$4)))</f>
@@ -18960,53 +19730,71 @@
       </c>
       <c r="V195" s="41" t="str">
         <f aca="false">IF($A195="","",IF($O195="FAIL","REJECT",IF($J195="","NEEDS PRICE",IF(OR($K195="",$L195=""),"NEEDS VALUATION",IF($T195&gt;=Assumptions!$B$13,"BUY",IF($T195&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W195" s="26"/>
-      <c r="X195" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W195" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X195" s="36" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="49"/>
+      <c r="A196" s="23" t="s">
+        <v>557</v>
+      </c>
       <c r="B196" s="37" t="str">
         <f aca="false">IF($A196="","",IF(ISERROR(FIND(".",$A196)),"",LOWER(MID($A196,FIND(CHAR(1),SUBSTITUTE($A196,".",CHAR(1),LEN($A196)-LEN(SUBSTITUTE($A196,".",""))))+1,LEN($A196)))))</f>
-        <v/>
-      </c>
-      <c r="C196" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C196" s="38" t="n">
         <f aca="false">IF($B196="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B196,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D196" s="26"/>
-      <c r="E196" s="26"/>
-      <c r="F196" s="26"/>
-      <c r="G196" s="26"/>
-      <c r="H196" s="26"/>
-      <c r="I196" s="26"/>
-      <c r="J196" s="27"/>
-      <c r="K196" s="28"/>
-      <c r="L196" s="49"/>
-      <c r="M196" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D196" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E196" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F196" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G196" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H196" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I196" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J196" s="47"/>
+      <c r="K196" s="48"/>
+      <c r="L196" s="26"/>
+      <c r="M196" s="39" t="n">
         <f aca="false">IF($B196="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B196,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N196" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N196" s="40" t="n">
         <f aca="false">IF(OR($A196="",$C196=""),"",$C196*Rubric!$B$5+$D196*Rubric!$B$6+$E196*Rubric!$B$7+$F196*Rubric!$B$8+$G196*Rubric!$B$9)</f>
-        <v/>
+        <v>4.26</v>
       </c>
       <c r="O196" s="41" t="str">
         <f aca="false">IF($A196="","",IF(OR(UPPER($H196)="Y",UPPER($I196)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P196" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P196" s="42" t="n">
         <f aca="false">IF($N196="","",Assumptions!$B$6*MAX(0.05,($N196/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q196" s="42" t="str">
+        <v>0.0284</v>
+      </c>
+      <c r="Q196" s="42" t="n">
         <f aca="false">IF($P196="","",1-(1-$P196)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R196" s="43" t="str">
+        <v>0.13416022882014</v>
+      </c>
+      <c r="R196" s="43" t="n">
         <f aca="false">IF($M196="","",$M196*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S196" s="43" t="str">
         <f aca="false">IF(OR($J196="",$Q196="",$Q196=0),"",($J196+$R196)/($Q196*(1-Assumptions!$B$4)))</f>
@@ -19022,53 +19810,71 @@
       </c>
       <c r="V196" s="41" t="str">
         <f aca="false">IF($A196="","",IF($O196="FAIL","REJECT",IF($J196="","NEEDS PRICE",IF(OR($K196="",$L196=""),"NEEDS VALUATION",IF($T196&gt;=Assumptions!$B$13,"BUY",IF($T196&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W196" s="26"/>
-      <c r="X196" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W196" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X196" s="36" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="49"/>
+      <c r="A197" s="23" t="s">
+        <v>559</v>
+      </c>
       <c r="B197" s="37" t="str">
         <f aca="false">IF($A197="","",IF(ISERROR(FIND(".",$A197)),"",LOWER(MID($A197,FIND(CHAR(1),SUBSTITUTE($A197,".",CHAR(1),LEN($A197)-LEN(SUBSTITUTE($A197,".",""))))+1,LEN($A197)))))</f>
-        <v/>
-      </c>
-      <c r="C197" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C197" s="38" t="n">
         <f aca="false">IF($B197="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B197,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D197" s="26"/>
-      <c r="E197" s="26"/>
-      <c r="F197" s="26"/>
-      <c r="G197" s="26"/>
-      <c r="H197" s="26"/>
-      <c r="I197" s="26"/>
-      <c r="J197" s="27"/>
-      <c r="K197" s="28"/>
-      <c r="L197" s="49"/>
-      <c r="M197" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D197" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E197" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F197" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G197" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H197" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I197" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J197" s="47"/>
+      <c r="K197" s="48"/>
+      <c r="L197" s="26"/>
+      <c r="M197" s="39" t="n">
         <f aca="false">IF($B197="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B197,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N197" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N197" s="40" t="n">
         <f aca="false">IF(OR($A197="",$C197=""),"",$C197*Rubric!$B$5+$D197*Rubric!$B$6+$E197*Rubric!$B$7+$F197*Rubric!$B$8+$G197*Rubric!$B$9)</f>
-        <v/>
+        <v>4.1</v>
       </c>
       <c r="O197" s="41" t="str">
         <f aca="false">IF($A197="","",IF(OR(UPPER($H197)="Y",UPPER($I197)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P197" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P197" s="42" t="n">
         <f aca="false">IF($N197="","",Assumptions!$B$6*MAX(0.05,($N197/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q197" s="42" t="str">
+        <v>0.0273333333333333</v>
+      </c>
+      <c r="Q197" s="42" t="n">
         <f aca="false">IF($P197="","",1-(1-$P197)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R197" s="43" t="str">
+        <v>0.129396990307648</v>
+      </c>
+      <c r="R197" s="43" t="n">
         <f aca="false">IF($M197="","",$M197*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S197" s="43" t="str">
         <f aca="false">IF(OR($J197="",$Q197="",$Q197=0),"",($J197+$R197)/($Q197*(1-Assumptions!$B$4)))</f>
@@ -19084,53 +19890,71 @@
       </c>
       <c r="V197" s="41" t="str">
         <f aca="false">IF($A197="","",IF($O197="FAIL","REJECT",IF($J197="","NEEDS PRICE",IF(OR($K197="",$L197=""),"NEEDS VALUATION",IF($T197&gt;=Assumptions!$B$13,"BUY",IF($T197&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W197" s="26"/>
-      <c r="X197" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W197" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X197" s="36" t="s">
+        <v>560</v>
+      </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="49"/>
+      <c r="A198" s="23" t="s">
+        <v>561</v>
+      </c>
       <c r="B198" s="37" t="str">
         <f aca="false">IF($A198="","",IF(ISERROR(FIND(".",$A198)),"",LOWER(MID($A198,FIND(CHAR(1),SUBSTITUTE($A198,".",CHAR(1),LEN($A198)-LEN(SUBSTITUTE($A198,".",""))))+1,LEN($A198)))))</f>
-        <v/>
-      </c>
-      <c r="C198" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C198" s="38" t="n">
         <f aca="false">IF($B198="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B198,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D198" s="26"/>
-      <c r="E198" s="26"/>
-      <c r="F198" s="26"/>
-      <c r="G198" s="26"/>
-      <c r="H198" s="26"/>
-      <c r="I198" s="26"/>
-      <c r="J198" s="27"/>
-      <c r="K198" s="28"/>
-      <c r="L198" s="49"/>
-      <c r="M198" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D198" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E198" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F198" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G198" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H198" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I198" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J198" s="47"/>
+      <c r="K198" s="48"/>
+      <c r="L198" s="26"/>
+      <c r="M198" s="39" t="n">
         <f aca="false">IF($B198="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B198,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N198" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N198" s="40" t="n">
         <f aca="false">IF(OR($A198="",$C198=""),"",$C198*Rubric!$B$5+$D198*Rubric!$B$6+$E198*Rubric!$B$7+$F198*Rubric!$B$8+$G198*Rubric!$B$9)</f>
-        <v/>
+        <v>4.1</v>
       </c>
       <c r="O198" s="41" t="str">
         <f aca="false">IF($A198="","",IF(OR(UPPER($H198)="Y",UPPER($I198)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P198" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P198" s="42" t="n">
         <f aca="false">IF($N198="","",Assumptions!$B$6*MAX(0.05,($N198/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q198" s="42" t="str">
+        <v>0.0273333333333333</v>
+      </c>
+      <c r="Q198" s="42" t="n">
         <f aca="false">IF($P198="","",1-(1-$P198)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R198" s="43" t="str">
+        <v>0.129396990307648</v>
+      </c>
+      <c r="R198" s="43" t="n">
         <f aca="false">IF($M198="","",$M198*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S198" s="43" t="str">
         <f aca="false">IF(OR($J198="",$Q198="",$Q198=0),"",($J198+$R198)/($Q198*(1-Assumptions!$B$4)))</f>
@@ -19146,53 +19970,71 @@
       </c>
       <c r="V198" s="41" t="str">
         <f aca="false">IF($A198="","",IF($O198="FAIL","REJECT",IF($J198="","NEEDS PRICE",IF(OR($K198="",$L198=""),"NEEDS VALUATION",IF($T198&gt;=Assumptions!$B$13,"BUY",IF($T198&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W198" s="26"/>
-      <c r="X198" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W198" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X198" s="36" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="49"/>
+      <c r="A199" s="23" t="s">
+        <v>563</v>
+      </c>
       <c r="B199" s="37" t="str">
         <f aca="false">IF($A199="","",IF(ISERROR(FIND(".",$A199)),"",LOWER(MID($A199,FIND(CHAR(1),SUBSTITUTE($A199,".",CHAR(1),LEN($A199)-LEN(SUBSTITUTE($A199,".",""))))+1,LEN($A199)))))</f>
-        <v/>
-      </c>
-      <c r="C199" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C199" s="38" t="n">
         <f aca="false">IF($B199="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B199,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D199" s="26"/>
-      <c r="E199" s="26"/>
-      <c r="F199" s="26"/>
-      <c r="G199" s="26"/>
-      <c r="H199" s="26"/>
-      <c r="I199" s="26"/>
-      <c r="J199" s="27"/>
-      <c r="K199" s="28"/>
-      <c r="L199" s="49"/>
-      <c r="M199" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D199" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E199" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F199" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G199" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H199" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I199" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J199" s="47"/>
+      <c r="K199" s="48"/>
+      <c r="L199" s="26"/>
+      <c r="M199" s="39" t="n">
         <f aca="false">IF($B199="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B199,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N199" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N199" s="40" t="n">
         <f aca="false">IF(OR($A199="",$C199=""),"",$C199*Rubric!$B$5+$D199*Rubric!$B$6+$E199*Rubric!$B$7+$F199*Rubric!$B$8+$G199*Rubric!$B$9)</f>
-        <v/>
+        <v>3.94</v>
       </c>
       <c r="O199" s="41" t="str">
         <f aca="false">IF($A199="","",IF(OR(UPPER($H199)="Y",UPPER($I199)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P199" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P199" s="42" t="n">
         <f aca="false">IF($N199="","",Assumptions!$B$6*MAX(0.05,($N199/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q199" s="42" t="str">
+        <v>0.0262666666666667</v>
+      </c>
+      <c r="Q199" s="42" t="n">
         <f aca="false">IF($P199="","",1-(1-$P199)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R199" s="43" t="str">
+        <v>0.12461281164447</v>
+      </c>
+      <c r="R199" s="43" t="n">
         <f aca="false">IF($M199="","",$M199*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S199" s="43" t="str">
         <f aca="false">IF(OR($J199="",$Q199="",$Q199=0),"",($J199+$R199)/($Q199*(1-Assumptions!$B$4)))</f>
@@ -19208,53 +20050,71 @@
       </c>
       <c r="V199" s="41" t="str">
         <f aca="false">IF($A199="","",IF($O199="FAIL","REJECT",IF($J199="","NEEDS PRICE",IF(OR($K199="",$L199=""),"NEEDS VALUATION",IF($T199&gt;=Assumptions!$B$13,"BUY",IF($T199&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W199" s="26"/>
-      <c r="X199" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W199" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X199" s="36" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="49"/>
+      <c r="A200" s="23" t="s">
+        <v>565</v>
+      </c>
       <c r="B200" s="37" t="str">
         <f aca="false">IF($A200="","",IF(ISERROR(FIND(".",$A200)),"",LOWER(MID($A200,FIND(CHAR(1),SUBSTITUTE($A200,".",CHAR(1),LEN($A200)-LEN(SUBSTITUTE($A200,".",""))))+1,LEN($A200)))))</f>
-        <v/>
-      </c>
-      <c r="C200" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C200" s="38" t="n">
         <f aca="false">IF($B200="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B200,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
-      <c r="F200" s="26"/>
-      <c r="G200" s="26"/>
-      <c r="H200" s="26"/>
-      <c r="I200" s="26"/>
-      <c r="J200" s="27"/>
-      <c r="K200" s="28"/>
-      <c r="L200" s="49"/>
-      <c r="M200" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D200" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E200" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G200" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H200" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I200" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J200" s="47"/>
+      <c r="K200" s="48"/>
+      <c r="L200" s="26"/>
+      <c r="M200" s="39" t="n">
         <f aca="false">IF($B200="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B200,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N200" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N200" s="40" t="n">
         <f aca="false">IF(OR($A200="",$C200=""),"",$C200*Rubric!$B$5+$D200*Rubric!$B$6+$E200*Rubric!$B$7+$F200*Rubric!$B$8+$G200*Rubric!$B$9)</f>
-        <v/>
+        <v>3.48</v>
       </c>
       <c r="O200" s="41" t="str">
         <f aca="false">IF($A200="","",IF(OR(UPPER($H200)="Y",UPPER($I200)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P200" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P200" s="42" t="n">
         <f aca="false">IF($N200="","",Assumptions!$B$6*MAX(0.05,($N200/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q200" s="42" t="str">
+        <v>0.0232</v>
+      </c>
+      <c r="Q200" s="42" t="n">
         <f aca="false">IF($P200="","",1-(1-$P200)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R200" s="43" t="str">
+        <v>0.110741029889605</v>
+      </c>
+      <c r="R200" s="43" t="n">
         <f aca="false">IF($M200="","",$M200*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S200" s="43" t="str">
         <f aca="false">IF(OR($J200="",$Q200="",$Q200=0),"",($J200+$R200)/($Q200*(1-Assumptions!$B$4)))</f>
@@ -19270,53 +20130,71 @@
       </c>
       <c r="V200" s="41" t="str">
         <f aca="false">IF($A200="","",IF($O200="FAIL","REJECT",IF($J200="","NEEDS PRICE",IF(OR($K200="",$L200=""),"NEEDS VALUATION",IF($T200&gt;=Assumptions!$B$13,"BUY",IF($T200&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W200" s="26"/>
-      <c r="X200" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W200" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X200" s="36" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="49"/>
+      <c r="A201" s="23" t="s">
+        <v>567</v>
+      </c>
       <c r="B201" s="37" t="str">
         <f aca="false">IF($A201="","",IF(ISERROR(FIND(".",$A201)),"",LOWER(MID($A201,FIND(CHAR(1),SUBSTITUTE($A201,".",CHAR(1),LEN($A201)-LEN(SUBSTITUTE($A201,".",""))))+1,LEN($A201)))))</f>
-        <v/>
-      </c>
-      <c r="C201" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C201" s="38" t="n">
         <f aca="false">IF($B201="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B201,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D201" s="26"/>
-      <c r="E201" s="26"/>
-      <c r="F201" s="26"/>
-      <c r="G201" s="26"/>
-      <c r="H201" s="26"/>
-      <c r="I201" s="26"/>
-      <c r="J201" s="27"/>
-      <c r="K201" s="28"/>
-      <c r="L201" s="49"/>
-      <c r="M201" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D201" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E201" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F201" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G201" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H201" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I201" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J201" s="47"/>
+      <c r="K201" s="48"/>
+      <c r="L201" s="26"/>
+      <c r="M201" s="39" t="n">
         <f aca="false">IF($B201="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B201,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N201" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N201" s="40" t="n">
         <f aca="false">IF(OR($A201="",$C201=""),"",$C201*Rubric!$B$5+$D201*Rubric!$B$6+$E201*Rubric!$B$7+$F201*Rubric!$B$8+$G201*Rubric!$B$9)</f>
-        <v/>
+        <v>4.4</v>
       </c>
       <c r="O201" s="41" t="str">
         <f aca="false">IF($A201="","",IF(OR(UPPER($H201)="Y",UPPER($I201)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P201" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P201" s="42" t="n">
         <f aca="false">IF($N201="","",Assumptions!$B$6*MAX(0.05,($N201/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q201" s="42" t="str">
+        <v>0.0293333333333333</v>
+      </c>
+      <c r="Q201" s="42" t="n">
         <f aca="false">IF($P201="","",1-(1-$P201)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R201" s="43" t="str">
+        <v>0.138310939153412</v>
+      </c>
+      <c r="R201" s="43" t="n">
         <f aca="false">IF($M201="","",$M201*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S201" s="43" t="str">
         <f aca="false">IF(OR($J201="",$Q201="",$Q201=0),"",($J201+$R201)/($Q201*(1-Assumptions!$B$4)))</f>
@@ -19332,53 +20210,71 @@
       </c>
       <c r="V201" s="41" t="str">
         <f aca="false">IF($A201="","",IF($O201="FAIL","REJECT",IF($J201="","NEEDS PRICE",IF(OR($K201="",$L201=""),"NEEDS VALUATION",IF($T201&gt;=Assumptions!$B$13,"BUY",IF($T201&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W201" s="26"/>
-      <c r="X201" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W201" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X201" s="36" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="49"/>
+      <c r="A202" s="23" t="s">
+        <v>569</v>
+      </c>
       <c r="B202" s="37" t="str">
         <f aca="false">IF($A202="","",IF(ISERROR(FIND(".",$A202)),"",LOWER(MID($A202,FIND(CHAR(1),SUBSTITUTE($A202,".",CHAR(1),LEN($A202)-LEN(SUBSTITUTE($A202,".",""))))+1,LEN($A202)))))</f>
-        <v/>
-      </c>
-      <c r="C202" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C202" s="38" t="n">
         <f aca="false">IF($B202="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B202,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D202" s="26"/>
-      <c r="E202" s="26"/>
-      <c r="F202" s="26"/>
-      <c r="G202" s="26"/>
-      <c r="H202" s="26"/>
-      <c r="I202" s="26"/>
-      <c r="J202" s="27"/>
-      <c r="K202" s="28"/>
-      <c r="L202" s="49"/>
-      <c r="M202" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D202" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E202" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F202" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G202" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H202" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I202" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J202" s="47"/>
+      <c r="K202" s="48"/>
+      <c r="L202" s="26"/>
+      <c r="M202" s="39" t="n">
         <f aca="false">IF($B202="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B202,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N202" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N202" s="40" t="n">
         <f aca="false">IF(OR($A202="",$C202=""),"",$C202*Rubric!$B$5+$D202*Rubric!$B$6+$E202*Rubric!$B$7+$F202*Rubric!$B$8+$G202*Rubric!$B$9)</f>
-        <v/>
+        <v>4.16</v>
       </c>
       <c r="O202" s="41" t="str">
         <f aca="false">IF($A202="","",IF(OR(UPPER($H202)="Y",UPPER($I202)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P202" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P202" s="42" t="n">
         <f aca="false">IF($N202="","",Assumptions!$B$6*MAX(0.05,($N202/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q202" s="42" t="str">
+        <v>0.0277333333333333</v>
+      </c>
+      <c r="Q202" s="42" t="n">
         <f aca="false">IF($P202="","",1-(1-$P202)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R202" s="43" t="str">
+        <v>0.131185654974276</v>
+      </c>
+      <c r="R202" s="43" t="n">
         <f aca="false">IF($M202="","",$M202*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S202" s="43" t="str">
         <f aca="false">IF(OR($J202="",$Q202="",$Q202=0),"",($J202+$R202)/($Q202*(1-Assumptions!$B$4)))</f>
@@ -19394,53 +20290,71 @@
       </c>
       <c r="V202" s="41" t="str">
         <f aca="false">IF($A202="","",IF($O202="FAIL","REJECT",IF($J202="","NEEDS PRICE",IF(OR($K202="",$L202=""),"NEEDS VALUATION",IF($T202&gt;=Assumptions!$B$13,"BUY",IF($T202&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W202" s="26"/>
-      <c r="X202" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W202" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X202" s="36" t="s">
+        <v>570</v>
+      </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="49"/>
+      <c r="A203" s="23" t="s">
+        <v>571</v>
+      </c>
       <c r="B203" s="37" t="str">
         <f aca="false">IF($A203="","",IF(ISERROR(FIND(".",$A203)),"",LOWER(MID($A203,FIND(CHAR(1),SUBSTITUTE($A203,".",CHAR(1),LEN($A203)-LEN(SUBSTITUTE($A203,".",""))))+1,LEN($A203)))))</f>
-        <v/>
-      </c>
-      <c r="C203" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C203" s="38" t="n">
         <f aca="false">IF($B203="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B203,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D203" s="26"/>
-      <c r="E203" s="26"/>
-      <c r="F203" s="26"/>
-      <c r="G203" s="26"/>
-      <c r="H203" s="26"/>
-      <c r="I203" s="26"/>
-      <c r="J203" s="27"/>
-      <c r="K203" s="28"/>
-      <c r="L203" s="49"/>
-      <c r="M203" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D203" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E203" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="H203" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I203" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J203" s="47"/>
+      <c r="K203" s="48"/>
+      <c r="L203" s="26"/>
+      <c r="M203" s="39" t="n">
         <f aca="false">IF($B203="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B203,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N203" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N203" s="40" t="n">
         <f aca="false">IF(OR($A203="",$C203=""),"",$C203*Rubric!$B$5+$D203*Rubric!$B$6+$E203*Rubric!$B$7+$F203*Rubric!$B$8+$G203*Rubric!$B$9)</f>
-        <v/>
+        <v>3.68</v>
       </c>
       <c r="O203" s="41" t="str">
         <f aca="false">IF($A203="","",IF(OR(UPPER($H203)="Y",UPPER($I203)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P203" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P203" s="42" t="n">
         <f aca="false">IF($N203="","",Assumptions!$B$6*MAX(0.05,($N203/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q203" s="42" t="str">
+        <v>0.0245333333333333</v>
+      </c>
+      <c r="Q203" s="42" t="n">
         <f aca="false">IF($P203="","",1-(1-$P203)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R203" s="43" t="str">
+        <v>0.116793682102402</v>
+      </c>
+      <c r="R203" s="43" t="n">
         <f aca="false">IF($M203="","",$M203*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S203" s="43" t="str">
         <f aca="false">IF(OR($J203="",$Q203="",$Q203=0),"",($J203+$R203)/($Q203*(1-Assumptions!$B$4)))</f>
@@ -19456,53 +20370,71 @@
       </c>
       <c r="V203" s="41" t="str">
         <f aca="false">IF($A203="","",IF($O203="FAIL","REJECT",IF($J203="","NEEDS PRICE",IF(OR($K203="",$L203=""),"NEEDS VALUATION",IF($T203&gt;=Assumptions!$B$13,"BUY",IF($T203&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W203" s="26"/>
-      <c r="X203" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W203" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X203" s="36" t="s">
+        <v>572</v>
+      </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="49"/>
+      <c r="A204" s="23" t="s">
+        <v>573</v>
+      </c>
       <c r="B204" s="37" t="str">
         <f aca="false">IF($A204="","",IF(ISERROR(FIND(".",$A204)),"",LOWER(MID($A204,FIND(CHAR(1),SUBSTITUTE($A204,".",CHAR(1),LEN($A204)-LEN(SUBSTITUTE($A204,".",""))))+1,LEN($A204)))))</f>
-        <v/>
-      </c>
-      <c r="C204" s="38" t="str">
+        <v>com</v>
+      </c>
+      <c r="C204" s="38" t="n">
         <f aca="false">IF($B204="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B204,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="D204" s="26"/>
-      <c r="E204" s="26"/>
-      <c r="F204" s="26"/>
-      <c r="G204" s="26"/>
-      <c r="H204" s="26"/>
-      <c r="I204" s="26"/>
-      <c r="J204" s="27"/>
-      <c r="K204" s="28"/>
-      <c r="L204" s="49"/>
-      <c r="M204" s="39" t="str">
+        <v>5</v>
+      </c>
+      <c r="D204" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E204" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G204" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="H204" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="I204" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="J204" s="47"/>
+      <c r="K204" s="48"/>
+      <c r="L204" s="26"/>
+      <c r="M204" s="39" t="n">
         <f aca="false">IF($B204="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B204,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
-        <v/>
-      </c>
-      <c r="N204" s="40" t="str">
+        <v>11</v>
+      </c>
+      <c r="N204" s="40" t="n">
         <f aca="false">IF(OR($A204="",$C204=""),"",$C204*Rubric!$B$5+$D204*Rubric!$B$6+$E204*Rubric!$B$7+$F204*Rubric!$B$8+$G204*Rubric!$B$9)</f>
-        <v/>
+        <v>3.94</v>
       </c>
       <c r="O204" s="41" t="str">
         <f aca="false">IF($A204="","",IF(OR(UPPER($H204)="Y",UPPER($I204)="Y"),"FAIL","PASS"))</f>
-        <v/>
-      </c>
-      <c r="P204" s="42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="P204" s="42" t="n">
         <f aca="false">IF($N204="","",Assumptions!$B$6*MAX(0.05,($N204/Assumptions!$B$11)^Assumptions!$B$12))</f>
-        <v/>
-      </c>
-      <c r="Q204" s="42" t="str">
+        <v>0.0262666666666667</v>
+      </c>
+      <c r="Q204" s="42" t="n">
         <f aca="false">IF($P204="","",1-(1-$P204)^Assumptions!$B$7)</f>
-        <v/>
-      </c>
-      <c r="R204" s="43" t="str">
+        <v>0.12461281164447</v>
+      </c>
+      <c r="R204" s="43" t="n">
         <f aca="false">IF($M204="","",$M204*Assumptions!$B$7)</f>
-        <v/>
+        <v>55</v>
       </c>
       <c r="S204" s="43" t="str">
         <f aca="false">IF(OR($J204="",$Q204="",$Q204=0),"",($J204+$R204)/($Q204*(1-Assumptions!$B$4)))</f>
@@ -19518,10 +20450,14 @@
       </c>
       <c r="V204" s="41" t="str">
         <f aca="false">IF($A204="","",IF($O204="FAIL","REJECT",IF($J204="","NEEDS PRICE",IF(OR($K204="",$L204=""),"NEEDS VALUATION",IF($T204&gt;=Assumptions!$B$13,"BUY",IF($T204&gt;=1,"MARGINAL","PASS"))))))</f>
-        <v/>
-      </c>
-      <c r="W204" s="26"/>
-      <c r="X204" s="36"/>
+        <v>NEEDS PRICE</v>
+      </c>
+      <c r="W204" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="X204" s="36" t="s">
+        <v>574</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:X204"/>
@@ -19581,7 +20517,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>497</v>
+        <v>575</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19594,36 +20530,36 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="50" t="s">
-        <v>498</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="A2" s="49" t="s">
+        <v>576</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="51" t="s">
-        <v>499</v>
-      </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
+      <c r="A4" s="50" t="s">
+        <v>577</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="53" t="s">
-        <v>500</v>
+      <c r="A5" s="52" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="53" t="s">
         <v>77</v>
       </c>
       <c r="B6" s="10" t="n">
@@ -19631,7 +20567,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>81</v>
       </c>
       <c r="B7" s="10" t="n">
@@ -19639,7 +20575,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>89</v>
       </c>
       <c r="B8" s="10" t="n">
@@ -19647,7 +20583,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="53" t="s">
         <v>93</v>
       </c>
       <c r="B9" s="10" t="n">
@@ -19655,412 +20591,412 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="55" t="s">
-        <v>501</v>
-      </c>
-      <c r="B10" s="56" t="n">
+      <c r="A10" s="54" t="s">
+        <v>579</v>
+      </c>
+      <c r="B10" s="55" t="n">
         <f aca="false">SUM(B6:B9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="55" t="str">
+      <c r="C10" s="54" t="str">
         <f aca="false">IF(ABS(B10-1)&lt;0.0001,"OK","ERROR - must total 100%")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="53" t="s">
-        <v>502</v>
+      <c r="A12" s="52" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="54" t="s">
-        <v>503</v>
+      <c r="A13" s="53" t="s">
+        <v>581</v>
       </c>
       <c r="B13" s="10" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="54" t="s">
-        <v>504</v>
+      <c r="A14" s="53" t="s">
+        <v>582</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>0.35</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="54" t="s">
-        <v>505</v>
+      <c r="A15" s="53" t="s">
+        <v>583</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="54" t="s">
-        <v>506</v>
+      <c r="A16" s="53" t="s">
+        <v>584</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="55" t="s">
-        <v>501</v>
-      </c>
-      <c r="B17" s="56" t="n">
+      <c r="A17" s="54" t="s">
+        <v>579</v>
+      </c>
+      <c r="B17" s="55" t="n">
         <f aca="false">SUM(B13:B16)</f>
         <v>1</v>
       </c>
-      <c r="C17" s="55" t="str">
+      <c r="C17" s="54" t="str">
         <f aca="false">IF(ABS(B17-1)&lt;0.0001,"OK","ERROR - must total 100%")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="54" t="s">
-        <v>507</v>
+      <c r="A19" s="53" t="s">
+        <v>585</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="C19" s="57" t="s">
-        <v>508</v>
-      </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
+      <c r="C19" s="56" t="s">
+        <v>586</v>
+      </c>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
+      <c r="H19" s="56"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="s">
-        <v>509</v>
-      </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
+      <c r="A21" s="50" t="s">
+        <v>587</v>
+      </c>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="55" t="s">
-        <v>503</v>
-      </c>
-      <c r="B22" s="58" t="s">
-        <v>510</v>
-      </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
+      <c r="A22" s="54" t="s">
+        <v>581</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>588</v>
+      </c>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="55" t="s">
-        <v>504</v>
-      </c>
-      <c r="B23" s="58" t="s">
-        <v>511</v>
-      </c>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
+      <c r="A23" s="54" t="s">
+        <v>582</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>589</v>
+      </c>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="55" t="s">
-        <v>505</v>
-      </c>
-      <c r="B24" s="58" t="s">
-        <v>512</v>
-      </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
+      <c r="A24" s="54" t="s">
+        <v>583</v>
+      </c>
+      <c r="B24" s="57" t="s">
+        <v>590</v>
+      </c>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="55" t="s">
-        <v>506</v>
-      </c>
-      <c r="B25" s="58" t="s">
-        <v>513</v>
-      </c>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
+      <c r="A25" s="54" t="s">
+        <v>584</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>591</v>
+      </c>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="s">
-        <v>514</v>
-      </c>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
+      <c r="A27" s="50" t="s">
+        <v>592</v>
+      </c>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="58" t="s">
-        <v>515</v>
-      </c>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="58"/>
+      <c r="B28" s="57" t="s">
+        <v>593</v>
+      </c>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="58" t="s">
-        <v>516</v>
-      </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
+      <c r="B29" s="57" t="s">
+        <v>594</v>
+      </c>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="58" t="s">
-        <v>517</v>
-      </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
+      <c r="B30" s="57" t="s">
+        <v>595</v>
+      </c>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="58" t="s">
-        <v>518</v>
-      </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
+      <c r="B31" s="57" t="s">
+        <v>596</v>
+      </c>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="51" t="s">
-        <v>519</v>
-      </c>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
+      <c r="A34" s="50" t="s">
+        <v>597</v>
+      </c>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="54" t="s">
-        <v>520</v>
-      </c>
-      <c r="B35" s="59" t="n">
+      <c r="A35" s="53" t="s">
+        <v>598</v>
+      </c>
+      <c r="B35" s="58" t="n">
         <f aca="false">COUNTIF($A$44:$A$163,"&lt;&gt;")</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="54" t="s">
-        <v>521</v>
-      </c>
-      <c r="B36" s="59" t="n">
+      <c r="A36" s="53" t="s">
+        <v>599</v>
+      </c>
+      <c r="B36" s="58" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"BUY")</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="54" t="s">
-        <v>522</v>
-      </c>
-      <c r="B37" s="59" t="n">
+      <c r="A37" s="53" t="s">
+        <v>600</v>
+      </c>
+      <c r="B37" s="58" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"BUY CHEAPER")+COUNTIF($AF$44:$AF$163,"FLOOR ONLY")</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="54" t="s">
-        <v>523</v>
-      </c>
-      <c r="B38" s="59" t="n">
+      <c r="A38" s="53" t="s">
+        <v>601</v>
+      </c>
+      <c r="B38" s="58" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"REJECT")+COUNTIF($AF$44:$AF$163,"OVERPRICED")+COUNTIF($AF$44:$AF$163,"SKIP")</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="54" t="s">
-        <v>524</v>
-      </c>
-      <c r="B39" s="59" t="n">
+      <c r="A39" s="53" t="s">
+        <v>602</v>
+      </c>
+      <c r="B39" s="58" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"NEEDS VALUATION")+COUNTIF($AF$44:$AF$163,"NEEDS PRICE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="54" t="s">
-        <v>525</v>
-      </c>
-      <c r="B40" s="60" t="n">
+      <c r="A40" s="53" t="s">
+        <v>603</v>
+      </c>
+      <c r="B40" s="59" t="n">
         <f aca="false">SUMIF($AF$44:$AF$163,"BUY",$F$44:$F$163)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="54" t="s">
-        <v>526</v>
-      </c>
-      <c r="B41" s="61" t="n">
+      <c r="A41" s="53" t="s">
+        <v>604</v>
+      </c>
+      <c r="B41" s="60" t="n">
         <f aca="false">SUMIF($AF$44:$AF$163,"BUY",$AE$44:$AE$163)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="62" t="s">
+      <c r="A43" s="61" t="s">
         <v>149</v>
       </c>
-      <c r="B43" s="62" t="s">
+      <c r="B43" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="C43" s="62" t="s">
+      <c r="C43" s="61" t="s">
         <v>151</v>
       </c>
-      <c r="D43" s="62" t="s">
-        <v>527</v>
-      </c>
-      <c r="E43" s="62" t="s">
-        <v>528</v>
-      </c>
-      <c r="F43" s="62" t="s">
-        <v>529</v>
-      </c>
-      <c r="G43" s="62" t="s">
+      <c r="D43" s="61" t="s">
+        <v>605</v>
+      </c>
+      <c r="E43" s="61" t="s">
+        <v>606</v>
+      </c>
+      <c r="F43" s="61" t="s">
+        <v>607</v>
+      </c>
+      <c r="G43" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="H43" s="62" t="s">
+      <c r="H43" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="I43" s="62" t="s">
+      <c r="I43" s="61" t="s">
         <v>155</v>
       </c>
-      <c r="J43" s="62" t="s">
-        <v>530</v>
-      </c>
-      <c r="K43" s="62" t="s">
-        <v>531</v>
-      </c>
-      <c r="L43" s="62" t="s">
-        <v>532</v>
-      </c>
-      <c r="M43" s="62" t="s">
-        <v>533</v>
-      </c>
-      <c r="N43" s="62" t="s">
-        <v>534</v>
-      </c>
-      <c r="O43" s="62" t="s">
-        <v>535</v>
-      </c>
-      <c r="P43" s="62" t="s">
-        <v>536</v>
-      </c>
-      <c r="Q43" s="62" t="s">
+      <c r="J43" s="61" t="s">
+        <v>608</v>
+      </c>
+      <c r="K43" s="61" t="s">
+        <v>609</v>
+      </c>
+      <c r="L43" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="M43" s="61" t="s">
+        <v>611</v>
+      </c>
+      <c r="N43" s="61" t="s">
+        <v>612</v>
+      </c>
+      <c r="O43" s="61" t="s">
+        <v>613</v>
+      </c>
+      <c r="P43" s="61" t="s">
+        <v>614</v>
+      </c>
+      <c r="Q43" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="R43" s="62" t="s">
+      <c r="R43" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="S43" s="62" t="s">
+      <c r="S43" s="61" t="s">
         <v>163</v>
       </c>
-      <c r="T43" s="62" t="s">
-        <v>537</v>
-      </c>
-      <c r="U43" s="62" t="s">
-        <v>538</v>
-      </c>
-      <c r="V43" s="62" t="s">
-        <v>539</v>
-      </c>
-      <c r="W43" s="62" t="s">
+      <c r="T43" s="61" t="s">
+        <v>615</v>
+      </c>
+      <c r="U43" s="61" t="s">
+        <v>616</v>
+      </c>
+      <c r="V43" s="61" t="s">
+        <v>617</v>
+      </c>
+      <c r="W43" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="X43" s="62" t="s">
+      <c r="X43" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="Y43" s="62" t="s">
-        <v>540</v>
-      </c>
-      <c r="Z43" s="62" t="s">
+      <c r="Y43" s="61" t="s">
+        <v>618</v>
+      </c>
+      <c r="Z43" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="AA43" s="62" t="s">
-        <v>541</v>
-      </c>
-      <c r="AB43" s="62" t="s">
+      <c r="AA43" s="61" t="s">
+        <v>619</v>
+      </c>
+      <c r="AB43" s="61" t="s">
         <v>167</v>
       </c>
-      <c r="AC43" s="62" t="s">
+      <c r="AC43" s="61" t="s">
         <v>168</v>
       </c>
-      <c r="AD43" s="62" t="s">
+      <c r="AD43" s="61" t="s">
         <v>169</v>
       </c>
-      <c r="AE43" s="62" t="s">
-        <v>542</v>
-      </c>
-      <c r="AF43" s="62" t="s">
+      <c r="AE43" s="61" t="s">
+        <v>620</v>
+      </c>
+      <c r="AF43" s="61" t="s">
         <v>129</v>
       </c>
-      <c r="AG43" s="62" t="s">
-        <v>543</v>
-      </c>
-      <c r="AH43" s="62" t="s">
+      <c r="AG43" s="61" t="s">
+        <v>621</v>
+      </c>
+      <c r="AH43" s="61" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="63" t="s">
-        <v>544</v>
+      <c r="A44" s="62" t="s">
+        <v>622</v>
       </c>
       <c r="B44" s="24" t="str">
         <f aca="false">IF($A44="","",IF(ISERROR(FIND(".",$A44)),"",LOWER(MID($A44,FIND(CHAR(1),SUBSTITUTE($A44,".",CHAR(1),LEN($A44)-LEN(SUBSTITUTE($A44,".",""))))+1,LEN($A44)))))</f>
@@ -20070,7 +21006,7 @@
         <f aca="false">IF($B44="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B44,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
         <v>5</v>
       </c>
-      <c r="D44" s="64" t="n">
+      <c r="D44" s="63" t="n">
         <v>11</v>
       </c>
       <c r="E44" s="29" t="n">
@@ -20081,41 +21017,41 @@
         <f aca="false">IF(OR($A44="",$D44=""),"",$D44+$E44)</f>
         <v>22</v>
       </c>
-      <c r="G44" s="65" t="n">
+      <c r="G44" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="H44" s="65" t="n">
+      <c r="H44" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="65" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="65" t="n">
+      <c r="I44" s="64" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" s="64" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="30" t="n">
         <f aca="false">IF($J44="","",IF($J44&gt;=15,5,IF($J44&gt;=10,4,IF($J44&gt;=5,3,IF($J44&gt;=2,2,1)))))</f>
         <v>4</v>
       </c>
-      <c r="L44" s="65" t="n">
+      <c r="L44" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="M44" s="65" t="n">
+      <c r="M44" s="64" t="n">
         <v>4</v>
       </c>
-      <c r="N44" s="65" t="n">
+      <c r="N44" s="64" t="n">
         <v>2</v>
       </c>
-      <c r="O44" s="65" t="s">
-        <v>172</v>
-      </c>
-      <c r="P44" s="65" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q44" s="65" t="s">
-        <v>172</v>
-      </c>
-      <c r="R44" s="65" t="s">
+      <c r="O44" s="64" t="s">
+        <v>172</v>
+      </c>
+      <c r="P44" s="64" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q44" s="64" t="s">
+        <v>172</v>
+      </c>
+      <c r="R44" s="64" t="s">
         <v>172</v>
       </c>
       <c r="S44" s="31" t="str">
@@ -20134,11 +21070,11 @@
         <f aca="false">IF(OR($T44="",$U44=""),"",$T44*$B$19+$U44*(1-$B$19))</f>
         <v>4.12</v>
       </c>
-      <c r="W44" s="66" t="n">
+      <c r="W44" s="65" t="n">
         <v>1200</v>
       </c>
-      <c r="X44" s="63" t="s">
-        <v>545</v>
+      <c r="X44" s="62" t="s">
+        <v>623</v>
       </c>
       <c r="Y44" s="33" t="n">
         <f aca="false">IF(OR($A44="",$W44=""),"",MAX(0,$W44-MAX($W44*Assumptions!$B$4,Assumptions!$B$5)))</f>
@@ -20172,11 +21108,11 @@
         <f aca="false">IF($A44="","",IF($S44="FAIL","REJECT",IF($D44="","NEEDS PRICE",IF(OR($W44="",$X44=""),"NEEDS VALUATION",IF($AC44&lt;1,"OVERPRICED",IF(AND($AC44&gt;=Assumptions!$B$13,$V44&gt;=4),"BUY",IF($V44&gt;=3.4,"BUY CHEAPER",IF($V44&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v>BUY CHEAPER</v>
       </c>
-      <c r="AG44" s="67" t="str">
+      <c r="AG44" s="66" t="str">
         <f aca="false">IF($AF44="","",IF($AF44="REJECT","Do not buy at any price",IF($AF44="NEEDS PRICE","Enter the current closeout price",IF($AF44="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF44="OVERPRICED","Worth less than break-even - walk",IF($AF44="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF44="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF44="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v>Wait to about $8 (day 3), walk if outbid</v>
       </c>
-      <c r="AH44" s="68"/>
+      <c r="AH44" s="67"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="23"/>
@@ -20262,7 +21198,7 @@
         <f aca="false">IF($A45="","",IF($S45="FAIL","REJECT",IF($D45="","NEEDS PRICE",IF(OR($W45="",$X45=""),"NEEDS VALUATION",IF($AC45&lt;1,"OVERPRICED",IF(AND($AC45&gt;=Assumptions!$B$13,$V45&gt;=4),"BUY",IF($V45&gt;=3.4,"BUY CHEAPER",IF($V45&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG45" s="54" t="str">
+      <c r="AG45" s="53" t="str">
         <f aca="false">IF($AF45="","",IF($AF45="REJECT","Do not buy at any price",IF($AF45="NEEDS PRICE","Enter the current closeout price",IF($AF45="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF45="OVERPRICED","Worth less than break-even - walk",IF($AF45="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF45="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF45="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20352,7 +21288,7 @@
         <f aca="false">IF($A46="","",IF($S46="FAIL","REJECT",IF($D46="","NEEDS PRICE",IF(OR($W46="",$X46=""),"NEEDS VALUATION",IF($AC46&lt;1,"OVERPRICED",IF(AND($AC46&gt;=Assumptions!$B$13,$V46&gt;=4),"BUY",IF($V46&gt;=3.4,"BUY CHEAPER",IF($V46&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG46" s="54" t="str">
+      <c r="AG46" s="53" t="str">
         <f aca="false">IF($AF46="","",IF($AF46="REJECT","Do not buy at any price",IF($AF46="NEEDS PRICE","Enter the current closeout price",IF($AF46="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF46="OVERPRICED","Worth less than break-even - walk",IF($AF46="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF46="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF46="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20442,7 +21378,7 @@
         <f aca="false">IF($A47="","",IF($S47="FAIL","REJECT",IF($D47="","NEEDS PRICE",IF(OR($W47="",$X47=""),"NEEDS VALUATION",IF($AC47&lt;1,"OVERPRICED",IF(AND($AC47&gt;=Assumptions!$B$13,$V47&gt;=4),"BUY",IF($V47&gt;=3.4,"BUY CHEAPER",IF($V47&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG47" s="54" t="str">
+      <c r="AG47" s="53" t="str">
         <f aca="false">IF($AF47="","",IF($AF47="REJECT","Do not buy at any price",IF($AF47="NEEDS PRICE","Enter the current closeout price",IF($AF47="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF47="OVERPRICED","Worth less than break-even - walk",IF($AF47="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF47="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF47="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20532,7 +21468,7 @@
         <f aca="false">IF($A48="","",IF($S48="FAIL","REJECT",IF($D48="","NEEDS PRICE",IF(OR($W48="",$X48=""),"NEEDS VALUATION",IF($AC48&lt;1,"OVERPRICED",IF(AND($AC48&gt;=Assumptions!$B$13,$V48&gt;=4),"BUY",IF($V48&gt;=3.4,"BUY CHEAPER",IF($V48&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG48" s="54" t="str">
+      <c r="AG48" s="53" t="str">
         <f aca="false">IF($AF48="","",IF($AF48="REJECT","Do not buy at any price",IF($AF48="NEEDS PRICE","Enter the current closeout price",IF($AF48="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF48="OVERPRICED","Worth less than break-even - walk",IF($AF48="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF48="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF48="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20622,7 +21558,7 @@
         <f aca="false">IF($A49="","",IF($S49="FAIL","REJECT",IF($D49="","NEEDS PRICE",IF(OR($W49="",$X49=""),"NEEDS VALUATION",IF($AC49&lt;1,"OVERPRICED",IF(AND($AC49&gt;=Assumptions!$B$13,$V49&gt;=4),"BUY",IF($V49&gt;=3.4,"BUY CHEAPER",IF($V49&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG49" s="54" t="str">
+      <c r="AG49" s="53" t="str">
         <f aca="false">IF($AF49="","",IF($AF49="REJECT","Do not buy at any price",IF($AF49="NEEDS PRICE","Enter the current closeout price",IF($AF49="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF49="OVERPRICED","Worth less than break-even - walk",IF($AF49="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF49="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF49="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20712,7 +21648,7 @@
         <f aca="false">IF($A50="","",IF($S50="FAIL","REJECT",IF($D50="","NEEDS PRICE",IF(OR($W50="",$X50=""),"NEEDS VALUATION",IF($AC50&lt;1,"OVERPRICED",IF(AND($AC50&gt;=Assumptions!$B$13,$V50&gt;=4),"BUY",IF($V50&gt;=3.4,"BUY CHEAPER",IF($V50&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG50" s="54" t="str">
+      <c r="AG50" s="53" t="str">
         <f aca="false">IF($AF50="","",IF($AF50="REJECT","Do not buy at any price",IF($AF50="NEEDS PRICE","Enter the current closeout price",IF($AF50="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF50="OVERPRICED","Worth less than break-even - walk",IF($AF50="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF50="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF50="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20802,7 +21738,7 @@
         <f aca="false">IF($A51="","",IF($S51="FAIL","REJECT",IF($D51="","NEEDS PRICE",IF(OR($W51="",$X51=""),"NEEDS VALUATION",IF($AC51&lt;1,"OVERPRICED",IF(AND($AC51&gt;=Assumptions!$B$13,$V51&gt;=4),"BUY",IF($V51&gt;=3.4,"BUY CHEAPER",IF($V51&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG51" s="54" t="str">
+      <c r="AG51" s="53" t="str">
         <f aca="false">IF($AF51="","",IF($AF51="REJECT","Do not buy at any price",IF($AF51="NEEDS PRICE","Enter the current closeout price",IF($AF51="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF51="OVERPRICED","Worth less than break-even - walk",IF($AF51="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF51="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF51="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20892,7 +21828,7 @@
         <f aca="false">IF($A52="","",IF($S52="FAIL","REJECT",IF($D52="","NEEDS PRICE",IF(OR($W52="",$X52=""),"NEEDS VALUATION",IF($AC52&lt;1,"OVERPRICED",IF(AND($AC52&gt;=Assumptions!$B$13,$V52&gt;=4),"BUY",IF($V52&gt;=3.4,"BUY CHEAPER",IF($V52&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG52" s="54" t="str">
+      <c r="AG52" s="53" t="str">
         <f aca="false">IF($AF52="","",IF($AF52="REJECT","Do not buy at any price",IF($AF52="NEEDS PRICE","Enter the current closeout price",IF($AF52="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF52="OVERPRICED","Worth less than break-even - walk",IF($AF52="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF52="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF52="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -20982,7 +21918,7 @@
         <f aca="false">IF($A53="","",IF($S53="FAIL","REJECT",IF($D53="","NEEDS PRICE",IF(OR($W53="",$X53=""),"NEEDS VALUATION",IF($AC53&lt;1,"OVERPRICED",IF(AND($AC53&gt;=Assumptions!$B$13,$V53&gt;=4),"BUY",IF($V53&gt;=3.4,"BUY CHEAPER",IF($V53&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG53" s="54" t="str">
+      <c r="AG53" s="53" t="str">
         <f aca="false">IF($AF53="","",IF($AF53="REJECT","Do not buy at any price",IF($AF53="NEEDS PRICE","Enter the current closeout price",IF($AF53="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF53="OVERPRICED","Worth less than break-even - walk",IF($AF53="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF53="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF53="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21072,7 +22008,7 @@
         <f aca="false">IF($A54="","",IF($S54="FAIL","REJECT",IF($D54="","NEEDS PRICE",IF(OR($W54="",$X54=""),"NEEDS VALUATION",IF($AC54&lt;1,"OVERPRICED",IF(AND($AC54&gt;=Assumptions!$B$13,$V54&gt;=4),"BUY",IF($V54&gt;=3.4,"BUY CHEAPER",IF($V54&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG54" s="54" t="str">
+      <c r="AG54" s="53" t="str">
         <f aca="false">IF($AF54="","",IF($AF54="REJECT","Do not buy at any price",IF($AF54="NEEDS PRICE","Enter the current closeout price",IF($AF54="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF54="OVERPRICED","Worth less than break-even - walk",IF($AF54="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF54="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF54="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21162,7 +22098,7 @@
         <f aca="false">IF($A55="","",IF($S55="FAIL","REJECT",IF($D55="","NEEDS PRICE",IF(OR($W55="",$X55=""),"NEEDS VALUATION",IF($AC55&lt;1,"OVERPRICED",IF(AND($AC55&gt;=Assumptions!$B$13,$V55&gt;=4),"BUY",IF($V55&gt;=3.4,"BUY CHEAPER",IF($V55&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG55" s="54" t="str">
+      <c r="AG55" s="53" t="str">
         <f aca="false">IF($AF55="","",IF($AF55="REJECT","Do not buy at any price",IF($AF55="NEEDS PRICE","Enter the current closeout price",IF($AF55="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF55="OVERPRICED","Worth less than break-even - walk",IF($AF55="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF55="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF55="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21252,7 +22188,7 @@
         <f aca="false">IF($A56="","",IF($S56="FAIL","REJECT",IF($D56="","NEEDS PRICE",IF(OR($W56="",$X56=""),"NEEDS VALUATION",IF($AC56&lt;1,"OVERPRICED",IF(AND($AC56&gt;=Assumptions!$B$13,$V56&gt;=4),"BUY",IF($V56&gt;=3.4,"BUY CHEAPER",IF($V56&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG56" s="54" t="str">
+      <c r="AG56" s="53" t="str">
         <f aca="false">IF($AF56="","",IF($AF56="REJECT","Do not buy at any price",IF($AF56="NEEDS PRICE","Enter the current closeout price",IF($AF56="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF56="OVERPRICED","Worth less than break-even - walk",IF($AF56="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF56="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF56="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21342,7 +22278,7 @@
         <f aca="false">IF($A57="","",IF($S57="FAIL","REJECT",IF($D57="","NEEDS PRICE",IF(OR($W57="",$X57=""),"NEEDS VALUATION",IF($AC57&lt;1,"OVERPRICED",IF(AND($AC57&gt;=Assumptions!$B$13,$V57&gt;=4),"BUY",IF($V57&gt;=3.4,"BUY CHEAPER",IF($V57&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG57" s="54" t="str">
+      <c r="AG57" s="53" t="str">
         <f aca="false">IF($AF57="","",IF($AF57="REJECT","Do not buy at any price",IF($AF57="NEEDS PRICE","Enter the current closeout price",IF($AF57="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF57="OVERPRICED","Worth less than break-even - walk",IF($AF57="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF57="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF57="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21432,7 +22368,7 @@
         <f aca="false">IF($A58="","",IF($S58="FAIL","REJECT",IF($D58="","NEEDS PRICE",IF(OR($W58="",$X58=""),"NEEDS VALUATION",IF($AC58&lt;1,"OVERPRICED",IF(AND($AC58&gt;=Assumptions!$B$13,$V58&gt;=4),"BUY",IF($V58&gt;=3.4,"BUY CHEAPER",IF($V58&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG58" s="54" t="str">
+      <c r="AG58" s="53" t="str">
         <f aca="false">IF($AF58="","",IF($AF58="REJECT","Do not buy at any price",IF($AF58="NEEDS PRICE","Enter the current closeout price",IF($AF58="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF58="OVERPRICED","Worth less than break-even - walk",IF($AF58="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF58="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF58="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21522,7 +22458,7 @@
         <f aca="false">IF($A59="","",IF($S59="FAIL","REJECT",IF($D59="","NEEDS PRICE",IF(OR($W59="",$X59=""),"NEEDS VALUATION",IF($AC59&lt;1,"OVERPRICED",IF(AND($AC59&gt;=Assumptions!$B$13,$V59&gt;=4),"BUY",IF($V59&gt;=3.4,"BUY CHEAPER",IF($V59&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG59" s="54" t="str">
+      <c r="AG59" s="53" t="str">
         <f aca="false">IF($AF59="","",IF($AF59="REJECT","Do not buy at any price",IF($AF59="NEEDS PRICE","Enter the current closeout price",IF($AF59="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF59="OVERPRICED","Worth less than break-even - walk",IF($AF59="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF59="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF59="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21612,7 +22548,7 @@
         <f aca="false">IF($A60="","",IF($S60="FAIL","REJECT",IF($D60="","NEEDS PRICE",IF(OR($W60="",$X60=""),"NEEDS VALUATION",IF($AC60&lt;1,"OVERPRICED",IF(AND($AC60&gt;=Assumptions!$B$13,$V60&gt;=4),"BUY",IF($V60&gt;=3.4,"BUY CHEAPER",IF($V60&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG60" s="54" t="str">
+      <c r="AG60" s="53" t="str">
         <f aca="false">IF($AF60="","",IF($AF60="REJECT","Do not buy at any price",IF($AF60="NEEDS PRICE","Enter the current closeout price",IF($AF60="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF60="OVERPRICED","Worth less than break-even - walk",IF($AF60="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF60="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF60="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21702,7 +22638,7 @@
         <f aca="false">IF($A61="","",IF($S61="FAIL","REJECT",IF($D61="","NEEDS PRICE",IF(OR($W61="",$X61=""),"NEEDS VALUATION",IF($AC61&lt;1,"OVERPRICED",IF(AND($AC61&gt;=Assumptions!$B$13,$V61&gt;=4),"BUY",IF($V61&gt;=3.4,"BUY CHEAPER",IF($V61&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG61" s="54" t="str">
+      <c r="AG61" s="53" t="str">
         <f aca="false">IF($AF61="","",IF($AF61="REJECT","Do not buy at any price",IF($AF61="NEEDS PRICE","Enter the current closeout price",IF($AF61="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF61="OVERPRICED","Worth less than break-even - walk",IF($AF61="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF61="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF61="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21792,7 +22728,7 @@
         <f aca="false">IF($A62="","",IF($S62="FAIL","REJECT",IF($D62="","NEEDS PRICE",IF(OR($W62="",$X62=""),"NEEDS VALUATION",IF($AC62&lt;1,"OVERPRICED",IF(AND($AC62&gt;=Assumptions!$B$13,$V62&gt;=4),"BUY",IF($V62&gt;=3.4,"BUY CHEAPER",IF($V62&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG62" s="54" t="str">
+      <c r="AG62" s="53" t="str">
         <f aca="false">IF($AF62="","",IF($AF62="REJECT","Do not buy at any price",IF($AF62="NEEDS PRICE","Enter the current closeout price",IF($AF62="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF62="OVERPRICED","Worth less than break-even - walk",IF($AF62="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF62="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF62="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21882,7 +22818,7 @@
         <f aca="false">IF($A63="","",IF($S63="FAIL","REJECT",IF($D63="","NEEDS PRICE",IF(OR($W63="",$X63=""),"NEEDS VALUATION",IF($AC63&lt;1,"OVERPRICED",IF(AND($AC63&gt;=Assumptions!$B$13,$V63&gt;=4),"BUY",IF($V63&gt;=3.4,"BUY CHEAPER",IF($V63&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG63" s="54" t="str">
+      <c r="AG63" s="53" t="str">
         <f aca="false">IF($AF63="","",IF($AF63="REJECT","Do not buy at any price",IF($AF63="NEEDS PRICE","Enter the current closeout price",IF($AF63="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF63="OVERPRICED","Worth less than break-even - walk",IF($AF63="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF63="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF63="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21972,7 +22908,7 @@
         <f aca="false">IF($A64="","",IF($S64="FAIL","REJECT",IF($D64="","NEEDS PRICE",IF(OR($W64="",$X64=""),"NEEDS VALUATION",IF($AC64&lt;1,"OVERPRICED",IF(AND($AC64&gt;=Assumptions!$B$13,$V64&gt;=4),"BUY",IF($V64&gt;=3.4,"BUY CHEAPER",IF($V64&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG64" s="54" t="str">
+      <c r="AG64" s="53" t="str">
         <f aca="false">IF($AF64="","",IF($AF64="REJECT","Do not buy at any price",IF($AF64="NEEDS PRICE","Enter the current closeout price",IF($AF64="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF64="OVERPRICED","Worth less than break-even - walk",IF($AF64="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF64="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF64="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22062,7 +22998,7 @@
         <f aca="false">IF($A65="","",IF($S65="FAIL","REJECT",IF($D65="","NEEDS PRICE",IF(OR($W65="",$X65=""),"NEEDS VALUATION",IF($AC65&lt;1,"OVERPRICED",IF(AND($AC65&gt;=Assumptions!$B$13,$V65&gt;=4),"BUY",IF($V65&gt;=3.4,"BUY CHEAPER",IF($V65&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG65" s="54" t="str">
+      <c r="AG65" s="53" t="str">
         <f aca="false">IF($AF65="","",IF($AF65="REJECT","Do not buy at any price",IF($AF65="NEEDS PRICE","Enter the current closeout price",IF($AF65="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF65="OVERPRICED","Worth less than break-even - walk",IF($AF65="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF65="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF65="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22152,7 +23088,7 @@
         <f aca="false">IF($A66="","",IF($S66="FAIL","REJECT",IF($D66="","NEEDS PRICE",IF(OR($W66="",$X66=""),"NEEDS VALUATION",IF($AC66&lt;1,"OVERPRICED",IF(AND($AC66&gt;=Assumptions!$B$13,$V66&gt;=4),"BUY",IF($V66&gt;=3.4,"BUY CHEAPER",IF($V66&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG66" s="54" t="str">
+      <c r="AG66" s="53" t="str">
         <f aca="false">IF($AF66="","",IF($AF66="REJECT","Do not buy at any price",IF($AF66="NEEDS PRICE","Enter the current closeout price",IF($AF66="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF66="OVERPRICED","Worth less than break-even - walk",IF($AF66="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF66="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF66="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22242,7 +23178,7 @@
         <f aca="false">IF($A67="","",IF($S67="FAIL","REJECT",IF($D67="","NEEDS PRICE",IF(OR($W67="",$X67=""),"NEEDS VALUATION",IF($AC67&lt;1,"OVERPRICED",IF(AND($AC67&gt;=Assumptions!$B$13,$V67&gt;=4),"BUY",IF($V67&gt;=3.4,"BUY CHEAPER",IF($V67&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG67" s="54" t="str">
+      <c r="AG67" s="53" t="str">
         <f aca="false">IF($AF67="","",IF($AF67="REJECT","Do not buy at any price",IF($AF67="NEEDS PRICE","Enter the current closeout price",IF($AF67="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF67="OVERPRICED","Worth less than break-even - walk",IF($AF67="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF67="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF67="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22332,7 +23268,7 @@
         <f aca="false">IF($A68="","",IF($S68="FAIL","REJECT",IF($D68="","NEEDS PRICE",IF(OR($W68="",$X68=""),"NEEDS VALUATION",IF($AC68&lt;1,"OVERPRICED",IF(AND($AC68&gt;=Assumptions!$B$13,$V68&gt;=4),"BUY",IF($V68&gt;=3.4,"BUY CHEAPER",IF($V68&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG68" s="54" t="str">
+      <c r="AG68" s="53" t="str">
         <f aca="false">IF($AF68="","",IF($AF68="REJECT","Do not buy at any price",IF($AF68="NEEDS PRICE","Enter the current closeout price",IF($AF68="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF68="OVERPRICED","Worth less than break-even - walk",IF($AF68="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF68="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF68="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22422,7 +23358,7 @@
         <f aca="false">IF($A69="","",IF($S69="FAIL","REJECT",IF($D69="","NEEDS PRICE",IF(OR($W69="",$X69=""),"NEEDS VALUATION",IF($AC69&lt;1,"OVERPRICED",IF(AND($AC69&gt;=Assumptions!$B$13,$V69&gt;=4),"BUY",IF($V69&gt;=3.4,"BUY CHEAPER",IF($V69&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG69" s="54" t="str">
+      <c r="AG69" s="53" t="str">
         <f aca="false">IF($AF69="","",IF($AF69="REJECT","Do not buy at any price",IF($AF69="NEEDS PRICE","Enter the current closeout price",IF($AF69="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF69="OVERPRICED","Worth less than break-even - walk",IF($AF69="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF69="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF69="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22512,7 +23448,7 @@
         <f aca="false">IF($A70="","",IF($S70="FAIL","REJECT",IF($D70="","NEEDS PRICE",IF(OR($W70="",$X70=""),"NEEDS VALUATION",IF($AC70&lt;1,"OVERPRICED",IF(AND($AC70&gt;=Assumptions!$B$13,$V70&gt;=4),"BUY",IF($V70&gt;=3.4,"BUY CHEAPER",IF($V70&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG70" s="54" t="str">
+      <c r="AG70" s="53" t="str">
         <f aca="false">IF($AF70="","",IF($AF70="REJECT","Do not buy at any price",IF($AF70="NEEDS PRICE","Enter the current closeout price",IF($AF70="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF70="OVERPRICED","Worth less than break-even - walk",IF($AF70="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF70="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF70="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22602,7 +23538,7 @@
         <f aca="false">IF($A71="","",IF($S71="FAIL","REJECT",IF($D71="","NEEDS PRICE",IF(OR($W71="",$X71=""),"NEEDS VALUATION",IF($AC71&lt;1,"OVERPRICED",IF(AND($AC71&gt;=Assumptions!$B$13,$V71&gt;=4),"BUY",IF($V71&gt;=3.4,"BUY CHEAPER",IF($V71&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG71" s="54" t="str">
+      <c r="AG71" s="53" t="str">
         <f aca="false">IF($AF71="","",IF($AF71="REJECT","Do not buy at any price",IF($AF71="NEEDS PRICE","Enter the current closeout price",IF($AF71="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF71="OVERPRICED","Worth less than break-even - walk",IF($AF71="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF71="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF71="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22692,7 +23628,7 @@
         <f aca="false">IF($A72="","",IF($S72="FAIL","REJECT",IF($D72="","NEEDS PRICE",IF(OR($W72="",$X72=""),"NEEDS VALUATION",IF($AC72&lt;1,"OVERPRICED",IF(AND($AC72&gt;=Assumptions!$B$13,$V72&gt;=4),"BUY",IF($V72&gt;=3.4,"BUY CHEAPER",IF($V72&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG72" s="54" t="str">
+      <c r="AG72" s="53" t="str">
         <f aca="false">IF($AF72="","",IF($AF72="REJECT","Do not buy at any price",IF($AF72="NEEDS PRICE","Enter the current closeout price",IF($AF72="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF72="OVERPRICED","Worth less than break-even - walk",IF($AF72="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF72="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF72="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22782,7 +23718,7 @@
         <f aca="false">IF($A73="","",IF($S73="FAIL","REJECT",IF($D73="","NEEDS PRICE",IF(OR($W73="",$X73=""),"NEEDS VALUATION",IF($AC73&lt;1,"OVERPRICED",IF(AND($AC73&gt;=Assumptions!$B$13,$V73&gt;=4),"BUY",IF($V73&gt;=3.4,"BUY CHEAPER",IF($V73&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG73" s="54" t="str">
+      <c r="AG73" s="53" t="str">
         <f aca="false">IF($AF73="","",IF($AF73="REJECT","Do not buy at any price",IF($AF73="NEEDS PRICE","Enter the current closeout price",IF($AF73="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF73="OVERPRICED","Worth less than break-even - walk",IF($AF73="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF73="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF73="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22872,7 +23808,7 @@
         <f aca="false">IF($A74="","",IF($S74="FAIL","REJECT",IF($D74="","NEEDS PRICE",IF(OR($W74="",$X74=""),"NEEDS VALUATION",IF($AC74&lt;1,"OVERPRICED",IF(AND($AC74&gt;=Assumptions!$B$13,$V74&gt;=4),"BUY",IF($V74&gt;=3.4,"BUY CHEAPER",IF($V74&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG74" s="54" t="str">
+      <c r="AG74" s="53" t="str">
         <f aca="false">IF($AF74="","",IF($AF74="REJECT","Do not buy at any price",IF($AF74="NEEDS PRICE","Enter the current closeout price",IF($AF74="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF74="OVERPRICED","Worth less than break-even - walk",IF($AF74="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF74="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF74="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22962,7 +23898,7 @@
         <f aca="false">IF($A75="","",IF($S75="FAIL","REJECT",IF($D75="","NEEDS PRICE",IF(OR($W75="",$X75=""),"NEEDS VALUATION",IF($AC75&lt;1,"OVERPRICED",IF(AND($AC75&gt;=Assumptions!$B$13,$V75&gt;=4),"BUY",IF($V75&gt;=3.4,"BUY CHEAPER",IF($V75&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG75" s="54" t="str">
+      <c r="AG75" s="53" t="str">
         <f aca="false">IF($AF75="","",IF($AF75="REJECT","Do not buy at any price",IF($AF75="NEEDS PRICE","Enter the current closeout price",IF($AF75="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF75="OVERPRICED","Worth less than break-even - walk",IF($AF75="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF75="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF75="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23052,7 +23988,7 @@
         <f aca="false">IF($A76="","",IF($S76="FAIL","REJECT",IF($D76="","NEEDS PRICE",IF(OR($W76="",$X76=""),"NEEDS VALUATION",IF($AC76&lt;1,"OVERPRICED",IF(AND($AC76&gt;=Assumptions!$B$13,$V76&gt;=4),"BUY",IF($V76&gt;=3.4,"BUY CHEAPER",IF($V76&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG76" s="54" t="str">
+      <c r="AG76" s="53" t="str">
         <f aca="false">IF($AF76="","",IF($AF76="REJECT","Do not buy at any price",IF($AF76="NEEDS PRICE","Enter the current closeout price",IF($AF76="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF76="OVERPRICED","Worth less than break-even - walk",IF($AF76="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF76="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF76="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23142,7 +24078,7 @@
         <f aca="false">IF($A77="","",IF($S77="FAIL","REJECT",IF($D77="","NEEDS PRICE",IF(OR($W77="",$X77=""),"NEEDS VALUATION",IF($AC77&lt;1,"OVERPRICED",IF(AND($AC77&gt;=Assumptions!$B$13,$V77&gt;=4),"BUY",IF($V77&gt;=3.4,"BUY CHEAPER",IF($V77&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG77" s="54" t="str">
+      <c r="AG77" s="53" t="str">
         <f aca="false">IF($AF77="","",IF($AF77="REJECT","Do not buy at any price",IF($AF77="NEEDS PRICE","Enter the current closeout price",IF($AF77="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF77="OVERPRICED","Worth less than break-even - walk",IF($AF77="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF77="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF77="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23232,7 +24168,7 @@
         <f aca="false">IF($A78="","",IF($S78="FAIL","REJECT",IF($D78="","NEEDS PRICE",IF(OR($W78="",$X78=""),"NEEDS VALUATION",IF($AC78&lt;1,"OVERPRICED",IF(AND($AC78&gt;=Assumptions!$B$13,$V78&gt;=4),"BUY",IF($V78&gt;=3.4,"BUY CHEAPER",IF($V78&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG78" s="54" t="str">
+      <c r="AG78" s="53" t="str">
         <f aca="false">IF($AF78="","",IF($AF78="REJECT","Do not buy at any price",IF($AF78="NEEDS PRICE","Enter the current closeout price",IF($AF78="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF78="OVERPRICED","Worth less than break-even - walk",IF($AF78="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF78="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF78="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23322,7 +24258,7 @@
         <f aca="false">IF($A79="","",IF($S79="FAIL","REJECT",IF($D79="","NEEDS PRICE",IF(OR($W79="",$X79=""),"NEEDS VALUATION",IF($AC79&lt;1,"OVERPRICED",IF(AND($AC79&gt;=Assumptions!$B$13,$V79&gt;=4),"BUY",IF($V79&gt;=3.4,"BUY CHEAPER",IF($V79&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG79" s="54" t="str">
+      <c r="AG79" s="53" t="str">
         <f aca="false">IF($AF79="","",IF($AF79="REJECT","Do not buy at any price",IF($AF79="NEEDS PRICE","Enter the current closeout price",IF($AF79="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF79="OVERPRICED","Worth less than break-even - walk",IF($AF79="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF79="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF79="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23412,7 +24348,7 @@
         <f aca="false">IF($A80="","",IF($S80="FAIL","REJECT",IF($D80="","NEEDS PRICE",IF(OR($W80="",$X80=""),"NEEDS VALUATION",IF($AC80&lt;1,"OVERPRICED",IF(AND($AC80&gt;=Assumptions!$B$13,$V80&gt;=4),"BUY",IF($V80&gt;=3.4,"BUY CHEAPER",IF($V80&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG80" s="54" t="str">
+      <c r="AG80" s="53" t="str">
         <f aca="false">IF($AF80="","",IF($AF80="REJECT","Do not buy at any price",IF($AF80="NEEDS PRICE","Enter the current closeout price",IF($AF80="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF80="OVERPRICED","Worth less than break-even - walk",IF($AF80="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF80="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF80="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23502,7 +24438,7 @@
         <f aca="false">IF($A81="","",IF($S81="FAIL","REJECT",IF($D81="","NEEDS PRICE",IF(OR($W81="",$X81=""),"NEEDS VALUATION",IF($AC81&lt;1,"OVERPRICED",IF(AND($AC81&gt;=Assumptions!$B$13,$V81&gt;=4),"BUY",IF($V81&gt;=3.4,"BUY CHEAPER",IF($V81&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG81" s="54" t="str">
+      <c r="AG81" s="53" t="str">
         <f aca="false">IF($AF81="","",IF($AF81="REJECT","Do not buy at any price",IF($AF81="NEEDS PRICE","Enter the current closeout price",IF($AF81="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF81="OVERPRICED","Worth less than break-even - walk",IF($AF81="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF81="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF81="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23592,7 +24528,7 @@
         <f aca="false">IF($A82="","",IF($S82="FAIL","REJECT",IF($D82="","NEEDS PRICE",IF(OR($W82="",$X82=""),"NEEDS VALUATION",IF($AC82&lt;1,"OVERPRICED",IF(AND($AC82&gt;=Assumptions!$B$13,$V82&gt;=4),"BUY",IF($V82&gt;=3.4,"BUY CHEAPER",IF($V82&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG82" s="54" t="str">
+      <c r="AG82" s="53" t="str">
         <f aca="false">IF($AF82="","",IF($AF82="REJECT","Do not buy at any price",IF($AF82="NEEDS PRICE","Enter the current closeout price",IF($AF82="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF82="OVERPRICED","Worth less than break-even - walk",IF($AF82="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF82="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF82="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23682,7 +24618,7 @@
         <f aca="false">IF($A83="","",IF($S83="FAIL","REJECT",IF($D83="","NEEDS PRICE",IF(OR($W83="",$X83=""),"NEEDS VALUATION",IF($AC83&lt;1,"OVERPRICED",IF(AND($AC83&gt;=Assumptions!$B$13,$V83&gt;=4),"BUY",IF($V83&gt;=3.4,"BUY CHEAPER",IF($V83&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG83" s="54" t="str">
+      <c r="AG83" s="53" t="str">
         <f aca="false">IF($AF83="","",IF($AF83="REJECT","Do not buy at any price",IF($AF83="NEEDS PRICE","Enter the current closeout price",IF($AF83="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF83="OVERPRICED","Worth less than break-even - walk",IF($AF83="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF83="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF83="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23772,7 +24708,7 @@
         <f aca="false">IF($A84="","",IF($S84="FAIL","REJECT",IF($D84="","NEEDS PRICE",IF(OR($W84="",$X84=""),"NEEDS VALUATION",IF($AC84&lt;1,"OVERPRICED",IF(AND($AC84&gt;=Assumptions!$B$13,$V84&gt;=4),"BUY",IF($V84&gt;=3.4,"BUY CHEAPER",IF($V84&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG84" s="54" t="str">
+      <c r="AG84" s="53" t="str">
         <f aca="false">IF($AF84="","",IF($AF84="REJECT","Do not buy at any price",IF($AF84="NEEDS PRICE","Enter the current closeout price",IF($AF84="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF84="OVERPRICED","Worth less than break-even - walk",IF($AF84="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF84="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF84="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23862,7 +24798,7 @@
         <f aca="false">IF($A85="","",IF($S85="FAIL","REJECT",IF($D85="","NEEDS PRICE",IF(OR($W85="",$X85=""),"NEEDS VALUATION",IF($AC85&lt;1,"OVERPRICED",IF(AND($AC85&gt;=Assumptions!$B$13,$V85&gt;=4),"BUY",IF($V85&gt;=3.4,"BUY CHEAPER",IF($V85&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG85" s="54" t="str">
+      <c r="AG85" s="53" t="str">
         <f aca="false">IF($AF85="","",IF($AF85="REJECT","Do not buy at any price",IF($AF85="NEEDS PRICE","Enter the current closeout price",IF($AF85="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF85="OVERPRICED","Worth less than break-even - walk",IF($AF85="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF85="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF85="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23952,7 +24888,7 @@
         <f aca="false">IF($A86="","",IF($S86="FAIL","REJECT",IF($D86="","NEEDS PRICE",IF(OR($W86="",$X86=""),"NEEDS VALUATION",IF($AC86&lt;1,"OVERPRICED",IF(AND($AC86&gt;=Assumptions!$B$13,$V86&gt;=4),"BUY",IF($V86&gt;=3.4,"BUY CHEAPER",IF($V86&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG86" s="54" t="str">
+      <c r="AG86" s="53" t="str">
         <f aca="false">IF($AF86="","",IF($AF86="REJECT","Do not buy at any price",IF($AF86="NEEDS PRICE","Enter the current closeout price",IF($AF86="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF86="OVERPRICED","Worth less than break-even - walk",IF($AF86="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF86="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF86="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24042,7 +24978,7 @@
         <f aca="false">IF($A87="","",IF($S87="FAIL","REJECT",IF($D87="","NEEDS PRICE",IF(OR($W87="",$X87=""),"NEEDS VALUATION",IF($AC87&lt;1,"OVERPRICED",IF(AND($AC87&gt;=Assumptions!$B$13,$V87&gt;=4),"BUY",IF($V87&gt;=3.4,"BUY CHEAPER",IF($V87&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG87" s="54" t="str">
+      <c r="AG87" s="53" t="str">
         <f aca="false">IF($AF87="","",IF($AF87="REJECT","Do not buy at any price",IF($AF87="NEEDS PRICE","Enter the current closeout price",IF($AF87="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF87="OVERPRICED","Worth less than break-even - walk",IF($AF87="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF87="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF87="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24132,7 +25068,7 @@
         <f aca="false">IF($A88="","",IF($S88="FAIL","REJECT",IF($D88="","NEEDS PRICE",IF(OR($W88="",$X88=""),"NEEDS VALUATION",IF($AC88&lt;1,"OVERPRICED",IF(AND($AC88&gt;=Assumptions!$B$13,$V88&gt;=4),"BUY",IF($V88&gt;=3.4,"BUY CHEAPER",IF($V88&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG88" s="54" t="str">
+      <c r="AG88" s="53" t="str">
         <f aca="false">IF($AF88="","",IF($AF88="REJECT","Do not buy at any price",IF($AF88="NEEDS PRICE","Enter the current closeout price",IF($AF88="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF88="OVERPRICED","Worth less than break-even - walk",IF($AF88="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF88="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF88="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24222,7 +25158,7 @@
         <f aca="false">IF($A89="","",IF($S89="FAIL","REJECT",IF($D89="","NEEDS PRICE",IF(OR($W89="",$X89=""),"NEEDS VALUATION",IF($AC89&lt;1,"OVERPRICED",IF(AND($AC89&gt;=Assumptions!$B$13,$V89&gt;=4),"BUY",IF($V89&gt;=3.4,"BUY CHEAPER",IF($V89&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG89" s="54" t="str">
+      <c r="AG89" s="53" t="str">
         <f aca="false">IF($AF89="","",IF($AF89="REJECT","Do not buy at any price",IF($AF89="NEEDS PRICE","Enter the current closeout price",IF($AF89="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF89="OVERPRICED","Worth less than break-even - walk",IF($AF89="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF89="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF89="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24312,7 +25248,7 @@
         <f aca="false">IF($A90="","",IF($S90="FAIL","REJECT",IF($D90="","NEEDS PRICE",IF(OR($W90="",$X90=""),"NEEDS VALUATION",IF($AC90&lt;1,"OVERPRICED",IF(AND($AC90&gt;=Assumptions!$B$13,$V90&gt;=4),"BUY",IF($V90&gt;=3.4,"BUY CHEAPER",IF($V90&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG90" s="54" t="str">
+      <c r="AG90" s="53" t="str">
         <f aca="false">IF($AF90="","",IF($AF90="REJECT","Do not buy at any price",IF($AF90="NEEDS PRICE","Enter the current closeout price",IF($AF90="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF90="OVERPRICED","Worth less than break-even - walk",IF($AF90="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF90="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF90="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24402,7 +25338,7 @@
         <f aca="false">IF($A91="","",IF($S91="FAIL","REJECT",IF($D91="","NEEDS PRICE",IF(OR($W91="",$X91=""),"NEEDS VALUATION",IF($AC91&lt;1,"OVERPRICED",IF(AND($AC91&gt;=Assumptions!$B$13,$V91&gt;=4),"BUY",IF($V91&gt;=3.4,"BUY CHEAPER",IF($V91&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG91" s="54" t="str">
+      <c r="AG91" s="53" t="str">
         <f aca="false">IF($AF91="","",IF($AF91="REJECT","Do not buy at any price",IF($AF91="NEEDS PRICE","Enter the current closeout price",IF($AF91="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF91="OVERPRICED","Worth less than break-even - walk",IF($AF91="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF91="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF91="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24492,7 +25428,7 @@
         <f aca="false">IF($A92="","",IF($S92="FAIL","REJECT",IF($D92="","NEEDS PRICE",IF(OR($W92="",$X92=""),"NEEDS VALUATION",IF($AC92&lt;1,"OVERPRICED",IF(AND($AC92&gt;=Assumptions!$B$13,$V92&gt;=4),"BUY",IF($V92&gt;=3.4,"BUY CHEAPER",IF($V92&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG92" s="54" t="str">
+      <c r="AG92" s="53" t="str">
         <f aca="false">IF($AF92="","",IF($AF92="REJECT","Do not buy at any price",IF($AF92="NEEDS PRICE","Enter the current closeout price",IF($AF92="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF92="OVERPRICED","Worth less than break-even - walk",IF($AF92="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF92="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF92="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24582,7 +25518,7 @@
         <f aca="false">IF($A93="","",IF($S93="FAIL","REJECT",IF($D93="","NEEDS PRICE",IF(OR($W93="",$X93=""),"NEEDS VALUATION",IF($AC93&lt;1,"OVERPRICED",IF(AND($AC93&gt;=Assumptions!$B$13,$V93&gt;=4),"BUY",IF($V93&gt;=3.4,"BUY CHEAPER",IF($V93&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG93" s="54" t="str">
+      <c r="AG93" s="53" t="str">
         <f aca="false">IF($AF93="","",IF($AF93="REJECT","Do not buy at any price",IF($AF93="NEEDS PRICE","Enter the current closeout price",IF($AF93="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF93="OVERPRICED","Worth less than break-even - walk",IF($AF93="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF93="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF93="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24672,7 +25608,7 @@
         <f aca="false">IF($A94="","",IF($S94="FAIL","REJECT",IF($D94="","NEEDS PRICE",IF(OR($W94="",$X94=""),"NEEDS VALUATION",IF($AC94&lt;1,"OVERPRICED",IF(AND($AC94&gt;=Assumptions!$B$13,$V94&gt;=4),"BUY",IF($V94&gt;=3.4,"BUY CHEAPER",IF($V94&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG94" s="54" t="str">
+      <c r="AG94" s="53" t="str">
         <f aca="false">IF($AF94="","",IF($AF94="REJECT","Do not buy at any price",IF($AF94="NEEDS PRICE","Enter the current closeout price",IF($AF94="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF94="OVERPRICED","Worth less than break-even - walk",IF($AF94="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF94="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF94="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24762,7 +25698,7 @@
         <f aca="false">IF($A95="","",IF($S95="FAIL","REJECT",IF($D95="","NEEDS PRICE",IF(OR($W95="",$X95=""),"NEEDS VALUATION",IF($AC95&lt;1,"OVERPRICED",IF(AND($AC95&gt;=Assumptions!$B$13,$V95&gt;=4),"BUY",IF($V95&gt;=3.4,"BUY CHEAPER",IF($V95&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG95" s="54" t="str">
+      <c r="AG95" s="53" t="str">
         <f aca="false">IF($AF95="","",IF($AF95="REJECT","Do not buy at any price",IF($AF95="NEEDS PRICE","Enter the current closeout price",IF($AF95="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF95="OVERPRICED","Worth less than break-even - walk",IF($AF95="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF95="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF95="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24852,7 +25788,7 @@
         <f aca="false">IF($A96="","",IF($S96="FAIL","REJECT",IF($D96="","NEEDS PRICE",IF(OR($W96="",$X96=""),"NEEDS VALUATION",IF($AC96&lt;1,"OVERPRICED",IF(AND($AC96&gt;=Assumptions!$B$13,$V96&gt;=4),"BUY",IF($V96&gt;=3.4,"BUY CHEAPER",IF($V96&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG96" s="54" t="str">
+      <c r="AG96" s="53" t="str">
         <f aca="false">IF($AF96="","",IF($AF96="REJECT","Do not buy at any price",IF($AF96="NEEDS PRICE","Enter the current closeout price",IF($AF96="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF96="OVERPRICED","Worth less than break-even - walk",IF($AF96="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF96="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF96="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24942,7 +25878,7 @@
         <f aca="false">IF($A97="","",IF($S97="FAIL","REJECT",IF($D97="","NEEDS PRICE",IF(OR($W97="",$X97=""),"NEEDS VALUATION",IF($AC97&lt;1,"OVERPRICED",IF(AND($AC97&gt;=Assumptions!$B$13,$V97&gt;=4),"BUY",IF($V97&gt;=3.4,"BUY CHEAPER",IF($V97&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG97" s="54" t="str">
+      <c r="AG97" s="53" t="str">
         <f aca="false">IF($AF97="","",IF($AF97="REJECT","Do not buy at any price",IF($AF97="NEEDS PRICE","Enter the current closeout price",IF($AF97="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF97="OVERPRICED","Worth less than break-even - walk",IF($AF97="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF97="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF97="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25032,7 +25968,7 @@
         <f aca="false">IF($A98="","",IF($S98="FAIL","REJECT",IF($D98="","NEEDS PRICE",IF(OR($W98="",$X98=""),"NEEDS VALUATION",IF($AC98&lt;1,"OVERPRICED",IF(AND($AC98&gt;=Assumptions!$B$13,$V98&gt;=4),"BUY",IF($V98&gt;=3.4,"BUY CHEAPER",IF($V98&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG98" s="54" t="str">
+      <c r="AG98" s="53" t="str">
         <f aca="false">IF($AF98="","",IF($AF98="REJECT","Do not buy at any price",IF($AF98="NEEDS PRICE","Enter the current closeout price",IF($AF98="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF98="OVERPRICED","Worth less than break-even - walk",IF($AF98="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF98="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF98="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25122,7 +26058,7 @@
         <f aca="false">IF($A99="","",IF($S99="FAIL","REJECT",IF($D99="","NEEDS PRICE",IF(OR($W99="",$X99=""),"NEEDS VALUATION",IF($AC99&lt;1,"OVERPRICED",IF(AND($AC99&gt;=Assumptions!$B$13,$V99&gt;=4),"BUY",IF($V99&gt;=3.4,"BUY CHEAPER",IF($V99&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG99" s="54" t="str">
+      <c r="AG99" s="53" t="str">
         <f aca="false">IF($AF99="","",IF($AF99="REJECT","Do not buy at any price",IF($AF99="NEEDS PRICE","Enter the current closeout price",IF($AF99="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF99="OVERPRICED","Worth less than break-even - walk",IF($AF99="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF99="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF99="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25212,7 +26148,7 @@
         <f aca="false">IF($A100="","",IF($S100="FAIL","REJECT",IF($D100="","NEEDS PRICE",IF(OR($W100="",$X100=""),"NEEDS VALUATION",IF($AC100&lt;1,"OVERPRICED",IF(AND($AC100&gt;=Assumptions!$B$13,$V100&gt;=4),"BUY",IF($V100&gt;=3.4,"BUY CHEAPER",IF($V100&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG100" s="54" t="str">
+      <c r="AG100" s="53" t="str">
         <f aca="false">IF($AF100="","",IF($AF100="REJECT","Do not buy at any price",IF($AF100="NEEDS PRICE","Enter the current closeout price",IF($AF100="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF100="OVERPRICED","Worth less than break-even - walk",IF($AF100="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF100="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF100="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25302,7 +26238,7 @@
         <f aca="false">IF($A101="","",IF($S101="FAIL","REJECT",IF($D101="","NEEDS PRICE",IF(OR($W101="",$X101=""),"NEEDS VALUATION",IF($AC101&lt;1,"OVERPRICED",IF(AND($AC101&gt;=Assumptions!$B$13,$V101&gt;=4),"BUY",IF($V101&gt;=3.4,"BUY CHEAPER",IF($V101&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG101" s="54" t="str">
+      <c r="AG101" s="53" t="str">
         <f aca="false">IF($AF101="","",IF($AF101="REJECT","Do not buy at any price",IF($AF101="NEEDS PRICE","Enter the current closeout price",IF($AF101="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF101="OVERPRICED","Worth less than break-even - walk",IF($AF101="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF101="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF101="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25392,7 +26328,7 @@
         <f aca="false">IF($A102="","",IF($S102="FAIL","REJECT",IF($D102="","NEEDS PRICE",IF(OR($W102="",$X102=""),"NEEDS VALUATION",IF($AC102&lt;1,"OVERPRICED",IF(AND($AC102&gt;=Assumptions!$B$13,$V102&gt;=4),"BUY",IF($V102&gt;=3.4,"BUY CHEAPER",IF($V102&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG102" s="54" t="str">
+      <c r="AG102" s="53" t="str">
         <f aca="false">IF($AF102="","",IF($AF102="REJECT","Do not buy at any price",IF($AF102="NEEDS PRICE","Enter the current closeout price",IF($AF102="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF102="OVERPRICED","Worth less than break-even - walk",IF($AF102="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF102="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF102="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25482,7 +26418,7 @@
         <f aca="false">IF($A103="","",IF($S103="FAIL","REJECT",IF($D103="","NEEDS PRICE",IF(OR($W103="",$X103=""),"NEEDS VALUATION",IF($AC103&lt;1,"OVERPRICED",IF(AND($AC103&gt;=Assumptions!$B$13,$V103&gt;=4),"BUY",IF($V103&gt;=3.4,"BUY CHEAPER",IF($V103&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG103" s="54" t="str">
+      <c r="AG103" s="53" t="str">
         <f aca="false">IF($AF103="","",IF($AF103="REJECT","Do not buy at any price",IF($AF103="NEEDS PRICE","Enter the current closeout price",IF($AF103="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF103="OVERPRICED","Worth less than break-even - walk",IF($AF103="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF103="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF103="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25572,7 +26508,7 @@
         <f aca="false">IF($A104="","",IF($S104="FAIL","REJECT",IF($D104="","NEEDS PRICE",IF(OR($W104="",$X104=""),"NEEDS VALUATION",IF($AC104&lt;1,"OVERPRICED",IF(AND($AC104&gt;=Assumptions!$B$13,$V104&gt;=4),"BUY",IF($V104&gt;=3.4,"BUY CHEAPER",IF($V104&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG104" s="54" t="str">
+      <c r="AG104" s="53" t="str">
         <f aca="false">IF($AF104="","",IF($AF104="REJECT","Do not buy at any price",IF($AF104="NEEDS PRICE","Enter the current closeout price",IF($AF104="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF104="OVERPRICED","Worth less than break-even - walk",IF($AF104="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF104="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF104="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25662,7 +26598,7 @@
         <f aca="false">IF($A105="","",IF($S105="FAIL","REJECT",IF($D105="","NEEDS PRICE",IF(OR($W105="",$X105=""),"NEEDS VALUATION",IF($AC105&lt;1,"OVERPRICED",IF(AND($AC105&gt;=Assumptions!$B$13,$V105&gt;=4),"BUY",IF($V105&gt;=3.4,"BUY CHEAPER",IF($V105&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG105" s="54" t="str">
+      <c r="AG105" s="53" t="str">
         <f aca="false">IF($AF105="","",IF($AF105="REJECT","Do not buy at any price",IF($AF105="NEEDS PRICE","Enter the current closeout price",IF($AF105="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF105="OVERPRICED","Worth less than break-even - walk",IF($AF105="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF105="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF105="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25752,7 +26688,7 @@
         <f aca="false">IF($A106="","",IF($S106="FAIL","REJECT",IF($D106="","NEEDS PRICE",IF(OR($W106="",$X106=""),"NEEDS VALUATION",IF($AC106&lt;1,"OVERPRICED",IF(AND($AC106&gt;=Assumptions!$B$13,$V106&gt;=4),"BUY",IF($V106&gt;=3.4,"BUY CHEAPER",IF($V106&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG106" s="54" t="str">
+      <c r="AG106" s="53" t="str">
         <f aca="false">IF($AF106="","",IF($AF106="REJECT","Do not buy at any price",IF($AF106="NEEDS PRICE","Enter the current closeout price",IF($AF106="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF106="OVERPRICED","Worth less than break-even - walk",IF($AF106="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF106="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF106="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25842,7 +26778,7 @@
         <f aca="false">IF($A107="","",IF($S107="FAIL","REJECT",IF($D107="","NEEDS PRICE",IF(OR($W107="",$X107=""),"NEEDS VALUATION",IF($AC107&lt;1,"OVERPRICED",IF(AND($AC107&gt;=Assumptions!$B$13,$V107&gt;=4),"BUY",IF($V107&gt;=3.4,"BUY CHEAPER",IF($V107&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG107" s="54" t="str">
+      <c r="AG107" s="53" t="str">
         <f aca="false">IF($AF107="","",IF($AF107="REJECT","Do not buy at any price",IF($AF107="NEEDS PRICE","Enter the current closeout price",IF($AF107="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF107="OVERPRICED","Worth less than break-even - walk",IF($AF107="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF107="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF107="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25932,7 +26868,7 @@
         <f aca="false">IF($A108="","",IF($S108="FAIL","REJECT",IF($D108="","NEEDS PRICE",IF(OR($W108="",$X108=""),"NEEDS VALUATION",IF($AC108&lt;1,"OVERPRICED",IF(AND($AC108&gt;=Assumptions!$B$13,$V108&gt;=4),"BUY",IF($V108&gt;=3.4,"BUY CHEAPER",IF($V108&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG108" s="54" t="str">
+      <c r="AG108" s="53" t="str">
         <f aca="false">IF($AF108="","",IF($AF108="REJECT","Do not buy at any price",IF($AF108="NEEDS PRICE","Enter the current closeout price",IF($AF108="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF108="OVERPRICED","Worth less than break-even - walk",IF($AF108="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF108="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF108="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26022,7 +26958,7 @@
         <f aca="false">IF($A109="","",IF($S109="FAIL","REJECT",IF($D109="","NEEDS PRICE",IF(OR($W109="",$X109=""),"NEEDS VALUATION",IF($AC109&lt;1,"OVERPRICED",IF(AND($AC109&gt;=Assumptions!$B$13,$V109&gt;=4),"BUY",IF($V109&gt;=3.4,"BUY CHEAPER",IF($V109&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG109" s="54" t="str">
+      <c r="AG109" s="53" t="str">
         <f aca="false">IF($AF109="","",IF($AF109="REJECT","Do not buy at any price",IF($AF109="NEEDS PRICE","Enter the current closeout price",IF($AF109="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF109="OVERPRICED","Worth less than break-even - walk",IF($AF109="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF109="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF109="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26112,7 +27048,7 @@
         <f aca="false">IF($A110="","",IF($S110="FAIL","REJECT",IF($D110="","NEEDS PRICE",IF(OR($W110="",$X110=""),"NEEDS VALUATION",IF($AC110&lt;1,"OVERPRICED",IF(AND($AC110&gt;=Assumptions!$B$13,$V110&gt;=4),"BUY",IF($V110&gt;=3.4,"BUY CHEAPER",IF($V110&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG110" s="54" t="str">
+      <c r="AG110" s="53" t="str">
         <f aca="false">IF($AF110="","",IF($AF110="REJECT","Do not buy at any price",IF($AF110="NEEDS PRICE","Enter the current closeout price",IF($AF110="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF110="OVERPRICED","Worth less than break-even - walk",IF($AF110="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF110="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF110="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26202,7 +27138,7 @@
         <f aca="false">IF($A111="","",IF($S111="FAIL","REJECT",IF($D111="","NEEDS PRICE",IF(OR($W111="",$X111=""),"NEEDS VALUATION",IF($AC111&lt;1,"OVERPRICED",IF(AND($AC111&gt;=Assumptions!$B$13,$V111&gt;=4),"BUY",IF($V111&gt;=3.4,"BUY CHEAPER",IF($V111&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG111" s="54" t="str">
+      <c r="AG111" s="53" t="str">
         <f aca="false">IF($AF111="","",IF($AF111="REJECT","Do not buy at any price",IF($AF111="NEEDS PRICE","Enter the current closeout price",IF($AF111="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF111="OVERPRICED","Worth less than break-even - walk",IF($AF111="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF111="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF111="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26292,7 +27228,7 @@
         <f aca="false">IF($A112="","",IF($S112="FAIL","REJECT",IF($D112="","NEEDS PRICE",IF(OR($W112="",$X112=""),"NEEDS VALUATION",IF($AC112&lt;1,"OVERPRICED",IF(AND($AC112&gt;=Assumptions!$B$13,$V112&gt;=4),"BUY",IF($V112&gt;=3.4,"BUY CHEAPER",IF($V112&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG112" s="54" t="str">
+      <c r="AG112" s="53" t="str">
         <f aca="false">IF($AF112="","",IF($AF112="REJECT","Do not buy at any price",IF($AF112="NEEDS PRICE","Enter the current closeout price",IF($AF112="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF112="OVERPRICED","Worth less than break-even - walk",IF($AF112="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF112="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF112="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26382,7 +27318,7 @@
         <f aca="false">IF($A113="","",IF($S113="FAIL","REJECT",IF($D113="","NEEDS PRICE",IF(OR($W113="",$X113=""),"NEEDS VALUATION",IF($AC113&lt;1,"OVERPRICED",IF(AND($AC113&gt;=Assumptions!$B$13,$V113&gt;=4),"BUY",IF($V113&gt;=3.4,"BUY CHEAPER",IF($V113&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG113" s="54" t="str">
+      <c r="AG113" s="53" t="str">
         <f aca="false">IF($AF113="","",IF($AF113="REJECT","Do not buy at any price",IF($AF113="NEEDS PRICE","Enter the current closeout price",IF($AF113="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF113="OVERPRICED","Worth less than break-even - walk",IF($AF113="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF113="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF113="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26472,7 +27408,7 @@
         <f aca="false">IF($A114="","",IF($S114="FAIL","REJECT",IF($D114="","NEEDS PRICE",IF(OR($W114="",$X114=""),"NEEDS VALUATION",IF($AC114&lt;1,"OVERPRICED",IF(AND($AC114&gt;=Assumptions!$B$13,$V114&gt;=4),"BUY",IF($V114&gt;=3.4,"BUY CHEAPER",IF($V114&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG114" s="54" t="str">
+      <c r="AG114" s="53" t="str">
         <f aca="false">IF($AF114="","",IF($AF114="REJECT","Do not buy at any price",IF($AF114="NEEDS PRICE","Enter the current closeout price",IF($AF114="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF114="OVERPRICED","Worth less than break-even - walk",IF($AF114="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF114="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF114="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26562,7 +27498,7 @@
         <f aca="false">IF($A115="","",IF($S115="FAIL","REJECT",IF($D115="","NEEDS PRICE",IF(OR($W115="",$X115=""),"NEEDS VALUATION",IF($AC115&lt;1,"OVERPRICED",IF(AND($AC115&gt;=Assumptions!$B$13,$V115&gt;=4),"BUY",IF($V115&gt;=3.4,"BUY CHEAPER",IF($V115&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG115" s="54" t="str">
+      <c r="AG115" s="53" t="str">
         <f aca="false">IF($AF115="","",IF($AF115="REJECT","Do not buy at any price",IF($AF115="NEEDS PRICE","Enter the current closeout price",IF($AF115="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF115="OVERPRICED","Worth less than break-even - walk",IF($AF115="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF115="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF115="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26652,7 +27588,7 @@
         <f aca="false">IF($A116="","",IF($S116="FAIL","REJECT",IF($D116="","NEEDS PRICE",IF(OR($W116="",$X116=""),"NEEDS VALUATION",IF($AC116&lt;1,"OVERPRICED",IF(AND($AC116&gt;=Assumptions!$B$13,$V116&gt;=4),"BUY",IF($V116&gt;=3.4,"BUY CHEAPER",IF($V116&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG116" s="54" t="str">
+      <c r="AG116" s="53" t="str">
         <f aca="false">IF($AF116="","",IF($AF116="REJECT","Do not buy at any price",IF($AF116="NEEDS PRICE","Enter the current closeout price",IF($AF116="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF116="OVERPRICED","Worth less than break-even - walk",IF($AF116="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF116="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF116="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26742,7 +27678,7 @@
         <f aca="false">IF($A117="","",IF($S117="FAIL","REJECT",IF($D117="","NEEDS PRICE",IF(OR($W117="",$X117=""),"NEEDS VALUATION",IF($AC117&lt;1,"OVERPRICED",IF(AND($AC117&gt;=Assumptions!$B$13,$V117&gt;=4),"BUY",IF($V117&gt;=3.4,"BUY CHEAPER",IF($V117&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG117" s="54" t="str">
+      <c r="AG117" s="53" t="str">
         <f aca="false">IF($AF117="","",IF($AF117="REJECT","Do not buy at any price",IF($AF117="NEEDS PRICE","Enter the current closeout price",IF($AF117="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF117="OVERPRICED","Worth less than break-even - walk",IF($AF117="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF117="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF117="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26832,7 +27768,7 @@
         <f aca="false">IF($A118="","",IF($S118="FAIL","REJECT",IF($D118="","NEEDS PRICE",IF(OR($W118="",$X118=""),"NEEDS VALUATION",IF($AC118&lt;1,"OVERPRICED",IF(AND($AC118&gt;=Assumptions!$B$13,$V118&gt;=4),"BUY",IF($V118&gt;=3.4,"BUY CHEAPER",IF($V118&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG118" s="54" t="str">
+      <c r="AG118" s="53" t="str">
         <f aca="false">IF($AF118="","",IF($AF118="REJECT","Do not buy at any price",IF($AF118="NEEDS PRICE","Enter the current closeout price",IF($AF118="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF118="OVERPRICED","Worth less than break-even - walk",IF($AF118="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF118="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF118="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26922,7 +27858,7 @@
         <f aca="false">IF($A119="","",IF($S119="FAIL","REJECT",IF($D119="","NEEDS PRICE",IF(OR($W119="",$X119=""),"NEEDS VALUATION",IF($AC119&lt;1,"OVERPRICED",IF(AND($AC119&gt;=Assumptions!$B$13,$V119&gt;=4),"BUY",IF($V119&gt;=3.4,"BUY CHEAPER",IF($V119&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG119" s="54" t="str">
+      <c r="AG119" s="53" t="str">
         <f aca="false">IF($AF119="","",IF($AF119="REJECT","Do not buy at any price",IF($AF119="NEEDS PRICE","Enter the current closeout price",IF($AF119="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF119="OVERPRICED","Worth less than break-even - walk",IF($AF119="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF119="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF119="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27012,7 +27948,7 @@
         <f aca="false">IF($A120="","",IF($S120="FAIL","REJECT",IF($D120="","NEEDS PRICE",IF(OR($W120="",$X120=""),"NEEDS VALUATION",IF($AC120&lt;1,"OVERPRICED",IF(AND($AC120&gt;=Assumptions!$B$13,$V120&gt;=4),"BUY",IF($V120&gt;=3.4,"BUY CHEAPER",IF($V120&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG120" s="54" t="str">
+      <c r="AG120" s="53" t="str">
         <f aca="false">IF($AF120="","",IF($AF120="REJECT","Do not buy at any price",IF($AF120="NEEDS PRICE","Enter the current closeout price",IF($AF120="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF120="OVERPRICED","Worth less than break-even - walk",IF($AF120="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF120="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF120="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27102,7 +28038,7 @@
         <f aca="false">IF($A121="","",IF($S121="FAIL","REJECT",IF($D121="","NEEDS PRICE",IF(OR($W121="",$X121=""),"NEEDS VALUATION",IF($AC121&lt;1,"OVERPRICED",IF(AND($AC121&gt;=Assumptions!$B$13,$V121&gt;=4),"BUY",IF($V121&gt;=3.4,"BUY CHEAPER",IF($V121&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG121" s="54" t="str">
+      <c r="AG121" s="53" t="str">
         <f aca="false">IF($AF121="","",IF($AF121="REJECT","Do not buy at any price",IF($AF121="NEEDS PRICE","Enter the current closeout price",IF($AF121="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF121="OVERPRICED","Worth less than break-even - walk",IF($AF121="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF121="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF121="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27192,7 +28128,7 @@
         <f aca="false">IF($A122="","",IF($S122="FAIL","REJECT",IF($D122="","NEEDS PRICE",IF(OR($W122="",$X122=""),"NEEDS VALUATION",IF($AC122&lt;1,"OVERPRICED",IF(AND($AC122&gt;=Assumptions!$B$13,$V122&gt;=4),"BUY",IF($V122&gt;=3.4,"BUY CHEAPER",IF($V122&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG122" s="54" t="str">
+      <c r="AG122" s="53" t="str">
         <f aca="false">IF($AF122="","",IF($AF122="REJECT","Do not buy at any price",IF($AF122="NEEDS PRICE","Enter the current closeout price",IF($AF122="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF122="OVERPRICED","Worth less than break-even - walk",IF($AF122="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF122="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF122="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27282,7 +28218,7 @@
         <f aca="false">IF($A123="","",IF($S123="FAIL","REJECT",IF($D123="","NEEDS PRICE",IF(OR($W123="",$X123=""),"NEEDS VALUATION",IF($AC123&lt;1,"OVERPRICED",IF(AND($AC123&gt;=Assumptions!$B$13,$V123&gt;=4),"BUY",IF($V123&gt;=3.4,"BUY CHEAPER",IF($V123&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG123" s="54" t="str">
+      <c r="AG123" s="53" t="str">
         <f aca="false">IF($AF123="","",IF($AF123="REJECT","Do not buy at any price",IF($AF123="NEEDS PRICE","Enter the current closeout price",IF($AF123="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF123="OVERPRICED","Worth less than break-even - walk",IF($AF123="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF123="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF123="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27372,7 +28308,7 @@
         <f aca="false">IF($A124="","",IF($S124="FAIL","REJECT",IF($D124="","NEEDS PRICE",IF(OR($W124="",$X124=""),"NEEDS VALUATION",IF($AC124&lt;1,"OVERPRICED",IF(AND($AC124&gt;=Assumptions!$B$13,$V124&gt;=4),"BUY",IF($V124&gt;=3.4,"BUY CHEAPER",IF($V124&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG124" s="54" t="str">
+      <c r="AG124" s="53" t="str">
         <f aca="false">IF($AF124="","",IF($AF124="REJECT","Do not buy at any price",IF($AF124="NEEDS PRICE","Enter the current closeout price",IF($AF124="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF124="OVERPRICED","Worth less than break-even - walk",IF($AF124="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF124="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF124="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27462,7 +28398,7 @@
         <f aca="false">IF($A125="","",IF($S125="FAIL","REJECT",IF($D125="","NEEDS PRICE",IF(OR($W125="",$X125=""),"NEEDS VALUATION",IF($AC125&lt;1,"OVERPRICED",IF(AND($AC125&gt;=Assumptions!$B$13,$V125&gt;=4),"BUY",IF($V125&gt;=3.4,"BUY CHEAPER",IF($V125&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG125" s="54" t="str">
+      <c r="AG125" s="53" t="str">
         <f aca="false">IF($AF125="","",IF($AF125="REJECT","Do not buy at any price",IF($AF125="NEEDS PRICE","Enter the current closeout price",IF($AF125="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF125="OVERPRICED","Worth less than break-even - walk",IF($AF125="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF125="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF125="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27552,7 +28488,7 @@
         <f aca="false">IF($A126="","",IF($S126="FAIL","REJECT",IF($D126="","NEEDS PRICE",IF(OR($W126="",$X126=""),"NEEDS VALUATION",IF($AC126&lt;1,"OVERPRICED",IF(AND($AC126&gt;=Assumptions!$B$13,$V126&gt;=4),"BUY",IF($V126&gt;=3.4,"BUY CHEAPER",IF($V126&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG126" s="54" t="str">
+      <c r="AG126" s="53" t="str">
         <f aca="false">IF($AF126="","",IF($AF126="REJECT","Do not buy at any price",IF($AF126="NEEDS PRICE","Enter the current closeout price",IF($AF126="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF126="OVERPRICED","Worth less than break-even - walk",IF($AF126="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF126="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF126="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27642,7 +28578,7 @@
         <f aca="false">IF($A127="","",IF($S127="FAIL","REJECT",IF($D127="","NEEDS PRICE",IF(OR($W127="",$X127=""),"NEEDS VALUATION",IF($AC127&lt;1,"OVERPRICED",IF(AND($AC127&gt;=Assumptions!$B$13,$V127&gt;=4),"BUY",IF($V127&gt;=3.4,"BUY CHEAPER",IF($V127&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG127" s="54" t="str">
+      <c r="AG127" s="53" t="str">
         <f aca="false">IF($AF127="","",IF($AF127="REJECT","Do not buy at any price",IF($AF127="NEEDS PRICE","Enter the current closeout price",IF($AF127="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF127="OVERPRICED","Worth less than break-even - walk",IF($AF127="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF127="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF127="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27732,7 +28668,7 @@
         <f aca="false">IF($A128="","",IF($S128="FAIL","REJECT",IF($D128="","NEEDS PRICE",IF(OR($W128="",$X128=""),"NEEDS VALUATION",IF($AC128&lt;1,"OVERPRICED",IF(AND($AC128&gt;=Assumptions!$B$13,$V128&gt;=4),"BUY",IF($V128&gt;=3.4,"BUY CHEAPER",IF($V128&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG128" s="54" t="str">
+      <c r="AG128" s="53" t="str">
         <f aca="false">IF($AF128="","",IF($AF128="REJECT","Do not buy at any price",IF($AF128="NEEDS PRICE","Enter the current closeout price",IF($AF128="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF128="OVERPRICED","Worth less than break-even - walk",IF($AF128="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF128="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF128="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27822,7 +28758,7 @@
         <f aca="false">IF($A129="","",IF($S129="FAIL","REJECT",IF($D129="","NEEDS PRICE",IF(OR($W129="",$X129=""),"NEEDS VALUATION",IF($AC129&lt;1,"OVERPRICED",IF(AND($AC129&gt;=Assumptions!$B$13,$V129&gt;=4),"BUY",IF($V129&gt;=3.4,"BUY CHEAPER",IF($V129&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG129" s="54" t="str">
+      <c r="AG129" s="53" t="str">
         <f aca="false">IF($AF129="","",IF($AF129="REJECT","Do not buy at any price",IF($AF129="NEEDS PRICE","Enter the current closeout price",IF($AF129="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF129="OVERPRICED","Worth less than break-even - walk",IF($AF129="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF129="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF129="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27912,7 +28848,7 @@
         <f aca="false">IF($A130="","",IF($S130="FAIL","REJECT",IF($D130="","NEEDS PRICE",IF(OR($W130="",$X130=""),"NEEDS VALUATION",IF($AC130&lt;1,"OVERPRICED",IF(AND($AC130&gt;=Assumptions!$B$13,$V130&gt;=4),"BUY",IF($V130&gt;=3.4,"BUY CHEAPER",IF($V130&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG130" s="54" t="str">
+      <c r="AG130" s="53" t="str">
         <f aca="false">IF($AF130="","",IF($AF130="REJECT","Do not buy at any price",IF($AF130="NEEDS PRICE","Enter the current closeout price",IF($AF130="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF130="OVERPRICED","Worth less than break-even - walk",IF($AF130="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF130="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF130="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28002,7 +28938,7 @@
         <f aca="false">IF($A131="","",IF($S131="FAIL","REJECT",IF($D131="","NEEDS PRICE",IF(OR($W131="",$X131=""),"NEEDS VALUATION",IF($AC131&lt;1,"OVERPRICED",IF(AND($AC131&gt;=Assumptions!$B$13,$V131&gt;=4),"BUY",IF($V131&gt;=3.4,"BUY CHEAPER",IF($V131&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG131" s="54" t="str">
+      <c r="AG131" s="53" t="str">
         <f aca="false">IF($AF131="","",IF($AF131="REJECT","Do not buy at any price",IF($AF131="NEEDS PRICE","Enter the current closeout price",IF($AF131="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF131="OVERPRICED","Worth less than break-even - walk",IF($AF131="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF131="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF131="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28092,7 +29028,7 @@
         <f aca="false">IF($A132="","",IF($S132="FAIL","REJECT",IF($D132="","NEEDS PRICE",IF(OR($W132="",$X132=""),"NEEDS VALUATION",IF($AC132&lt;1,"OVERPRICED",IF(AND($AC132&gt;=Assumptions!$B$13,$V132&gt;=4),"BUY",IF($V132&gt;=3.4,"BUY CHEAPER",IF($V132&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG132" s="54" t="str">
+      <c r="AG132" s="53" t="str">
         <f aca="false">IF($AF132="","",IF($AF132="REJECT","Do not buy at any price",IF($AF132="NEEDS PRICE","Enter the current closeout price",IF($AF132="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF132="OVERPRICED","Worth less than break-even - walk",IF($AF132="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF132="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF132="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28182,7 +29118,7 @@
         <f aca="false">IF($A133="","",IF($S133="FAIL","REJECT",IF($D133="","NEEDS PRICE",IF(OR($W133="",$X133=""),"NEEDS VALUATION",IF($AC133&lt;1,"OVERPRICED",IF(AND($AC133&gt;=Assumptions!$B$13,$V133&gt;=4),"BUY",IF($V133&gt;=3.4,"BUY CHEAPER",IF($V133&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG133" s="54" t="str">
+      <c r="AG133" s="53" t="str">
         <f aca="false">IF($AF133="","",IF($AF133="REJECT","Do not buy at any price",IF($AF133="NEEDS PRICE","Enter the current closeout price",IF($AF133="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF133="OVERPRICED","Worth less than break-even - walk",IF($AF133="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF133="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF133="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28272,7 +29208,7 @@
         <f aca="false">IF($A134="","",IF($S134="FAIL","REJECT",IF($D134="","NEEDS PRICE",IF(OR($W134="",$X134=""),"NEEDS VALUATION",IF($AC134&lt;1,"OVERPRICED",IF(AND($AC134&gt;=Assumptions!$B$13,$V134&gt;=4),"BUY",IF($V134&gt;=3.4,"BUY CHEAPER",IF($V134&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG134" s="54" t="str">
+      <c r="AG134" s="53" t="str">
         <f aca="false">IF($AF134="","",IF($AF134="REJECT","Do not buy at any price",IF($AF134="NEEDS PRICE","Enter the current closeout price",IF($AF134="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF134="OVERPRICED","Worth less than break-even - walk",IF($AF134="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF134="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF134="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28362,7 +29298,7 @@
         <f aca="false">IF($A135="","",IF($S135="FAIL","REJECT",IF($D135="","NEEDS PRICE",IF(OR($W135="",$X135=""),"NEEDS VALUATION",IF($AC135&lt;1,"OVERPRICED",IF(AND($AC135&gt;=Assumptions!$B$13,$V135&gt;=4),"BUY",IF($V135&gt;=3.4,"BUY CHEAPER",IF($V135&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG135" s="54" t="str">
+      <c r="AG135" s="53" t="str">
         <f aca="false">IF($AF135="","",IF($AF135="REJECT","Do not buy at any price",IF($AF135="NEEDS PRICE","Enter the current closeout price",IF($AF135="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF135="OVERPRICED","Worth less than break-even - walk",IF($AF135="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF135="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF135="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28452,7 +29388,7 @@
         <f aca="false">IF($A136="","",IF($S136="FAIL","REJECT",IF($D136="","NEEDS PRICE",IF(OR($W136="",$X136=""),"NEEDS VALUATION",IF($AC136&lt;1,"OVERPRICED",IF(AND($AC136&gt;=Assumptions!$B$13,$V136&gt;=4),"BUY",IF($V136&gt;=3.4,"BUY CHEAPER",IF($V136&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG136" s="54" t="str">
+      <c r="AG136" s="53" t="str">
         <f aca="false">IF($AF136="","",IF($AF136="REJECT","Do not buy at any price",IF($AF136="NEEDS PRICE","Enter the current closeout price",IF($AF136="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF136="OVERPRICED","Worth less than break-even - walk",IF($AF136="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF136="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF136="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28542,7 +29478,7 @@
         <f aca="false">IF($A137="","",IF($S137="FAIL","REJECT",IF($D137="","NEEDS PRICE",IF(OR($W137="",$X137=""),"NEEDS VALUATION",IF($AC137&lt;1,"OVERPRICED",IF(AND($AC137&gt;=Assumptions!$B$13,$V137&gt;=4),"BUY",IF($V137&gt;=3.4,"BUY CHEAPER",IF($V137&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG137" s="54" t="str">
+      <c r="AG137" s="53" t="str">
         <f aca="false">IF($AF137="","",IF($AF137="REJECT","Do not buy at any price",IF($AF137="NEEDS PRICE","Enter the current closeout price",IF($AF137="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF137="OVERPRICED","Worth less than break-even - walk",IF($AF137="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF137="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF137="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28632,7 +29568,7 @@
         <f aca="false">IF($A138="","",IF($S138="FAIL","REJECT",IF($D138="","NEEDS PRICE",IF(OR($W138="",$X138=""),"NEEDS VALUATION",IF($AC138&lt;1,"OVERPRICED",IF(AND($AC138&gt;=Assumptions!$B$13,$V138&gt;=4),"BUY",IF($V138&gt;=3.4,"BUY CHEAPER",IF($V138&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG138" s="54" t="str">
+      <c r="AG138" s="53" t="str">
         <f aca="false">IF($AF138="","",IF($AF138="REJECT","Do not buy at any price",IF($AF138="NEEDS PRICE","Enter the current closeout price",IF($AF138="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF138="OVERPRICED","Worth less than break-even - walk",IF($AF138="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF138="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF138="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28722,7 +29658,7 @@
         <f aca="false">IF($A139="","",IF($S139="FAIL","REJECT",IF($D139="","NEEDS PRICE",IF(OR($W139="",$X139=""),"NEEDS VALUATION",IF($AC139&lt;1,"OVERPRICED",IF(AND($AC139&gt;=Assumptions!$B$13,$V139&gt;=4),"BUY",IF($V139&gt;=3.4,"BUY CHEAPER",IF($V139&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG139" s="54" t="str">
+      <c r="AG139" s="53" t="str">
         <f aca="false">IF($AF139="","",IF($AF139="REJECT","Do not buy at any price",IF($AF139="NEEDS PRICE","Enter the current closeout price",IF($AF139="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF139="OVERPRICED","Worth less than break-even - walk",IF($AF139="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF139="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF139="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28812,7 +29748,7 @@
         <f aca="false">IF($A140="","",IF($S140="FAIL","REJECT",IF($D140="","NEEDS PRICE",IF(OR($W140="",$X140=""),"NEEDS VALUATION",IF($AC140&lt;1,"OVERPRICED",IF(AND($AC140&gt;=Assumptions!$B$13,$V140&gt;=4),"BUY",IF($V140&gt;=3.4,"BUY CHEAPER",IF($V140&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG140" s="54" t="str">
+      <c r="AG140" s="53" t="str">
         <f aca="false">IF($AF140="","",IF($AF140="REJECT","Do not buy at any price",IF($AF140="NEEDS PRICE","Enter the current closeout price",IF($AF140="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF140="OVERPRICED","Worth less than break-even - walk",IF($AF140="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF140="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF140="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28902,7 +29838,7 @@
         <f aca="false">IF($A141="","",IF($S141="FAIL","REJECT",IF($D141="","NEEDS PRICE",IF(OR($W141="",$X141=""),"NEEDS VALUATION",IF($AC141&lt;1,"OVERPRICED",IF(AND($AC141&gt;=Assumptions!$B$13,$V141&gt;=4),"BUY",IF($V141&gt;=3.4,"BUY CHEAPER",IF($V141&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG141" s="54" t="str">
+      <c r="AG141" s="53" t="str">
         <f aca="false">IF($AF141="","",IF($AF141="REJECT","Do not buy at any price",IF($AF141="NEEDS PRICE","Enter the current closeout price",IF($AF141="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF141="OVERPRICED","Worth less than break-even - walk",IF($AF141="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF141="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF141="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28992,7 +29928,7 @@
         <f aca="false">IF($A142="","",IF($S142="FAIL","REJECT",IF($D142="","NEEDS PRICE",IF(OR($W142="",$X142=""),"NEEDS VALUATION",IF($AC142&lt;1,"OVERPRICED",IF(AND($AC142&gt;=Assumptions!$B$13,$V142&gt;=4),"BUY",IF($V142&gt;=3.4,"BUY CHEAPER",IF($V142&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG142" s="54" t="str">
+      <c r="AG142" s="53" t="str">
         <f aca="false">IF($AF142="","",IF($AF142="REJECT","Do not buy at any price",IF($AF142="NEEDS PRICE","Enter the current closeout price",IF($AF142="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF142="OVERPRICED","Worth less than break-even - walk",IF($AF142="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF142="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF142="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29082,7 +30018,7 @@
         <f aca="false">IF($A143="","",IF($S143="FAIL","REJECT",IF($D143="","NEEDS PRICE",IF(OR($W143="",$X143=""),"NEEDS VALUATION",IF($AC143&lt;1,"OVERPRICED",IF(AND($AC143&gt;=Assumptions!$B$13,$V143&gt;=4),"BUY",IF($V143&gt;=3.4,"BUY CHEAPER",IF($V143&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG143" s="54" t="str">
+      <c r="AG143" s="53" t="str">
         <f aca="false">IF($AF143="","",IF($AF143="REJECT","Do not buy at any price",IF($AF143="NEEDS PRICE","Enter the current closeout price",IF($AF143="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF143="OVERPRICED","Worth less than break-even - walk",IF($AF143="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF143="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF143="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29172,7 +30108,7 @@
         <f aca="false">IF($A144="","",IF($S144="FAIL","REJECT",IF($D144="","NEEDS PRICE",IF(OR($W144="",$X144=""),"NEEDS VALUATION",IF($AC144&lt;1,"OVERPRICED",IF(AND($AC144&gt;=Assumptions!$B$13,$V144&gt;=4),"BUY",IF($V144&gt;=3.4,"BUY CHEAPER",IF($V144&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG144" s="54" t="str">
+      <c r="AG144" s="53" t="str">
         <f aca="false">IF($AF144="","",IF($AF144="REJECT","Do not buy at any price",IF($AF144="NEEDS PRICE","Enter the current closeout price",IF($AF144="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF144="OVERPRICED","Worth less than break-even - walk",IF($AF144="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF144="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF144="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29262,7 +30198,7 @@
         <f aca="false">IF($A145="","",IF($S145="FAIL","REJECT",IF($D145="","NEEDS PRICE",IF(OR($W145="",$X145=""),"NEEDS VALUATION",IF($AC145&lt;1,"OVERPRICED",IF(AND($AC145&gt;=Assumptions!$B$13,$V145&gt;=4),"BUY",IF($V145&gt;=3.4,"BUY CHEAPER",IF($V145&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG145" s="54" t="str">
+      <c r="AG145" s="53" t="str">
         <f aca="false">IF($AF145="","",IF($AF145="REJECT","Do not buy at any price",IF($AF145="NEEDS PRICE","Enter the current closeout price",IF($AF145="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF145="OVERPRICED","Worth less than break-even - walk",IF($AF145="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF145="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF145="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29352,7 +30288,7 @@
         <f aca="false">IF($A146="","",IF($S146="FAIL","REJECT",IF($D146="","NEEDS PRICE",IF(OR($W146="",$X146=""),"NEEDS VALUATION",IF($AC146&lt;1,"OVERPRICED",IF(AND($AC146&gt;=Assumptions!$B$13,$V146&gt;=4),"BUY",IF($V146&gt;=3.4,"BUY CHEAPER",IF($V146&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG146" s="54" t="str">
+      <c r="AG146" s="53" t="str">
         <f aca="false">IF($AF146="","",IF($AF146="REJECT","Do not buy at any price",IF($AF146="NEEDS PRICE","Enter the current closeout price",IF($AF146="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF146="OVERPRICED","Worth less than break-even - walk",IF($AF146="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF146="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF146="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29442,7 +30378,7 @@
         <f aca="false">IF($A147="","",IF($S147="FAIL","REJECT",IF($D147="","NEEDS PRICE",IF(OR($W147="",$X147=""),"NEEDS VALUATION",IF($AC147&lt;1,"OVERPRICED",IF(AND($AC147&gt;=Assumptions!$B$13,$V147&gt;=4),"BUY",IF($V147&gt;=3.4,"BUY CHEAPER",IF($V147&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG147" s="54" t="str">
+      <c r="AG147" s="53" t="str">
         <f aca="false">IF($AF147="","",IF($AF147="REJECT","Do not buy at any price",IF($AF147="NEEDS PRICE","Enter the current closeout price",IF($AF147="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF147="OVERPRICED","Worth less than break-even - walk",IF($AF147="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF147="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF147="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29532,7 +30468,7 @@
         <f aca="false">IF($A148="","",IF($S148="FAIL","REJECT",IF($D148="","NEEDS PRICE",IF(OR($W148="",$X148=""),"NEEDS VALUATION",IF($AC148&lt;1,"OVERPRICED",IF(AND($AC148&gt;=Assumptions!$B$13,$V148&gt;=4),"BUY",IF($V148&gt;=3.4,"BUY CHEAPER",IF($V148&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG148" s="54" t="str">
+      <c r="AG148" s="53" t="str">
         <f aca="false">IF($AF148="","",IF($AF148="REJECT","Do not buy at any price",IF($AF148="NEEDS PRICE","Enter the current closeout price",IF($AF148="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF148="OVERPRICED","Worth less than break-even - walk",IF($AF148="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF148="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF148="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29622,7 +30558,7 @@
         <f aca="false">IF($A149="","",IF($S149="FAIL","REJECT",IF($D149="","NEEDS PRICE",IF(OR($W149="",$X149=""),"NEEDS VALUATION",IF($AC149&lt;1,"OVERPRICED",IF(AND($AC149&gt;=Assumptions!$B$13,$V149&gt;=4),"BUY",IF($V149&gt;=3.4,"BUY CHEAPER",IF($V149&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG149" s="54" t="str">
+      <c r="AG149" s="53" t="str">
         <f aca="false">IF($AF149="","",IF($AF149="REJECT","Do not buy at any price",IF($AF149="NEEDS PRICE","Enter the current closeout price",IF($AF149="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF149="OVERPRICED","Worth less than break-even - walk",IF($AF149="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF149="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF149="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29712,7 +30648,7 @@
         <f aca="false">IF($A150="","",IF($S150="FAIL","REJECT",IF($D150="","NEEDS PRICE",IF(OR($W150="",$X150=""),"NEEDS VALUATION",IF($AC150&lt;1,"OVERPRICED",IF(AND($AC150&gt;=Assumptions!$B$13,$V150&gt;=4),"BUY",IF($V150&gt;=3.4,"BUY CHEAPER",IF($V150&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG150" s="54" t="str">
+      <c r="AG150" s="53" t="str">
         <f aca="false">IF($AF150="","",IF($AF150="REJECT","Do not buy at any price",IF($AF150="NEEDS PRICE","Enter the current closeout price",IF($AF150="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF150="OVERPRICED","Worth less than break-even - walk",IF($AF150="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF150="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF150="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29802,7 +30738,7 @@
         <f aca="false">IF($A151="","",IF($S151="FAIL","REJECT",IF($D151="","NEEDS PRICE",IF(OR($W151="",$X151=""),"NEEDS VALUATION",IF($AC151&lt;1,"OVERPRICED",IF(AND($AC151&gt;=Assumptions!$B$13,$V151&gt;=4),"BUY",IF($V151&gt;=3.4,"BUY CHEAPER",IF($V151&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG151" s="54" t="str">
+      <c r="AG151" s="53" t="str">
         <f aca="false">IF($AF151="","",IF($AF151="REJECT","Do not buy at any price",IF($AF151="NEEDS PRICE","Enter the current closeout price",IF($AF151="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF151="OVERPRICED","Worth less than break-even - walk",IF($AF151="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF151="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF151="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29892,7 +30828,7 @@
         <f aca="false">IF($A152="","",IF($S152="FAIL","REJECT",IF($D152="","NEEDS PRICE",IF(OR($W152="",$X152=""),"NEEDS VALUATION",IF($AC152&lt;1,"OVERPRICED",IF(AND($AC152&gt;=Assumptions!$B$13,$V152&gt;=4),"BUY",IF($V152&gt;=3.4,"BUY CHEAPER",IF($V152&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG152" s="54" t="str">
+      <c r="AG152" s="53" t="str">
         <f aca="false">IF($AF152="","",IF($AF152="REJECT","Do not buy at any price",IF($AF152="NEEDS PRICE","Enter the current closeout price",IF($AF152="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF152="OVERPRICED","Worth less than break-even - walk",IF($AF152="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF152="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF152="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29982,7 +30918,7 @@
         <f aca="false">IF($A153="","",IF($S153="FAIL","REJECT",IF($D153="","NEEDS PRICE",IF(OR($W153="",$X153=""),"NEEDS VALUATION",IF($AC153&lt;1,"OVERPRICED",IF(AND($AC153&gt;=Assumptions!$B$13,$V153&gt;=4),"BUY",IF($V153&gt;=3.4,"BUY CHEAPER",IF($V153&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG153" s="54" t="str">
+      <c r="AG153" s="53" t="str">
         <f aca="false">IF($AF153="","",IF($AF153="REJECT","Do not buy at any price",IF($AF153="NEEDS PRICE","Enter the current closeout price",IF($AF153="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF153="OVERPRICED","Worth less than break-even - walk",IF($AF153="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF153="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF153="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30072,7 +31008,7 @@
         <f aca="false">IF($A154="","",IF($S154="FAIL","REJECT",IF($D154="","NEEDS PRICE",IF(OR($W154="",$X154=""),"NEEDS VALUATION",IF($AC154&lt;1,"OVERPRICED",IF(AND($AC154&gt;=Assumptions!$B$13,$V154&gt;=4),"BUY",IF($V154&gt;=3.4,"BUY CHEAPER",IF($V154&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG154" s="54" t="str">
+      <c r="AG154" s="53" t="str">
         <f aca="false">IF($AF154="","",IF($AF154="REJECT","Do not buy at any price",IF($AF154="NEEDS PRICE","Enter the current closeout price",IF($AF154="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF154="OVERPRICED","Worth less than break-even - walk",IF($AF154="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF154="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF154="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30162,7 +31098,7 @@
         <f aca="false">IF($A155="","",IF($S155="FAIL","REJECT",IF($D155="","NEEDS PRICE",IF(OR($W155="",$X155=""),"NEEDS VALUATION",IF($AC155&lt;1,"OVERPRICED",IF(AND($AC155&gt;=Assumptions!$B$13,$V155&gt;=4),"BUY",IF($V155&gt;=3.4,"BUY CHEAPER",IF($V155&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG155" s="54" t="str">
+      <c r="AG155" s="53" t="str">
         <f aca="false">IF($AF155="","",IF($AF155="REJECT","Do not buy at any price",IF($AF155="NEEDS PRICE","Enter the current closeout price",IF($AF155="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF155="OVERPRICED","Worth less than break-even - walk",IF($AF155="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF155="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF155="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30252,7 +31188,7 @@
         <f aca="false">IF($A156="","",IF($S156="FAIL","REJECT",IF($D156="","NEEDS PRICE",IF(OR($W156="",$X156=""),"NEEDS VALUATION",IF($AC156&lt;1,"OVERPRICED",IF(AND($AC156&gt;=Assumptions!$B$13,$V156&gt;=4),"BUY",IF($V156&gt;=3.4,"BUY CHEAPER",IF($V156&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG156" s="54" t="str">
+      <c r="AG156" s="53" t="str">
         <f aca="false">IF($AF156="","",IF($AF156="REJECT","Do not buy at any price",IF($AF156="NEEDS PRICE","Enter the current closeout price",IF($AF156="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF156="OVERPRICED","Worth less than break-even - walk",IF($AF156="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF156="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF156="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30342,7 +31278,7 @@
         <f aca="false">IF($A157="","",IF($S157="FAIL","REJECT",IF($D157="","NEEDS PRICE",IF(OR($W157="",$X157=""),"NEEDS VALUATION",IF($AC157&lt;1,"OVERPRICED",IF(AND($AC157&gt;=Assumptions!$B$13,$V157&gt;=4),"BUY",IF($V157&gt;=3.4,"BUY CHEAPER",IF($V157&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG157" s="54" t="str">
+      <c r="AG157" s="53" t="str">
         <f aca="false">IF($AF157="","",IF($AF157="REJECT","Do not buy at any price",IF($AF157="NEEDS PRICE","Enter the current closeout price",IF($AF157="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF157="OVERPRICED","Worth less than break-even - walk",IF($AF157="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF157="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF157="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30432,7 +31368,7 @@
         <f aca="false">IF($A158="","",IF($S158="FAIL","REJECT",IF($D158="","NEEDS PRICE",IF(OR($W158="",$X158=""),"NEEDS VALUATION",IF($AC158&lt;1,"OVERPRICED",IF(AND($AC158&gt;=Assumptions!$B$13,$V158&gt;=4),"BUY",IF($V158&gt;=3.4,"BUY CHEAPER",IF($V158&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG158" s="54" t="str">
+      <c r="AG158" s="53" t="str">
         <f aca="false">IF($AF158="","",IF($AF158="REJECT","Do not buy at any price",IF($AF158="NEEDS PRICE","Enter the current closeout price",IF($AF158="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF158="OVERPRICED","Worth less than break-even - walk",IF($AF158="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF158="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF158="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30522,7 +31458,7 @@
         <f aca="false">IF($A159="","",IF($S159="FAIL","REJECT",IF($D159="","NEEDS PRICE",IF(OR($W159="",$X159=""),"NEEDS VALUATION",IF($AC159&lt;1,"OVERPRICED",IF(AND($AC159&gt;=Assumptions!$B$13,$V159&gt;=4),"BUY",IF($V159&gt;=3.4,"BUY CHEAPER",IF($V159&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG159" s="54" t="str">
+      <c r="AG159" s="53" t="str">
         <f aca="false">IF($AF159="","",IF($AF159="REJECT","Do not buy at any price",IF($AF159="NEEDS PRICE","Enter the current closeout price",IF($AF159="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF159="OVERPRICED","Worth less than break-even - walk",IF($AF159="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF159="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF159="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30612,7 +31548,7 @@
         <f aca="false">IF($A160="","",IF($S160="FAIL","REJECT",IF($D160="","NEEDS PRICE",IF(OR($W160="",$X160=""),"NEEDS VALUATION",IF($AC160&lt;1,"OVERPRICED",IF(AND($AC160&gt;=Assumptions!$B$13,$V160&gt;=4),"BUY",IF($V160&gt;=3.4,"BUY CHEAPER",IF($V160&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG160" s="54" t="str">
+      <c r="AG160" s="53" t="str">
         <f aca="false">IF($AF160="","",IF($AF160="REJECT","Do not buy at any price",IF($AF160="NEEDS PRICE","Enter the current closeout price",IF($AF160="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF160="OVERPRICED","Worth less than break-even - walk",IF($AF160="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF160="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF160="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30702,7 +31638,7 @@
         <f aca="false">IF($A161="","",IF($S161="FAIL","REJECT",IF($D161="","NEEDS PRICE",IF(OR($W161="",$X161=""),"NEEDS VALUATION",IF($AC161&lt;1,"OVERPRICED",IF(AND($AC161&gt;=Assumptions!$B$13,$V161&gt;=4),"BUY",IF($V161&gt;=3.4,"BUY CHEAPER",IF($V161&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG161" s="54" t="str">
+      <c r="AG161" s="53" t="str">
         <f aca="false">IF($AF161="","",IF($AF161="REJECT","Do not buy at any price",IF($AF161="NEEDS PRICE","Enter the current closeout price",IF($AF161="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF161="OVERPRICED","Worth less than break-even - walk",IF($AF161="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF161="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF161="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30792,7 +31728,7 @@
         <f aca="false">IF($A162="","",IF($S162="FAIL","REJECT",IF($D162="","NEEDS PRICE",IF(OR($W162="",$X162=""),"NEEDS VALUATION",IF($AC162&lt;1,"OVERPRICED",IF(AND($AC162&gt;=Assumptions!$B$13,$V162&gt;=4),"BUY",IF($V162&gt;=3.4,"BUY CHEAPER",IF($V162&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG162" s="54" t="str">
+      <c r="AG162" s="53" t="str">
         <f aca="false">IF($AF162="","",IF($AF162="REJECT","Do not buy at any price",IF($AF162="NEEDS PRICE","Enter the current closeout price",IF($AF162="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF162="OVERPRICED","Worth less than break-even - walk",IF($AF162="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF162="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF162="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30882,7 +31818,7 @@
         <f aca="false">IF($A163="","",IF($S163="FAIL","REJECT",IF($D163="","NEEDS PRICE",IF(OR($W163="",$X163=""),"NEEDS VALUATION",IF($AC163&lt;1,"OVERPRICED",IF(AND($AC163&gt;=Assumptions!$B$13,$V163&gt;=4),"BUY",IF($V163&gt;=3.4,"BUY CHEAPER",IF($V163&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG163" s="54" t="str">
+      <c r="AG163" s="53" t="str">
         <f aca="false">IF($AF163="","",IF($AF163="REJECT","Do not buy at any price",IF($AF163="NEEDS PRICE","Enter the current closeout price",IF($AF163="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF163="OVERPRICED","Worth less than break-even - walk",IF($AF163="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF163="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF163="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30938,7 +31874,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>546</v>
+        <v>624</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -30956,7 +31892,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>547</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30967,10 +31903,10 @@
         <v>150</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>548</v>
+        <v>626</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>549</v>
+        <v>627</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>158</v>
@@ -30979,45 +31915,45 @@
         <v>161</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>550</v>
+        <v>628</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>551</v>
+        <v>629</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>552</v>
+        <v>630</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>553</v>
+        <v>631</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>554</v>
+        <v>632</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>555</v>
+        <v>633</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="68" t="s">
         <v>177</v>
       </c>
       <c r="B5" s="24" t="str">
         <f aca="false">IF($A5="","",IF(ISERROR(FIND(".",$A5)),"",LOWER(MID($A5,FIND(CHAR(1),SUBSTITUTE($A5,".",CHAR(1),LEN($A5)-LEN(SUBSTITUTE($A5,".",""))))+1,LEN($A5)))))</f>
         <v>com</v>
       </c>
-      <c r="C5" s="65" t="s">
-        <v>557</v>
-      </c>
-      <c r="D5" s="70" t="n">
+      <c r="C5" s="64" t="s">
+        <v>635</v>
+      </c>
+      <c r="D5" s="69" t="n">
         <v>45363</v>
       </c>
-      <c r="E5" s="66" t="n">
+      <c r="E5" s="65" t="n">
         <v>2400</v>
       </c>
       <c r="F5" s="29" t="n">
@@ -31028,7 +31964,7 @@
         <f aca="true">IF(OR($A5="",$D5=""),"",YEARFRAC($D5,TODAY()))</f>
         <v>2.39444444444444</v>
       </c>
-      <c r="H5" s="71" t="n">
+      <c r="H5" s="70" t="n">
         <f aca="false">IF($G5="","",MAX(0,INT($G5)))</f>
         <v>2</v>
       </c>
@@ -31048,15 +31984,15 @@
         <f aca="false">IF($K5="","",MAX($K5,$E5*Assumptions!$B$10))</f>
         <v>24000</v>
       </c>
-      <c r="M5" s="66" t="n">
+      <c r="M5" s="65" t="n">
         <v>12000</v>
       </c>
-      <c r="N5" s="68" t="s">
-        <v>558</v>
+      <c r="N5" s="67" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="37" t="str">
         <f aca="false">IF($A6="","",IF(ISERROR(FIND(".",$A6)),"",LOWER(MID($A6,FIND(CHAR(1),SUBSTITUTE($A6,".",CHAR(1),LEN($A6)-LEN(SUBSTITUTE($A6,".",""))))+1,LEN($A6)))))</f>
         <v/>
@@ -31096,7 +32032,7 @@
       <c r="N6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="37" t="str">
         <f aca="false">IF($A7="","",IF(ISERROR(FIND(".",$A7)),"",LOWER(MID($A7,FIND(CHAR(1),SUBSTITUTE($A7,".",CHAR(1),LEN($A7)-LEN(SUBSTITUTE($A7,".",""))))+1,LEN($A7)))))</f>
         <v/>
@@ -31136,7 +32072,7 @@
       <c r="N7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="37" t="str">
         <f aca="false">IF($A8="","",IF(ISERROR(FIND(".",$A8)),"",LOWER(MID($A8,FIND(CHAR(1),SUBSTITUTE($A8,".",CHAR(1),LEN($A8)-LEN(SUBSTITUTE($A8,".",""))))+1,LEN($A8)))))</f>
         <v/>
@@ -31176,7 +32112,7 @@
       <c r="N8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="37" t="str">
         <f aca="false">IF($A9="","",IF(ISERROR(FIND(".",$A9)),"",LOWER(MID($A9,FIND(CHAR(1),SUBSTITUTE($A9,".",CHAR(1),LEN($A9)-LEN(SUBSTITUTE($A9,".",""))))+1,LEN($A9)))))</f>
         <v/>
@@ -31216,7 +32152,7 @@
       <c r="N9" s="36"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="37" t="str">
         <f aca="false">IF($A10="","",IF(ISERROR(FIND(".",$A10)),"",LOWER(MID($A10,FIND(CHAR(1),SUBSTITUTE($A10,".",CHAR(1),LEN($A10)-LEN(SUBSTITUTE($A10,".",""))))+1,LEN($A10)))))</f>
         <v/>
@@ -31256,7 +32192,7 @@
       <c r="N10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="37" t="str">
         <f aca="false">IF($A11="","",IF(ISERROR(FIND(".",$A11)),"",LOWER(MID($A11,FIND(CHAR(1),SUBSTITUTE($A11,".",CHAR(1),LEN($A11)-LEN(SUBSTITUTE($A11,".",""))))+1,LEN($A11)))))</f>
         <v/>
@@ -31296,7 +32232,7 @@
       <c r="N11" s="36"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="37" t="str">
         <f aca="false">IF($A12="","",IF(ISERROR(FIND(".",$A12)),"",LOWER(MID($A12,FIND(CHAR(1),SUBSTITUTE($A12,".",CHAR(1),LEN($A12)-LEN(SUBSTITUTE($A12,".",""))))+1,LEN($A12)))))</f>
         <v/>
@@ -31336,7 +32272,7 @@
       <c r="N12" s="36"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="37" t="str">
         <f aca="false">IF($A13="","",IF(ISERROR(FIND(".",$A13)),"",LOWER(MID($A13,FIND(CHAR(1),SUBSTITUTE($A13,".",CHAR(1),LEN($A13)-LEN(SUBSTITUTE($A13,".",""))))+1,LEN($A13)))))</f>
         <v/>
@@ -31376,7 +32312,7 @@
       <c r="N13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49"/>
+      <c r="A14" s="71"/>
       <c r="B14" s="37" t="str">
         <f aca="false">IF($A14="","",IF(ISERROR(FIND(".",$A14)),"",LOWER(MID($A14,FIND(CHAR(1),SUBSTITUTE($A14,".",CHAR(1),LEN($A14)-LEN(SUBSTITUTE($A14,".",""))))+1,LEN($A14)))))</f>
         <v/>
@@ -31416,7 +32352,7 @@
       <c r="N14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="37" t="str">
         <f aca="false">IF($A15="","",IF(ISERROR(FIND(".",$A15)),"",LOWER(MID($A15,FIND(CHAR(1),SUBSTITUTE($A15,".",CHAR(1),LEN($A15)-LEN(SUBSTITUTE($A15,".",""))))+1,LEN($A15)))))</f>
         <v/>
@@ -31456,7 +32392,7 @@
       <c r="N15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="37" t="str">
         <f aca="false">IF($A16="","",IF(ISERROR(FIND(".",$A16)),"",LOWER(MID($A16,FIND(CHAR(1),SUBSTITUTE($A16,".",CHAR(1),LEN($A16)-LEN(SUBSTITUTE($A16,".",""))))+1,LEN($A16)))))</f>
         <v/>
@@ -31496,7 +32432,7 @@
       <c r="N16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="37" t="str">
         <f aca="false">IF($A17="","",IF(ISERROR(FIND(".",$A17)),"",LOWER(MID($A17,FIND(CHAR(1),SUBSTITUTE($A17,".",CHAR(1),LEN($A17)-LEN(SUBSTITUTE($A17,".",""))))+1,LEN($A17)))))</f>
         <v/>
@@ -31536,7 +32472,7 @@
       <c r="N17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="37" t="str">
         <f aca="false">IF($A18="","",IF(ISERROR(FIND(".",$A18)),"",LOWER(MID($A18,FIND(CHAR(1),SUBSTITUTE($A18,".",CHAR(1),LEN($A18)-LEN(SUBSTITUTE($A18,".",""))))+1,LEN($A18)))))</f>
         <v/>
@@ -31576,7 +32512,7 @@
       <c r="N18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="37" t="str">
         <f aca="false">IF($A19="","",IF(ISERROR(FIND(".",$A19)),"",LOWER(MID($A19,FIND(CHAR(1),SUBSTITUTE($A19,".",CHAR(1),LEN($A19)-LEN(SUBSTITUTE($A19,".",""))))+1,LEN($A19)))))</f>
         <v/>
@@ -31616,7 +32552,7 @@
       <c r="N19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="37" t="str">
         <f aca="false">IF($A20="","",IF(ISERROR(FIND(".",$A20)),"",LOWER(MID($A20,FIND(CHAR(1),SUBSTITUTE($A20,".",CHAR(1),LEN($A20)-LEN(SUBSTITUTE($A20,".",""))))+1,LEN($A20)))))</f>
         <v/>
@@ -31656,7 +32592,7 @@
       <c r="N20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="37" t="str">
         <f aca="false">IF($A21="","",IF(ISERROR(FIND(".",$A21)),"",LOWER(MID($A21,FIND(CHAR(1),SUBSTITUTE($A21,".",CHAR(1),LEN($A21)-LEN(SUBSTITUTE($A21,".",""))))+1,LEN($A21)))))</f>
         <v/>
@@ -31696,7 +32632,7 @@
       <c r="N21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49"/>
+      <c r="A22" s="71"/>
       <c r="B22" s="37" t="str">
         <f aca="false">IF($A22="","",IF(ISERROR(FIND(".",$A22)),"",LOWER(MID($A22,FIND(CHAR(1),SUBSTITUTE($A22,".",CHAR(1),LEN($A22)-LEN(SUBSTITUTE($A22,".",""))))+1,LEN($A22)))))</f>
         <v/>
@@ -31736,7 +32672,7 @@
       <c r="N22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49"/>
+      <c r="A23" s="71"/>
       <c r="B23" s="37" t="str">
         <f aca="false">IF($A23="","",IF(ISERROR(FIND(".",$A23)),"",LOWER(MID($A23,FIND(CHAR(1),SUBSTITUTE($A23,".",CHAR(1),LEN($A23)-LEN(SUBSTITUTE($A23,".",""))))+1,LEN($A23)))))</f>
         <v/>
@@ -31776,7 +32712,7 @@
       <c r="N23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49"/>
+      <c r="A24" s="71"/>
       <c r="B24" s="37" t="str">
         <f aca="false">IF($A24="","",IF(ISERROR(FIND(".",$A24)),"",LOWER(MID($A24,FIND(CHAR(1),SUBSTITUTE($A24,".",CHAR(1),LEN($A24)-LEN(SUBSTITUTE($A24,".",""))))+1,LEN($A24)))))</f>
         <v/>
@@ -31816,7 +32752,7 @@
       <c r="N24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49"/>
+      <c r="A25" s="71"/>
       <c r="B25" s="37" t="str">
         <f aca="false">IF($A25="","",IF(ISERROR(FIND(".",$A25)),"",LOWER(MID($A25,FIND(CHAR(1),SUBSTITUTE($A25,".",CHAR(1),LEN($A25)-LEN(SUBSTITUTE($A25,".",""))))+1,LEN($A25)))))</f>
         <v/>
@@ -31856,7 +32792,7 @@
       <c r="N25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49"/>
+      <c r="A26" s="71"/>
       <c r="B26" s="37" t="str">
         <f aca="false">IF($A26="","",IF(ISERROR(FIND(".",$A26)),"",LOWER(MID($A26,FIND(CHAR(1),SUBSTITUTE($A26,".",CHAR(1),LEN($A26)-LEN(SUBSTITUTE($A26,".",""))))+1,LEN($A26)))))</f>
         <v/>
@@ -31896,7 +32832,7 @@
       <c r="N26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49"/>
+      <c r="A27" s="71"/>
       <c r="B27" s="37" t="str">
         <f aca="false">IF($A27="","",IF(ISERROR(FIND(".",$A27)),"",LOWER(MID($A27,FIND(CHAR(1),SUBSTITUTE($A27,".",CHAR(1),LEN($A27)-LEN(SUBSTITUTE($A27,".",""))))+1,LEN($A27)))))</f>
         <v/>
@@ -31936,7 +32872,7 @@
       <c r="N27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49"/>
+      <c r="A28" s="71"/>
       <c r="B28" s="37" t="str">
         <f aca="false">IF($A28="","",IF(ISERROR(FIND(".",$A28)),"",LOWER(MID($A28,FIND(CHAR(1),SUBSTITUTE($A28,".",CHAR(1),LEN($A28)-LEN(SUBSTITUTE($A28,".",""))))+1,LEN($A28)))))</f>
         <v/>
@@ -31976,7 +32912,7 @@
       <c r="N28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49"/>
+      <c r="A29" s="71"/>
       <c r="B29" s="37" t="str">
         <f aca="false">IF($A29="","",IF(ISERROR(FIND(".",$A29)),"",LOWER(MID($A29,FIND(CHAR(1),SUBSTITUTE($A29,".",CHAR(1),LEN($A29)-LEN(SUBSTITUTE($A29,".",""))))+1,LEN($A29)))))</f>
         <v/>
@@ -32016,7 +32952,7 @@
       <c r="N29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49"/>
+      <c r="A30" s="71"/>
       <c r="B30" s="37" t="str">
         <f aca="false">IF($A30="","",IF(ISERROR(FIND(".",$A30)),"",LOWER(MID($A30,FIND(CHAR(1),SUBSTITUTE($A30,".",CHAR(1),LEN($A30)-LEN(SUBSTITUTE($A30,".",""))))+1,LEN($A30)))))</f>
         <v/>
@@ -32056,7 +32992,7 @@
       <c r="N30" s="36"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49"/>
+      <c r="A31" s="71"/>
       <c r="B31" s="37" t="str">
         <f aca="false">IF($A31="","",IF(ISERROR(FIND(".",$A31)),"",LOWER(MID($A31,FIND(CHAR(1),SUBSTITUTE($A31,".",CHAR(1),LEN($A31)-LEN(SUBSTITUTE($A31,".",""))))+1,LEN($A31)))))</f>
         <v/>
@@ -32096,7 +33032,7 @@
       <c r="N31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49"/>
+      <c r="A32" s="71"/>
       <c r="B32" s="37" t="str">
         <f aca="false">IF($A32="","",IF(ISERROR(FIND(".",$A32)),"",LOWER(MID($A32,FIND(CHAR(1),SUBSTITUTE($A32,".",CHAR(1),LEN($A32)-LEN(SUBSTITUTE($A32,".",""))))+1,LEN($A32)))))</f>
         <v/>
@@ -32136,7 +33072,7 @@
       <c r="N32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49"/>
+      <c r="A33" s="71"/>
       <c r="B33" s="37" t="str">
         <f aca="false">IF($A33="","",IF(ISERROR(FIND(".",$A33)),"",LOWER(MID($A33,FIND(CHAR(1),SUBSTITUTE($A33,".",CHAR(1),LEN($A33)-LEN(SUBSTITUTE($A33,".",""))))+1,LEN($A33)))))</f>
         <v/>
@@ -32176,7 +33112,7 @@
       <c r="N33" s="36"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49"/>
+      <c r="A34" s="71"/>
       <c r="B34" s="37" t="str">
         <f aca="false">IF($A34="","",IF(ISERROR(FIND(".",$A34)),"",LOWER(MID($A34,FIND(CHAR(1),SUBSTITUTE($A34,".",CHAR(1),LEN($A34)-LEN(SUBSTITUTE($A34,".",""))))+1,LEN($A34)))))</f>
         <v/>
@@ -32216,7 +33152,7 @@
       <c r="N34" s="36"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49"/>
+      <c r="A35" s="71"/>
       <c r="B35" s="37" t="str">
         <f aca="false">IF($A35="","",IF(ISERROR(FIND(".",$A35)),"",LOWER(MID($A35,FIND(CHAR(1),SUBSTITUTE($A35,".",CHAR(1),LEN($A35)-LEN(SUBSTITUTE($A35,".",""))))+1,LEN($A35)))))</f>
         <v/>
@@ -32256,7 +33192,7 @@
       <c r="N35" s="36"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49"/>
+      <c r="A36" s="71"/>
       <c r="B36" s="37" t="str">
         <f aca="false">IF($A36="","",IF(ISERROR(FIND(".",$A36)),"",LOWER(MID($A36,FIND(CHAR(1),SUBSTITUTE($A36,".",CHAR(1),LEN($A36)-LEN(SUBSTITUTE($A36,".",""))))+1,LEN($A36)))))</f>
         <v/>
@@ -32296,7 +33232,7 @@
       <c r="N36" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49"/>
+      <c r="A37" s="71"/>
       <c r="B37" s="37" t="str">
         <f aca="false">IF($A37="","",IF(ISERROR(FIND(".",$A37)),"",LOWER(MID($A37,FIND(CHAR(1),SUBSTITUTE($A37,".",CHAR(1),LEN($A37)-LEN(SUBSTITUTE($A37,".",""))))+1,LEN($A37)))))</f>
         <v/>
@@ -32336,7 +33272,7 @@
       <c r="N37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="49"/>
+      <c r="A38" s="71"/>
       <c r="B38" s="37" t="str">
         <f aca="false">IF($A38="","",IF(ISERROR(FIND(".",$A38)),"",LOWER(MID($A38,FIND(CHAR(1),SUBSTITUTE($A38,".",CHAR(1),LEN($A38)-LEN(SUBSTITUTE($A38,".",""))))+1,LEN($A38)))))</f>
         <v/>
@@ -32376,7 +33312,7 @@
       <c r="N38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49"/>
+      <c r="A39" s="71"/>
       <c r="B39" s="37" t="str">
         <f aca="false">IF($A39="","",IF(ISERROR(FIND(".",$A39)),"",LOWER(MID($A39,FIND(CHAR(1),SUBSTITUTE($A39,".",CHAR(1),LEN($A39)-LEN(SUBSTITUTE($A39,".",""))))+1,LEN($A39)))))</f>
         <v/>
@@ -32416,7 +33352,7 @@
       <c r="N39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49"/>
+      <c r="A40" s="71"/>
       <c r="B40" s="37" t="str">
         <f aca="false">IF($A40="","",IF(ISERROR(FIND(".",$A40)),"",LOWER(MID($A40,FIND(CHAR(1),SUBSTITUTE($A40,".",CHAR(1),LEN($A40)-LEN(SUBSTITUTE($A40,".",""))))+1,LEN($A40)))))</f>
         <v/>
@@ -32456,7 +33392,7 @@
       <c r="N40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="49"/>
+      <c r="A41" s="71"/>
       <c r="B41" s="37" t="str">
         <f aca="false">IF($A41="","",IF(ISERROR(FIND(".",$A41)),"",LOWER(MID($A41,FIND(CHAR(1),SUBSTITUTE($A41,".",CHAR(1),LEN($A41)-LEN(SUBSTITUTE($A41,".",""))))+1,LEN($A41)))))</f>
         <v/>
@@ -32496,7 +33432,7 @@
       <c r="N41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="49"/>
+      <c r="A42" s="71"/>
       <c r="B42" s="37" t="str">
         <f aca="false">IF($A42="","",IF(ISERROR(FIND(".",$A42)),"",LOWER(MID($A42,FIND(CHAR(1),SUBSTITUTE($A42,".",CHAR(1),LEN($A42)-LEN(SUBSTITUTE($A42,".",""))))+1,LEN($A42)))))</f>
         <v/>
@@ -32536,7 +33472,7 @@
       <c r="N42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="49"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="37" t="str">
         <f aca="false">IF($A43="","",IF(ISERROR(FIND(".",$A43)),"",LOWER(MID($A43,FIND(CHAR(1),SUBSTITUTE($A43,".",CHAR(1),LEN($A43)-LEN(SUBSTITUTE($A43,".",""))))+1,LEN($A43)))))</f>
         <v/>
@@ -32576,7 +33512,7 @@
       <c r="N43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="49"/>
+      <c r="A44" s="71"/>
       <c r="B44" s="37" t="str">
         <f aca="false">IF($A44="","",IF(ISERROR(FIND(".",$A44)),"",LOWER(MID($A44,FIND(CHAR(1),SUBSTITUTE($A44,".",CHAR(1),LEN($A44)-LEN(SUBSTITUTE($A44,".",""))))+1,LEN($A44)))))</f>
         <v/>
@@ -32616,7 +33552,7 @@
       <c r="N44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49"/>
+      <c r="A45" s="71"/>
       <c r="B45" s="37" t="str">
         <f aca="false">IF($A45="","",IF(ISERROR(FIND(".",$A45)),"",LOWER(MID($A45,FIND(CHAR(1),SUBSTITUTE($A45,".",CHAR(1),LEN($A45)-LEN(SUBSTITUTE($A45,".",""))))+1,LEN($A45)))))</f>
         <v/>
@@ -32656,7 +33592,7 @@
       <c r="N45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49"/>
+      <c r="A46" s="71"/>
       <c r="B46" s="37" t="str">
         <f aca="false">IF($A46="","",IF(ISERROR(FIND(".",$A46)),"",LOWER(MID($A46,FIND(CHAR(1),SUBSTITUTE($A46,".",CHAR(1),LEN($A46)-LEN(SUBSTITUTE($A46,".",""))))+1,LEN($A46)))))</f>
         <v/>
@@ -32696,7 +33632,7 @@
       <c r="N46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="49"/>
+      <c r="A47" s="71"/>
       <c r="B47" s="37" t="str">
         <f aca="false">IF($A47="","",IF(ISERROR(FIND(".",$A47)),"",LOWER(MID($A47,FIND(CHAR(1),SUBSTITUTE($A47,".",CHAR(1),LEN($A47)-LEN(SUBSTITUTE($A47,".",""))))+1,LEN($A47)))))</f>
         <v/>
@@ -32736,7 +33672,7 @@
       <c r="N47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="49"/>
+      <c r="A48" s="71"/>
       <c r="B48" s="37" t="str">
         <f aca="false">IF($A48="","",IF(ISERROR(FIND(".",$A48)),"",LOWER(MID($A48,FIND(CHAR(1),SUBSTITUTE($A48,".",CHAR(1),LEN($A48)-LEN(SUBSTITUTE($A48,".",""))))+1,LEN($A48)))))</f>
         <v/>
@@ -32776,7 +33712,7 @@
       <c r="N48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="49"/>
+      <c r="A49" s="71"/>
       <c r="B49" s="37" t="str">
         <f aca="false">IF($A49="","",IF(ISERROR(FIND(".",$A49)),"",LOWER(MID($A49,FIND(CHAR(1),SUBSTITUTE($A49,".",CHAR(1),LEN($A49)-LEN(SUBSTITUTE($A49,".",""))))+1,LEN($A49)))))</f>
         <v/>
@@ -32816,7 +33752,7 @@
       <c r="N49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="49"/>
+      <c r="A50" s="71"/>
       <c r="B50" s="37" t="str">
         <f aca="false">IF($A50="","",IF(ISERROR(FIND(".",$A50)),"",LOWER(MID($A50,FIND(CHAR(1),SUBSTITUTE($A50,".",CHAR(1),LEN($A50)-LEN(SUBSTITUTE($A50,".",""))))+1,LEN($A50)))))</f>
         <v/>
@@ -32856,7 +33792,7 @@
       <c r="N50" s="36"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49"/>
+      <c r="A51" s="71"/>
       <c r="B51" s="37" t="str">
         <f aca="false">IF($A51="","",IF(ISERROR(FIND(".",$A51)),"",LOWER(MID($A51,FIND(CHAR(1),SUBSTITUTE($A51,".",CHAR(1),LEN($A51)-LEN(SUBSTITUTE($A51,".",""))))+1,LEN($A51)))))</f>
         <v/>
@@ -32896,7 +33832,7 @@
       <c r="N51" s="36"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49"/>
+      <c r="A52" s="71"/>
       <c r="B52" s="37" t="str">
         <f aca="false">IF($A52="","",IF(ISERROR(FIND(".",$A52)),"",LOWER(MID($A52,FIND(CHAR(1),SUBSTITUTE($A52,".",CHAR(1),LEN($A52)-LEN(SUBSTITUTE($A52,".",""))))+1,LEN($A52)))))</f>
         <v/>
@@ -32936,7 +33872,7 @@
       <c r="N52" s="36"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="49"/>
+      <c r="A53" s="71"/>
       <c r="B53" s="37" t="str">
         <f aca="false">IF($A53="","",IF(ISERROR(FIND(".",$A53)),"",LOWER(MID($A53,FIND(CHAR(1),SUBSTITUTE($A53,".",CHAR(1),LEN($A53)-LEN(SUBSTITUTE($A53,".",""))))+1,LEN($A53)))))</f>
         <v/>
@@ -32976,7 +33912,7 @@
       <c r="N53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="49"/>
+      <c r="A54" s="71"/>
       <c r="B54" s="37" t="str">
         <f aca="false">IF($A54="","",IF(ISERROR(FIND(".",$A54)),"",LOWER(MID($A54,FIND(CHAR(1),SUBSTITUTE($A54,".",CHAR(1),LEN($A54)-LEN(SUBSTITUTE($A54,".",""))))+1,LEN($A54)))))</f>
         <v/>
@@ -33016,7 +33952,7 @@
       <c r="N54" s="36"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="49"/>
+      <c r="A55" s="71"/>
       <c r="B55" s="37" t="str">
         <f aca="false">IF($A55="","",IF(ISERROR(FIND(".",$A55)),"",LOWER(MID($A55,FIND(CHAR(1),SUBSTITUTE($A55,".",CHAR(1),LEN($A55)-LEN(SUBSTITUTE($A55,".",""))))+1,LEN($A55)))))</f>
         <v/>
@@ -33056,7 +33992,7 @@
       <c r="N55" s="36"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="49"/>
+      <c r="A56" s="71"/>
       <c r="B56" s="37" t="str">
         <f aca="false">IF($A56="","",IF(ISERROR(FIND(".",$A56)),"",LOWER(MID($A56,FIND(CHAR(1),SUBSTITUTE($A56,".",CHAR(1),LEN($A56)-LEN(SUBSTITUTE($A56,".",""))))+1,LEN($A56)))))</f>
         <v/>
@@ -33096,7 +34032,7 @@
       <c r="N56" s="36"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49"/>
+      <c r="A57" s="71"/>
       <c r="B57" s="37" t="str">
         <f aca="false">IF($A57="","",IF(ISERROR(FIND(".",$A57)),"",LOWER(MID($A57,FIND(CHAR(1),SUBSTITUTE($A57,".",CHAR(1),LEN($A57)-LEN(SUBSTITUTE($A57,".",""))))+1,LEN($A57)))))</f>
         <v/>
@@ -33136,7 +34072,7 @@
       <c r="N57" s="36"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49"/>
+      <c r="A58" s="71"/>
       <c r="B58" s="37" t="str">
         <f aca="false">IF($A58="","",IF(ISERROR(FIND(".",$A58)),"",LOWER(MID($A58,FIND(CHAR(1),SUBSTITUTE($A58,".",CHAR(1),LEN($A58)-LEN(SUBSTITUTE($A58,".",""))))+1,LEN($A58)))))</f>
         <v/>
@@ -33176,7 +34112,7 @@
       <c r="N58" s="36"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="49"/>
+      <c r="A59" s="71"/>
       <c r="B59" s="37" t="str">
         <f aca="false">IF($A59="","",IF(ISERROR(FIND(".",$A59)),"",LOWER(MID($A59,FIND(CHAR(1),SUBSTITUTE($A59,".",CHAR(1),LEN($A59)-LEN(SUBSTITUTE($A59,".",""))))+1,LEN($A59)))))</f>
         <v/>
@@ -33216,7 +34152,7 @@
       <c r="N59" s="36"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="49"/>
+      <c r="A60" s="71"/>
       <c r="B60" s="37" t="str">
         <f aca="false">IF($A60="","",IF(ISERROR(FIND(".",$A60)),"",LOWER(MID($A60,FIND(CHAR(1),SUBSTITUTE($A60,".",CHAR(1),LEN($A60)-LEN(SUBSTITUTE($A60,".",""))))+1,LEN($A60)))))</f>
         <v/>
@@ -33256,7 +34192,7 @@
       <c r="N60" s="36"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49"/>
+      <c r="A61" s="71"/>
       <c r="B61" s="37" t="str">
         <f aca="false">IF($A61="","",IF(ISERROR(FIND(".",$A61)),"",LOWER(MID($A61,FIND(CHAR(1),SUBSTITUTE($A61,".",CHAR(1),LEN($A61)-LEN(SUBSTITUTE($A61,".",""))))+1,LEN($A61)))))</f>
         <v/>
@@ -33296,7 +34232,7 @@
       <c r="N61" s="36"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49"/>
+      <c r="A62" s="71"/>
       <c r="B62" s="37" t="str">
         <f aca="false">IF($A62="","",IF(ISERROR(FIND(".",$A62)),"",LOWER(MID($A62,FIND(CHAR(1),SUBSTITUTE($A62,".",CHAR(1),LEN($A62)-LEN(SUBSTITUTE($A62,".",""))))+1,LEN($A62)))))</f>
         <v/>
@@ -33336,7 +34272,7 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="49"/>
+      <c r="A63" s="71"/>
       <c r="B63" s="37" t="str">
         <f aca="false">IF($A63="","",IF(ISERROR(FIND(".",$A63)),"",LOWER(MID($A63,FIND(CHAR(1),SUBSTITUTE($A63,".",CHAR(1),LEN($A63)-LEN(SUBSTITUTE($A63,".",""))))+1,LEN($A63)))))</f>
         <v/>
@@ -33376,7 +34312,7 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="49"/>
+      <c r="A64" s="71"/>
       <c r="B64" s="37" t="str">
         <f aca="false">IF($A64="","",IF(ISERROR(FIND(".",$A64)),"",LOWER(MID($A64,FIND(CHAR(1),SUBSTITUTE($A64,".",CHAR(1),LEN($A64)-LEN(SUBSTITUTE($A64,".",""))))+1,LEN($A64)))))</f>
         <v/>
@@ -33416,7 +34352,7 @@
       <c r="N64" s="36"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49"/>
+      <c r="A65" s="71"/>
       <c r="B65" s="37" t="str">
         <f aca="false">IF($A65="","",IF(ISERROR(FIND(".",$A65)),"",LOWER(MID($A65,FIND(CHAR(1),SUBSTITUTE($A65,".",CHAR(1),LEN($A65)-LEN(SUBSTITUTE($A65,".",""))))+1,LEN($A65)))))</f>
         <v/>
@@ -33456,7 +34392,7 @@
       <c r="N65" s="36"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="49"/>
+      <c r="A66" s="71"/>
       <c r="B66" s="37" t="str">
         <f aca="false">IF($A66="","",IF(ISERROR(FIND(".",$A66)),"",LOWER(MID($A66,FIND(CHAR(1),SUBSTITUTE($A66,".",CHAR(1),LEN($A66)-LEN(SUBSTITUTE($A66,".",""))))+1,LEN($A66)))))</f>
         <v/>
@@ -33496,7 +34432,7 @@
       <c r="N66" s="36"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49"/>
+      <c r="A67" s="71"/>
       <c r="B67" s="37" t="str">
         <f aca="false">IF($A67="","",IF(ISERROR(FIND(".",$A67)),"",LOWER(MID($A67,FIND(CHAR(1),SUBSTITUTE($A67,".",CHAR(1),LEN($A67)-LEN(SUBSTITUTE($A67,".",""))))+1,LEN($A67)))))</f>
         <v/>
@@ -33536,7 +34472,7 @@
       <c r="N67" s="36"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49"/>
+      <c r="A68" s="71"/>
       <c r="B68" s="37" t="str">
         <f aca="false">IF($A68="","",IF(ISERROR(FIND(".",$A68)),"",LOWER(MID($A68,FIND(CHAR(1),SUBSTITUTE($A68,".",CHAR(1),LEN($A68)-LEN(SUBSTITUTE($A68,".",""))))+1,LEN($A68)))))</f>
         <v/>
@@ -33576,7 +34512,7 @@
       <c r="N68" s="36"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="49"/>
+      <c r="A69" s="71"/>
       <c r="B69" s="37" t="str">
         <f aca="false">IF($A69="","",IF(ISERROR(FIND(".",$A69)),"",LOWER(MID($A69,FIND(CHAR(1),SUBSTITUTE($A69,".",CHAR(1),LEN($A69)-LEN(SUBSTITUTE($A69,".",""))))+1,LEN($A69)))))</f>
         <v/>
@@ -33616,7 +34552,7 @@
       <c r="N69" s="36"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="49"/>
+      <c r="A70" s="71"/>
       <c r="B70" s="37" t="str">
         <f aca="false">IF($A70="","",IF(ISERROR(FIND(".",$A70)),"",LOWER(MID($A70,FIND(CHAR(1),SUBSTITUTE($A70,".",CHAR(1),LEN($A70)-LEN(SUBSTITUTE($A70,".",""))))+1,LEN($A70)))))</f>
         <v/>
@@ -33656,7 +34592,7 @@
       <c r="N70" s="36"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="49"/>
+      <c r="A71" s="71"/>
       <c r="B71" s="37" t="str">
         <f aca="false">IF($A71="","",IF(ISERROR(FIND(".",$A71)),"",LOWER(MID($A71,FIND(CHAR(1),SUBSTITUTE($A71,".",CHAR(1),LEN($A71)-LEN(SUBSTITUTE($A71,".",""))))+1,LEN($A71)))))</f>
         <v/>
@@ -33696,7 +34632,7 @@
       <c r="N71" s="36"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="49"/>
+      <c r="A72" s="71"/>
       <c r="B72" s="37" t="str">
         <f aca="false">IF($A72="","",IF(ISERROR(FIND(".",$A72)),"",LOWER(MID($A72,FIND(CHAR(1),SUBSTITUTE($A72,".",CHAR(1),LEN($A72)-LEN(SUBSTITUTE($A72,".",""))))+1,LEN($A72)))))</f>
         <v/>
@@ -33736,7 +34672,7 @@
       <c r="N72" s="36"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="49"/>
+      <c r="A73" s="71"/>
       <c r="B73" s="37" t="str">
         <f aca="false">IF($A73="","",IF(ISERROR(FIND(".",$A73)),"",LOWER(MID($A73,FIND(CHAR(1),SUBSTITUTE($A73,".",CHAR(1),LEN($A73)-LEN(SUBSTITUTE($A73,".",""))))+1,LEN($A73)))))</f>
         <v/>
@@ -33776,7 +34712,7 @@
       <c r="N73" s="36"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="49"/>
+      <c r="A74" s="71"/>
       <c r="B74" s="37" t="str">
         <f aca="false">IF($A74="","",IF(ISERROR(FIND(".",$A74)),"",LOWER(MID($A74,FIND(CHAR(1),SUBSTITUTE($A74,".",CHAR(1),LEN($A74)-LEN(SUBSTITUTE($A74,".",""))))+1,LEN($A74)))))</f>
         <v/>
@@ -33816,7 +34752,7 @@
       <c r="N74" s="36"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="49"/>
+      <c r="A75" s="71"/>
       <c r="B75" s="37" t="str">
         <f aca="false">IF($A75="","",IF(ISERROR(FIND(".",$A75)),"",LOWER(MID($A75,FIND(CHAR(1),SUBSTITUTE($A75,".",CHAR(1),LEN($A75)-LEN(SUBSTITUTE($A75,".",""))))+1,LEN($A75)))))</f>
         <v/>
@@ -33856,7 +34792,7 @@
       <c r="N75" s="36"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="49"/>
+      <c r="A76" s="71"/>
       <c r="B76" s="37" t="str">
         <f aca="false">IF($A76="","",IF(ISERROR(FIND(".",$A76)),"",LOWER(MID($A76,FIND(CHAR(1),SUBSTITUTE($A76,".",CHAR(1),LEN($A76)-LEN(SUBSTITUTE($A76,".",""))))+1,LEN($A76)))))</f>
         <v/>
@@ -33896,7 +34832,7 @@
       <c r="N76" s="36"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="49"/>
+      <c r="A77" s="71"/>
       <c r="B77" s="37" t="str">
         <f aca="false">IF($A77="","",IF(ISERROR(FIND(".",$A77)),"",LOWER(MID($A77,FIND(CHAR(1),SUBSTITUTE($A77,".",CHAR(1),LEN($A77)-LEN(SUBSTITUTE($A77,".",""))))+1,LEN($A77)))))</f>
         <v/>
@@ -33936,7 +34872,7 @@
       <c r="N77" s="36"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="49"/>
+      <c r="A78" s="71"/>
       <c r="B78" s="37" t="str">
         <f aca="false">IF($A78="","",IF(ISERROR(FIND(".",$A78)),"",LOWER(MID($A78,FIND(CHAR(1),SUBSTITUTE($A78,".",CHAR(1),LEN($A78)-LEN(SUBSTITUTE($A78,".",""))))+1,LEN($A78)))))</f>
         <v/>
@@ -33976,7 +34912,7 @@
       <c r="N78" s="36"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="49"/>
+      <c r="A79" s="71"/>
       <c r="B79" s="37" t="str">
         <f aca="false">IF($A79="","",IF(ISERROR(FIND(".",$A79)),"",LOWER(MID($A79,FIND(CHAR(1),SUBSTITUTE($A79,".",CHAR(1),LEN($A79)-LEN(SUBSTITUTE($A79,".",""))))+1,LEN($A79)))))</f>
         <v/>
@@ -34016,7 +34952,7 @@
       <c r="N79" s="36"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="49"/>
+      <c r="A80" s="71"/>
       <c r="B80" s="37" t="str">
         <f aca="false">IF($A80="","",IF(ISERROR(FIND(".",$A80)),"",LOWER(MID($A80,FIND(CHAR(1),SUBSTITUTE($A80,".",CHAR(1),LEN($A80)-LEN(SUBSTITUTE($A80,".",""))))+1,LEN($A80)))))</f>
         <v/>
@@ -34056,7 +34992,7 @@
       <c r="N80" s="36"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="49"/>
+      <c r="A81" s="71"/>
       <c r="B81" s="37" t="str">
         <f aca="false">IF($A81="","",IF(ISERROR(FIND(".",$A81)),"",LOWER(MID($A81,FIND(CHAR(1),SUBSTITUTE($A81,".",CHAR(1),LEN($A81)-LEN(SUBSTITUTE($A81,".",""))))+1,LEN($A81)))))</f>
         <v/>
@@ -34096,7 +35032,7 @@
       <c r="N81" s="36"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="49"/>
+      <c r="A82" s="71"/>
       <c r="B82" s="37" t="str">
         <f aca="false">IF($A82="","",IF(ISERROR(FIND(".",$A82)),"",LOWER(MID($A82,FIND(CHAR(1),SUBSTITUTE($A82,".",CHAR(1),LEN($A82)-LEN(SUBSTITUTE($A82,".",""))))+1,LEN($A82)))))</f>
         <v/>
@@ -34136,7 +35072,7 @@
       <c r="N82" s="36"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="49"/>
+      <c r="A83" s="71"/>
       <c r="B83" s="37" t="str">
         <f aca="false">IF($A83="","",IF(ISERROR(FIND(".",$A83)),"",LOWER(MID($A83,FIND(CHAR(1),SUBSTITUTE($A83,".",CHAR(1),LEN($A83)-LEN(SUBSTITUTE($A83,".",""))))+1,LEN($A83)))))</f>
         <v/>
@@ -34176,7 +35112,7 @@
       <c r="N83" s="36"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="49"/>
+      <c r="A84" s="71"/>
       <c r="B84" s="37" t="str">
         <f aca="false">IF($A84="","",IF(ISERROR(FIND(".",$A84)),"",LOWER(MID($A84,FIND(CHAR(1),SUBSTITUTE($A84,".",CHAR(1),LEN($A84)-LEN(SUBSTITUTE($A84,".",""))))+1,LEN($A84)))))</f>
         <v/>
@@ -34216,7 +35152,7 @@
       <c r="N84" s="36"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="49"/>
+      <c r="A85" s="71"/>
       <c r="B85" s="37" t="str">
         <f aca="false">IF($A85="","",IF(ISERROR(FIND(".",$A85)),"",LOWER(MID($A85,FIND(CHAR(1),SUBSTITUTE($A85,".",CHAR(1),LEN($A85)-LEN(SUBSTITUTE($A85,".",""))))+1,LEN($A85)))))</f>
         <v/>
@@ -34256,7 +35192,7 @@
       <c r="N85" s="36"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="49"/>
+      <c r="A86" s="71"/>
       <c r="B86" s="37" t="str">
         <f aca="false">IF($A86="","",IF(ISERROR(FIND(".",$A86)),"",LOWER(MID($A86,FIND(CHAR(1),SUBSTITUTE($A86,".",CHAR(1),LEN($A86)-LEN(SUBSTITUTE($A86,".",""))))+1,LEN($A86)))))</f>
         <v/>
@@ -34296,7 +35232,7 @@
       <c r="N86" s="36"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="49"/>
+      <c r="A87" s="71"/>
       <c r="B87" s="37" t="str">
         <f aca="false">IF($A87="","",IF(ISERROR(FIND(".",$A87)),"",LOWER(MID($A87,FIND(CHAR(1),SUBSTITUTE($A87,".",CHAR(1),LEN($A87)-LEN(SUBSTITUTE($A87,".",""))))+1,LEN($A87)))))</f>
         <v/>
@@ -34336,7 +35272,7 @@
       <c r="N87" s="36"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="49"/>
+      <c r="A88" s="71"/>
       <c r="B88" s="37" t="str">
         <f aca="false">IF($A88="","",IF(ISERROR(FIND(".",$A88)),"",LOWER(MID($A88,FIND(CHAR(1),SUBSTITUTE($A88,".",CHAR(1),LEN($A88)-LEN(SUBSTITUTE($A88,".",""))))+1,LEN($A88)))))</f>
         <v/>
@@ -34376,7 +35312,7 @@
       <c r="N88" s="36"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="49"/>
+      <c r="A89" s="71"/>
       <c r="B89" s="37" t="str">
         <f aca="false">IF($A89="","",IF(ISERROR(FIND(".",$A89)),"",LOWER(MID($A89,FIND(CHAR(1),SUBSTITUTE($A89,".",CHAR(1),LEN($A89)-LEN(SUBSTITUTE($A89,".",""))))+1,LEN($A89)))))</f>
         <v/>
@@ -34416,7 +35352,7 @@
       <c r="N89" s="36"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="49"/>
+      <c r="A90" s="71"/>
       <c r="B90" s="37" t="str">
         <f aca="false">IF($A90="","",IF(ISERROR(FIND(".",$A90)),"",LOWER(MID($A90,FIND(CHAR(1),SUBSTITUTE($A90,".",CHAR(1),LEN($A90)-LEN(SUBSTITUTE($A90,".",""))))+1,LEN($A90)))))</f>
         <v/>
@@ -34456,7 +35392,7 @@
       <c r="N90" s="36"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="49"/>
+      <c r="A91" s="71"/>
       <c r="B91" s="37" t="str">
         <f aca="false">IF($A91="","",IF(ISERROR(FIND(".",$A91)),"",LOWER(MID($A91,FIND(CHAR(1),SUBSTITUTE($A91,".",CHAR(1),LEN($A91)-LEN(SUBSTITUTE($A91,".",""))))+1,LEN($A91)))))</f>
         <v/>
@@ -34496,7 +35432,7 @@
       <c r="N91" s="36"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="49"/>
+      <c r="A92" s="71"/>
       <c r="B92" s="37" t="str">
         <f aca="false">IF($A92="","",IF(ISERROR(FIND(".",$A92)),"",LOWER(MID($A92,FIND(CHAR(1),SUBSTITUTE($A92,".",CHAR(1),LEN($A92)-LEN(SUBSTITUTE($A92,".",""))))+1,LEN($A92)))))</f>
         <v/>
@@ -34536,7 +35472,7 @@
       <c r="N92" s="36"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="49"/>
+      <c r="A93" s="71"/>
       <c r="B93" s="37" t="str">
         <f aca="false">IF($A93="","",IF(ISERROR(FIND(".",$A93)),"",LOWER(MID($A93,FIND(CHAR(1),SUBSTITUTE($A93,".",CHAR(1),LEN($A93)-LEN(SUBSTITUTE($A93,".",""))))+1,LEN($A93)))))</f>
         <v/>
@@ -34576,7 +35512,7 @@
       <c r="N93" s="36"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="49"/>
+      <c r="A94" s="71"/>
       <c r="B94" s="37" t="str">
         <f aca="false">IF($A94="","",IF(ISERROR(FIND(".",$A94)),"",LOWER(MID($A94,FIND(CHAR(1),SUBSTITUTE($A94,".",CHAR(1),LEN($A94)-LEN(SUBSTITUTE($A94,".",""))))+1,LEN($A94)))))</f>
         <v/>
@@ -34616,7 +35552,7 @@
       <c r="N94" s="36"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="49"/>
+      <c r="A95" s="71"/>
       <c r="B95" s="37" t="str">
         <f aca="false">IF($A95="","",IF(ISERROR(FIND(".",$A95)),"",LOWER(MID($A95,FIND(CHAR(1),SUBSTITUTE($A95,".",CHAR(1),LEN($A95)-LEN(SUBSTITUTE($A95,".",""))))+1,LEN($A95)))))</f>
         <v/>
@@ -34656,7 +35592,7 @@
       <c r="N95" s="36"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="49"/>
+      <c r="A96" s="71"/>
       <c r="B96" s="37" t="str">
         <f aca="false">IF($A96="","",IF(ISERROR(FIND(".",$A96)),"",LOWER(MID($A96,FIND(CHAR(1),SUBSTITUTE($A96,".",CHAR(1),LEN($A96)-LEN(SUBSTITUTE($A96,".",""))))+1,LEN($A96)))))</f>
         <v/>
@@ -34696,7 +35632,7 @@
       <c r="N96" s="36"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="49"/>
+      <c r="A97" s="71"/>
       <c r="B97" s="37" t="str">
         <f aca="false">IF($A97="","",IF(ISERROR(FIND(".",$A97)),"",LOWER(MID($A97,FIND(CHAR(1),SUBSTITUTE($A97,".",CHAR(1),LEN($A97)-LEN(SUBSTITUTE($A97,".",""))))+1,LEN($A97)))))</f>
         <v/>
@@ -34736,7 +35672,7 @@
       <c r="N97" s="36"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="49"/>
+      <c r="A98" s="71"/>
       <c r="B98" s="37" t="str">
         <f aca="false">IF($A98="","",IF(ISERROR(FIND(".",$A98)),"",LOWER(MID($A98,FIND(CHAR(1),SUBSTITUTE($A98,".",CHAR(1),LEN($A98)-LEN(SUBSTITUTE($A98,".",""))))+1,LEN($A98)))))</f>
         <v/>
@@ -34776,7 +35712,7 @@
       <c r="N98" s="36"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="49"/>
+      <c r="A99" s="71"/>
       <c r="B99" s="37" t="str">
         <f aca="false">IF($A99="","",IF(ISERROR(FIND(".",$A99)),"",LOWER(MID($A99,FIND(CHAR(1),SUBSTITUTE($A99,".",CHAR(1),LEN($A99)-LEN(SUBSTITUTE($A99,".",""))))+1,LEN($A99)))))</f>
         <v/>
@@ -34816,7 +35752,7 @@
       <c r="N99" s="36"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="49"/>
+      <c r="A100" s="71"/>
       <c r="B100" s="37" t="str">
         <f aca="false">IF($A100="","",IF(ISERROR(FIND(".",$A100)),"",LOWER(MID($A100,FIND(CHAR(1),SUBSTITUTE($A100,".",CHAR(1),LEN($A100)-LEN(SUBSTITUTE($A100,".",""))))+1,LEN($A100)))))</f>
         <v/>
@@ -34856,7 +35792,7 @@
       <c r="N100" s="36"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="49"/>
+      <c r="A101" s="71"/>
       <c r="B101" s="37" t="str">
         <f aca="false">IF($A101="","",IF(ISERROR(FIND(".",$A101)),"",LOWER(MID($A101,FIND(CHAR(1),SUBSTITUTE($A101,".",CHAR(1),LEN($A101)-LEN(SUBSTITUTE($A101,".",""))))+1,LEN($A101)))))</f>
         <v/>
@@ -34896,7 +35832,7 @@
       <c r="N101" s="36"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="49"/>
+      <c r="A102" s="71"/>
       <c r="B102" s="37" t="str">
         <f aca="false">IF($A102="","",IF(ISERROR(FIND(".",$A102)),"",LOWER(MID($A102,FIND(CHAR(1),SUBSTITUTE($A102,".",CHAR(1),LEN($A102)-LEN(SUBSTITUTE($A102,".",""))))+1,LEN($A102)))))</f>
         <v/>
@@ -34936,7 +35872,7 @@
       <c r="N102" s="36"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="49"/>
+      <c r="A103" s="71"/>
       <c r="B103" s="37" t="str">
         <f aca="false">IF($A103="","",IF(ISERROR(FIND(".",$A103)),"",LOWER(MID($A103,FIND(CHAR(1),SUBSTITUTE($A103,".",CHAR(1),LEN($A103)-LEN(SUBSTITUTE($A103,".",""))))+1,LEN($A103)))))</f>
         <v/>
@@ -34976,7 +35912,7 @@
       <c r="N103" s="36"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="49"/>
+      <c r="A104" s="71"/>
       <c r="B104" s="37" t="str">
         <f aca="false">IF($A104="","",IF(ISERROR(FIND(".",$A104)),"",LOWER(MID($A104,FIND(CHAR(1),SUBSTITUTE($A104,".",CHAR(1),LEN($A104)-LEN(SUBSTITUTE($A104,".",""))))+1,LEN($A104)))))</f>
         <v/>
@@ -35053,7 +35989,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>559</v>
+        <v>637</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -35068,56 +36004,56 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>560</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>561</v>
+        <v>639</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>562</v>
+        <v>640</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>563</v>
+        <v>641</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>564</v>
+        <v>642</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>565</v>
+        <v>643</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>566</v>
+        <v>644</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>567</v>
+        <v>645</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>553</v>
+        <v>631</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>568</v>
+        <v>646</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>569</v>
+        <v>647</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="68" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="70" t="n">
+      <c r="B5" s="69" t="n">
         <v>46162</v>
       </c>
-      <c r="C5" s="66" t="n">
+      <c r="C5" s="65" t="n">
         <v>11500</v>
       </c>
-      <c r="D5" s="65" t="s">
-        <v>570</v>
+      <c r="D5" s="64" t="s">
+        <v>648</v>
       </c>
       <c r="E5" s="74" t="n">
         <v>0.2</v>
@@ -35130,7 +36066,7 @@
         <f aca="false">IF($F5="","",$C5-$F5)</f>
         <v>9200</v>
       </c>
-      <c r="H5" s="66" t="n">
+      <c r="H5" s="65" t="n">
         <v>2433</v>
       </c>
       <c r="I5" s="33" t="n">
@@ -35141,12 +36077,12 @@
         <f aca="false">IF(OR($I5="",$H5="",$H5=0),"",$I5/$H5)</f>
         <v>2.78133990957665</v>
       </c>
-      <c r="K5" s="68" t="s">
-        <v>558</v>
+      <c r="K5" s="67" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49"/>
+      <c r="A6" s="71"/>
       <c r="B6" s="72"/>
       <c r="C6" s="28"/>
       <c r="D6" s="26"/>
@@ -35174,7 +36110,7 @@
       <c r="K6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="72"/>
       <c r="C7" s="28"/>
       <c r="D7" s="26"/>
@@ -35202,7 +36138,7 @@
       <c r="K7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49"/>
+      <c r="A8" s="71"/>
       <c r="B8" s="72"/>
       <c r="C8" s="28"/>
       <c r="D8" s="26"/>
@@ -35230,7 +36166,7 @@
       <c r="K8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49"/>
+      <c r="A9" s="71"/>
       <c r="B9" s="72"/>
       <c r="C9" s="28"/>
       <c r="D9" s="26"/>
@@ -35258,7 +36194,7 @@
       <c r="K9" s="36"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49"/>
+      <c r="A10" s="71"/>
       <c r="B10" s="72"/>
       <c r="C10" s="28"/>
       <c r="D10" s="26"/>
@@ -35286,7 +36222,7 @@
       <c r="K10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49"/>
+      <c r="A11" s="71"/>
       <c r="B11" s="72"/>
       <c r="C11" s="28"/>
       <c r="D11" s="26"/>
@@ -35314,7 +36250,7 @@
       <c r="K11" s="36"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="72"/>
       <c r="C12" s="28"/>
       <c r="D12" s="26"/>
@@ -35342,7 +36278,7 @@
       <c r="K12" s="36"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49"/>
+      <c r="A13" s="71"/>
       <c r="B13" s="72"/>
       <c r="C13" s="28"/>
       <c r="D13" s="26"/>
@@ -35370,7 +36306,7 @@
       <c r="K13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49"/>
+      <c r="A14" s="71"/>
       <c r="B14" s="72"/>
       <c r="C14" s="28"/>
       <c r="D14" s="26"/>
@@ -35398,7 +36334,7 @@
       <c r="K14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="72"/>
       <c r="C15" s="28"/>
       <c r="D15" s="26"/>
@@ -35426,7 +36362,7 @@
       <c r="K15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49"/>
+      <c r="A16" s="71"/>
       <c r="B16" s="72"/>
       <c r="C16" s="28"/>
       <c r="D16" s="26"/>
@@ -35454,7 +36390,7 @@
       <c r="K16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49"/>
+      <c r="A17" s="71"/>
       <c r="B17" s="72"/>
       <c r="C17" s="28"/>
       <c r="D17" s="26"/>
@@ -35482,7 +36418,7 @@
       <c r="K17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="72"/>
       <c r="C18" s="28"/>
       <c r="D18" s="26"/>
@@ -35510,7 +36446,7 @@
       <c r="K18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49"/>
+      <c r="A19" s="71"/>
       <c r="B19" s="72"/>
       <c r="C19" s="28"/>
       <c r="D19" s="26"/>
@@ -35538,7 +36474,7 @@
       <c r="K19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49"/>
+      <c r="A20" s="71"/>
       <c r="B20" s="72"/>
       <c r="C20" s="28"/>
       <c r="D20" s="26"/>
@@ -35566,7 +36502,7 @@
       <c r="K20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="72"/>
       <c r="C21" s="28"/>
       <c r="D21" s="26"/>
@@ -35594,7 +36530,7 @@
       <c r="K21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49"/>
+      <c r="A22" s="71"/>
       <c r="B22" s="72"/>
       <c r="C22" s="28"/>
       <c r="D22" s="26"/>
@@ -35622,7 +36558,7 @@
       <c r="K22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49"/>
+      <c r="A23" s="71"/>
       <c r="B23" s="72"/>
       <c r="C23" s="28"/>
       <c r="D23" s="26"/>
@@ -35650,7 +36586,7 @@
       <c r="K23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49"/>
+      <c r="A24" s="71"/>
       <c r="B24" s="72"/>
       <c r="C24" s="28"/>
       <c r="D24" s="26"/>
@@ -35678,7 +36614,7 @@
       <c r="K24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49"/>
+      <c r="A25" s="71"/>
       <c r="B25" s="72"/>
       <c r="C25" s="28"/>
       <c r="D25" s="26"/>
@@ -35706,7 +36642,7 @@
       <c r="K25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49"/>
+      <c r="A26" s="71"/>
       <c r="B26" s="72"/>
       <c r="C26" s="28"/>
       <c r="D26" s="26"/>
@@ -35734,7 +36670,7 @@
       <c r="K26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49"/>
+      <c r="A27" s="71"/>
       <c r="B27" s="72"/>
       <c r="C27" s="28"/>
       <c r="D27" s="26"/>
@@ -35762,7 +36698,7 @@
       <c r="K27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49"/>
+      <c r="A28" s="71"/>
       <c r="B28" s="72"/>
       <c r="C28" s="28"/>
       <c r="D28" s="26"/>
@@ -35790,7 +36726,7 @@
       <c r="K28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49"/>
+      <c r="A29" s="71"/>
       <c r="B29" s="72"/>
       <c r="C29" s="28"/>
       <c r="D29" s="26"/>
@@ -35818,7 +36754,7 @@
       <c r="K29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49"/>
+      <c r="A30" s="71"/>
       <c r="B30" s="72"/>
       <c r="C30" s="28"/>
       <c r="D30" s="26"/>
@@ -35846,7 +36782,7 @@
       <c r="K30" s="36"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49"/>
+      <c r="A31" s="71"/>
       <c r="B31" s="72"/>
       <c r="C31" s="28"/>
       <c r="D31" s="26"/>
@@ -35874,7 +36810,7 @@
       <c r="K31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49"/>
+      <c r="A32" s="71"/>
       <c r="B32" s="72"/>
       <c r="C32" s="28"/>
       <c r="D32" s="26"/>
@@ -35902,7 +36838,7 @@
       <c r="K32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49"/>
+      <c r="A33" s="71"/>
       <c r="B33" s="72"/>
       <c r="C33" s="28"/>
       <c r="D33" s="26"/>
@@ -35930,7 +36866,7 @@
       <c r="K33" s="36"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49"/>
+      <c r="A34" s="71"/>
       <c r="B34" s="72"/>
       <c r="C34" s="28"/>
       <c r="D34" s="26"/>
@@ -35958,7 +36894,7 @@
       <c r="K34" s="36"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49"/>
+      <c r="A35" s="71"/>
       <c r="B35" s="72"/>
       <c r="C35" s="28"/>
       <c r="D35" s="26"/>
@@ -35986,7 +36922,7 @@
       <c r="K35" s="36"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="49"/>
+      <c r="A36" s="71"/>
       <c r="B36" s="72"/>
       <c r="C36" s="28"/>
       <c r="D36" s="26"/>
@@ -36014,7 +36950,7 @@
       <c r="K36" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="49"/>
+      <c r="A37" s="71"/>
       <c r="B37" s="72"/>
       <c r="C37" s="28"/>
       <c r="D37" s="26"/>
@@ -36042,7 +36978,7 @@
       <c r="K37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="49"/>
+      <c r="A38" s="71"/>
       <c r="B38" s="72"/>
       <c r="C38" s="28"/>
       <c r="D38" s="26"/>
@@ -36070,7 +37006,7 @@
       <c r="K38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49"/>
+      <c r="A39" s="71"/>
       <c r="B39" s="72"/>
       <c r="C39" s="28"/>
       <c r="D39" s="26"/>
@@ -36098,7 +37034,7 @@
       <c r="K39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49"/>
+      <c r="A40" s="71"/>
       <c r="B40" s="72"/>
       <c r="C40" s="28"/>
       <c r="D40" s="26"/>
@@ -36126,7 +37062,7 @@
       <c r="K40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="49"/>
+      <c r="A41" s="71"/>
       <c r="B41" s="72"/>
       <c r="C41" s="28"/>
       <c r="D41" s="26"/>
@@ -36154,7 +37090,7 @@
       <c r="K41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="49"/>
+      <c r="A42" s="71"/>
       <c r="B42" s="72"/>
       <c r="C42" s="28"/>
       <c r="D42" s="26"/>
@@ -36182,7 +37118,7 @@
       <c r="K42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="49"/>
+      <c r="A43" s="71"/>
       <c r="B43" s="72"/>
       <c r="C43" s="28"/>
       <c r="D43" s="26"/>
@@ -36210,7 +37146,7 @@
       <c r="K43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="49"/>
+      <c r="A44" s="71"/>
       <c r="B44" s="72"/>
       <c r="C44" s="28"/>
       <c r="D44" s="26"/>
@@ -36238,7 +37174,7 @@
       <c r="K44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49"/>
+      <c r="A45" s="71"/>
       <c r="B45" s="72"/>
       <c r="C45" s="28"/>
       <c r="D45" s="26"/>
@@ -36266,7 +37202,7 @@
       <c r="K45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49"/>
+      <c r="A46" s="71"/>
       <c r="B46" s="72"/>
       <c r="C46" s="28"/>
       <c r="D46" s="26"/>
@@ -36294,7 +37230,7 @@
       <c r="K46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="49"/>
+      <c r="A47" s="71"/>
       <c r="B47" s="72"/>
       <c r="C47" s="28"/>
       <c r="D47" s="26"/>
@@ -36322,7 +37258,7 @@
       <c r="K47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="49"/>
+      <c r="A48" s="71"/>
       <c r="B48" s="72"/>
       <c r="C48" s="28"/>
       <c r="D48" s="26"/>
@@ -36350,7 +37286,7 @@
       <c r="K48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="49"/>
+      <c r="A49" s="71"/>
       <c r="B49" s="72"/>
       <c r="C49" s="28"/>
       <c r="D49" s="26"/>
@@ -36378,7 +37314,7 @@
       <c r="K49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="49"/>
+      <c r="A50" s="71"/>
       <c r="B50" s="72"/>
       <c r="C50" s="28"/>
       <c r="D50" s="26"/>
@@ -36406,7 +37342,7 @@
       <c r="K50" s="36"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49"/>
+      <c r="A51" s="71"/>
       <c r="B51" s="72"/>
       <c r="C51" s="28"/>
       <c r="D51" s="26"/>
@@ -36434,7 +37370,7 @@
       <c r="K51" s="36"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49"/>
+      <c r="A52" s="71"/>
       <c r="B52" s="72"/>
       <c r="C52" s="28"/>
       <c r="D52" s="26"/>
@@ -36462,7 +37398,7 @@
       <c r="K52" s="36"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="49"/>
+      <c r="A53" s="71"/>
       <c r="B53" s="72"/>
       <c r="C53" s="28"/>
       <c r="D53" s="26"/>
@@ -36490,7 +37426,7 @@
       <c r="K53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="49"/>
+      <c r="A54" s="71"/>
       <c r="B54" s="72"/>
       <c r="C54" s="28"/>
       <c r="D54" s="26"/>
@@ -36547,258 +37483,258 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>571</v>
+        <v>649</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="51" t="s">
-        <v>572</v>
-      </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
+      <c r="A3" s="50" t="s">
+        <v>650</v>
+      </c>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>573</v>
+        <v>651</v>
       </c>
       <c r="B4" s="76" t="n">
         <f aca="false">COUNTIF(Portfolio!$C$5:$C$104,"Active")</f>
         <v>1</v>
       </c>
       <c r="D4" s="77" t="s">
-        <v>574</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>575</v>
+        <v>653</v>
       </c>
       <c r="B5" s="78" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$E$5:$E$104)</f>
         <v>2400</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>576</v>
+        <v>654</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>577</v>
+        <v>655</v>
       </c>
       <c r="B6" s="78" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$I$5:$I$104)</f>
         <v>22</v>
       </c>
       <c r="D6" s="77" t="s">
-        <v>578</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>579</v>
+        <v>657</v>
       </c>
       <c r="B7" s="78" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$J$5:$J$104)</f>
         <v>2422</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>580</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>581</v>
+        <v>659</v>
       </c>
       <c r="B8" s="78" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$F$5:$F$104)</f>
         <v>11</v>
       </c>
       <c r="D8" s="77" t="s">
-        <v>582</v>
+        <v>660</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="s">
-        <v>583</v>
-      </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
+      <c r="A10" s="50" t="s">
+        <v>661</v>
+      </c>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>584</v>
+        <v>662</v>
       </c>
       <c r="B11" s="76" t="n">
         <f aca="false">COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;")</f>
         <v>1</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>585</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>586</v>
+        <v>664</v>
       </c>
       <c r="B12" s="78" t="n">
         <f aca="false">SUM('Sales Log'!$C$5:$C$54)</f>
         <v>11500</v>
       </c>
       <c r="D12" s="77" t="s">
-        <v>587</v>
+        <v>665</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>588</v>
+        <v>666</v>
       </c>
       <c r="B13" s="78" t="n">
         <f aca="false">SUM('Sales Log'!$G$5:$G$54)</f>
         <v>9200</v>
       </c>
       <c r="D13" s="77" t="s">
-        <v>589</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>590</v>
+        <v>668</v>
       </c>
       <c r="B14" s="78" t="n">
         <f aca="false">SUM('Sales Log'!$I$5:$I$54)</f>
         <v>6767</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>591</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>592</v>
+        <v>670</v>
       </c>
       <c r="B15" s="79" t="n">
         <f aca="false">IF($B$8=0,"n/a",SUM('Sales Log'!$I$5:$I$54)/$B$8)</f>
         <v>615.181818181818</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>593</v>
+        <v>671</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="s">
-        <v>594</v>
-      </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
+      <c r="A17" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>595</v>
+        <v>673</v>
       </c>
       <c r="B18" s="80" t="n">
         <f aca="false">IF(($B$4+COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;"))=0,"n/a",COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;")/($B$4+COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;")))</f>
         <v>0.5</v>
       </c>
       <c r="D18" s="77" t="s">
-        <v>596</v>
+        <v>674</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>597</v>
+        <v>675</v>
       </c>
       <c r="B19" s="80" t="n">
         <f aca="false">Assumptions!$B$6</f>
         <v>0.02</v>
       </c>
       <c r="D19" s="77" t="s">
-        <v>598</v>
+        <v>676</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>599</v>
+        <v>677</v>
       </c>
       <c r="B20" s="81" t="n">
         <f aca="false">$B$4*Assumptions!$B$6</f>
         <v>0.02</v>
       </c>
       <c r="D20" s="77" t="s">
-        <v>600</v>
+        <v>678</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="s">
-        <v>601</v>
-      </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
+      <c r="A22" s="50" t="s">
+        <v>679</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>602</v>
+        <v>680</v>
       </c>
       <c r="B23" s="76" t="n">
         <f aca="false">COUNTIF(Candidates!$A$5:$A$204,"&lt;&gt;")</f>
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="D23" s="77" t="s">
-        <v>603</v>
+        <v>681</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>604</v>
+        <v>682</v>
       </c>
       <c r="B24" s="76" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"BUY")</f>
         <v>0</v>
       </c>
       <c r="D24" s="77" t="s">
-        <v>605</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>606</v>
+        <v>684</v>
       </c>
       <c r="B25" s="76" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"MARGINAL")</f>
         <v>0</v>
       </c>
       <c r="D25" s="77" t="s">
-        <v>607</v>
+        <v>685</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>608</v>
+        <v>686</v>
       </c>
       <c r="B26" s="76" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"NEEDS VALUATION")+COUNTIF(Candidates!$V$5:$V$204,"NEEDS PRICE")</f>
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="D26" s="77" t="s">
-        <v>609</v>
+        <v>687</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>610</v>
+        <v>688</v>
       </c>
       <c r="B27" s="76" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"PASS")+COUNTIF(Candidates!$V$5:$V$204,"REJECT")</f>
         <v>10</v>
       </c>
       <c r="D27" s="77" t="s">
-        <v>611</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -36832,7 +37768,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>612</v>
+        <v>690</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -36841,323 +37777,323 @@
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="82" t="s">
-        <v>613</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>614</v>
+        <v>692</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>615</v>
+        <v>693</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>616</v>
+        <v>694</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>617</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>618</v>
+        <v>696</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>619</v>
+        <v>697</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>621</v>
+        <v>699</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>623</v>
+        <v>701</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>624</v>
+        <v>702</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>625</v>
+        <v>703</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>626</v>
+        <v>704</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>627</v>
+        <v>705</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>628</v>
+        <v>706</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>629</v>
+        <v>707</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>630</v>
+        <v>708</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>631</v>
+        <v>709</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>632</v>
+        <v>710</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>633</v>
+        <v>711</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>634</v>
+        <v>712</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>635</v>
+        <v>713</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>636</v>
+        <v>714</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="19" t="s">
-        <v>637</v>
+        <v>715</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>638</v>
+        <v>716</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>639</v>
+        <v>717</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>640</v>
+        <v>718</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>641</v>
+        <v>719</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>642</v>
+        <v>720</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>643</v>
+        <v>721</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>644</v>
+        <v>722</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>642</v>
+        <v>720</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>645</v>
+        <v>723</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>646</v>
+        <v>724</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>647</v>
+        <v>725</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>622</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>648</v>
+        <v>726</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>649</v>
+        <v>727</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>650</v>
+        <v>728</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>633</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>651</v>
+        <v>729</v>
       </c>
       <c r="B16" s="41" t="s">
-        <v>652</v>
+        <v>730</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>631</v>
+        <v>709</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>653</v>
+        <v>731</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>633</v>
+        <v>711</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>654</v>
+        <v>732</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>655</v>
+        <v>733</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>656</v>
+        <v>734</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>657</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>658</v>
+        <v>736</v>
       </c>
       <c r="B18" s="41" t="s">
-        <v>659</v>
+        <v>737</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>660</v>
+        <v>738</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>661</v>
+        <v>739</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>662</v>
+        <v>740</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>663</v>
+        <v>741</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>664</v>
+        <v>742</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>665</v>
+        <v>743</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>666</v>
+        <v>744</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>667</v>
+        <v>745</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>668</v>
+        <v>746</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>669</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>670</v>
+        <v>748</v>
       </c>
       <c r="B21" s="41" t="s">
-        <v>671</v>
+        <v>749</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>672</v>
+        <v>750</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>669</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>673</v>
+        <v>751</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>674</v>
+        <v>752</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>620</v>
+        <v>698</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>675</v>
+        <v>753</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>676</v>
+        <v>754</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="53" t="s">
-        <v>677</v>
+      <c r="A24" s="52" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="83" t="s">
-        <v>678</v>
+        <v>756</v>
       </c>
       <c r="B25" s="83"/>
       <c r="C25" s="83"/>
@@ -37166,7 +38102,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="83" t="s">
-        <v>679</v>
+        <v>757</v>
       </c>
       <c r="B26" s="83"/>
       <c r="C26" s="83"/>
@@ -37175,7 +38111,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="83" t="s">
-        <v>680</v>
+        <v>758</v>
       </c>
       <c r="B27" s="83"/>
       <c r="C27" s="83"/>
@@ -37184,7 +38120,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="83" t="s">
-        <v>681</v>
+        <v>759</v>
       </c>
       <c r="B28" s="83"/>
       <c r="C28" s="83"/>
@@ -37193,7 +38129,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="83" t="s">
-        <v>682</v>
+        <v>760</v>
       </c>
       <c r="B29" s="83"/>
       <c r="C29" s="83"/>

--- a/domain-investing/domain-portfolio-tracker.xlsx
+++ b/domain-investing/domain-portfolio-tracker.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Sales Log" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Dashboard" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Comps" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Market Frequency" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">Candidates!$A$4:$X$204</definedName>
@@ -30,6 +31,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cumulative: the share of all .com sales that close at or above this band's floor. Computed from the band shares, so it stays correct if you edit them.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -183,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="855">
   <si>
     <t xml:space="preserve">Domain Investing — Rubric &amp; Portfolio Tracker</t>
   </si>
@@ -2466,13 +2489,295 @@
   </si>
   <si>
     <t xml:space="preserve">Monefy, domain investing profitability analysis — https://www.monefy.com/article/domain-investing-profitability-data-backed-answer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market Frequency — how often domains actually sell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VOLUME — how much moves, and how fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported sales, all TLDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 full year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industry reporting — $314.7m total, +31% transactions YoY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported dollar volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same. Average transaction about $1,655.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NameBio-listed sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NamePros analysis of NameBio — roughly $146m dollar volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied sales per day ($100+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1 2026 average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128,300 over ~183 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-day sample, $100+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 April 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,468,306 volume, $2,104 average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-day sample, under $100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same day. Most activity is below the reporting threshold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.com sales analysed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan 2024 - May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28-month .com dataset (bishopi.io)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied .com sales per year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derived</t>
+  </si>
+  <si>
+    <t xml:space="preserve">480,667 over 28 months, annualised. DERIVED, not reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total .com registered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 45% of all domains globally</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual turnover of the whole .com base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of all registered .com that change hands in the aftermarket each year. Do NOT confuse this with the sell-through rate on the Assumptions tab: that one is per LISTED name, this one is per REGISTERED name. Different denominators.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRICE DISTRIBUTION — 480,667 .com sales, Jan 2024 to May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of all sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median in band</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of sales AT OR ABOVE this band's floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under $100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$100 - $999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,000 - $9,999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$10,000 - $99,999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$100,000 and above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six-figure sales, count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the whole 28-month window — about 85 a year worldwide, across every .com. Four hundredths of one percent of transactions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median sale price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported .com median. Sedo's all-TLD median is lower at $549, against a $2,345 average — the gap between median and average is the whole story: a few large sales drag the mean up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: the 'Under $100' share is DERIVED (87% under $1,000 minus the 56.5% in the $100-999 band), not directly reported.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALIBRATOR — what percentile does your break-even sit at?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter a break-even resale price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy a figure from the BREAK-EVEN RESALE column on the Candidates tab. At $22.99 acquisition these run about $650-$1,050.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Band it falls in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Band index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Band floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next band floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of sales clearing band floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of sales clearing next floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of .com sales that clear it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-interpolated between the two band floors above, so treat it as approximate. It answers the question that matters: if this name does sell, how likely is the price to clear break-even?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roughly one sale in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same number, inverted — easier to hold in your head.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHAT THIS MEANS FOR THE MODEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87% of .com sales close under $1,000. A typical break-even on a $22.99 registration is around $700-$900, which sits near the 78th-80th percentile. So the name does not just have to sell — it has to sell for an ABOVE-MEDIAN price. Two independent things have to go right.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The median .com sale is $818 and the median across all TLDs at Sedo is $549. If your mental model of a 'normal' sale is four or five figures, it is wrong by an order of magnitude — that is the same mistake that put $1,800 on brewingfinancing.com.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Six-figure sales run about 85 a year worldwide. Any strategy whose returns depend on one is not a strategy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About 700 sales a day clear $100, and roughly three times that number close below it. The market is genuinely liquid at the bottom and extremely thin at the top.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aftermarket turnover is under a tenth of a percent of registered .com per year. The 2% on the Assumptions tab is per name LISTED FOR SALE, which is a much smaller and more self-selected pool. Both numbers are real; they answer different questions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHERE TO GET THIS YOURSELF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What it gives you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NameBio — namebio.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free search; paid export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The core dataset: 6.8m+ recorded sales. Search by keyword, TLD, price and date. Its /trends page carries volume charts. Paid tier unlocks bulk export and full history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NameBio Trends — namebio.com/trends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aggregate volume and average-price charts. The fastest read on whether the market is moving.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNJournal — dnjournal.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly top-sales chart and a YTD top-100. High end only, so useful for ceilings, useless for the median.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NamePros analysis threads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ad hoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Members publish periodic NameBio breakdowns — the source of the H1 2026 volume figures here. Search the forum for 'NameBio analysis'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sedo annual/quarterly report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median and average by TLD across ~350 extensions. The best source for medians rather than headlines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afternic / GoDaddy sales feeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported sales flow into NameBio anyway, but the marketplaces publish their own summaries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpiredDomains.net</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free registration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not sales — supply. Shows what is dropping and what is in closeout, which is the input to the Closeout Screener tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HumbleWorth — humbleworth.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free; bulk + API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automated valuations, three estimates per name. An estimate rather than evidence, but it beats an unsourced guess, and the bulk tool fills the Est. Resale Value column fast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figures gathered 2026-08-04. Volume and distribution move slowly, but re-check before leaning on them.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -2480,12 +2785,15 @@
     <numFmt numFmtId="168" formatCode="0.0\x"/>
     <numFmt numFmtId="169" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="170" formatCode="0.00\x"/>
-    <numFmt numFmtId="171" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="173" formatCode="0"/>
-    <numFmt numFmtId="174" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="171" formatCode="0"/>
+    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="173" formatCode="#,##0"/>
+    <numFmt numFmtId="174" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
+    <numFmt numFmtId="175" formatCode="0.000%"/>
+    <numFmt numFmtId="176" formatCode="0.00%"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2646,6 +2954,21 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFAAAAAA"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -2741,7 +3064,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="106">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2930,14 +3253,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2974,7 +3289,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3018,11 +3333,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3030,11 +3345,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3046,7 +3361,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3075,6 +3390,102 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="177" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3148,7 +3559,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -3588,6 +3999,638 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>761</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="83" t="s">
+        <v>762</v>
+      </c>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="85" t="s">
+        <v>763</v>
+      </c>
+      <c r="B4" s="85" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="85" t="s">
+        <v>764</v>
+      </c>
+      <c r="D4" s="85" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="86" t="s">
+        <v>765</v>
+      </c>
+      <c r="B5" s="87" t="n">
+        <v>190109</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>766</v>
+      </c>
+      <c r="D5" s="88" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="86" t="s">
+        <v>768</v>
+      </c>
+      <c r="B6" s="89" t="n">
+        <v>314700000</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>766</v>
+      </c>
+      <c r="D6" s="88" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="86" t="s">
+        <v>770</v>
+      </c>
+      <c r="B7" s="87" t="n">
+        <v>128300</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>771</v>
+      </c>
+      <c r="D7" s="88" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="86" t="s">
+        <v>773</v>
+      </c>
+      <c r="B8" s="87" t="n">
+        <v>700</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>774</v>
+      </c>
+      <c r="D8" s="88" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="B9" s="87" t="n">
+        <v>698</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>777</v>
+      </c>
+      <c r="D9" s="88" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="B10" s="87" t="n">
+        <v>2262</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>777</v>
+      </c>
+      <c r="D10" s="88" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="86" t="s">
+        <v>781</v>
+      </c>
+      <c r="B11" s="87" t="n">
+        <v>480667</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>782</v>
+      </c>
+      <c r="D11" s="88" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="86" t="s">
+        <v>784</v>
+      </c>
+      <c r="B12" s="87" t="n">
+        <v>206000</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>785</v>
+      </c>
+      <c r="D12" s="88" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="86" t="s">
+        <v>787</v>
+      </c>
+      <c r="B13" s="89" t="n">
+        <v>303700000</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>698</v>
+      </c>
+      <c r="D13" s="88" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="90" t="s">
+        <v>789</v>
+      </c>
+      <c r="B14" s="91" t="n">
+        <f aca="false">B12/B13</f>
+        <v>0.000678300954889694</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>785</v>
+      </c>
+      <c r="D14" s="88" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="83" t="s">
+        <v>791</v>
+      </c>
+      <c r="B16" s="84"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>793</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>794</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="86" t="s">
+        <v>796</v>
+      </c>
+      <c r="B18" s="92" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="C18" s="93"/>
+      <c r="D18" s="94" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="E18" s="95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="86" t="s">
+        <v>797</v>
+      </c>
+      <c r="B19" s="92" t="n">
+        <v>0.565</v>
+      </c>
+      <c r="C19" s="93" t="n">
+        <v>255</v>
+      </c>
+      <c r="D19" s="94" t="n">
+        <f aca="false">1-SUM($B$18:$B$18)</f>
+        <v>0.695</v>
+      </c>
+      <c r="E19" s="95" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="86" t="s">
+        <v>798</v>
+      </c>
+      <c r="B20" s="92" t="n">
+        <v>0.1236</v>
+      </c>
+      <c r="C20" s="93"/>
+      <c r="D20" s="94" t="n">
+        <f aca="false">1-SUM($B$18:$B$19)</f>
+        <v>0.13</v>
+      </c>
+      <c r="E20" s="95" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="86" t="s">
+        <v>799</v>
+      </c>
+      <c r="B21" s="92" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C21" s="93"/>
+      <c r="D21" s="94" t="n">
+        <f aca="false">1-SUM($B$18:$B$20)</f>
+        <v>0.00640000000000007</v>
+      </c>
+      <c r="E21" s="95" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="86" t="s">
+        <v>800</v>
+      </c>
+      <c r="B22" s="92" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="C22" s="93"/>
+      <c r="D22" s="94" t="n">
+        <f aca="false">1-SUM($B$18:$B$21)</f>
+        <v>0.000400000000000067</v>
+      </c>
+      <c r="E22" s="95" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="90" t="s">
+        <v>801</v>
+      </c>
+      <c r="B23" s="87" t="n">
+        <v>198</v>
+      </c>
+      <c r="D23" s="88" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="90" t="s">
+        <v>803</v>
+      </c>
+      <c r="B24" s="89" t="n">
+        <v>818</v>
+      </c>
+      <c r="D24" s="88" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="96" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="83" t="s">
+        <v>806</v>
+      </c>
+      <c r="B27" s="84"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="86" t="s">
+        <v>807</v>
+      </c>
+      <c r="B28" s="97" t="n">
+        <v>700</v>
+      </c>
+      <c r="D28" s="88" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="86" t="s">
+        <v>809</v>
+      </c>
+      <c r="B29" s="98" t="str">
+        <f aca="false">INDEX($A$18:$A$22,MATCH($B$28,$E$18:$E$22,1))</f>
+        <v>$100 - $999</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="86" t="s">
+        <v>810</v>
+      </c>
+      <c r="B30" s="56" t="n">
+        <f aca="false">MATCH($B$28,$E$18:$E$22,1)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="86" t="s">
+        <v>811</v>
+      </c>
+      <c r="B31" s="99" t="n">
+        <f aca="false">MAX(1,INDEX($E$18:$E$22,$B$30))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="86" t="s">
+        <v>812</v>
+      </c>
+      <c r="B32" s="99" t="n">
+        <f aca="false">INDEX($E$18:$E$22,MIN($B$30+1,5))</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="86" t="s">
+        <v>813</v>
+      </c>
+      <c r="B33" s="100" t="n">
+        <f aca="false">INDEX($D$18:$D$22,$B$30)</f>
+        <v>0.695</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="86" t="s">
+        <v>814</v>
+      </c>
+      <c r="B34" s="100" t="n">
+        <f aca="false">INDEX($D$18:$D$22,MIN($B$30+1,5))</f>
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="90" t="s">
+        <v>815</v>
+      </c>
+      <c r="B35" s="94" t="n">
+        <f aca="false">IF($B$30&gt;=5,$B$33,$B$33+($B$34-$B$33)*LOG($B$28/$B$31)/LOG($B$32/$B$31))</f>
+        <v>0.217519607391945</v>
+      </c>
+      <c r="D35" s="88" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="90" t="s">
+        <v>817</v>
+      </c>
+      <c r="B36" s="101" t="n">
+        <f aca="false">IF(OR($B$35="",$B$35=0),"",1/$B$35)</f>
+        <v>4.59728670895455</v>
+      </c>
+      <c r="D36" s="88" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="83" t="s">
+        <v>819</v>
+      </c>
+      <c r="B38" s="84"/>
+      <c r="C38" s="84"/>
+      <c r="D38" s="84"/>
+      <c r="E38" s="84"/>
+    </row>
+    <row r="39" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="102" t="s">
+        <v>820</v>
+      </c>
+      <c r="B39" s="102"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="102"/>
+    </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="102" t="s">
+        <v>821</v>
+      </c>
+      <c r="B40" s="102"/>
+      <c r="C40" s="102"/>
+      <c r="D40" s="102"/>
+      <c r="E40" s="102"/>
+    </row>
+    <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="102" t="s">
+        <v>822</v>
+      </c>
+      <c r="B41" s="102"/>
+      <c r="C41" s="102"/>
+      <c r="D41" s="102"/>
+      <c r="E41" s="102"/>
+    </row>
+    <row r="42" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="102" t="s">
+        <v>823</v>
+      </c>
+      <c r="B42" s="102"/>
+      <c r="C42" s="102"/>
+      <c r="D42" s="102"/>
+      <c r="E42" s="102"/>
+    </row>
+    <row r="43" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="102" t="s">
+        <v>824</v>
+      </c>
+      <c r="B43" s="102"/>
+      <c r="C43" s="102"/>
+      <c r="D43" s="102"/>
+      <c r="E43" s="102"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="83" t="s">
+        <v>825</v>
+      </c>
+      <c r="B45" s="84"/>
+      <c r="C45" s="84"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="85" t="s">
+        <v>695</v>
+      </c>
+      <c r="B46" s="85" t="s">
+        <v>826</v>
+      </c>
+      <c r="C46" s="85" t="s">
+        <v>827</v>
+      </c>
+      <c r="D46" s="85" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="103" t="s">
+        <v>829</v>
+      </c>
+      <c r="B47" s="104" t="s">
+        <v>830</v>
+      </c>
+      <c r="C47" s="104" t="s">
+        <v>831</v>
+      </c>
+      <c r="D47" s="88" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="103" t="s">
+        <v>833</v>
+      </c>
+      <c r="B48" s="104" t="s">
+        <v>834</v>
+      </c>
+      <c r="C48" s="104" t="s">
+        <v>831</v>
+      </c>
+      <c r="D48" s="88" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="103" t="s">
+        <v>836</v>
+      </c>
+      <c r="B49" s="104" t="s">
+        <v>834</v>
+      </c>
+      <c r="C49" s="104" t="s">
+        <v>837</v>
+      </c>
+      <c r="D49" s="88" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="103" t="s">
+        <v>839</v>
+      </c>
+      <c r="B50" s="104" t="s">
+        <v>834</v>
+      </c>
+      <c r="C50" s="104" t="s">
+        <v>840</v>
+      </c>
+      <c r="D50" s="88" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="103" t="s">
+        <v>842</v>
+      </c>
+      <c r="B51" s="104" t="s">
+        <v>834</v>
+      </c>
+      <c r="C51" s="104" t="s">
+        <v>843</v>
+      </c>
+      <c r="D51" s="88" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="103" t="s">
+        <v>845</v>
+      </c>
+      <c r="B52" s="104" t="s">
+        <v>834</v>
+      </c>
+      <c r="C52" s="104" t="s">
+        <v>831</v>
+      </c>
+      <c r="D52" s="88" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="103" t="s">
+        <v>847</v>
+      </c>
+      <c r="B53" s="104" t="s">
+        <v>848</v>
+      </c>
+      <c r="C53" s="104" t="s">
+        <v>831</v>
+      </c>
+      <c r="D53" s="88" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="103" t="s">
+        <v>850</v>
+      </c>
+      <c r="B54" s="104" t="s">
+        <v>851</v>
+      </c>
+      <c r="C54" s="104" t="s">
+        <v>852</v>
+      </c>
+      <c r="D54" s="88" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="105" t="s">
+        <v>854</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A43:E43"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -17369,8 +18412,8 @@
       <c r="I166" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J166" s="47"/>
-      <c r="K166" s="48"/>
+      <c r="J166" s="27"/>
+      <c r="K166" s="28"/>
       <c r="L166" s="26"/>
       <c r="M166" s="39" t="n">
         <f aca="false">IF($B166="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B166,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17449,8 +18492,8 @@
       <c r="I167" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J167" s="47"/>
-      <c r="K167" s="48"/>
+      <c r="J167" s="27"/>
+      <c r="K167" s="28"/>
       <c r="L167" s="26"/>
       <c r="M167" s="39" t="n">
         <f aca="false">IF($B167="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B167,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17529,8 +18572,8 @@
       <c r="I168" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J168" s="47"/>
-      <c r="K168" s="48"/>
+      <c r="J168" s="27"/>
+      <c r="K168" s="28"/>
       <c r="L168" s="26"/>
       <c r="M168" s="39" t="n">
         <f aca="false">IF($B168="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B168,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17609,8 +18652,8 @@
       <c r="I169" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J169" s="47"/>
-      <c r="K169" s="48"/>
+      <c r="J169" s="27"/>
+      <c r="K169" s="28"/>
       <c r="L169" s="26"/>
       <c r="M169" s="39" t="n">
         <f aca="false">IF($B169="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B169,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17689,8 +18732,8 @@
       <c r="I170" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J170" s="47"/>
-      <c r="K170" s="48"/>
+      <c r="J170" s="27"/>
+      <c r="K170" s="28"/>
       <c r="L170" s="26"/>
       <c r="M170" s="39" t="n">
         <f aca="false">IF($B170="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B170,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17769,8 +18812,8 @@
       <c r="I171" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J171" s="47"/>
-      <c r="K171" s="48"/>
+      <c r="J171" s="27"/>
+      <c r="K171" s="28"/>
       <c r="L171" s="26"/>
       <c r="M171" s="39" t="n">
         <f aca="false">IF($B171="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B171,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17849,8 +18892,8 @@
       <c r="I172" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J172" s="47"/>
-      <c r="K172" s="48"/>
+      <c r="J172" s="27"/>
+      <c r="K172" s="28"/>
       <c r="L172" s="26"/>
       <c r="M172" s="39" t="n">
         <f aca="false">IF($B172="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B172,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -17929,8 +18972,8 @@
       <c r="I173" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J173" s="47"/>
-      <c r="K173" s="48"/>
+      <c r="J173" s="27"/>
+      <c r="K173" s="28"/>
       <c r="L173" s="26"/>
       <c r="M173" s="39" t="n">
         <f aca="false">IF($B173="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B173,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18009,8 +19052,8 @@
       <c r="I174" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J174" s="47"/>
-      <c r="K174" s="48"/>
+      <c r="J174" s="27"/>
+      <c r="K174" s="28"/>
       <c r="L174" s="26"/>
       <c r="M174" s="39" t="n">
         <f aca="false">IF($B174="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B174,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18089,8 +19132,8 @@
       <c r="I175" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J175" s="47"/>
-      <c r="K175" s="48"/>
+      <c r="J175" s="27"/>
+      <c r="K175" s="28"/>
       <c r="L175" s="26"/>
       <c r="M175" s="39" t="n">
         <f aca="false">IF($B175="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B175,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18169,8 +19212,8 @@
       <c r="I176" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J176" s="47"/>
-      <c r="K176" s="48"/>
+      <c r="J176" s="27"/>
+      <c r="K176" s="28"/>
       <c r="L176" s="26"/>
       <c r="M176" s="39" t="n">
         <f aca="false">IF($B176="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B176,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18249,8 +19292,8 @@
       <c r="I177" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J177" s="47"/>
-      <c r="K177" s="48"/>
+      <c r="J177" s="27"/>
+      <c r="K177" s="28"/>
       <c r="L177" s="26"/>
       <c r="M177" s="39" t="n">
         <f aca="false">IF($B177="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B177,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18329,8 +19372,8 @@
       <c r="I178" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J178" s="47"/>
-      <c r="K178" s="48"/>
+      <c r="J178" s="27"/>
+      <c r="K178" s="28"/>
       <c r="L178" s="26"/>
       <c r="M178" s="39" t="n">
         <f aca="false">IF($B178="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B178,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18409,8 +19452,8 @@
       <c r="I179" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J179" s="47"/>
-      <c r="K179" s="48"/>
+      <c r="J179" s="27"/>
+      <c r="K179" s="28"/>
       <c r="L179" s="26"/>
       <c r="M179" s="39" t="n">
         <f aca="false">IF($B179="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B179,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18489,8 +19532,8 @@
       <c r="I180" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J180" s="47"/>
-      <c r="K180" s="48"/>
+      <c r="J180" s="27"/>
+      <c r="K180" s="28"/>
       <c r="L180" s="26"/>
       <c r="M180" s="39" t="n">
         <f aca="false">IF($B180="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B180,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18569,8 +19612,8 @@
       <c r="I181" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J181" s="47"/>
-      <c r="K181" s="48"/>
+      <c r="J181" s="27"/>
+      <c r="K181" s="28"/>
       <c r="L181" s="26"/>
       <c r="M181" s="39" t="n">
         <f aca="false">IF($B181="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B181,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18649,8 +19692,8 @@
       <c r="I182" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J182" s="47"/>
-      <c r="K182" s="48"/>
+      <c r="J182" s="27"/>
+      <c r="K182" s="28"/>
       <c r="L182" s="26"/>
       <c r="M182" s="39" t="n">
         <f aca="false">IF($B182="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B182,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18729,8 +19772,8 @@
       <c r="I183" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J183" s="47"/>
-      <c r="K183" s="48"/>
+      <c r="J183" s="27"/>
+      <c r="K183" s="28"/>
       <c r="L183" s="26"/>
       <c r="M183" s="39" t="n">
         <f aca="false">IF($B183="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B183,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18809,8 +19852,8 @@
       <c r="I184" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J184" s="47"/>
-      <c r="K184" s="48"/>
+      <c r="J184" s="27"/>
+      <c r="K184" s="28"/>
       <c r="L184" s="26"/>
       <c r="M184" s="39" t="n">
         <f aca="false">IF($B184="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B184,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18889,8 +19932,8 @@
       <c r="I185" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J185" s="47"/>
-      <c r="K185" s="48"/>
+      <c r="J185" s="27"/>
+      <c r="K185" s="28"/>
       <c r="L185" s="26"/>
       <c r="M185" s="39" t="n">
         <f aca="false">IF($B185="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B185,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -18969,8 +20012,8 @@
       <c r="I186" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J186" s="47"/>
-      <c r="K186" s="48"/>
+      <c r="J186" s="27"/>
+      <c r="K186" s="28"/>
       <c r="L186" s="26"/>
       <c r="M186" s="39" t="n">
         <f aca="false">IF($B186="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B186,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19049,8 +20092,8 @@
       <c r="I187" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J187" s="47"/>
-      <c r="K187" s="48"/>
+      <c r="J187" s="27"/>
+      <c r="K187" s="28"/>
       <c r="L187" s="26"/>
       <c r="M187" s="39" t="n">
         <f aca="false">IF($B187="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B187,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19129,8 +20172,8 @@
       <c r="I188" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J188" s="47"/>
-      <c r="K188" s="48"/>
+      <c r="J188" s="27"/>
+      <c r="K188" s="28"/>
       <c r="L188" s="26"/>
       <c r="M188" s="39" t="n">
         <f aca="false">IF($B188="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B188,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19209,8 +20252,8 @@
       <c r="I189" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J189" s="47"/>
-      <c r="K189" s="48"/>
+      <c r="J189" s="27"/>
+      <c r="K189" s="28"/>
       <c r="L189" s="26"/>
       <c r="M189" s="39" t="n">
         <f aca="false">IF($B189="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B189,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19289,8 +20332,8 @@
       <c r="I190" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J190" s="47"/>
-      <c r="K190" s="48"/>
+      <c r="J190" s="27"/>
+      <c r="K190" s="28"/>
       <c r="L190" s="26"/>
       <c r="M190" s="39" t="n">
         <f aca="false">IF($B190="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B190,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19369,8 +20412,8 @@
       <c r="I191" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J191" s="47"/>
-      <c r="K191" s="48"/>
+      <c r="J191" s="27"/>
+      <c r="K191" s="28"/>
       <c r="L191" s="26"/>
       <c r="M191" s="39" t="n">
         <f aca="false">IF($B191="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B191,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19449,8 +20492,8 @@
       <c r="I192" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J192" s="47"/>
-      <c r="K192" s="48"/>
+      <c r="J192" s="27"/>
+      <c r="K192" s="28"/>
       <c r="L192" s="26"/>
       <c r="M192" s="39" t="n">
         <f aca="false">IF($B192="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B192,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19529,8 +20572,8 @@
       <c r="I193" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J193" s="47"/>
-      <c r="K193" s="48"/>
+      <c r="J193" s="27"/>
+      <c r="K193" s="28"/>
       <c r="L193" s="26"/>
       <c r="M193" s="39" t="n">
         <f aca="false">IF($B193="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B193,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19609,8 +20652,8 @@
       <c r="I194" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J194" s="47"/>
-      <c r="K194" s="48"/>
+      <c r="J194" s="27"/>
+      <c r="K194" s="28"/>
       <c r="L194" s="26"/>
       <c r="M194" s="39" t="n">
         <f aca="false">IF($B194="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B194,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19689,8 +20732,8 @@
       <c r="I195" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J195" s="47"/>
-      <c r="K195" s="48"/>
+      <c r="J195" s="27"/>
+      <c r="K195" s="28"/>
       <c r="L195" s="26"/>
       <c r="M195" s="39" t="n">
         <f aca="false">IF($B195="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B195,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19769,8 +20812,8 @@
       <c r="I196" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J196" s="47"/>
-      <c r="K196" s="48"/>
+      <c r="J196" s="27"/>
+      <c r="K196" s="28"/>
       <c r="L196" s="26"/>
       <c r="M196" s="39" t="n">
         <f aca="false">IF($B196="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B196,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19849,8 +20892,8 @@
       <c r="I197" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J197" s="47"/>
-      <c r="K197" s="48"/>
+      <c r="J197" s="27"/>
+      <c r="K197" s="28"/>
       <c r="L197" s="26"/>
       <c r="M197" s="39" t="n">
         <f aca="false">IF($B197="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B197,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -19929,8 +20972,8 @@
       <c r="I198" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J198" s="47"/>
-      <c r="K198" s="48"/>
+      <c r="J198" s="27"/>
+      <c r="K198" s="28"/>
       <c r="L198" s="26"/>
       <c r="M198" s="39" t="n">
         <f aca="false">IF($B198="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B198,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -20009,8 +21052,8 @@
       <c r="I199" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J199" s="47"/>
-      <c r="K199" s="48"/>
+      <c r="J199" s="27"/>
+      <c r="K199" s="28"/>
       <c r="L199" s="26"/>
       <c r="M199" s="39" t="n">
         <f aca="false">IF($B199="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B199,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -20089,8 +21132,8 @@
       <c r="I200" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J200" s="47"/>
-      <c r="K200" s="48"/>
+      <c r="J200" s="27"/>
+      <c r="K200" s="28"/>
       <c r="L200" s="26"/>
       <c r="M200" s="39" t="n">
         <f aca="false">IF($B200="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B200,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -20169,8 +21212,8 @@
       <c r="I201" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J201" s="47"/>
-      <c r="K201" s="48"/>
+      <c r="J201" s="27"/>
+      <c r="K201" s="28"/>
       <c r="L201" s="26"/>
       <c r="M201" s="39" t="n">
         <f aca="false">IF($B201="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B201,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -20249,8 +21292,8 @@
       <c r="I202" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J202" s="47"/>
-      <c r="K202" s="48"/>
+      <c r="J202" s="27"/>
+      <c r="K202" s="28"/>
       <c r="L202" s="26"/>
       <c r="M202" s="39" t="n">
         <f aca="false">IF($B202="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B202,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -20329,8 +21372,8 @@
       <c r="I203" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J203" s="47"/>
-      <c r="K203" s="48"/>
+      <c r="J203" s="27"/>
+      <c r="K203" s="28"/>
       <c r="L203" s="26"/>
       <c r="M203" s="39" t="n">
         <f aca="false">IF($B203="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B203,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -20409,8 +21452,8 @@
       <c r="I204" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="J204" s="47"/>
-      <c r="K204" s="48"/>
+      <c r="J204" s="27"/>
+      <c r="K204" s="28"/>
       <c r="L204" s="26"/>
       <c r="M204" s="39" t="n">
         <f aca="false">IF($B204="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH($B204,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -20530,36 +21573,36 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="47" t="s">
         <v>576</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="48" t="s">
         <v>577</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="50" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="51" t="s">
         <v>77</v>
       </c>
       <c r="B6" s="10" t="n">
@@ -20567,7 +21610,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="51" t="s">
         <v>81</v>
       </c>
       <c r="B7" s="10" t="n">
@@ -20575,7 +21618,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="51" t="s">
         <v>89</v>
       </c>
       <c r="B8" s="10" t="n">
@@ -20583,7 +21626,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="51" t="s">
         <v>93</v>
       </c>
       <c r="B9" s="10" t="n">
@@ -20591,25 +21634,25 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="52" t="s">
         <v>579</v>
       </c>
-      <c r="B10" s="55" t="n">
+      <c r="B10" s="53" t="n">
         <f aca="false">SUM(B6:B9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="54" t="str">
+      <c r="C10" s="52" t="str">
         <f aca="false">IF(ABS(B10-1)&lt;0.0001,"OK","ERROR - must total 100%")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="50" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="51" t="s">
         <v>581</v>
       </c>
       <c r="B13" s="10" t="n">
@@ -20617,7 +21660,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="51" t="s">
         <v>582</v>
       </c>
       <c r="B14" s="10" t="n">
@@ -20625,7 +21668,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>583</v>
       </c>
       <c r="B15" s="10" t="n">
@@ -20633,7 +21676,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="51" t="s">
         <v>584</v>
       </c>
       <c r="B16" s="10" t="n">
@@ -20641,361 +21684,361 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="52" t="s">
         <v>579</v>
       </c>
-      <c r="B17" s="55" t="n">
+      <c r="B17" s="53" t="n">
         <f aca="false">SUM(B13:B16)</f>
         <v>1</v>
       </c>
-      <c r="C17" s="54" t="str">
+      <c r="C17" s="52" t="str">
         <f aca="false">IF(ABS(B17-1)&lt;0.0001,"OK","ERROR - must total 100%")</f>
         <v>OK</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="51" t="s">
         <v>585</v>
       </c>
       <c r="B19" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="54" t="s">
         <v>586</v>
       </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="50" t="s">
+      <c r="A21" s="48" t="s">
         <v>587</v>
       </c>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="52" t="s">
         <v>581</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="55" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="55"/>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="54" t="s">
+      <c r="A23" s="52" t="s">
         <v>582</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="55" t="s">
         <v>589</v>
       </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="52" t="s">
         <v>583</v>
       </c>
-      <c r="B24" s="57" t="s">
+      <c r="B24" s="55" t="s">
         <v>590</v>
       </c>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
-      <c r="J24" s="57"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="52" t="s">
         <v>584</v>
       </c>
-      <c r="B25" s="57" t="s">
+      <c r="B25" s="55" t="s">
         <v>591</v>
       </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="55"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="48" t="s">
         <v>592</v>
       </c>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="55" t="s">
         <v>593</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
     </row>
     <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="B29" s="57" t="s">
+      <c r="B29" s="55" t="s">
         <v>594</v>
       </c>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="55"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="55"/>
+      <c r="H29" s="55"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="55"/>
     </row>
     <row r="30" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="54" t="s">
+      <c r="A30" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="55" t="s">
         <v>595</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="55"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="54" t="s">
+      <c r="A31" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="57" t="s">
+      <c r="B31" s="55" t="s">
         <v>596</v>
       </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="50" t="s">
+      <c r="A34" s="48" t="s">
         <v>597</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="53" t="s">
+      <c r="A35" s="51" t="s">
         <v>598</v>
       </c>
-      <c r="B35" s="58" t="n">
+      <c r="B35" s="56" t="n">
         <f aca="false">COUNTIF($A$44:$A$163,"&lt;&gt;")</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="53" t="s">
+      <c r="A36" s="51" t="s">
         <v>599</v>
       </c>
-      <c r="B36" s="58" t="n">
+      <c r="B36" s="56" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"BUY")</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="53" t="s">
+      <c r="A37" s="51" t="s">
         <v>600</v>
       </c>
-      <c r="B37" s="58" t="n">
+      <c r="B37" s="56" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"BUY CHEAPER")+COUNTIF($AF$44:$AF$163,"FLOOR ONLY")</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="53" t="s">
+      <c r="A38" s="51" t="s">
         <v>601</v>
       </c>
-      <c r="B38" s="58" t="n">
+      <c r="B38" s="56" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"REJECT")+COUNTIF($AF$44:$AF$163,"OVERPRICED")+COUNTIF($AF$44:$AF$163,"SKIP")</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="51" t="s">
         <v>602</v>
       </c>
-      <c r="B39" s="58" t="n">
+      <c r="B39" s="56" t="n">
         <f aca="false">COUNTIF($AF$44:$AF$163,"NEEDS VALUATION")+COUNTIF($AF$44:$AF$163,"NEEDS PRICE")</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="53" t="s">
+      <c r="A40" s="51" t="s">
         <v>603</v>
       </c>
-      <c r="B40" s="59" t="n">
+      <c r="B40" s="57" t="n">
         <f aca="false">SUMIF($AF$44:$AF$163,"BUY",$F$44:$F$163)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="51" t="s">
         <v>604</v>
       </c>
-      <c r="B41" s="60" t="n">
+      <c r="B41" s="58" t="n">
         <f aca="false">SUMIF($AF$44:$AF$163,"BUY",$AE$44:$AE$163)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="B43" s="61" t="s">
+      <c r="B43" s="59" t="s">
         <v>150</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="C43" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="D43" s="61" t="s">
+      <c r="D43" s="59" t="s">
         <v>605</v>
       </c>
-      <c r="E43" s="61" t="s">
+      <c r="E43" s="59" t="s">
         <v>606</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="59" t="s">
         <v>607</v>
       </c>
-      <c r="G43" s="61" t="s">
+      <c r="G43" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="H43" s="61" t="s">
+      <c r="H43" s="59" t="s">
         <v>154</v>
       </c>
-      <c r="I43" s="61" t="s">
+      <c r="I43" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="J43" s="61" t="s">
+      <c r="J43" s="59" t="s">
         <v>608</v>
       </c>
-      <c r="K43" s="61" t="s">
+      <c r="K43" s="59" t="s">
         <v>609</v>
       </c>
-      <c r="L43" s="61" t="s">
+      <c r="L43" s="59" t="s">
         <v>610</v>
       </c>
-      <c r="M43" s="61" t="s">
+      <c r="M43" s="59" t="s">
         <v>611</v>
       </c>
-      <c r="N43" s="61" t="s">
+      <c r="N43" s="59" t="s">
         <v>612</v>
       </c>
-      <c r="O43" s="61" t="s">
+      <c r="O43" s="59" t="s">
         <v>613</v>
       </c>
-      <c r="P43" s="61" t="s">
+      <c r="P43" s="59" t="s">
         <v>614</v>
       </c>
-      <c r="Q43" s="61" t="s">
+      <c r="Q43" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="R43" s="61" t="s">
+      <c r="R43" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="S43" s="61" t="s">
+      <c r="S43" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="T43" s="61" t="s">
+      <c r="T43" s="59" t="s">
         <v>615</v>
       </c>
-      <c r="U43" s="61" t="s">
+      <c r="U43" s="59" t="s">
         <v>616</v>
       </c>
-      <c r="V43" s="61" t="s">
+      <c r="V43" s="59" t="s">
         <v>617</v>
       </c>
-      <c r="W43" s="61" t="s">
+      <c r="W43" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="X43" s="61" t="s">
+      <c r="X43" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="Y43" s="61" t="s">
+      <c r="Y43" s="59" t="s">
         <v>618</v>
       </c>
-      <c r="Z43" s="61" t="s">
+      <c r="Z43" s="59" t="s">
         <v>164</v>
       </c>
-      <c r="AA43" s="61" t="s">
+      <c r="AA43" s="59" t="s">
         <v>619</v>
       </c>
-      <c r="AB43" s="61" t="s">
+      <c r="AB43" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="AC43" s="61" t="s">
+      <c r="AC43" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="AD43" s="61" t="s">
+      <c r="AD43" s="59" t="s">
         <v>169</v>
       </c>
-      <c r="AE43" s="61" t="s">
+      <c r="AE43" s="59" t="s">
         <v>620</v>
       </c>
-      <c r="AF43" s="61" t="s">
+      <c r="AF43" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="AG43" s="61" t="s">
+      <c r="AG43" s="59" t="s">
         <v>621</v>
       </c>
-      <c r="AH43" s="61" t="s">
+      <c r="AH43" s="59" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="62" t="s">
+      <c r="A44" s="60" t="s">
         <v>622</v>
       </c>
       <c r="B44" s="24" t="str">
@@ -21006,7 +22049,7 @@
         <f aca="false">IF($B44="","",IFERROR(INDEX(Rubric!$B$14:$B$23,MATCH($B44,Rubric!$A$14:$A$23,0)),INDEX(Rubric!$B$14:$B$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
         <v>5</v>
       </c>
-      <c r="D44" s="63" t="n">
+      <c r="D44" s="61" t="n">
         <v>11</v>
       </c>
       <c r="E44" s="29" t="n">
@@ -21017,41 +22060,41 @@
         <f aca="false">IF(OR($A44="",$D44=""),"",$D44+$E44)</f>
         <v>22</v>
       </c>
-      <c r="G44" s="64" t="n">
+      <c r="G44" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="H44" s="64" t="n">
+      <c r="H44" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="64" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="64" t="n">
+      <c r="I44" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" s="62" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="30" t="n">
         <f aca="false">IF($J44="","",IF($J44&gt;=15,5,IF($J44&gt;=10,4,IF($J44&gt;=5,3,IF($J44&gt;=2,2,1)))))</f>
         <v>4</v>
       </c>
-      <c r="L44" s="64" t="n">
+      <c r="L44" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="M44" s="64" t="n">
+      <c r="M44" s="62" t="n">
         <v>4</v>
       </c>
-      <c r="N44" s="64" t="n">
+      <c r="N44" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="O44" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="P44" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q44" s="64" t="s">
-        <v>172</v>
-      </c>
-      <c r="R44" s="64" t="s">
+      <c r="O44" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="P44" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q44" s="62" t="s">
+        <v>172</v>
+      </c>
+      <c r="R44" s="62" t="s">
         <v>172</v>
       </c>
       <c r="S44" s="31" t="str">
@@ -21070,10 +22113,10 @@
         <f aca="false">IF(OR($T44="",$U44=""),"",$T44*$B$19+$U44*(1-$B$19))</f>
         <v>4.12</v>
       </c>
-      <c r="W44" s="65" t="n">
+      <c r="W44" s="63" t="n">
         <v>1200</v>
       </c>
-      <c r="X44" s="62" t="s">
+      <c r="X44" s="60" t="s">
         <v>623</v>
       </c>
       <c r="Y44" s="33" t="n">
@@ -21108,11 +22151,11 @@
         <f aca="false">IF($A44="","",IF($S44="FAIL","REJECT",IF($D44="","NEEDS PRICE",IF(OR($W44="",$X44=""),"NEEDS VALUATION",IF($AC44&lt;1,"OVERPRICED",IF(AND($AC44&gt;=Assumptions!$B$13,$V44&gt;=4),"BUY",IF($V44&gt;=3.4,"BUY CHEAPER",IF($V44&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v>BUY CHEAPER</v>
       </c>
-      <c r="AG44" s="66" t="str">
+      <c r="AG44" s="64" t="str">
         <f aca="false">IF($AF44="","",IF($AF44="REJECT","Do not buy at any price",IF($AF44="NEEDS PRICE","Enter the current closeout price",IF($AF44="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF44="OVERPRICED","Worth less than break-even - walk",IF($AF44="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF44="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF44="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v>Wait to about $8 (day 3), walk if outbid</v>
       </c>
-      <c r="AH44" s="67"/>
+      <c r="AH44" s="65"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="23"/>
@@ -21198,7 +22241,7 @@
         <f aca="false">IF($A45="","",IF($S45="FAIL","REJECT",IF($D45="","NEEDS PRICE",IF(OR($W45="",$X45=""),"NEEDS VALUATION",IF($AC45&lt;1,"OVERPRICED",IF(AND($AC45&gt;=Assumptions!$B$13,$V45&gt;=4),"BUY",IF($V45&gt;=3.4,"BUY CHEAPER",IF($V45&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG45" s="53" t="str">
+      <c r="AG45" s="51" t="str">
         <f aca="false">IF($AF45="","",IF($AF45="REJECT","Do not buy at any price",IF($AF45="NEEDS PRICE","Enter the current closeout price",IF($AF45="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF45="OVERPRICED","Worth less than break-even - walk",IF($AF45="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF45="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF45="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21288,7 +22331,7 @@
         <f aca="false">IF($A46="","",IF($S46="FAIL","REJECT",IF($D46="","NEEDS PRICE",IF(OR($W46="",$X46=""),"NEEDS VALUATION",IF($AC46&lt;1,"OVERPRICED",IF(AND($AC46&gt;=Assumptions!$B$13,$V46&gt;=4),"BUY",IF($V46&gt;=3.4,"BUY CHEAPER",IF($V46&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG46" s="53" t="str">
+      <c r="AG46" s="51" t="str">
         <f aca="false">IF($AF46="","",IF($AF46="REJECT","Do not buy at any price",IF($AF46="NEEDS PRICE","Enter the current closeout price",IF($AF46="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF46="OVERPRICED","Worth less than break-even - walk",IF($AF46="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF46="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF46="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21378,7 +22421,7 @@
         <f aca="false">IF($A47="","",IF($S47="FAIL","REJECT",IF($D47="","NEEDS PRICE",IF(OR($W47="",$X47=""),"NEEDS VALUATION",IF($AC47&lt;1,"OVERPRICED",IF(AND($AC47&gt;=Assumptions!$B$13,$V47&gt;=4),"BUY",IF($V47&gt;=3.4,"BUY CHEAPER",IF($V47&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG47" s="53" t="str">
+      <c r="AG47" s="51" t="str">
         <f aca="false">IF($AF47="","",IF($AF47="REJECT","Do not buy at any price",IF($AF47="NEEDS PRICE","Enter the current closeout price",IF($AF47="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF47="OVERPRICED","Worth less than break-even - walk",IF($AF47="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF47="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF47="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21468,7 +22511,7 @@
         <f aca="false">IF($A48="","",IF($S48="FAIL","REJECT",IF($D48="","NEEDS PRICE",IF(OR($W48="",$X48=""),"NEEDS VALUATION",IF($AC48&lt;1,"OVERPRICED",IF(AND($AC48&gt;=Assumptions!$B$13,$V48&gt;=4),"BUY",IF($V48&gt;=3.4,"BUY CHEAPER",IF($V48&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG48" s="53" t="str">
+      <c r="AG48" s="51" t="str">
         <f aca="false">IF($AF48="","",IF($AF48="REJECT","Do not buy at any price",IF($AF48="NEEDS PRICE","Enter the current closeout price",IF($AF48="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF48="OVERPRICED","Worth less than break-even - walk",IF($AF48="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF48="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF48="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21558,7 +22601,7 @@
         <f aca="false">IF($A49="","",IF($S49="FAIL","REJECT",IF($D49="","NEEDS PRICE",IF(OR($W49="",$X49=""),"NEEDS VALUATION",IF($AC49&lt;1,"OVERPRICED",IF(AND($AC49&gt;=Assumptions!$B$13,$V49&gt;=4),"BUY",IF($V49&gt;=3.4,"BUY CHEAPER",IF($V49&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG49" s="53" t="str">
+      <c r="AG49" s="51" t="str">
         <f aca="false">IF($AF49="","",IF($AF49="REJECT","Do not buy at any price",IF($AF49="NEEDS PRICE","Enter the current closeout price",IF($AF49="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF49="OVERPRICED","Worth less than break-even - walk",IF($AF49="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF49="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF49="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21648,7 +22691,7 @@
         <f aca="false">IF($A50="","",IF($S50="FAIL","REJECT",IF($D50="","NEEDS PRICE",IF(OR($W50="",$X50=""),"NEEDS VALUATION",IF($AC50&lt;1,"OVERPRICED",IF(AND($AC50&gt;=Assumptions!$B$13,$V50&gt;=4),"BUY",IF($V50&gt;=3.4,"BUY CHEAPER",IF($V50&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG50" s="53" t="str">
+      <c r="AG50" s="51" t="str">
         <f aca="false">IF($AF50="","",IF($AF50="REJECT","Do not buy at any price",IF($AF50="NEEDS PRICE","Enter the current closeout price",IF($AF50="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF50="OVERPRICED","Worth less than break-even - walk",IF($AF50="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF50="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF50="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21738,7 +22781,7 @@
         <f aca="false">IF($A51="","",IF($S51="FAIL","REJECT",IF($D51="","NEEDS PRICE",IF(OR($W51="",$X51=""),"NEEDS VALUATION",IF($AC51&lt;1,"OVERPRICED",IF(AND($AC51&gt;=Assumptions!$B$13,$V51&gt;=4),"BUY",IF($V51&gt;=3.4,"BUY CHEAPER",IF($V51&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG51" s="53" t="str">
+      <c r="AG51" s="51" t="str">
         <f aca="false">IF($AF51="","",IF($AF51="REJECT","Do not buy at any price",IF($AF51="NEEDS PRICE","Enter the current closeout price",IF($AF51="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF51="OVERPRICED","Worth less than break-even - walk",IF($AF51="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF51="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF51="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21828,7 +22871,7 @@
         <f aca="false">IF($A52="","",IF($S52="FAIL","REJECT",IF($D52="","NEEDS PRICE",IF(OR($W52="",$X52=""),"NEEDS VALUATION",IF($AC52&lt;1,"OVERPRICED",IF(AND($AC52&gt;=Assumptions!$B$13,$V52&gt;=4),"BUY",IF($V52&gt;=3.4,"BUY CHEAPER",IF($V52&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG52" s="53" t="str">
+      <c r="AG52" s="51" t="str">
         <f aca="false">IF($AF52="","",IF($AF52="REJECT","Do not buy at any price",IF($AF52="NEEDS PRICE","Enter the current closeout price",IF($AF52="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF52="OVERPRICED","Worth less than break-even - walk",IF($AF52="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF52="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF52="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -21918,7 +22961,7 @@
         <f aca="false">IF($A53="","",IF($S53="FAIL","REJECT",IF($D53="","NEEDS PRICE",IF(OR($W53="",$X53=""),"NEEDS VALUATION",IF($AC53&lt;1,"OVERPRICED",IF(AND($AC53&gt;=Assumptions!$B$13,$V53&gt;=4),"BUY",IF($V53&gt;=3.4,"BUY CHEAPER",IF($V53&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG53" s="53" t="str">
+      <c r="AG53" s="51" t="str">
         <f aca="false">IF($AF53="","",IF($AF53="REJECT","Do not buy at any price",IF($AF53="NEEDS PRICE","Enter the current closeout price",IF($AF53="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF53="OVERPRICED","Worth less than break-even - walk",IF($AF53="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF53="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF53="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22008,7 +23051,7 @@
         <f aca="false">IF($A54="","",IF($S54="FAIL","REJECT",IF($D54="","NEEDS PRICE",IF(OR($W54="",$X54=""),"NEEDS VALUATION",IF($AC54&lt;1,"OVERPRICED",IF(AND($AC54&gt;=Assumptions!$B$13,$V54&gt;=4),"BUY",IF($V54&gt;=3.4,"BUY CHEAPER",IF($V54&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG54" s="53" t="str">
+      <c r="AG54" s="51" t="str">
         <f aca="false">IF($AF54="","",IF($AF54="REJECT","Do not buy at any price",IF($AF54="NEEDS PRICE","Enter the current closeout price",IF($AF54="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF54="OVERPRICED","Worth less than break-even - walk",IF($AF54="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF54="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF54="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22098,7 +23141,7 @@
         <f aca="false">IF($A55="","",IF($S55="FAIL","REJECT",IF($D55="","NEEDS PRICE",IF(OR($W55="",$X55=""),"NEEDS VALUATION",IF($AC55&lt;1,"OVERPRICED",IF(AND($AC55&gt;=Assumptions!$B$13,$V55&gt;=4),"BUY",IF($V55&gt;=3.4,"BUY CHEAPER",IF($V55&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG55" s="53" t="str">
+      <c r="AG55" s="51" t="str">
         <f aca="false">IF($AF55="","",IF($AF55="REJECT","Do not buy at any price",IF($AF55="NEEDS PRICE","Enter the current closeout price",IF($AF55="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF55="OVERPRICED","Worth less than break-even - walk",IF($AF55="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF55="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF55="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22188,7 +23231,7 @@
         <f aca="false">IF($A56="","",IF($S56="FAIL","REJECT",IF($D56="","NEEDS PRICE",IF(OR($W56="",$X56=""),"NEEDS VALUATION",IF($AC56&lt;1,"OVERPRICED",IF(AND($AC56&gt;=Assumptions!$B$13,$V56&gt;=4),"BUY",IF($V56&gt;=3.4,"BUY CHEAPER",IF($V56&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG56" s="53" t="str">
+      <c r="AG56" s="51" t="str">
         <f aca="false">IF($AF56="","",IF($AF56="REJECT","Do not buy at any price",IF($AF56="NEEDS PRICE","Enter the current closeout price",IF($AF56="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF56="OVERPRICED","Worth less than break-even - walk",IF($AF56="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF56="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF56="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22278,7 +23321,7 @@
         <f aca="false">IF($A57="","",IF($S57="FAIL","REJECT",IF($D57="","NEEDS PRICE",IF(OR($W57="",$X57=""),"NEEDS VALUATION",IF($AC57&lt;1,"OVERPRICED",IF(AND($AC57&gt;=Assumptions!$B$13,$V57&gt;=4),"BUY",IF($V57&gt;=3.4,"BUY CHEAPER",IF($V57&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG57" s="53" t="str">
+      <c r="AG57" s="51" t="str">
         <f aca="false">IF($AF57="","",IF($AF57="REJECT","Do not buy at any price",IF($AF57="NEEDS PRICE","Enter the current closeout price",IF($AF57="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF57="OVERPRICED","Worth less than break-even - walk",IF($AF57="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF57="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF57="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22368,7 +23411,7 @@
         <f aca="false">IF($A58="","",IF($S58="FAIL","REJECT",IF($D58="","NEEDS PRICE",IF(OR($W58="",$X58=""),"NEEDS VALUATION",IF($AC58&lt;1,"OVERPRICED",IF(AND($AC58&gt;=Assumptions!$B$13,$V58&gt;=4),"BUY",IF($V58&gt;=3.4,"BUY CHEAPER",IF($V58&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG58" s="53" t="str">
+      <c r="AG58" s="51" t="str">
         <f aca="false">IF($AF58="","",IF($AF58="REJECT","Do not buy at any price",IF($AF58="NEEDS PRICE","Enter the current closeout price",IF($AF58="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF58="OVERPRICED","Worth less than break-even - walk",IF($AF58="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF58="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF58="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22458,7 +23501,7 @@
         <f aca="false">IF($A59="","",IF($S59="FAIL","REJECT",IF($D59="","NEEDS PRICE",IF(OR($W59="",$X59=""),"NEEDS VALUATION",IF($AC59&lt;1,"OVERPRICED",IF(AND($AC59&gt;=Assumptions!$B$13,$V59&gt;=4),"BUY",IF($V59&gt;=3.4,"BUY CHEAPER",IF($V59&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG59" s="53" t="str">
+      <c r="AG59" s="51" t="str">
         <f aca="false">IF($AF59="","",IF($AF59="REJECT","Do not buy at any price",IF($AF59="NEEDS PRICE","Enter the current closeout price",IF($AF59="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF59="OVERPRICED","Worth less than break-even - walk",IF($AF59="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF59="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF59="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22548,7 +23591,7 @@
         <f aca="false">IF($A60="","",IF($S60="FAIL","REJECT",IF($D60="","NEEDS PRICE",IF(OR($W60="",$X60=""),"NEEDS VALUATION",IF($AC60&lt;1,"OVERPRICED",IF(AND($AC60&gt;=Assumptions!$B$13,$V60&gt;=4),"BUY",IF($V60&gt;=3.4,"BUY CHEAPER",IF($V60&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG60" s="53" t="str">
+      <c r="AG60" s="51" t="str">
         <f aca="false">IF($AF60="","",IF($AF60="REJECT","Do not buy at any price",IF($AF60="NEEDS PRICE","Enter the current closeout price",IF($AF60="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF60="OVERPRICED","Worth less than break-even - walk",IF($AF60="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF60="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF60="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22638,7 +23681,7 @@
         <f aca="false">IF($A61="","",IF($S61="FAIL","REJECT",IF($D61="","NEEDS PRICE",IF(OR($W61="",$X61=""),"NEEDS VALUATION",IF($AC61&lt;1,"OVERPRICED",IF(AND($AC61&gt;=Assumptions!$B$13,$V61&gt;=4),"BUY",IF($V61&gt;=3.4,"BUY CHEAPER",IF($V61&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG61" s="53" t="str">
+      <c r="AG61" s="51" t="str">
         <f aca="false">IF($AF61="","",IF($AF61="REJECT","Do not buy at any price",IF($AF61="NEEDS PRICE","Enter the current closeout price",IF($AF61="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF61="OVERPRICED","Worth less than break-even - walk",IF($AF61="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF61="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF61="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22728,7 +23771,7 @@
         <f aca="false">IF($A62="","",IF($S62="FAIL","REJECT",IF($D62="","NEEDS PRICE",IF(OR($W62="",$X62=""),"NEEDS VALUATION",IF($AC62&lt;1,"OVERPRICED",IF(AND($AC62&gt;=Assumptions!$B$13,$V62&gt;=4),"BUY",IF($V62&gt;=3.4,"BUY CHEAPER",IF($V62&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG62" s="53" t="str">
+      <c r="AG62" s="51" t="str">
         <f aca="false">IF($AF62="","",IF($AF62="REJECT","Do not buy at any price",IF($AF62="NEEDS PRICE","Enter the current closeout price",IF($AF62="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF62="OVERPRICED","Worth less than break-even - walk",IF($AF62="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF62="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF62="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22818,7 +23861,7 @@
         <f aca="false">IF($A63="","",IF($S63="FAIL","REJECT",IF($D63="","NEEDS PRICE",IF(OR($W63="",$X63=""),"NEEDS VALUATION",IF($AC63&lt;1,"OVERPRICED",IF(AND($AC63&gt;=Assumptions!$B$13,$V63&gt;=4),"BUY",IF($V63&gt;=3.4,"BUY CHEAPER",IF($V63&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG63" s="53" t="str">
+      <c r="AG63" s="51" t="str">
         <f aca="false">IF($AF63="","",IF($AF63="REJECT","Do not buy at any price",IF($AF63="NEEDS PRICE","Enter the current closeout price",IF($AF63="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF63="OVERPRICED","Worth less than break-even - walk",IF($AF63="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF63="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF63="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22908,7 +23951,7 @@
         <f aca="false">IF($A64="","",IF($S64="FAIL","REJECT",IF($D64="","NEEDS PRICE",IF(OR($W64="",$X64=""),"NEEDS VALUATION",IF($AC64&lt;1,"OVERPRICED",IF(AND($AC64&gt;=Assumptions!$B$13,$V64&gt;=4),"BUY",IF($V64&gt;=3.4,"BUY CHEAPER",IF($V64&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG64" s="53" t="str">
+      <c r="AG64" s="51" t="str">
         <f aca="false">IF($AF64="","",IF($AF64="REJECT","Do not buy at any price",IF($AF64="NEEDS PRICE","Enter the current closeout price",IF($AF64="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF64="OVERPRICED","Worth less than break-even - walk",IF($AF64="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF64="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF64="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -22998,7 +24041,7 @@
         <f aca="false">IF($A65="","",IF($S65="FAIL","REJECT",IF($D65="","NEEDS PRICE",IF(OR($W65="",$X65=""),"NEEDS VALUATION",IF($AC65&lt;1,"OVERPRICED",IF(AND($AC65&gt;=Assumptions!$B$13,$V65&gt;=4),"BUY",IF($V65&gt;=3.4,"BUY CHEAPER",IF($V65&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG65" s="53" t="str">
+      <c r="AG65" s="51" t="str">
         <f aca="false">IF($AF65="","",IF($AF65="REJECT","Do not buy at any price",IF($AF65="NEEDS PRICE","Enter the current closeout price",IF($AF65="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF65="OVERPRICED","Worth less than break-even - walk",IF($AF65="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF65="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF65="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23088,7 +24131,7 @@
         <f aca="false">IF($A66="","",IF($S66="FAIL","REJECT",IF($D66="","NEEDS PRICE",IF(OR($W66="",$X66=""),"NEEDS VALUATION",IF($AC66&lt;1,"OVERPRICED",IF(AND($AC66&gt;=Assumptions!$B$13,$V66&gt;=4),"BUY",IF($V66&gt;=3.4,"BUY CHEAPER",IF($V66&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG66" s="53" t="str">
+      <c r="AG66" s="51" t="str">
         <f aca="false">IF($AF66="","",IF($AF66="REJECT","Do not buy at any price",IF($AF66="NEEDS PRICE","Enter the current closeout price",IF($AF66="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF66="OVERPRICED","Worth less than break-even - walk",IF($AF66="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF66="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF66="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23178,7 +24221,7 @@
         <f aca="false">IF($A67="","",IF($S67="FAIL","REJECT",IF($D67="","NEEDS PRICE",IF(OR($W67="",$X67=""),"NEEDS VALUATION",IF($AC67&lt;1,"OVERPRICED",IF(AND($AC67&gt;=Assumptions!$B$13,$V67&gt;=4),"BUY",IF($V67&gt;=3.4,"BUY CHEAPER",IF($V67&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG67" s="53" t="str">
+      <c r="AG67" s="51" t="str">
         <f aca="false">IF($AF67="","",IF($AF67="REJECT","Do not buy at any price",IF($AF67="NEEDS PRICE","Enter the current closeout price",IF($AF67="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF67="OVERPRICED","Worth less than break-even - walk",IF($AF67="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF67="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF67="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23268,7 +24311,7 @@
         <f aca="false">IF($A68="","",IF($S68="FAIL","REJECT",IF($D68="","NEEDS PRICE",IF(OR($W68="",$X68=""),"NEEDS VALUATION",IF($AC68&lt;1,"OVERPRICED",IF(AND($AC68&gt;=Assumptions!$B$13,$V68&gt;=4),"BUY",IF($V68&gt;=3.4,"BUY CHEAPER",IF($V68&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG68" s="53" t="str">
+      <c r="AG68" s="51" t="str">
         <f aca="false">IF($AF68="","",IF($AF68="REJECT","Do not buy at any price",IF($AF68="NEEDS PRICE","Enter the current closeout price",IF($AF68="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF68="OVERPRICED","Worth less than break-even - walk",IF($AF68="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF68="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF68="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23358,7 +24401,7 @@
         <f aca="false">IF($A69="","",IF($S69="FAIL","REJECT",IF($D69="","NEEDS PRICE",IF(OR($W69="",$X69=""),"NEEDS VALUATION",IF($AC69&lt;1,"OVERPRICED",IF(AND($AC69&gt;=Assumptions!$B$13,$V69&gt;=4),"BUY",IF($V69&gt;=3.4,"BUY CHEAPER",IF($V69&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG69" s="53" t="str">
+      <c r="AG69" s="51" t="str">
         <f aca="false">IF($AF69="","",IF($AF69="REJECT","Do not buy at any price",IF($AF69="NEEDS PRICE","Enter the current closeout price",IF($AF69="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF69="OVERPRICED","Worth less than break-even - walk",IF($AF69="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF69="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF69="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23448,7 +24491,7 @@
         <f aca="false">IF($A70="","",IF($S70="FAIL","REJECT",IF($D70="","NEEDS PRICE",IF(OR($W70="",$X70=""),"NEEDS VALUATION",IF($AC70&lt;1,"OVERPRICED",IF(AND($AC70&gt;=Assumptions!$B$13,$V70&gt;=4),"BUY",IF($V70&gt;=3.4,"BUY CHEAPER",IF($V70&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG70" s="53" t="str">
+      <c r="AG70" s="51" t="str">
         <f aca="false">IF($AF70="","",IF($AF70="REJECT","Do not buy at any price",IF($AF70="NEEDS PRICE","Enter the current closeout price",IF($AF70="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF70="OVERPRICED","Worth less than break-even - walk",IF($AF70="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF70="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF70="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23538,7 +24581,7 @@
         <f aca="false">IF($A71="","",IF($S71="FAIL","REJECT",IF($D71="","NEEDS PRICE",IF(OR($W71="",$X71=""),"NEEDS VALUATION",IF($AC71&lt;1,"OVERPRICED",IF(AND($AC71&gt;=Assumptions!$B$13,$V71&gt;=4),"BUY",IF($V71&gt;=3.4,"BUY CHEAPER",IF($V71&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG71" s="53" t="str">
+      <c r="AG71" s="51" t="str">
         <f aca="false">IF($AF71="","",IF($AF71="REJECT","Do not buy at any price",IF($AF71="NEEDS PRICE","Enter the current closeout price",IF($AF71="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF71="OVERPRICED","Worth less than break-even - walk",IF($AF71="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF71="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF71="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23628,7 +24671,7 @@
         <f aca="false">IF($A72="","",IF($S72="FAIL","REJECT",IF($D72="","NEEDS PRICE",IF(OR($W72="",$X72=""),"NEEDS VALUATION",IF($AC72&lt;1,"OVERPRICED",IF(AND($AC72&gt;=Assumptions!$B$13,$V72&gt;=4),"BUY",IF($V72&gt;=3.4,"BUY CHEAPER",IF($V72&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG72" s="53" t="str">
+      <c r="AG72" s="51" t="str">
         <f aca="false">IF($AF72="","",IF($AF72="REJECT","Do not buy at any price",IF($AF72="NEEDS PRICE","Enter the current closeout price",IF($AF72="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF72="OVERPRICED","Worth less than break-even - walk",IF($AF72="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF72="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF72="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23718,7 +24761,7 @@
         <f aca="false">IF($A73="","",IF($S73="FAIL","REJECT",IF($D73="","NEEDS PRICE",IF(OR($W73="",$X73=""),"NEEDS VALUATION",IF($AC73&lt;1,"OVERPRICED",IF(AND($AC73&gt;=Assumptions!$B$13,$V73&gt;=4),"BUY",IF($V73&gt;=3.4,"BUY CHEAPER",IF($V73&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG73" s="53" t="str">
+      <c r="AG73" s="51" t="str">
         <f aca="false">IF($AF73="","",IF($AF73="REJECT","Do not buy at any price",IF($AF73="NEEDS PRICE","Enter the current closeout price",IF($AF73="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF73="OVERPRICED","Worth less than break-even - walk",IF($AF73="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF73="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF73="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23808,7 +24851,7 @@
         <f aca="false">IF($A74="","",IF($S74="FAIL","REJECT",IF($D74="","NEEDS PRICE",IF(OR($W74="",$X74=""),"NEEDS VALUATION",IF($AC74&lt;1,"OVERPRICED",IF(AND($AC74&gt;=Assumptions!$B$13,$V74&gt;=4),"BUY",IF($V74&gt;=3.4,"BUY CHEAPER",IF($V74&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG74" s="53" t="str">
+      <c r="AG74" s="51" t="str">
         <f aca="false">IF($AF74="","",IF($AF74="REJECT","Do not buy at any price",IF($AF74="NEEDS PRICE","Enter the current closeout price",IF($AF74="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF74="OVERPRICED","Worth less than break-even - walk",IF($AF74="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF74="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF74="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23898,7 +24941,7 @@
         <f aca="false">IF($A75="","",IF($S75="FAIL","REJECT",IF($D75="","NEEDS PRICE",IF(OR($W75="",$X75=""),"NEEDS VALUATION",IF($AC75&lt;1,"OVERPRICED",IF(AND($AC75&gt;=Assumptions!$B$13,$V75&gt;=4),"BUY",IF($V75&gt;=3.4,"BUY CHEAPER",IF($V75&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG75" s="53" t="str">
+      <c r="AG75" s="51" t="str">
         <f aca="false">IF($AF75="","",IF($AF75="REJECT","Do not buy at any price",IF($AF75="NEEDS PRICE","Enter the current closeout price",IF($AF75="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF75="OVERPRICED","Worth less than break-even - walk",IF($AF75="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF75="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF75="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -23988,7 +25031,7 @@
         <f aca="false">IF($A76="","",IF($S76="FAIL","REJECT",IF($D76="","NEEDS PRICE",IF(OR($W76="",$X76=""),"NEEDS VALUATION",IF($AC76&lt;1,"OVERPRICED",IF(AND($AC76&gt;=Assumptions!$B$13,$V76&gt;=4),"BUY",IF($V76&gt;=3.4,"BUY CHEAPER",IF($V76&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG76" s="53" t="str">
+      <c r="AG76" s="51" t="str">
         <f aca="false">IF($AF76="","",IF($AF76="REJECT","Do not buy at any price",IF($AF76="NEEDS PRICE","Enter the current closeout price",IF($AF76="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF76="OVERPRICED","Worth less than break-even - walk",IF($AF76="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF76="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF76="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24078,7 +25121,7 @@
         <f aca="false">IF($A77="","",IF($S77="FAIL","REJECT",IF($D77="","NEEDS PRICE",IF(OR($W77="",$X77=""),"NEEDS VALUATION",IF($AC77&lt;1,"OVERPRICED",IF(AND($AC77&gt;=Assumptions!$B$13,$V77&gt;=4),"BUY",IF($V77&gt;=3.4,"BUY CHEAPER",IF($V77&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG77" s="53" t="str">
+      <c r="AG77" s="51" t="str">
         <f aca="false">IF($AF77="","",IF($AF77="REJECT","Do not buy at any price",IF($AF77="NEEDS PRICE","Enter the current closeout price",IF($AF77="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF77="OVERPRICED","Worth less than break-even - walk",IF($AF77="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF77="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF77="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24168,7 +25211,7 @@
         <f aca="false">IF($A78="","",IF($S78="FAIL","REJECT",IF($D78="","NEEDS PRICE",IF(OR($W78="",$X78=""),"NEEDS VALUATION",IF($AC78&lt;1,"OVERPRICED",IF(AND($AC78&gt;=Assumptions!$B$13,$V78&gt;=4),"BUY",IF($V78&gt;=3.4,"BUY CHEAPER",IF($V78&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG78" s="53" t="str">
+      <c r="AG78" s="51" t="str">
         <f aca="false">IF($AF78="","",IF($AF78="REJECT","Do not buy at any price",IF($AF78="NEEDS PRICE","Enter the current closeout price",IF($AF78="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF78="OVERPRICED","Worth less than break-even - walk",IF($AF78="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF78="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF78="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24258,7 +25301,7 @@
         <f aca="false">IF($A79="","",IF($S79="FAIL","REJECT",IF($D79="","NEEDS PRICE",IF(OR($W79="",$X79=""),"NEEDS VALUATION",IF($AC79&lt;1,"OVERPRICED",IF(AND($AC79&gt;=Assumptions!$B$13,$V79&gt;=4),"BUY",IF($V79&gt;=3.4,"BUY CHEAPER",IF($V79&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG79" s="53" t="str">
+      <c r="AG79" s="51" t="str">
         <f aca="false">IF($AF79="","",IF($AF79="REJECT","Do not buy at any price",IF($AF79="NEEDS PRICE","Enter the current closeout price",IF($AF79="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF79="OVERPRICED","Worth less than break-even - walk",IF($AF79="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF79="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF79="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24348,7 +25391,7 @@
         <f aca="false">IF($A80="","",IF($S80="FAIL","REJECT",IF($D80="","NEEDS PRICE",IF(OR($W80="",$X80=""),"NEEDS VALUATION",IF($AC80&lt;1,"OVERPRICED",IF(AND($AC80&gt;=Assumptions!$B$13,$V80&gt;=4),"BUY",IF($V80&gt;=3.4,"BUY CHEAPER",IF($V80&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG80" s="53" t="str">
+      <c r="AG80" s="51" t="str">
         <f aca="false">IF($AF80="","",IF($AF80="REJECT","Do not buy at any price",IF($AF80="NEEDS PRICE","Enter the current closeout price",IF($AF80="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF80="OVERPRICED","Worth less than break-even - walk",IF($AF80="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF80="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF80="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24438,7 +25481,7 @@
         <f aca="false">IF($A81="","",IF($S81="FAIL","REJECT",IF($D81="","NEEDS PRICE",IF(OR($W81="",$X81=""),"NEEDS VALUATION",IF($AC81&lt;1,"OVERPRICED",IF(AND($AC81&gt;=Assumptions!$B$13,$V81&gt;=4),"BUY",IF($V81&gt;=3.4,"BUY CHEAPER",IF($V81&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG81" s="53" t="str">
+      <c r="AG81" s="51" t="str">
         <f aca="false">IF($AF81="","",IF($AF81="REJECT","Do not buy at any price",IF($AF81="NEEDS PRICE","Enter the current closeout price",IF($AF81="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF81="OVERPRICED","Worth less than break-even - walk",IF($AF81="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF81="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF81="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24528,7 +25571,7 @@
         <f aca="false">IF($A82="","",IF($S82="FAIL","REJECT",IF($D82="","NEEDS PRICE",IF(OR($W82="",$X82=""),"NEEDS VALUATION",IF($AC82&lt;1,"OVERPRICED",IF(AND($AC82&gt;=Assumptions!$B$13,$V82&gt;=4),"BUY",IF($V82&gt;=3.4,"BUY CHEAPER",IF($V82&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG82" s="53" t="str">
+      <c r="AG82" s="51" t="str">
         <f aca="false">IF($AF82="","",IF($AF82="REJECT","Do not buy at any price",IF($AF82="NEEDS PRICE","Enter the current closeout price",IF($AF82="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF82="OVERPRICED","Worth less than break-even - walk",IF($AF82="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF82="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF82="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24618,7 +25661,7 @@
         <f aca="false">IF($A83="","",IF($S83="FAIL","REJECT",IF($D83="","NEEDS PRICE",IF(OR($W83="",$X83=""),"NEEDS VALUATION",IF($AC83&lt;1,"OVERPRICED",IF(AND($AC83&gt;=Assumptions!$B$13,$V83&gt;=4),"BUY",IF($V83&gt;=3.4,"BUY CHEAPER",IF($V83&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG83" s="53" t="str">
+      <c r="AG83" s="51" t="str">
         <f aca="false">IF($AF83="","",IF($AF83="REJECT","Do not buy at any price",IF($AF83="NEEDS PRICE","Enter the current closeout price",IF($AF83="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF83="OVERPRICED","Worth less than break-even - walk",IF($AF83="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF83="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF83="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24708,7 +25751,7 @@
         <f aca="false">IF($A84="","",IF($S84="FAIL","REJECT",IF($D84="","NEEDS PRICE",IF(OR($W84="",$X84=""),"NEEDS VALUATION",IF($AC84&lt;1,"OVERPRICED",IF(AND($AC84&gt;=Assumptions!$B$13,$V84&gt;=4),"BUY",IF($V84&gt;=3.4,"BUY CHEAPER",IF($V84&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG84" s="53" t="str">
+      <c r="AG84" s="51" t="str">
         <f aca="false">IF($AF84="","",IF($AF84="REJECT","Do not buy at any price",IF($AF84="NEEDS PRICE","Enter the current closeout price",IF($AF84="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF84="OVERPRICED","Worth less than break-even - walk",IF($AF84="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF84="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF84="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24798,7 +25841,7 @@
         <f aca="false">IF($A85="","",IF($S85="FAIL","REJECT",IF($D85="","NEEDS PRICE",IF(OR($W85="",$X85=""),"NEEDS VALUATION",IF($AC85&lt;1,"OVERPRICED",IF(AND($AC85&gt;=Assumptions!$B$13,$V85&gt;=4),"BUY",IF($V85&gt;=3.4,"BUY CHEAPER",IF($V85&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG85" s="53" t="str">
+      <c r="AG85" s="51" t="str">
         <f aca="false">IF($AF85="","",IF($AF85="REJECT","Do not buy at any price",IF($AF85="NEEDS PRICE","Enter the current closeout price",IF($AF85="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF85="OVERPRICED","Worth less than break-even - walk",IF($AF85="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF85="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF85="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24888,7 +25931,7 @@
         <f aca="false">IF($A86="","",IF($S86="FAIL","REJECT",IF($D86="","NEEDS PRICE",IF(OR($W86="",$X86=""),"NEEDS VALUATION",IF($AC86&lt;1,"OVERPRICED",IF(AND($AC86&gt;=Assumptions!$B$13,$V86&gt;=4),"BUY",IF($V86&gt;=3.4,"BUY CHEAPER",IF($V86&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG86" s="53" t="str">
+      <c r="AG86" s="51" t="str">
         <f aca="false">IF($AF86="","",IF($AF86="REJECT","Do not buy at any price",IF($AF86="NEEDS PRICE","Enter the current closeout price",IF($AF86="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF86="OVERPRICED","Worth less than break-even - walk",IF($AF86="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF86="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF86="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -24978,7 +26021,7 @@
         <f aca="false">IF($A87="","",IF($S87="FAIL","REJECT",IF($D87="","NEEDS PRICE",IF(OR($W87="",$X87=""),"NEEDS VALUATION",IF($AC87&lt;1,"OVERPRICED",IF(AND($AC87&gt;=Assumptions!$B$13,$V87&gt;=4),"BUY",IF($V87&gt;=3.4,"BUY CHEAPER",IF($V87&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG87" s="53" t="str">
+      <c r="AG87" s="51" t="str">
         <f aca="false">IF($AF87="","",IF($AF87="REJECT","Do not buy at any price",IF($AF87="NEEDS PRICE","Enter the current closeout price",IF($AF87="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF87="OVERPRICED","Worth less than break-even - walk",IF($AF87="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF87="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF87="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25068,7 +26111,7 @@
         <f aca="false">IF($A88="","",IF($S88="FAIL","REJECT",IF($D88="","NEEDS PRICE",IF(OR($W88="",$X88=""),"NEEDS VALUATION",IF($AC88&lt;1,"OVERPRICED",IF(AND($AC88&gt;=Assumptions!$B$13,$V88&gt;=4),"BUY",IF($V88&gt;=3.4,"BUY CHEAPER",IF($V88&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG88" s="53" t="str">
+      <c r="AG88" s="51" t="str">
         <f aca="false">IF($AF88="","",IF($AF88="REJECT","Do not buy at any price",IF($AF88="NEEDS PRICE","Enter the current closeout price",IF($AF88="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF88="OVERPRICED","Worth less than break-even - walk",IF($AF88="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF88="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF88="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25158,7 +26201,7 @@
         <f aca="false">IF($A89="","",IF($S89="FAIL","REJECT",IF($D89="","NEEDS PRICE",IF(OR($W89="",$X89=""),"NEEDS VALUATION",IF($AC89&lt;1,"OVERPRICED",IF(AND($AC89&gt;=Assumptions!$B$13,$V89&gt;=4),"BUY",IF($V89&gt;=3.4,"BUY CHEAPER",IF($V89&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG89" s="53" t="str">
+      <c r="AG89" s="51" t="str">
         <f aca="false">IF($AF89="","",IF($AF89="REJECT","Do not buy at any price",IF($AF89="NEEDS PRICE","Enter the current closeout price",IF($AF89="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF89="OVERPRICED","Worth less than break-even - walk",IF($AF89="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF89="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF89="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25248,7 +26291,7 @@
         <f aca="false">IF($A90="","",IF($S90="FAIL","REJECT",IF($D90="","NEEDS PRICE",IF(OR($W90="",$X90=""),"NEEDS VALUATION",IF($AC90&lt;1,"OVERPRICED",IF(AND($AC90&gt;=Assumptions!$B$13,$V90&gt;=4),"BUY",IF($V90&gt;=3.4,"BUY CHEAPER",IF($V90&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG90" s="53" t="str">
+      <c r="AG90" s="51" t="str">
         <f aca="false">IF($AF90="","",IF($AF90="REJECT","Do not buy at any price",IF($AF90="NEEDS PRICE","Enter the current closeout price",IF($AF90="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF90="OVERPRICED","Worth less than break-even - walk",IF($AF90="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF90="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF90="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25338,7 +26381,7 @@
         <f aca="false">IF($A91="","",IF($S91="FAIL","REJECT",IF($D91="","NEEDS PRICE",IF(OR($W91="",$X91=""),"NEEDS VALUATION",IF($AC91&lt;1,"OVERPRICED",IF(AND($AC91&gt;=Assumptions!$B$13,$V91&gt;=4),"BUY",IF($V91&gt;=3.4,"BUY CHEAPER",IF($V91&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG91" s="53" t="str">
+      <c r="AG91" s="51" t="str">
         <f aca="false">IF($AF91="","",IF($AF91="REJECT","Do not buy at any price",IF($AF91="NEEDS PRICE","Enter the current closeout price",IF($AF91="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF91="OVERPRICED","Worth less than break-even - walk",IF($AF91="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF91="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF91="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25428,7 +26471,7 @@
         <f aca="false">IF($A92="","",IF($S92="FAIL","REJECT",IF($D92="","NEEDS PRICE",IF(OR($W92="",$X92=""),"NEEDS VALUATION",IF($AC92&lt;1,"OVERPRICED",IF(AND($AC92&gt;=Assumptions!$B$13,$V92&gt;=4),"BUY",IF($V92&gt;=3.4,"BUY CHEAPER",IF($V92&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG92" s="53" t="str">
+      <c r="AG92" s="51" t="str">
         <f aca="false">IF($AF92="","",IF($AF92="REJECT","Do not buy at any price",IF($AF92="NEEDS PRICE","Enter the current closeout price",IF($AF92="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF92="OVERPRICED","Worth less than break-even - walk",IF($AF92="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF92="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF92="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25518,7 +26561,7 @@
         <f aca="false">IF($A93="","",IF($S93="FAIL","REJECT",IF($D93="","NEEDS PRICE",IF(OR($W93="",$X93=""),"NEEDS VALUATION",IF($AC93&lt;1,"OVERPRICED",IF(AND($AC93&gt;=Assumptions!$B$13,$V93&gt;=4),"BUY",IF($V93&gt;=3.4,"BUY CHEAPER",IF($V93&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG93" s="53" t="str">
+      <c r="AG93" s="51" t="str">
         <f aca="false">IF($AF93="","",IF($AF93="REJECT","Do not buy at any price",IF($AF93="NEEDS PRICE","Enter the current closeout price",IF($AF93="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF93="OVERPRICED","Worth less than break-even - walk",IF($AF93="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF93="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF93="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25608,7 +26651,7 @@
         <f aca="false">IF($A94="","",IF($S94="FAIL","REJECT",IF($D94="","NEEDS PRICE",IF(OR($W94="",$X94=""),"NEEDS VALUATION",IF($AC94&lt;1,"OVERPRICED",IF(AND($AC94&gt;=Assumptions!$B$13,$V94&gt;=4),"BUY",IF($V94&gt;=3.4,"BUY CHEAPER",IF($V94&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG94" s="53" t="str">
+      <c r="AG94" s="51" t="str">
         <f aca="false">IF($AF94="","",IF($AF94="REJECT","Do not buy at any price",IF($AF94="NEEDS PRICE","Enter the current closeout price",IF($AF94="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF94="OVERPRICED","Worth less than break-even - walk",IF($AF94="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF94="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF94="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25698,7 +26741,7 @@
         <f aca="false">IF($A95="","",IF($S95="FAIL","REJECT",IF($D95="","NEEDS PRICE",IF(OR($W95="",$X95=""),"NEEDS VALUATION",IF($AC95&lt;1,"OVERPRICED",IF(AND($AC95&gt;=Assumptions!$B$13,$V95&gt;=4),"BUY",IF($V95&gt;=3.4,"BUY CHEAPER",IF($V95&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG95" s="53" t="str">
+      <c r="AG95" s="51" t="str">
         <f aca="false">IF($AF95="","",IF($AF95="REJECT","Do not buy at any price",IF($AF95="NEEDS PRICE","Enter the current closeout price",IF($AF95="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF95="OVERPRICED","Worth less than break-even - walk",IF($AF95="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF95="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF95="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25788,7 +26831,7 @@
         <f aca="false">IF($A96="","",IF($S96="FAIL","REJECT",IF($D96="","NEEDS PRICE",IF(OR($W96="",$X96=""),"NEEDS VALUATION",IF($AC96&lt;1,"OVERPRICED",IF(AND($AC96&gt;=Assumptions!$B$13,$V96&gt;=4),"BUY",IF($V96&gt;=3.4,"BUY CHEAPER",IF($V96&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG96" s="53" t="str">
+      <c r="AG96" s="51" t="str">
         <f aca="false">IF($AF96="","",IF($AF96="REJECT","Do not buy at any price",IF($AF96="NEEDS PRICE","Enter the current closeout price",IF($AF96="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF96="OVERPRICED","Worth less than break-even - walk",IF($AF96="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF96="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF96="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25878,7 +26921,7 @@
         <f aca="false">IF($A97="","",IF($S97="FAIL","REJECT",IF($D97="","NEEDS PRICE",IF(OR($W97="",$X97=""),"NEEDS VALUATION",IF($AC97&lt;1,"OVERPRICED",IF(AND($AC97&gt;=Assumptions!$B$13,$V97&gt;=4),"BUY",IF($V97&gt;=3.4,"BUY CHEAPER",IF($V97&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG97" s="53" t="str">
+      <c r="AG97" s="51" t="str">
         <f aca="false">IF($AF97="","",IF($AF97="REJECT","Do not buy at any price",IF($AF97="NEEDS PRICE","Enter the current closeout price",IF($AF97="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF97="OVERPRICED","Worth less than break-even - walk",IF($AF97="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF97="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF97="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -25968,7 +27011,7 @@
         <f aca="false">IF($A98="","",IF($S98="FAIL","REJECT",IF($D98="","NEEDS PRICE",IF(OR($W98="",$X98=""),"NEEDS VALUATION",IF($AC98&lt;1,"OVERPRICED",IF(AND($AC98&gt;=Assumptions!$B$13,$V98&gt;=4),"BUY",IF($V98&gt;=3.4,"BUY CHEAPER",IF($V98&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG98" s="53" t="str">
+      <c r="AG98" s="51" t="str">
         <f aca="false">IF($AF98="","",IF($AF98="REJECT","Do not buy at any price",IF($AF98="NEEDS PRICE","Enter the current closeout price",IF($AF98="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF98="OVERPRICED","Worth less than break-even - walk",IF($AF98="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF98="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF98="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26058,7 +27101,7 @@
         <f aca="false">IF($A99="","",IF($S99="FAIL","REJECT",IF($D99="","NEEDS PRICE",IF(OR($W99="",$X99=""),"NEEDS VALUATION",IF($AC99&lt;1,"OVERPRICED",IF(AND($AC99&gt;=Assumptions!$B$13,$V99&gt;=4),"BUY",IF($V99&gt;=3.4,"BUY CHEAPER",IF($V99&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG99" s="53" t="str">
+      <c r="AG99" s="51" t="str">
         <f aca="false">IF($AF99="","",IF($AF99="REJECT","Do not buy at any price",IF($AF99="NEEDS PRICE","Enter the current closeout price",IF($AF99="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF99="OVERPRICED","Worth less than break-even - walk",IF($AF99="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF99="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF99="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26148,7 +27191,7 @@
         <f aca="false">IF($A100="","",IF($S100="FAIL","REJECT",IF($D100="","NEEDS PRICE",IF(OR($W100="",$X100=""),"NEEDS VALUATION",IF($AC100&lt;1,"OVERPRICED",IF(AND($AC100&gt;=Assumptions!$B$13,$V100&gt;=4),"BUY",IF($V100&gt;=3.4,"BUY CHEAPER",IF($V100&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG100" s="53" t="str">
+      <c r="AG100" s="51" t="str">
         <f aca="false">IF($AF100="","",IF($AF100="REJECT","Do not buy at any price",IF($AF100="NEEDS PRICE","Enter the current closeout price",IF($AF100="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF100="OVERPRICED","Worth less than break-even - walk",IF($AF100="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF100="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF100="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26238,7 +27281,7 @@
         <f aca="false">IF($A101="","",IF($S101="FAIL","REJECT",IF($D101="","NEEDS PRICE",IF(OR($W101="",$X101=""),"NEEDS VALUATION",IF($AC101&lt;1,"OVERPRICED",IF(AND($AC101&gt;=Assumptions!$B$13,$V101&gt;=4),"BUY",IF($V101&gt;=3.4,"BUY CHEAPER",IF($V101&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG101" s="53" t="str">
+      <c r="AG101" s="51" t="str">
         <f aca="false">IF($AF101="","",IF($AF101="REJECT","Do not buy at any price",IF($AF101="NEEDS PRICE","Enter the current closeout price",IF($AF101="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF101="OVERPRICED","Worth less than break-even - walk",IF($AF101="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF101="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF101="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26328,7 +27371,7 @@
         <f aca="false">IF($A102="","",IF($S102="FAIL","REJECT",IF($D102="","NEEDS PRICE",IF(OR($W102="",$X102=""),"NEEDS VALUATION",IF($AC102&lt;1,"OVERPRICED",IF(AND($AC102&gt;=Assumptions!$B$13,$V102&gt;=4),"BUY",IF($V102&gt;=3.4,"BUY CHEAPER",IF($V102&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG102" s="53" t="str">
+      <c r="AG102" s="51" t="str">
         <f aca="false">IF($AF102="","",IF($AF102="REJECT","Do not buy at any price",IF($AF102="NEEDS PRICE","Enter the current closeout price",IF($AF102="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF102="OVERPRICED","Worth less than break-even - walk",IF($AF102="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF102="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF102="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26418,7 +27461,7 @@
         <f aca="false">IF($A103="","",IF($S103="FAIL","REJECT",IF($D103="","NEEDS PRICE",IF(OR($W103="",$X103=""),"NEEDS VALUATION",IF($AC103&lt;1,"OVERPRICED",IF(AND($AC103&gt;=Assumptions!$B$13,$V103&gt;=4),"BUY",IF($V103&gt;=3.4,"BUY CHEAPER",IF($V103&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG103" s="53" t="str">
+      <c r="AG103" s="51" t="str">
         <f aca="false">IF($AF103="","",IF($AF103="REJECT","Do not buy at any price",IF($AF103="NEEDS PRICE","Enter the current closeout price",IF($AF103="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF103="OVERPRICED","Worth less than break-even - walk",IF($AF103="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF103="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF103="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26508,7 +27551,7 @@
         <f aca="false">IF($A104="","",IF($S104="FAIL","REJECT",IF($D104="","NEEDS PRICE",IF(OR($W104="",$X104=""),"NEEDS VALUATION",IF($AC104&lt;1,"OVERPRICED",IF(AND($AC104&gt;=Assumptions!$B$13,$V104&gt;=4),"BUY",IF($V104&gt;=3.4,"BUY CHEAPER",IF($V104&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG104" s="53" t="str">
+      <c r="AG104" s="51" t="str">
         <f aca="false">IF($AF104="","",IF($AF104="REJECT","Do not buy at any price",IF($AF104="NEEDS PRICE","Enter the current closeout price",IF($AF104="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF104="OVERPRICED","Worth less than break-even - walk",IF($AF104="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF104="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF104="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26598,7 +27641,7 @@
         <f aca="false">IF($A105="","",IF($S105="FAIL","REJECT",IF($D105="","NEEDS PRICE",IF(OR($W105="",$X105=""),"NEEDS VALUATION",IF($AC105&lt;1,"OVERPRICED",IF(AND($AC105&gt;=Assumptions!$B$13,$V105&gt;=4),"BUY",IF($V105&gt;=3.4,"BUY CHEAPER",IF($V105&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG105" s="53" t="str">
+      <c r="AG105" s="51" t="str">
         <f aca="false">IF($AF105="","",IF($AF105="REJECT","Do not buy at any price",IF($AF105="NEEDS PRICE","Enter the current closeout price",IF($AF105="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF105="OVERPRICED","Worth less than break-even - walk",IF($AF105="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF105="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF105="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26688,7 +27731,7 @@
         <f aca="false">IF($A106="","",IF($S106="FAIL","REJECT",IF($D106="","NEEDS PRICE",IF(OR($W106="",$X106=""),"NEEDS VALUATION",IF($AC106&lt;1,"OVERPRICED",IF(AND($AC106&gt;=Assumptions!$B$13,$V106&gt;=4),"BUY",IF($V106&gt;=3.4,"BUY CHEAPER",IF($V106&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG106" s="53" t="str">
+      <c r="AG106" s="51" t="str">
         <f aca="false">IF($AF106="","",IF($AF106="REJECT","Do not buy at any price",IF($AF106="NEEDS PRICE","Enter the current closeout price",IF($AF106="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF106="OVERPRICED","Worth less than break-even - walk",IF($AF106="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF106="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF106="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26778,7 +27821,7 @@
         <f aca="false">IF($A107="","",IF($S107="FAIL","REJECT",IF($D107="","NEEDS PRICE",IF(OR($W107="",$X107=""),"NEEDS VALUATION",IF($AC107&lt;1,"OVERPRICED",IF(AND($AC107&gt;=Assumptions!$B$13,$V107&gt;=4),"BUY",IF($V107&gt;=3.4,"BUY CHEAPER",IF($V107&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG107" s="53" t="str">
+      <c r="AG107" s="51" t="str">
         <f aca="false">IF($AF107="","",IF($AF107="REJECT","Do not buy at any price",IF($AF107="NEEDS PRICE","Enter the current closeout price",IF($AF107="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF107="OVERPRICED","Worth less than break-even - walk",IF($AF107="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF107="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF107="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26868,7 +27911,7 @@
         <f aca="false">IF($A108="","",IF($S108="FAIL","REJECT",IF($D108="","NEEDS PRICE",IF(OR($W108="",$X108=""),"NEEDS VALUATION",IF($AC108&lt;1,"OVERPRICED",IF(AND($AC108&gt;=Assumptions!$B$13,$V108&gt;=4),"BUY",IF($V108&gt;=3.4,"BUY CHEAPER",IF($V108&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG108" s="53" t="str">
+      <c r="AG108" s="51" t="str">
         <f aca="false">IF($AF108="","",IF($AF108="REJECT","Do not buy at any price",IF($AF108="NEEDS PRICE","Enter the current closeout price",IF($AF108="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF108="OVERPRICED","Worth less than break-even - walk",IF($AF108="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF108="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF108="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -26958,7 +28001,7 @@
         <f aca="false">IF($A109="","",IF($S109="FAIL","REJECT",IF($D109="","NEEDS PRICE",IF(OR($W109="",$X109=""),"NEEDS VALUATION",IF($AC109&lt;1,"OVERPRICED",IF(AND($AC109&gt;=Assumptions!$B$13,$V109&gt;=4),"BUY",IF($V109&gt;=3.4,"BUY CHEAPER",IF($V109&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG109" s="53" t="str">
+      <c r="AG109" s="51" t="str">
         <f aca="false">IF($AF109="","",IF($AF109="REJECT","Do not buy at any price",IF($AF109="NEEDS PRICE","Enter the current closeout price",IF($AF109="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF109="OVERPRICED","Worth less than break-even - walk",IF($AF109="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF109="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF109="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27048,7 +28091,7 @@
         <f aca="false">IF($A110="","",IF($S110="FAIL","REJECT",IF($D110="","NEEDS PRICE",IF(OR($W110="",$X110=""),"NEEDS VALUATION",IF($AC110&lt;1,"OVERPRICED",IF(AND($AC110&gt;=Assumptions!$B$13,$V110&gt;=4),"BUY",IF($V110&gt;=3.4,"BUY CHEAPER",IF($V110&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG110" s="53" t="str">
+      <c r="AG110" s="51" t="str">
         <f aca="false">IF($AF110="","",IF($AF110="REJECT","Do not buy at any price",IF($AF110="NEEDS PRICE","Enter the current closeout price",IF($AF110="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF110="OVERPRICED","Worth less than break-even - walk",IF($AF110="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF110="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF110="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27138,7 +28181,7 @@
         <f aca="false">IF($A111="","",IF($S111="FAIL","REJECT",IF($D111="","NEEDS PRICE",IF(OR($W111="",$X111=""),"NEEDS VALUATION",IF($AC111&lt;1,"OVERPRICED",IF(AND($AC111&gt;=Assumptions!$B$13,$V111&gt;=4),"BUY",IF($V111&gt;=3.4,"BUY CHEAPER",IF($V111&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG111" s="53" t="str">
+      <c r="AG111" s="51" t="str">
         <f aca="false">IF($AF111="","",IF($AF111="REJECT","Do not buy at any price",IF($AF111="NEEDS PRICE","Enter the current closeout price",IF($AF111="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF111="OVERPRICED","Worth less than break-even - walk",IF($AF111="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF111="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF111="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27228,7 +28271,7 @@
         <f aca="false">IF($A112="","",IF($S112="FAIL","REJECT",IF($D112="","NEEDS PRICE",IF(OR($W112="",$X112=""),"NEEDS VALUATION",IF($AC112&lt;1,"OVERPRICED",IF(AND($AC112&gt;=Assumptions!$B$13,$V112&gt;=4),"BUY",IF($V112&gt;=3.4,"BUY CHEAPER",IF($V112&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG112" s="53" t="str">
+      <c r="AG112" s="51" t="str">
         <f aca="false">IF($AF112="","",IF($AF112="REJECT","Do not buy at any price",IF($AF112="NEEDS PRICE","Enter the current closeout price",IF($AF112="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF112="OVERPRICED","Worth less than break-even - walk",IF($AF112="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF112="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF112="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27318,7 +28361,7 @@
         <f aca="false">IF($A113="","",IF($S113="FAIL","REJECT",IF($D113="","NEEDS PRICE",IF(OR($W113="",$X113=""),"NEEDS VALUATION",IF($AC113&lt;1,"OVERPRICED",IF(AND($AC113&gt;=Assumptions!$B$13,$V113&gt;=4),"BUY",IF($V113&gt;=3.4,"BUY CHEAPER",IF($V113&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG113" s="53" t="str">
+      <c r="AG113" s="51" t="str">
         <f aca="false">IF($AF113="","",IF($AF113="REJECT","Do not buy at any price",IF($AF113="NEEDS PRICE","Enter the current closeout price",IF($AF113="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF113="OVERPRICED","Worth less than break-even - walk",IF($AF113="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF113="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF113="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27408,7 +28451,7 @@
         <f aca="false">IF($A114="","",IF($S114="FAIL","REJECT",IF($D114="","NEEDS PRICE",IF(OR($W114="",$X114=""),"NEEDS VALUATION",IF($AC114&lt;1,"OVERPRICED",IF(AND($AC114&gt;=Assumptions!$B$13,$V114&gt;=4),"BUY",IF($V114&gt;=3.4,"BUY CHEAPER",IF($V114&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG114" s="53" t="str">
+      <c r="AG114" s="51" t="str">
         <f aca="false">IF($AF114="","",IF($AF114="REJECT","Do not buy at any price",IF($AF114="NEEDS PRICE","Enter the current closeout price",IF($AF114="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF114="OVERPRICED","Worth less than break-even - walk",IF($AF114="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF114="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF114="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27498,7 +28541,7 @@
         <f aca="false">IF($A115="","",IF($S115="FAIL","REJECT",IF($D115="","NEEDS PRICE",IF(OR($W115="",$X115=""),"NEEDS VALUATION",IF($AC115&lt;1,"OVERPRICED",IF(AND($AC115&gt;=Assumptions!$B$13,$V115&gt;=4),"BUY",IF($V115&gt;=3.4,"BUY CHEAPER",IF($V115&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG115" s="53" t="str">
+      <c r="AG115" s="51" t="str">
         <f aca="false">IF($AF115="","",IF($AF115="REJECT","Do not buy at any price",IF($AF115="NEEDS PRICE","Enter the current closeout price",IF($AF115="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF115="OVERPRICED","Worth less than break-even - walk",IF($AF115="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF115="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF115="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27588,7 +28631,7 @@
         <f aca="false">IF($A116="","",IF($S116="FAIL","REJECT",IF($D116="","NEEDS PRICE",IF(OR($W116="",$X116=""),"NEEDS VALUATION",IF($AC116&lt;1,"OVERPRICED",IF(AND($AC116&gt;=Assumptions!$B$13,$V116&gt;=4),"BUY",IF($V116&gt;=3.4,"BUY CHEAPER",IF($V116&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG116" s="53" t="str">
+      <c r="AG116" s="51" t="str">
         <f aca="false">IF($AF116="","",IF($AF116="REJECT","Do not buy at any price",IF($AF116="NEEDS PRICE","Enter the current closeout price",IF($AF116="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF116="OVERPRICED","Worth less than break-even - walk",IF($AF116="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF116="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF116="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27678,7 +28721,7 @@
         <f aca="false">IF($A117="","",IF($S117="FAIL","REJECT",IF($D117="","NEEDS PRICE",IF(OR($W117="",$X117=""),"NEEDS VALUATION",IF($AC117&lt;1,"OVERPRICED",IF(AND($AC117&gt;=Assumptions!$B$13,$V117&gt;=4),"BUY",IF($V117&gt;=3.4,"BUY CHEAPER",IF($V117&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG117" s="53" t="str">
+      <c r="AG117" s="51" t="str">
         <f aca="false">IF($AF117="","",IF($AF117="REJECT","Do not buy at any price",IF($AF117="NEEDS PRICE","Enter the current closeout price",IF($AF117="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF117="OVERPRICED","Worth less than break-even - walk",IF($AF117="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF117="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF117="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27768,7 +28811,7 @@
         <f aca="false">IF($A118="","",IF($S118="FAIL","REJECT",IF($D118="","NEEDS PRICE",IF(OR($W118="",$X118=""),"NEEDS VALUATION",IF($AC118&lt;1,"OVERPRICED",IF(AND($AC118&gt;=Assumptions!$B$13,$V118&gt;=4),"BUY",IF($V118&gt;=3.4,"BUY CHEAPER",IF($V118&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG118" s="53" t="str">
+      <c r="AG118" s="51" t="str">
         <f aca="false">IF($AF118="","",IF($AF118="REJECT","Do not buy at any price",IF($AF118="NEEDS PRICE","Enter the current closeout price",IF($AF118="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF118="OVERPRICED","Worth less than break-even - walk",IF($AF118="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF118="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF118="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27858,7 +28901,7 @@
         <f aca="false">IF($A119="","",IF($S119="FAIL","REJECT",IF($D119="","NEEDS PRICE",IF(OR($W119="",$X119=""),"NEEDS VALUATION",IF($AC119&lt;1,"OVERPRICED",IF(AND($AC119&gt;=Assumptions!$B$13,$V119&gt;=4),"BUY",IF($V119&gt;=3.4,"BUY CHEAPER",IF($V119&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG119" s="53" t="str">
+      <c r="AG119" s="51" t="str">
         <f aca="false">IF($AF119="","",IF($AF119="REJECT","Do not buy at any price",IF($AF119="NEEDS PRICE","Enter the current closeout price",IF($AF119="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF119="OVERPRICED","Worth less than break-even - walk",IF($AF119="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF119="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF119="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -27948,7 +28991,7 @@
         <f aca="false">IF($A120="","",IF($S120="FAIL","REJECT",IF($D120="","NEEDS PRICE",IF(OR($W120="",$X120=""),"NEEDS VALUATION",IF($AC120&lt;1,"OVERPRICED",IF(AND($AC120&gt;=Assumptions!$B$13,$V120&gt;=4),"BUY",IF($V120&gt;=3.4,"BUY CHEAPER",IF($V120&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG120" s="53" t="str">
+      <c r="AG120" s="51" t="str">
         <f aca="false">IF($AF120="","",IF($AF120="REJECT","Do not buy at any price",IF($AF120="NEEDS PRICE","Enter the current closeout price",IF($AF120="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF120="OVERPRICED","Worth less than break-even - walk",IF($AF120="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF120="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF120="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28038,7 +29081,7 @@
         <f aca="false">IF($A121="","",IF($S121="FAIL","REJECT",IF($D121="","NEEDS PRICE",IF(OR($W121="",$X121=""),"NEEDS VALUATION",IF($AC121&lt;1,"OVERPRICED",IF(AND($AC121&gt;=Assumptions!$B$13,$V121&gt;=4),"BUY",IF($V121&gt;=3.4,"BUY CHEAPER",IF($V121&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG121" s="53" t="str">
+      <c r="AG121" s="51" t="str">
         <f aca="false">IF($AF121="","",IF($AF121="REJECT","Do not buy at any price",IF($AF121="NEEDS PRICE","Enter the current closeout price",IF($AF121="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF121="OVERPRICED","Worth less than break-even - walk",IF($AF121="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF121="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF121="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28128,7 +29171,7 @@
         <f aca="false">IF($A122="","",IF($S122="FAIL","REJECT",IF($D122="","NEEDS PRICE",IF(OR($W122="",$X122=""),"NEEDS VALUATION",IF($AC122&lt;1,"OVERPRICED",IF(AND($AC122&gt;=Assumptions!$B$13,$V122&gt;=4),"BUY",IF($V122&gt;=3.4,"BUY CHEAPER",IF($V122&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG122" s="53" t="str">
+      <c r="AG122" s="51" t="str">
         <f aca="false">IF($AF122="","",IF($AF122="REJECT","Do not buy at any price",IF($AF122="NEEDS PRICE","Enter the current closeout price",IF($AF122="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF122="OVERPRICED","Worth less than break-even - walk",IF($AF122="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF122="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF122="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28218,7 +29261,7 @@
         <f aca="false">IF($A123="","",IF($S123="FAIL","REJECT",IF($D123="","NEEDS PRICE",IF(OR($W123="",$X123=""),"NEEDS VALUATION",IF($AC123&lt;1,"OVERPRICED",IF(AND($AC123&gt;=Assumptions!$B$13,$V123&gt;=4),"BUY",IF($V123&gt;=3.4,"BUY CHEAPER",IF($V123&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG123" s="53" t="str">
+      <c r="AG123" s="51" t="str">
         <f aca="false">IF($AF123="","",IF($AF123="REJECT","Do not buy at any price",IF($AF123="NEEDS PRICE","Enter the current closeout price",IF($AF123="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF123="OVERPRICED","Worth less than break-even - walk",IF($AF123="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF123="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF123="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28308,7 +29351,7 @@
         <f aca="false">IF($A124="","",IF($S124="FAIL","REJECT",IF($D124="","NEEDS PRICE",IF(OR($W124="",$X124=""),"NEEDS VALUATION",IF($AC124&lt;1,"OVERPRICED",IF(AND($AC124&gt;=Assumptions!$B$13,$V124&gt;=4),"BUY",IF($V124&gt;=3.4,"BUY CHEAPER",IF($V124&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG124" s="53" t="str">
+      <c r="AG124" s="51" t="str">
         <f aca="false">IF($AF124="","",IF($AF124="REJECT","Do not buy at any price",IF($AF124="NEEDS PRICE","Enter the current closeout price",IF($AF124="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF124="OVERPRICED","Worth less than break-even - walk",IF($AF124="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF124="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF124="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28398,7 +29441,7 @@
         <f aca="false">IF($A125="","",IF($S125="FAIL","REJECT",IF($D125="","NEEDS PRICE",IF(OR($W125="",$X125=""),"NEEDS VALUATION",IF($AC125&lt;1,"OVERPRICED",IF(AND($AC125&gt;=Assumptions!$B$13,$V125&gt;=4),"BUY",IF($V125&gt;=3.4,"BUY CHEAPER",IF($V125&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG125" s="53" t="str">
+      <c r="AG125" s="51" t="str">
         <f aca="false">IF($AF125="","",IF($AF125="REJECT","Do not buy at any price",IF($AF125="NEEDS PRICE","Enter the current closeout price",IF($AF125="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF125="OVERPRICED","Worth less than break-even - walk",IF($AF125="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF125="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF125="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28488,7 +29531,7 @@
         <f aca="false">IF($A126="","",IF($S126="FAIL","REJECT",IF($D126="","NEEDS PRICE",IF(OR($W126="",$X126=""),"NEEDS VALUATION",IF($AC126&lt;1,"OVERPRICED",IF(AND($AC126&gt;=Assumptions!$B$13,$V126&gt;=4),"BUY",IF($V126&gt;=3.4,"BUY CHEAPER",IF($V126&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG126" s="53" t="str">
+      <c r="AG126" s="51" t="str">
         <f aca="false">IF($AF126="","",IF($AF126="REJECT","Do not buy at any price",IF($AF126="NEEDS PRICE","Enter the current closeout price",IF($AF126="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF126="OVERPRICED","Worth less than break-even - walk",IF($AF126="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF126="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF126="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28578,7 +29621,7 @@
         <f aca="false">IF($A127="","",IF($S127="FAIL","REJECT",IF($D127="","NEEDS PRICE",IF(OR($W127="",$X127=""),"NEEDS VALUATION",IF($AC127&lt;1,"OVERPRICED",IF(AND($AC127&gt;=Assumptions!$B$13,$V127&gt;=4),"BUY",IF($V127&gt;=3.4,"BUY CHEAPER",IF($V127&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG127" s="53" t="str">
+      <c r="AG127" s="51" t="str">
         <f aca="false">IF($AF127="","",IF($AF127="REJECT","Do not buy at any price",IF($AF127="NEEDS PRICE","Enter the current closeout price",IF($AF127="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF127="OVERPRICED","Worth less than break-even - walk",IF($AF127="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF127="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF127="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28668,7 +29711,7 @@
         <f aca="false">IF($A128="","",IF($S128="FAIL","REJECT",IF($D128="","NEEDS PRICE",IF(OR($W128="",$X128=""),"NEEDS VALUATION",IF($AC128&lt;1,"OVERPRICED",IF(AND($AC128&gt;=Assumptions!$B$13,$V128&gt;=4),"BUY",IF($V128&gt;=3.4,"BUY CHEAPER",IF($V128&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG128" s="53" t="str">
+      <c r="AG128" s="51" t="str">
         <f aca="false">IF($AF128="","",IF($AF128="REJECT","Do not buy at any price",IF($AF128="NEEDS PRICE","Enter the current closeout price",IF($AF128="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF128="OVERPRICED","Worth less than break-even - walk",IF($AF128="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF128="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF128="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28758,7 +29801,7 @@
         <f aca="false">IF($A129="","",IF($S129="FAIL","REJECT",IF($D129="","NEEDS PRICE",IF(OR($W129="",$X129=""),"NEEDS VALUATION",IF($AC129&lt;1,"OVERPRICED",IF(AND($AC129&gt;=Assumptions!$B$13,$V129&gt;=4),"BUY",IF($V129&gt;=3.4,"BUY CHEAPER",IF($V129&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG129" s="53" t="str">
+      <c r="AG129" s="51" t="str">
         <f aca="false">IF($AF129="","",IF($AF129="REJECT","Do not buy at any price",IF($AF129="NEEDS PRICE","Enter the current closeout price",IF($AF129="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF129="OVERPRICED","Worth less than break-even - walk",IF($AF129="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF129="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF129="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28848,7 +29891,7 @@
         <f aca="false">IF($A130="","",IF($S130="FAIL","REJECT",IF($D130="","NEEDS PRICE",IF(OR($W130="",$X130=""),"NEEDS VALUATION",IF($AC130&lt;1,"OVERPRICED",IF(AND($AC130&gt;=Assumptions!$B$13,$V130&gt;=4),"BUY",IF($V130&gt;=3.4,"BUY CHEAPER",IF($V130&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG130" s="53" t="str">
+      <c r="AG130" s="51" t="str">
         <f aca="false">IF($AF130="","",IF($AF130="REJECT","Do not buy at any price",IF($AF130="NEEDS PRICE","Enter the current closeout price",IF($AF130="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF130="OVERPRICED","Worth less than break-even - walk",IF($AF130="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF130="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF130="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -28938,7 +29981,7 @@
         <f aca="false">IF($A131="","",IF($S131="FAIL","REJECT",IF($D131="","NEEDS PRICE",IF(OR($W131="",$X131=""),"NEEDS VALUATION",IF($AC131&lt;1,"OVERPRICED",IF(AND($AC131&gt;=Assumptions!$B$13,$V131&gt;=4),"BUY",IF($V131&gt;=3.4,"BUY CHEAPER",IF($V131&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG131" s="53" t="str">
+      <c r="AG131" s="51" t="str">
         <f aca="false">IF($AF131="","",IF($AF131="REJECT","Do not buy at any price",IF($AF131="NEEDS PRICE","Enter the current closeout price",IF($AF131="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF131="OVERPRICED","Worth less than break-even - walk",IF($AF131="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF131="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF131="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29028,7 +30071,7 @@
         <f aca="false">IF($A132="","",IF($S132="FAIL","REJECT",IF($D132="","NEEDS PRICE",IF(OR($W132="",$X132=""),"NEEDS VALUATION",IF($AC132&lt;1,"OVERPRICED",IF(AND($AC132&gt;=Assumptions!$B$13,$V132&gt;=4),"BUY",IF($V132&gt;=3.4,"BUY CHEAPER",IF($V132&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG132" s="53" t="str">
+      <c r="AG132" s="51" t="str">
         <f aca="false">IF($AF132="","",IF($AF132="REJECT","Do not buy at any price",IF($AF132="NEEDS PRICE","Enter the current closeout price",IF($AF132="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF132="OVERPRICED","Worth less than break-even - walk",IF($AF132="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF132="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF132="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29118,7 +30161,7 @@
         <f aca="false">IF($A133="","",IF($S133="FAIL","REJECT",IF($D133="","NEEDS PRICE",IF(OR($W133="",$X133=""),"NEEDS VALUATION",IF($AC133&lt;1,"OVERPRICED",IF(AND($AC133&gt;=Assumptions!$B$13,$V133&gt;=4),"BUY",IF($V133&gt;=3.4,"BUY CHEAPER",IF($V133&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG133" s="53" t="str">
+      <c r="AG133" s="51" t="str">
         <f aca="false">IF($AF133="","",IF($AF133="REJECT","Do not buy at any price",IF($AF133="NEEDS PRICE","Enter the current closeout price",IF($AF133="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF133="OVERPRICED","Worth less than break-even - walk",IF($AF133="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF133="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF133="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29208,7 +30251,7 @@
         <f aca="false">IF($A134="","",IF($S134="FAIL","REJECT",IF($D134="","NEEDS PRICE",IF(OR($W134="",$X134=""),"NEEDS VALUATION",IF($AC134&lt;1,"OVERPRICED",IF(AND($AC134&gt;=Assumptions!$B$13,$V134&gt;=4),"BUY",IF($V134&gt;=3.4,"BUY CHEAPER",IF($V134&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG134" s="53" t="str">
+      <c r="AG134" s="51" t="str">
         <f aca="false">IF($AF134="","",IF($AF134="REJECT","Do not buy at any price",IF($AF134="NEEDS PRICE","Enter the current closeout price",IF($AF134="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF134="OVERPRICED","Worth less than break-even - walk",IF($AF134="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF134="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF134="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29298,7 +30341,7 @@
         <f aca="false">IF($A135="","",IF($S135="FAIL","REJECT",IF($D135="","NEEDS PRICE",IF(OR($W135="",$X135=""),"NEEDS VALUATION",IF($AC135&lt;1,"OVERPRICED",IF(AND($AC135&gt;=Assumptions!$B$13,$V135&gt;=4),"BUY",IF($V135&gt;=3.4,"BUY CHEAPER",IF($V135&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG135" s="53" t="str">
+      <c r="AG135" s="51" t="str">
         <f aca="false">IF($AF135="","",IF($AF135="REJECT","Do not buy at any price",IF($AF135="NEEDS PRICE","Enter the current closeout price",IF($AF135="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF135="OVERPRICED","Worth less than break-even - walk",IF($AF135="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF135="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF135="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29388,7 +30431,7 @@
         <f aca="false">IF($A136="","",IF($S136="FAIL","REJECT",IF($D136="","NEEDS PRICE",IF(OR($W136="",$X136=""),"NEEDS VALUATION",IF($AC136&lt;1,"OVERPRICED",IF(AND($AC136&gt;=Assumptions!$B$13,$V136&gt;=4),"BUY",IF($V136&gt;=3.4,"BUY CHEAPER",IF($V136&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG136" s="53" t="str">
+      <c r="AG136" s="51" t="str">
         <f aca="false">IF($AF136="","",IF($AF136="REJECT","Do not buy at any price",IF($AF136="NEEDS PRICE","Enter the current closeout price",IF($AF136="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF136="OVERPRICED","Worth less than break-even - walk",IF($AF136="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF136="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF136="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29478,7 +30521,7 @@
         <f aca="false">IF($A137="","",IF($S137="FAIL","REJECT",IF($D137="","NEEDS PRICE",IF(OR($W137="",$X137=""),"NEEDS VALUATION",IF($AC137&lt;1,"OVERPRICED",IF(AND($AC137&gt;=Assumptions!$B$13,$V137&gt;=4),"BUY",IF($V137&gt;=3.4,"BUY CHEAPER",IF($V137&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG137" s="53" t="str">
+      <c r="AG137" s="51" t="str">
         <f aca="false">IF($AF137="","",IF($AF137="REJECT","Do not buy at any price",IF($AF137="NEEDS PRICE","Enter the current closeout price",IF($AF137="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF137="OVERPRICED","Worth less than break-even - walk",IF($AF137="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF137="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF137="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29568,7 +30611,7 @@
         <f aca="false">IF($A138="","",IF($S138="FAIL","REJECT",IF($D138="","NEEDS PRICE",IF(OR($W138="",$X138=""),"NEEDS VALUATION",IF($AC138&lt;1,"OVERPRICED",IF(AND($AC138&gt;=Assumptions!$B$13,$V138&gt;=4),"BUY",IF($V138&gt;=3.4,"BUY CHEAPER",IF($V138&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG138" s="53" t="str">
+      <c r="AG138" s="51" t="str">
         <f aca="false">IF($AF138="","",IF($AF138="REJECT","Do not buy at any price",IF($AF138="NEEDS PRICE","Enter the current closeout price",IF($AF138="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF138="OVERPRICED","Worth less than break-even - walk",IF($AF138="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF138="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF138="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29658,7 +30701,7 @@
         <f aca="false">IF($A139="","",IF($S139="FAIL","REJECT",IF($D139="","NEEDS PRICE",IF(OR($W139="",$X139=""),"NEEDS VALUATION",IF($AC139&lt;1,"OVERPRICED",IF(AND($AC139&gt;=Assumptions!$B$13,$V139&gt;=4),"BUY",IF($V139&gt;=3.4,"BUY CHEAPER",IF($V139&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG139" s="53" t="str">
+      <c r="AG139" s="51" t="str">
         <f aca="false">IF($AF139="","",IF($AF139="REJECT","Do not buy at any price",IF($AF139="NEEDS PRICE","Enter the current closeout price",IF($AF139="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF139="OVERPRICED","Worth less than break-even - walk",IF($AF139="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF139="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF139="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29748,7 +30791,7 @@
         <f aca="false">IF($A140="","",IF($S140="FAIL","REJECT",IF($D140="","NEEDS PRICE",IF(OR($W140="",$X140=""),"NEEDS VALUATION",IF($AC140&lt;1,"OVERPRICED",IF(AND($AC140&gt;=Assumptions!$B$13,$V140&gt;=4),"BUY",IF($V140&gt;=3.4,"BUY CHEAPER",IF($V140&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG140" s="53" t="str">
+      <c r="AG140" s="51" t="str">
         <f aca="false">IF($AF140="","",IF($AF140="REJECT","Do not buy at any price",IF($AF140="NEEDS PRICE","Enter the current closeout price",IF($AF140="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF140="OVERPRICED","Worth less than break-even - walk",IF($AF140="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF140="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF140="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29838,7 +30881,7 @@
         <f aca="false">IF($A141="","",IF($S141="FAIL","REJECT",IF($D141="","NEEDS PRICE",IF(OR($W141="",$X141=""),"NEEDS VALUATION",IF($AC141&lt;1,"OVERPRICED",IF(AND($AC141&gt;=Assumptions!$B$13,$V141&gt;=4),"BUY",IF($V141&gt;=3.4,"BUY CHEAPER",IF($V141&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG141" s="53" t="str">
+      <c r="AG141" s="51" t="str">
         <f aca="false">IF($AF141="","",IF($AF141="REJECT","Do not buy at any price",IF($AF141="NEEDS PRICE","Enter the current closeout price",IF($AF141="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF141="OVERPRICED","Worth less than break-even - walk",IF($AF141="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF141="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF141="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -29928,7 +30971,7 @@
         <f aca="false">IF($A142="","",IF($S142="FAIL","REJECT",IF($D142="","NEEDS PRICE",IF(OR($W142="",$X142=""),"NEEDS VALUATION",IF($AC142&lt;1,"OVERPRICED",IF(AND($AC142&gt;=Assumptions!$B$13,$V142&gt;=4),"BUY",IF($V142&gt;=3.4,"BUY CHEAPER",IF($V142&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG142" s="53" t="str">
+      <c r="AG142" s="51" t="str">
         <f aca="false">IF($AF142="","",IF($AF142="REJECT","Do not buy at any price",IF($AF142="NEEDS PRICE","Enter the current closeout price",IF($AF142="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF142="OVERPRICED","Worth less than break-even - walk",IF($AF142="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF142="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF142="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30018,7 +31061,7 @@
         <f aca="false">IF($A143="","",IF($S143="FAIL","REJECT",IF($D143="","NEEDS PRICE",IF(OR($W143="",$X143=""),"NEEDS VALUATION",IF($AC143&lt;1,"OVERPRICED",IF(AND($AC143&gt;=Assumptions!$B$13,$V143&gt;=4),"BUY",IF($V143&gt;=3.4,"BUY CHEAPER",IF($V143&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG143" s="53" t="str">
+      <c r="AG143" s="51" t="str">
         <f aca="false">IF($AF143="","",IF($AF143="REJECT","Do not buy at any price",IF($AF143="NEEDS PRICE","Enter the current closeout price",IF($AF143="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF143="OVERPRICED","Worth less than break-even - walk",IF($AF143="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF143="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF143="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30108,7 +31151,7 @@
         <f aca="false">IF($A144="","",IF($S144="FAIL","REJECT",IF($D144="","NEEDS PRICE",IF(OR($W144="",$X144=""),"NEEDS VALUATION",IF($AC144&lt;1,"OVERPRICED",IF(AND($AC144&gt;=Assumptions!$B$13,$V144&gt;=4),"BUY",IF($V144&gt;=3.4,"BUY CHEAPER",IF($V144&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG144" s="53" t="str">
+      <c r="AG144" s="51" t="str">
         <f aca="false">IF($AF144="","",IF($AF144="REJECT","Do not buy at any price",IF($AF144="NEEDS PRICE","Enter the current closeout price",IF($AF144="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF144="OVERPRICED","Worth less than break-even - walk",IF($AF144="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF144="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF144="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30198,7 +31241,7 @@
         <f aca="false">IF($A145="","",IF($S145="FAIL","REJECT",IF($D145="","NEEDS PRICE",IF(OR($W145="",$X145=""),"NEEDS VALUATION",IF($AC145&lt;1,"OVERPRICED",IF(AND($AC145&gt;=Assumptions!$B$13,$V145&gt;=4),"BUY",IF($V145&gt;=3.4,"BUY CHEAPER",IF($V145&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG145" s="53" t="str">
+      <c r="AG145" s="51" t="str">
         <f aca="false">IF($AF145="","",IF($AF145="REJECT","Do not buy at any price",IF($AF145="NEEDS PRICE","Enter the current closeout price",IF($AF145="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF145="OVERPRICED","Worth less than break-even - walk",IF($AF145="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF145="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF145="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30288,7 +31331,7 @@
         <f aca="false">IF($A146="","",IF($S146="FAIL","REJECT",IF($D146="","NEEDS PRICE",IF(OR($W146="",$X146=""),"NEEDS VALUATION",IF($AC146&lt;1,"OVERPRICED",IF(AND($AC146&gt;=Assumptions!$B$13,$V146&gt;=4),"BUY",IF($V146&gt;=3.4,"BUY CHEAPER",IF($V146&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG146" s="53" t="str">
+      <c r="AG146" s="51" t="str">
         <f aca="false">IF($AF146="","",IF($AF146="REJECT","Do not buy at any price",IF($AF146="NEEDS PRICE","Enter the current closeout price",IF($AF146="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF146="OVERPRICED","Worth less than break-even - walk",IF($AF146="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF146="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF146="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30378,7 +31421,7 @@
         <f aca="false">IF($A147="","",IF($S147="FAIL","REJECT",IF($D147="","NEEDS PRICE",IF(OR($W147="",$X147=""),"NEEDS VALUATION",IF($AC147&lt;1,"OVERPRICED",IF(AND($AC147&gt;=Assumptions!$B$13,$V147&gt;=4),"BUY",IF($V147&gt;=3.4,"BUY CHEAPER",IF($V147&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG147" s="53" t="str">
+      <c r="AG147" s="51" t="str">
         <f aca="false">IF($AF147="","",IF($AF147="REJECT","Do not buy at any price",IF($AF147="NEEDS PRICE","Enter the current closeout price",IF($AF147="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF147="OVERPRICED","Worth less than break-even - walk",IF($AF147="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF147="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF147="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30468,7 +31511,7 @@
         <f aca="false">IF($A148="","",IF($S148="FAIL","REJECT",IF($D148="","NEEDS PRICE",IF(OR($W148="",$X148=""),"NEEDS VALUATION",IF($AC148&lt;1,"OVERPRICED",IF(AND($AC148&gt;=Assumptions!$B$13,$V148&gt;=4),"BUY",IF($V148&gt;=3.4,"BUY CHEAPER",IF($V148&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG148" s="53" t="str">
+      <c r="AG148" s="51" t="str">
         <f aca="false">IF($AF148="","",IF($AF148="REJECT","Do not buy at any price",IF($AF148="NEEDS PRICE","Enter the current closeout price",IF($AF148="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF148="OVERPRICED","Worth less than break-even - walk",IF($AF148="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF148="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF148="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30558,7 +31601,7 @@
         <f aca="false">IF($A149="","",IF($S149="FAIL","REJECT",IF($D149="","NEEDS PRICE",IF(OR($W149="",$X149=""),"NEEDS VALUATION",IF($AC149&lt;1,"OVERPRICED",IF(AND($AC149&gt;=Assumptions!$B$13,$V149&gt;=4),"BUY",IF($V149&gt;=3.4,"BUY CHEAPER",IF($V149&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG149" s="53" t="str">
+      <c r="AG149" s="51" t="str">
         <f aca="false">IF($AF149="","",IF($AF149="REJECT","Do not buy at any price",IF($AF149="NEEDS PRICE","Enter the current closeout price",IF($AF149="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF149="OVERPRICED","Worth less than break-even - walk",IF($AF149="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF149="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF149="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30648,7 +31691,7 @@
         <f aca="false">IF($A150="","",IF($S150="FAIL","REJECT",IF($D150="","NEEDS PRICE",IF(OR($W150="",$X150=""),"NEEDS VALUATION",IF($AC150&lt;1,"OVERPRICED",IF(AND($AC150&gt;=Assumptions!$B$13,$V150&gt;=4),"BUY",IF($V150&gt;=3.4,"BUY CHEAPER",IF($V150&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG150" s="53" t="str">
+      <c r="AG150" s="51" t="str">
         <f aca="false">IF($AF150="","",IF($AF150="REJECT","Do not buy at any price",IF($AF150="NEEDS PRICE","Enter the current closeout price",IF($AF150="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF150="OVERPRICED","Worth less than break-even - walk",IF($AF150="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF150="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF150="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30738,7 +31781,7 @@
         <f aca="false">IF($A151="","",IF($S151="FAIL","REJECT",IF($D151="","NEEDS PRICE",IF(OR($W151="",$X151=""),"NEEDS VALUATION",IF($AC151&lt;1,"OVERPRICED",IF(AND($AC151&gt;=Assumptions!$B$13,$V151&gt;=4),"BUY",IF($V151&gt;=3.4,"BUY CHEAPER",IF($V151&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG151" s="53" t="str">
+      <c r="AG151" s="51" t="str">
         <f aca="false">IF($AF151="","",IF($AF151="REJECT","Do not buy at any price",IF($AF151="NEEDS PRICE","Enter the current closeout price",IF($AF151="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF151="OVERPRICED","Worth less than break-even - walk",IF($AF151="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF151="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF151="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30828,7 +31871,7 @@
         <f aca="false">IF($A152="","",IF($S152="FAIL","REJECT",IF($D152="","NEEDS PRICE",IF(OR($W152="",$X152=""),"NEEDS VALUATION",IF($AC152&lt;1,"OVERPRICED",IF(AND($AC152&gt;=Assumptions!$B$13,$V152&gt;=4),"BUY",IF($V152&gt;=3.4,"BUY CHEAPER",IF($V152&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG152" s="53" t="str">
+      <c r="AG152" s="51" t="str">
         <f aca="false">IF($AF152="","",IF($AF152="REJECT","Do not buy at any price",IF($AF152="NEEDS PRICE","Enter the current closeout price",IF($AF152="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF152="OVERPRICED","Worth less than break-even - walk",IF($AF152="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF152="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF152="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -30918,7 +31961,7 @@
         <f aca="false">IF($A153="","",IF($S153="FAIL","REJECT",IF($D153="","NEEDS PRICE",IF(OR($W153="",$X153=""),"NEEDS VALUATION",IF($AC153&lt;1,"OVERPRICED",IF(AND($AC153&gt;=Assumptions!$B$13,$V153&gt;=4),"BUY",IF($V153&gt;=3.4,"BUY CHEAPER",IF($V153&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG153" s="53" t="str">
+      <c r="AG153" s="51" t="str">
         <f aca="false">IF($AF153="","",IF($AF153="REJECT","Do not buy at any price",IF($AF153="NEEDS PRICE","Enter the current closeout price",IF($AF153="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF153="OVERPRICED","Worth less than break-even - walk",IF($AF153="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF153="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF153="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31008,7 +32051,7 @@
         <f aca="false">IF($A154="","",IF($S154="FAIL","REJECT",IF($D154="","NEEDS PRICE",IF(OR($W154="",$X154=""),"NEEDS VALUATION",IF($AC154&lt;1,"OVERPRICED",IF(AND($AC154&gt;=Assumptions!$B$13,$V154&gt;=4),"BUY",IF($V154&gt;=3.4,"BUY CHEAPER",IF($V154&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG154" s="53" t="str">
+      <c r="AG154" s="51" t="str">
         <f aca="false">IF($AF154="","",IF($AF154="REJECT","Do not buy at any price",IF($AF154="NEEDS PRICE","Enter the current closeout price",IF($AF154="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF154="OVERPRICED","Worth less than break-even - walk",IF($AF154="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF154="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF154="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31098,7 +32141,7 @@
         <f aca="false">IF($A155="","",IF($S155="FAIL","REJECT",IF($D155="","NEEDS PRICE",IF(OR($W155="",$X155=""),"NEEDS VALUATION",IF($AC155&lt;1,"OVERPRICED",IF(AND($AC155&gt;=Assumptions!$B$13,$V155&gt;=4),"BUY",IF($V155&gt;=3.4,"BUY CHEAPER",IF($V155&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG155" s="53" t="str">
+      <c r="AG155" s="51" t="str">
         <f aca="false">IF($AF155="","",IF($AF155="REJECT","Do not buy at any price",IF($AF155="NEEDS PRICE","Enter the current closeout price",IF($AF155="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF155="OVERPRICED","Worth less than break-even - walk",IF($AF155="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF155="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF155="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31188,7 +32231,7 @@
         <f aca="false">IF($A156="","",IF($S156="FAIL","REJECT",IF($D156="","NEEDS PRICE",IF(OR($W156="",$X156=""),"NEEDS VALUATION",IF($AC156&lt;1,"OVERPRICED",IF(AND($AC156&gt;=Assumptions!$B$13,$V156&gt;=4),"BUY",IF($V156&gt;=3.4,"BUY CHEAPER",IF($V156&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG156" s="53" t="str">
+      <c r="AG156" s="51" t="str">
         <f aca="false">IF($AF156="","",IF($AF156="REJECT","Do not buy at any price",IF($AF156="NEEDS PRICE","Enter the current closeout price",IF($AF156="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF156="OVERPRICED","Worth less than break-even - walk",IF($AF156="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF156="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF156="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31278,7 +32321,7 @@
         <f aca="false">IF($A157="","",IF($S157="FAIL","REJECT",IF($D157="","NEEDS PRICE",IF(OR($W157="",$X157=""),"NEEDS VALUATION",IF($AC157&lt;1,"OVERPRICED",IF(AND($AC157&gt;=Assumptions!$B$13,$V157&gt;=4),"BUY",IF($V157&gt;=3.4,"BUY CHEAPER",IF($V157&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG157" s="53" t="str">
+      <c r="AG157" s="51" t="str">
         <f aca="false">IF($AF157="","",IF($AF157="REJECT","Do not buy at any price",IF($AF157="NEEDS PRICE","Enter the current closeout price",IF($AF157="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF157="OVERPRICED","Worth less than break-even - walk",IF($AF157="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF157="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF157="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31368,7 +32411,7 @@
         <f aca="false">IF($A158="","",IF($S158="FAIL","REJECT",IF($D158="","NEEDS PRICE",IF(OR($W158="",$X158=""),"NEEDS VALUATION",IF($AC158&lt;1,"OVERPRICED",IF(AND($AC158&gt;=Assumptions!$B$13,$V158&gt;=4),"BUY",IF($V158&gt;=3.4,"BUY CHEAPER",IF($V158&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG158" s="53" t="str">
+      <c r="AG158" s="51" t="str">
         <f aca="false">IF($AF158="","",IF($AF158="REJECT","Do not buy at any price",IF($AF158="NEEDS PRICE","Enter the current closeout price",IF($AF158="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF158="OVERPRICED","Worth less than break-even - walk",IF($AF158="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF158="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF158="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31458,7 +32501,7 @@
         <f aca="false">IF($A159="","",IF($S159="FAIL","REJECT",IF($D159="","NEEDS PRICE",IF(OR($W159="",$X159=""),"NEEDS VALUATION",IF($AC159&lt;1,"OVERPRICED",IF(AND($AC159&gt;=Assumptions!$B$13,$V159&gt;=4),"BUY",IF($V159&gt;=3.4,"BUY CHEAPER",IF($V159&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG159" s="53" t="str">
+      <c r="AG159" s="51" t="str">
         <f aca="false">IF($AF159="","",IF($AF159="REJECT","Do not buy at any price",IF($AF159="NEEDS PRICE","Enter the current closeout price",IF($AF159="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF159="OVERPRICED","Worth less than break-even - walk",IF($AF159="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF159="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF159="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31548,7 +32591,7 @@
         <f aca="false">IF($A160="","",IF($S160="FAIL","REJECT",IF($D160="","NEEDS PRICE",IF(OR($W160="",$X160=""),"NEEDS VALUATION",IF($AC160&lt;1,"OVERPRICED",IF(AND($AC160&gt;=Assumptions!$B$13,$V160&gt;=4),"BUY",IF($V160&gt;=3.4,"BUY CHEAPER",IF($V160&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG160" s="53" t="str">
+      <c r="AG160" s="51" t="str">
         <f aca="false">IF($AF160="","",IF($AF160="REJECT","Do not buy at any price",IF($AF160="NEEDS PRICE","Enter the current closeout price",IF($AF160="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF160="OVERPRICED","Worth less than break-even - walk",IF($AF160="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF160="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF160="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31638,7 +32681,7 @@
         <f aca="false">IF($A161="","",IF($S161="FAIL","REJECT",IF($D161="","NEEDS PRICE",IF(OR($W161="",$X161=""),"NEEDS VALUATION",IF($AC161&lt;1,"OVERPRICED",IF(AND($AC161&gt;=Assumptions!$B$13,$V161&gt;=4),"BUY",IF($V161&gt;=3.4,"BUY CHEAPER",IF($V161&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG161" s="53" t="str">
+      <c r="AG161" s="51" t="str">
         <f aca="false">IF($AF161="","",IF($AF161="REJECT","Do not buy at any price",IF($AF161="NEEDS PRICE","Enter the current closeout price",IF($AF161="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF161="OVERPRICED","Worth less than break-even - walk",IF($AF161="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF161="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF161="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31728,7 +32771,7 @@
         <f aca="false">IF($A162="","",IF($S162="FAIL","REJECT",IF($D162="","NEEDS PRICE",IF(OR($W162="",$X162=""),"NEEDS VALUATION",IF($AC162&lt;1,"OVERPRICED",IF(AND($AC162&gt;=Assumptions!$B$13,$V162&gt;=4),"BUY",IF($V162&gt;=3.4,"BUY CHEAPER",IF($V162&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG162" s="53" t="str">
+      <c r="AG162" s="51" t="str">
         <f aca="false">IF($AF162="","",IF($AF162="REJECT","Do not buy at any price",IF($AF162="NEEDS PRICE","Enter the current closeout price",IF($AF162="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF162="OVERPRICED","Worth less than break-even - walk",IF($AF162="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF162="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF162="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31818,7 +32861,7 @@
         <f aca="false">IF($A163="","",IF($S163="FAIL","REJECT",IF($D163="","NEEDS PRICE",IF(OR($W163="",$X163=""),"NEEDS VALUATION",IF($AC163&lt;1,"OVERPRICED",IF(AND($AC163&gt;=Assumptions!$B$13,$V163&gt;=4),"BUY",IF($V163&gt;=3.4,"BUY CHEAPER",IF($V163&gt;=2.8,"FLOOR ONLY","SKIP"))))))))</f>
         <v/>
       </c>
-      <c r="AG163" s="53" t="str">
+      <c r="AG163" s="51" t="str">
         <f aca="false">IF($AF163="","",IF($AF163="REJECT","Do not buy at any price",IF($AF163="NEEDS PRICE","Enter the current closeout price",IF($AF163="NEEDS VALUATION","Enter a valuation AND its source before bidding",IF($AF163="OVERPRICED","Worth less than break-even - walk",IF($AF163="BUY","Take it on day 1 at $11 - will not reach the floor",IF($AF163="BUY CHEAPER","Wait to about $8 (day 3), walk if outbid",IF($AF163="FLOOR ONLY","Only at the $5 floor","Skip"))))))))</f>
         <v/>
       </c>
@@ -31940,20 +32983,20 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="66" t="s">
         <v>177</v>
       </c>
       <c r="B5" s="24" t="str">
         <f aca="false">IF($A5="","",IF(ISERROR(FIND(".",$A5)),"",LOWER(MID($A5,FIND(CHAR(1),SUBSTITUTE($A5,".",CHAR(1),LEN($A5)-LEN(SUBSTITUTE($A5,".",""))))+1,LEN($A5)))))</f>
         <v>com</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="62" t="s">
         <v>635</v>
       </c>
-      <c r="D5" s="69" t="n">
+      <c r="D5" s="67" t="n">
         <v>45363</v>
       </c>
-      <c r="E5" s="65" t="n">
+      <c r="E5" s="63" t="n">
         <v>2400</v>
       </c>
       <c r="F5" s="29" t="n">
@@ -31964,7 +33007,7 @@
         <f aca="true">IF(OR($A5="",$D5=""),"",YEARFRAC($D5,TODAY()))</f>
         <v>2.39444444444444</v>
       </c>
-      <c r="H5" s="70" t="n">
+      <c r="H5" s="68" t="n">
         <f aca="false">IF($G5="","",MAX(0,INT($G5)))</f>
         <v>2</v>
       </c>
@@ -31984,21 +33027,21 @@
         <f aca="false">IF($K5="","",MAX($K5,$E5*Assumptions!$B$10))</f>
         <v>24000</v>
       </c>
-      <c r="M5" s="65" t="n">
+      <c r="M5" s="63" t="n">
         <v>12000</v>
       </c>
-      <c r="N5" s="67" t="s">
+      <c r="N5" s="65" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="37" t="str">
         <f aca="false">IF($A6="","",IF(ISERROR(FIND(".",$A6)),"",LOWER(MID($A6,FIND(CHAR(1),SUBSTITUTE($A6,".",CHAR(1),LEN($A6)-LEN(SUBSTITUTE($A6,".",""))))+1,LEN($A6)))))</f>
         <v/>
       </c>
       <c r="C6" s="26"/>
-      <c r="D6" s="72"/>
+      <c r="D6" s="70"/>
       <c r="E6" s="28"/>
       <c r="F6" s="39" t="str">
         <f aca="false">IF($B6="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B6),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32008,7 +33051,7 @@
         <f aca="true">IF(OR($A6="",$D6=""),"",YEARFRAC($D6,TODAY()))</f>
         <v/>
       </c>
-      <c r="H6" s="73" t="str">
+      <c r="H6" s="71" t="str">
         <f aca="false">IF($G6="","",MAX(0,INT($G6)))</f>
         <v/>
       </c>
@@ -32032,13 +33075,13 @@
       <c r="N6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71"/>
+      <c r="A7" s="69"/>
       <c r="B7" s="37" t="str">
         <f aca="false">IF($A7="","",IF(ISERROR(FIND(".",$A7)),"",LOWER(MID($A7,FIND(CHAR(1),SUBSTITUTE($A7,".",CHAR(1),LEN($A7)-LEN(SUBSTITUTE($A7,".",""))))+1,LEN($A7)))))</f>
         <v/>
       </c>
       <c r="C7" s="26"/>
-      <c r="D7" s="72"/>
+      <c r="D7" s="70"/>
       <c r="E7" s="28"/>
       <c r="F7" s="39" t="str">
         <f aca="false">IF($B7="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B7),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32048,7 +33091,7 @@
         <f aca="true">IF(OR($A7="",$D7=""),"",YEARFRAC($D7,TODAY()))</f>
         <v/>
       </c>
-      <c r="H7" s="73" t="str">
+      <c r="H7" s="71" t="str">
         <f aca="false">IF($G7="","",MAX(0,INT($G7)))</f>
         <v/>
       </c>
@@ -32072,13 +33115,13 @@
       <c r="N7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71"/>
+      <c r="A8" s="69"/>
       <c r="B8" s="37" t="str">
         <f aca="false">IF($A8="","",IF(ISERROR(FIND(".",$A8)),"",LOWER(MID($A8,FIND(CHAR(1),SUBSTITUTE($A8,".",CHAR(1),LEN($A8)-LEN(SUBSTITUTE($A8,".",""))))+1,LEN($A8)))))</f>
         <v/>
       </c>
       <c r="C8" s="26"/>
-      <c r="D8" s="72"/>
+      <c r="D8" s="70"/>
       <c r="E8" s="28"/>
       <c r="F8" s="39" t="str">
         <f aca="false">IF($B8="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B8),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32088,7 +33131,7 @@
         <f aca="true">IF(OR($A8="",$D8=""),"",YEARFRAC($D8,TODAY()))</f>
         <v/>
       </c>
-      <c r="H8" s="73" t="str">
+      <c r="H8" s="71" t="str">
         <f aca="false">IF($G8="","",MAX(0,INT($G8)))</f>
         <v/>
       </c>
@@ -32112,13 +33155,13 @@
       <c r="N8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71"/>
+      <c r="A9" s="69"/>
       <c r="B9" s="37" t="str">
         <f aca="false">IF($A9="","",IF(ISERROR(FIND(".",$A9)),"",LOWER(MID($A9,FIND(CHAR(1),SUBSTITUTE($A9,".",CHAR(1),LEN($A9)-LEN(SUBSTITUTE($A9,".",""))))+1,LEN($A9)))))</f>
         <v/>
       </c>
       <c r="C9" s="26"/>
-      <c r="D9" s="72"/>
+      <c r="D9" s="70"/>
       <c r="E9" s="28"/>
       <c r="F9" s="39" t="str">
         <f aca="false">IF($B9="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B9),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32128,7 +33171,7 @@
         <f aca="true">IF(OR($A9="",$D9=""),"",YEARFRAC($D9,TODAY()))</f>
         <v/>
       </c>
-      <c r="H9" s="73" t="str">
+      <c r="H9" s="71" t="str">
         <f aca="false">IF($G9="","",MAX(0,INT($G9)))</f>
         <v/>
       </c>
@@ -32152,13 +33195,13 @@
       <c r="N9" s="36"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="37" t="str">
         <f aca="false">IF($A10="","",IF(ISERROR(FIND(".",$A10)),"",LOWER(MID($A10,FIND(CHAR(1),SUBSTITUTE($A10,".",CHAR(1),LEN($A10)-LEN(SUBSTITUTE($A10,".",""))))+1,LEN($A10)))))</f>
         <v/>
       </c>
       <c r="C10" s="26"/>
-      <c r="D10" s="72"/>
+      <c r="D10" s="70"/>
       <c r="E10" s="28"/>
       <c r="F10" s="39" t="str">
         <f aca="false">IF($B10="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B10),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32168,7 +33211,7 @@
         <f aca="true">IF(OR($A10="",$D10=""),"",YEARFRAC($D10,TODAY()))</f>
         <v/>
       </c>
-      <c r="H10" s="73" t="str">
+      <c r="H10" s="71" t="str">
         <f aca="false">IF($G10="","",MAX(0,INT($G10)))</f>
         <v/>
       </c>
@@ -32192,13 +33235,13 @@
       <c r="N10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71"/>
+      <c r="A11" s="69"/>
       <c r="B11" s="37" t="str">
         <f aca="false">IF($A11="","",IF(ISERROR(FIND(".",$A11)),"",LOWER(MID($A11,FIND(CHAR(1),SUBSTITUTE($A11,".",CHAR(1),LEN($A11)-LEN(SUBSTITUTE($A11,".",""))))+1,LEN($A11)))))</f>
         <v/>
       </c>
       <c r="C11" s="26"/>
-      <c r="D11" s="72"/>
+      <c r="D11" s="70"/>
       <c r="E11" s="28"/>
       <c r="F11" s="39" t="str">
         <f aca="false">IF($B11="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B11),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32208,7 +33251,7 @@
         <f aca="true">IF(OR($A11="",$D11=""),"",YEARFRAC($D11,TODAY()))</f>
         <v/>
       </c>
-      <c r="H11" s="73" t="str">
+      <c r="H11" s="71" t="str">
         <f aca="false">IF($G11="","",MAX(0,INT($G11)))</f>
         <v/>
       </c>
@@ -32232,13 +33275,13 @@
       <c r="N11" s="36"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="37" t="str">
         <f aca="false">IF($A12="","",IF(ISERROR(FIND(".",$A12)),"",LOWER(MID($A12,FIND(CHAR(1),SUBSTITUTE($A12,".",CHAR(1),LEN($A12)-LEN(SUBSTITUTE($A12,".",""))))+1,LEN($A12)))))</f>
         <v/>
       </c>
       <c r="C12" s="26"/>
-      <c r="D12" s="72"/>
+      <c r="D12" s="70"/>
       <c r="E12" s="28"/>
       <c r="F12" s="39" t="str">
         <f aca="false">IF($B12="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B12),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32248,7 +33291,7 @@
         <f aca="true">IF(OR($A12="",$D12=""),"",YEARFRAC($D12,TODAY()))</f>
         <v/>
       </c>
-      <c r="H12" s="73" t="str">
+      <c r="H12" s="71" t="str">
         <f aca="false">IF($G12="","",MAX(0,INT($G12)))</f>
         <v/>
       </c>
@@ -32272,13 +33315,13 @@
       <c r="N12" s="36"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71"/>
+      <c r="A13" s="69"/>
       <c r="B13" s="37" t="str">
         <f aca="false">IF($A13="","",IF(ISERROR(FIND(".",$A13)),"",LOWER(MID($A13,FIND(CHAR(1),SUBSTITUTE($A13,".",CHAR(1),LEN($A13)-LEN(SUBSTITUTE($A13,".",""))))+1,LEN($A13)))))</f>
         <v/>
       </c>
       <c r="C13" s="26"/>
-      <c r="D13" s="72"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="28"/>
       <c r="F13" s="39" t="str">
         <f aca="false">IF($B13="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B13),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32288,7 +33331,7 @@
         <f aca="true">IF(OR($A13="",$D13=""),"",YEARFRAC($D13,TODAY()))</f>
         <v/>
       </c>
-      <c r="H13" s="73" t="str">
+      <c r="H13" s="71" t="str">
         <f aca="false">IF($G13="","",MAX(0,INT($G13)))</f>
         <v/>
       </c>
@@ -32312,13 +33355,13 @@
       <c r="N13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71"/>
+      <c r="A14" s="69"/>
       <c r="B14" s="37" t="str">
         <f aca="false">IF($A14="","",IF(ISERROR(FIND(".",$A14)),"",LOWER(MID($A14,FIND(CHAR(1),SUBSTITUTE($A14,".",CHAR(1),LEN($A14)-LEN(SUBSTITUTE($A14,".",""))))+1,LEN($A14)))))</f>
         <v/>
       </c>
       <c r="C14" s="26"/>
-      <c r="D14" s="72"/>
+      <c r="D14" s="70"/>
       <c r="E14" s="28"/>
       <c r="F14" s="39" t="str">
         <f aca="false">IF($B14="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B14),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32328,7 +33371,7 @@
         <f aca="true">IF(OR($A14="",$D14=""),"",YEARFRAC($D14,TODAY()))</f>
         <v/>
       </c>
-      <c r="H14" s="73" t="str">
+      <c r="H14" s="71" t="str">
         <f aca="false">IF($G14="","",MAX(0,INT($G14)))</f>
         <v/>
       </c>
@@ -32352,13 +33395,13 @@
       <c r="N14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71"/>
+      <c r="A15" s="69"/>
       <c r="B15" s="37" t="str">
         <f aca="false">IF($A15="","",IF(ISERROR(FIND(".",$A15)),"",LOWER(MID($A15,FIND(CHAR(1),SUBSTITUTE($A15,".",CHAR(1),LEN($A15)-LEN(SUBSTITUTE($A15,".",""))))+1,LEN($A15)))))</f>
         <v/>
       </c>
       <c r="C15" s="26"/>
-      <c r="D15" s="72"/>
+      <c r="D15" s="70"/>
       <c r="E15" s="28"/>
       <c r="F15" s="39" t="str">
         <f aca="false">IF($B15="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B15),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32368,7 +33411,7 @@
         <f aca="true">IF(OR($A15="",$D15=""),"",YEARFRAC($D15,TODAY()))</f>
         <v/>
       </c>
-      <c r="H15" s="73" t="str">
+      <c r="H15" s="71" t="str">
         <f aca="false">IF($G15="","",MAX(0,INT($G15)))</f>
         <v/>
       </c>
@@ -32392,13 +33435,13 @@
       <c r="N15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71"/>
+      <c r="A16" s="69"/>
       <c r="B16" s="37" t="str">
         <f aca="false">IF($A16="","",IF(ISERROR(FIND(".",$A16)),"",LOWER(MID($A16,FIND(CHAR(1),SUBSTITUTE($A16,".",CHAR(1),LEN($A16)-LEN(SUBSTITUTE($A16,".",""))))+1,LEN($A16)))))</f>
         <v/>
       </c>
       <c r="C16" s="26"/>
-      <c r="D16" s="72"/>
+      <c r="D16" s="70"/>
       <c r="E16" s="28"/>
       <c r="F16" s="39" t="str">
         <f aca="false">IF($B16="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B16),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32408,7 +33451,7 @@
         <f aca="true">IF(OR($A16="",$D16=""),"",YEARFRAC($D16,TODAY()))</f>
         <v/>
       </c>
-      <c r="H16" s="73" t="str">
+      <c r="H16" s="71" t="str">
         <f aca="false">IF($G16="","",MAX(0,INT($G16)))</f>
         <v/>
       </c>
@@ -32432,13 +33475,13 @@
       <c r="N16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71"/>
+      <c r="A17" s="69"/>
       <c r="B17" s="37" t="str">
         <f aca="false">IF($A17="","",IF(ISERROR(FIND(".",$A17)),"",LOWER(MID($A17,FIND(CHAR(1),SUBSTITUTE($A17,".",CHAR(1),LEN($A17)-LEN(SUBSTITUTE($A17,".",""))))+1,LEN($A17)))))</f>
         <v/>
       </c>
       <c r="C17" s="26"/>
-      <c r="D17" s="72"/>
+      <c r="D17" s="70"/>
       <c r="E17" s="28"/>
       <c r="F17" s="39" t="str">
         <f aca="false">IF($B17="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B17),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32448,7 +33491,7 @@
         <f aca="true">IF(OR($A17="",$D17=""),"",YEARFRAC($D17,TODAY()))</f>
         <v/>
       </c>
-      <c r="H17" s="73" t="str">
+      <c r="H17" s="71" t="str">
         <f aca="false">IF($G17="","",MAX(0,INT($G17)))</f>
         <v/>
       </c>
@@ -32472,13 +33515,13 @@
       <c r="N17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="71"/>
+      <c r="A18" s="69"/>
       <c r="B18" s="37" t="str">
         <f aca="false">IF($A18="","",IF(ISERROR(FIND(".",$A18)),"",LOWER(MID($A18,FIND(CHAR(1),SUBSTITUTE($A18,".",CHAR(1),LEN($A18)-LEN(SUBSTITUTE($A18,".",""))))+1,LEN($A18)))))</f>
         <v/>
       </c>
       <c r="C18" s="26"/>
-      <c r="D18" s="72"/>
+      <c r="D18" s="70"/>
       <c r="E18" s="28"/>
       <c r="F18" s="39" t="str">
         <f aca="false">IF($B18="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B18),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32488,7 +33531,7 @@
         <f aca="true">IF(OR($A18="",$D18=""),"",YEARFRAC($D18,TODAY()))</f>
         <v/>
       </c>
-      <c r="H18" s="73" t="str">
+      <c r="H18" s="71" t="str">
         <f aca="false">IF($G18="","",MAX(0,INT($G18)))</f>
         <v/>
       </c>
@@ -32512,13 +33555,13 @@
       <c r="N18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71"/>
+      <c r="A19" s="69"/>
       <c r="B19" s="37" t="str">
         <f aca="false">IF($A19="","",IF(ISERROR(FIND(".",$A19)),"",LOWER(MID($A19,FIND(CHAR(1),SUBSTITUTE($A19,".",CHAR(1),LEN($A19)-LEN(SUBSTITUTE($A19,".",""))))+1,LEN($A19)))))</f>
         <v/>
       </c>
       <c r="C19" s="26"/>
-      <c r="D19" s="72"/>
+      <c r="D19" s="70"/>
       <c r="E19" s="28"/>
       <c r="F19" s="39" t="str">
         <f aca="false">IF($B19="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B19),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32528,7 +33571,7 @@
         <f aca="true">IF(OR($A19="",$D19=""),"",YEARFRAC($D19,TODAY()))</f>
         <v/>
       </c>
-      <c r="H19" s="73" t="str">
+      <c r="H19" s="71" t="str">
         <f aca="false">IF($G19="","",MAX(0,INT($G19)))</f>
         <v/>
       </c>
@@ -32552,13 +33595,13 @@
       <c r="N19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="71"/>
+      <c r="A20" s="69"/>
       <c r="B20" s="37" t="str">
         <f aca="false">IF($A20="","",IF(ISERROR(FIND(".",$A20)),"",LOWER(MID($A20,FIND(CHAR(1),SUBSTITUTE($A20,".",CHAR(1),LEN($A20)-LEN(SUBSTITUTE($A20,".",""))))+1,LEN($A20)))))</f>
         <v/>
       </c>
       <c r="C20" s="26"/>
-      <c r="D20" s="72"/>
+      <c r="D20" s="70"/>
       <c r="E20" s="28"/>
       <c r="F20" s="39" t="str">
         <f aca="false">IF($B20="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B20),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32568,7 +33611,7 @@
         <f aca="true">IF(OR($A20="",$D20=""),"",YEARFRAC($D20,TODAY()))</f>
         <v/>
       </c>
-      <c r="H20" s="73" t="str">
+      <c r="H20" s="71" t="str">
         <f aca="false">IF($G20="","",MAX(0,INT($G20)))</f>
         <v/>
       </c>
@@ -32592,13 +33635,13 @@
       <c r="N20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71"/>
+      <c r="A21" s="69"/>
       <c r="B21" s="37" t="str">
         <f aca="false">IF($A21="","",IF(ISERROR(FIND(".",$A21)),"",LOWER(MID($A21,FIND(CHAR(1),SUBSTITUTE($A21,".",CHAR(1),LEN($A21)-LEN(SUBSTITUTE($A21,".",""))))+1,LEN($A21)))))</f>
         <v/>
       </c>
       <c r="C21" s="26"/>
-      <c r="D21" s="72"/>
+      <c r="D21" s="70"/>
       <c r="E21" s="28"/>
       <c r="F21" s="39" t="str">
         <f aca="false">IF($B21="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B21),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32608,7 +33651,7 @@
         <f aca="true">IF(OR($A21="",$D21=""),"",YEARFRAC($D21,TODAY()))</f>
         <v/>
       </c>
-      <c r="H21" s="73" t="str">
+      <c r="H21" s="71" t="str">
         <f aca="false">IF($G21="","",MAX(0,INT($G21)))</f>
         <v/>
       </c>
@@ -32632,13 +33675,13 @@
       <c r="N21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71"/>
+      <c r="A22" s="69"/>
       <c r="B22" s="37" t="str">
         <f aca="false">IF($A22="","",IF(ISERROR(FIND(".",$A22)),"",LOWER(MID($A22,FIND(CHAR(1),SUBSTITUTE($A22,".",CHAR(1),LEN($A22)-LEN(SUBSTITUTE($A22,".",""))))+1,LEN($A22)))))</f>
         <v/>
       </c>
       <c r="C22" s="26"/>
-      <c r="D22" s="72"/>
+      <c r="D22" s="70"/>
       <c r="E22" s="28"/>
       <c r="F22" s="39" t="str">
         <f aca="false">IF($B22="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B22),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32648,7 +33691,7 @@
         <f aca="true">IF(OR($A22="",$D22=""),"",YEARFRAC($D22,TODAY()))</f>
         <v/>
       </c>
-      <c r="H22" s="73" t="str">
+      <c r="H22" s="71" t="str">
         <f aca="false">IF($G22="","",MAX(0,INT($G22)))</f>
         <v/>
       </c>
@@ -32672,13 +33715,13 @@
       <c r="N22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71"/>
+      <c r="A23" s="69"/>
       <c r="B23" s="37" t="str">
         <f aca="false">IF($A23="","",IF(ISERROR(FIND(".",$A23)),"",LOWER(MID($A23,FIND(CHAR(1),SUBSTITUTE($A23,".",CHAR(1),LEN($A23)-LEN(SUBSTITUTE($A23,".",""))))+1,LEN($A23)))))</f>
         <v/>
       </c>
       <c r="C23" s="26"/>
-      <c r="D23" s="72"/>
+      <c r="D23" s="70"/>
       <c r="E23" s="28"/>
       <c r="F23" s="39" t="str">
         <f aca="false">IF($B23="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B23),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32688,7 +33731,7 @@
         <f aca="true">IF(OR($A23="",$D23=""),"",YEARFRAC($D23,TODAY()))</f>
         <v/>
       </c>
-      <c r="H23" s="73" t="str">
+      <c r="H23" s="71" t="str">
         <f aca="false">IF($G23="","",MAX(0,INT($G23)))</f>
         <v/>
       </c>
@@ -32712,13 +33755,13 @@
       <c r="N23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71"/>
+      <c r="A24" s="69"/>
       <c r="B24" s="37" t="str">
         <f aca="false">IF($A24="","",IF(ISERROR(FIND(".",$A24)),"",LOWER(MID($A24,FIND(CHAR(1),SUBSTITUTE($A24,".",CHAR(1),LEN($A24)-LEN(SUBSTITUTE($A24,".",""))))+1,LEN($A24)))))</f>
         <v/>
       </c>
       <c r="C24" s="26"/>
-      <c r="D24" s="72"/>
+      <c r="D24" s="70"/>
       <c r="E24" s="28"/>
       <c r="F24" s="39" t="str">
         <f aca="false">IF($B24="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B24),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32728,7 +33771,7 @@
         <f aca="true">IF(OR($A24="",$D24=""),"",YEARFRAC($D24,TODAY()))</f>
         <v/>
       </c>
-      <c r="H24" s="73" t="str">
+      <c r="H24" s="71" t="str">
         <f aca="false">IF($G24="","",MAX(0,INT($G24)))</f>
         <v/>
       </c>
@@ -32752,13 +33795,13 @@
       <c r="N24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71"/>
+      <c r="A25" s="69"/>
       <c r="B25" s="37" t="str">
         <f aca="false">IF($A25="","",IF(ISERROR(FIND(".",$A25)),"",LOWER(MID($A25,FIND(CHAR(1),SUBSTITUTE($A25,".",CHAR(1),LEN($A25)-LEN(SUBSTITUTE($A25,".",""))))+1,LEN($A25)))))</f>
         <v/>
       </c>
       <c r="C25" s="26"/>
-      <c r="D25" s="72"/>
+      <c r="D25" s="70"/>
       <c r="E25" s="28"/>
       <c r="F25" s="39" t="str">
         <f aca="false">IF($B25="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B25),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32768,7 +33811,7 @@
         <f aca="true">IF(OR($A25="",$D25=""),"",YEARFRAC($D25,TODAY()))</f>
         <v/>
       </c>
-      <c r="H25" s="73" t="str">
+      <c r="H25" s="71" t="str">
         <f aca="false">IF($G25="","",MAX(0,INT($G25)))</f>
         <v/>
       </c>
@@ -32792,13 +33835,13 @@
       <c r="N25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="71"/>
+      <c r="A26" s="69"/>
       <c r="B26" s="37" t="str">
         <f aca="false">IF($A26="","",IF(ISERROR(FIND(".",$A26)),"",LOWER(MID($A26,FIND(CHAR(1),SUBSTITUTE($A26,".",CHAR(1),LEN($A26)-LEN(SUBSTITUTE($A26,".",""))))+1,LEN($A26)))))</f>
         <v/>
       </c>
       <c r="C26" s="26"/>
-      <c r="D26" s="72"/>
+      <c r="D26" s="70"/>
       <c r="E26" s="28"/>
       <c r="F26" s="39" t="str">
         <f aca="false">IF($B26="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B26),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32808,7 +33851,7 @@
         <f aca="true">IF(OR($A26="",$D26=""),"",YEARFRAC($D26,TODAY()))</f>
         <v/>
       </c>
-      <c r="H26" s="73" t="str">
+      <c r="H26" s="71" t="str">
         <f aca="false">IF($G26="","",MAX(0,INT($G26)))</f>
         <v/>
       </c>
@@ -32832,13 +33875,13 @@
       <c r="N26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="71"/>
+      <c r="A27" s="69"/>
       <c r="B27" s="37" t="str">
         <f aca="false">IF($A27="","",IF(ISERROR(FIND(".",$A27)),"",LOWER(MID($A27,FIND(CHAR(1),SUBSTITUTE($A27,".",CHAR(1),LEN($A27)-LEN(SUBSTITUTE($A27,".",""))))+1,LEN($A27)))))</f>
         <v/>
       </c>
       <c r="C27" s="26"/>
-      <c r="D27" s="72"/>
+      <c r="D27" s="70"/>
       <c r="E27" s="28"/>
       <c r="F27" s="39" t="str">
         <f aca="false">IF($B27="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B27),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32848,7 +33891,7 @@
         <f aca="true">IF(OR($A27="",$D27=""),"",YEARFRAC($D27,TODAY()))</f>
         <v/>
       </c>
-      <c r="H27" s="73" t="str">
+      <c r="H27" s="71" t="str">
         <f aca="false">IF($G27="","",MAX(0,INT($G27)))</f>
         <v/>
       </c>
@@ -32872,13 +33915,13 @@
       <c r="N27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="71"/>
+      <c r="A28" s="69"/>
       <c r="B28" s="37" t="str">
         <f aca="false">IF($A28="","",IF(ISERROR(FIND(".",$A28)),"",LOWER(MID($A28,FIND(CHAR(1),SUBSTITUTE($A28,".",CHAR(1),LEN($A28)-LEN(SUBSTITUTE($A28,".",""))))+1,LEN($A28)))))</f>
         <v/>
       </c>
       <c r="C28" s="26"/>
-      <c r="D28" s="72"/>
+      <c r="D28" s="70"/>
       <c r="E28" s="28"/>
       <c r="F28" s="39" t="str">
         <f aca="false">IF($B28="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B28),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32888,7 +33931,7 @@
         <f aca="true">IF(OR($A28="",$D28=""),"",YEARFRAC($D28,TODAY()))</f>
         <v/>
       </c>
-      <c r="H28" s="73" t="str">
+      <c r="H28" s="71" t="str">
         <f aca="false">IF($G28="","",MAX(0,INT($G28)))</f>
         <v/>
       </c>
@@ -32912,13 +33955,13 @@
       <c r="N28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="71"/>
+      <c r="A29" s="69"/>
       <c r="B29" s="37" t="str">
         <f aca="false">IF($A29="","",IF(ISERROR(FIND(".",$A29)),"",LOWER(MID($A29,FIND(CHAR(1),SUBSTITUTE($A29,".",CHAR(1),LEN($A29)-LEN(SUBSTITUTE($A29,".",""))))+1,LEN($A29)))))</f>
         <v/>
       </c>
       <c r="C29" s="26"/>
-      <c r="D29" s="72"/>
+      <c r="D29" s="70"/>
       <c r="E29" s="28"/>
       <c r="F29" s="39" t="str">
         <f aca="false">IF($B29="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B29),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32928,7 +33971,7 @@
         <f aca="true">IF(OR($A29="",$D29=""),"",YEARFRAC($D29,TODAY()))</f>
         <v/>
       </c>
-      <c r="H29" s="73" t="str">
+      <c r="H29" s="71" t="str">
         <f aca="false">IF($G29="","",MAX(0,INT($G29)))</f>
         <v/>
       </c>
@@ -32952,13 +33995,13 @@
       <c r="N29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="71"/>
+      <c r="A30" s="69"/>
       <c r="B30" s="37" t="str">
         <f aca="false">IF($A30="","",IF(ISERROR(FIND(".",$A30)),"",LOWER(MID($A30,FIND(CHAR(1),SUBSTITUTE($A30,".",CHAR(1),LEN($A30)-LEN(SUBSTITUTE($A30,".",""))))+1,LEN($A30)))))</f>
         <v/>
       </c>
       <c r="C30" s="26"/>
-      <c r="D30" s="72"/>
+      <c r="D30" s="70"/>
       <c r="E30" s="28"/>
       <c r="F30" s="39" t="str">
         <f aca="false">IF($B30="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B30),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -32968,7 +34011,7 @@
         <f aca="true">IF(OR($A30="",$D30=""),"",YEARFRAC($D30,TODAY()))</f>
         <v/>
       </c>
-      <c r="H30" s="73" t="str">
+      <c r="H30" s="71" t="str">
         <f aca="false">IF($G30="","",MAX(0,INT($G30)))</f>
         <v/>
       </c>
@@ -32992,13 +34035,13 @@
       <c r="N30" s="36"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="71"/>
+      <c r="A31" s="69"/>
       <c r="B31" s="37" t="str">
         <f aca="false">IF($A31="","",IF(ISERROR(FIND(".",$A31)),"",LOWER(MID($A31,FIND(CHAR(1),SUBSTITUTE($A31,".",CHAR(1),LEN($A31)-LEN(SUBSTITUTE($A31,".",""))))+1,LEN($A31)))))</f>
         <v/>
       </c>
       <c r="C31" s="26"/>
-      <c r="D31" s="72"/>
+      <c r="D31" s="70"/>
       <c r="E31" s="28"/>
       <c r="F31" s="39" t="str">
         <f aca="false">IF($B31="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B31),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33008,7 +34051,7 @@
         <f aca="true">IF(OR($A31="",$D31=""),"",YEARFRAC($D31,TODAY()))</f>
         <v/>
       </c>
-      <c r="H31" s="73" t="str">
+      <c r="H31" s="71" t="str">
         <f aca="false">IF($G31="","",MAX(0,INT($G31)))</f>
         <v/>
       </c>
@@ -33032,13 +34075,13 @@
       <c r="N31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="71"/>
+      <c r="A32" s="69"/>
       <c r="B32" s="37" t="str">
         <f aca="false">IF($A32="","",IF(ISERROR(FIND(".",$A32)),"",LOWER(MID($A32,FIND(CHAR(1),SUBSTITUTE($A32,".",CHAR(1),LEN($A32)-LEN(SUBSTITUTE($A32,".",""))))+1,LEN($A32)))))</f>
         <v/>
       </c>
       <c r="C32" s="26"/>
-      <c r="D32" s="72"/>
+      <c r="D32" s="70"/>
       <c r="E32" s="28"/>
       <c r="F32" s="39" t="str">
         <f aca="false">IF($B32="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B32),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33048,7 +34091,7 @@
         <f aca="true">IF(OR($A32="",$D32=""),"",YEARFRAC($D32,TODAY()))</f>
         <v/>
       </c>
-      <c r="H32" s="73" t="str">
+      <c r="H32" s="71" t="str">
         <f aca="false">IF($G32="","",MAX(0,INT($G32)))</f>
         <v/>
       </c>
@@ -33072,13 +34115,13 @@
       <c r="N32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="71"/>
+      <c r="A33" s="69"/>
       <c r="B33" s="37" t="str">
         <f aca="false">IF($A33="","",IF(ISERROR(FIND(".",$A33)),"",LOWER(MID($A33,FIND(CHAR(1),SUBSTITUTE($A33,".",CHAR(1),LEN($A33)-LEN(SUBSTITUTE($A33,".",""))))+1,LEN($A33)))))</f>
         <v/>
       </c>
       <c r="C33" s="26"/>
-      <c r="D33" s="72"/>
+      <c r="D33" s="70"/>
       <c r="E33" s="28"/>
       <c r="F33" s="39" t="str">
         <f aca="false">IF($B33="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B33),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33088,7 +34131,7 @@
         <f aca="true">IF(OR($A33="",$D33=""),"",YEARFRAC($D33,TODAY()))</f>
         <v/>
       </c>
-      <c r="H33" s="73" t="str">
+      <c r="H33" s="71" t="str">
         <f aca="false">IF($G33="","",MAX(0,INT($G33)))</f>
         <v/>
       </c>
@@ -33112,13 +34155,13 @@
       <c r="N33" s="36"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="71"/>
+      <c r="A34" s="69"/>
       <c r="B34" s="37" t="str">
         <f aca="false">IF($A34="","",IF(ISERROR(FIND(".",$A34)),"",LOWER(MID($A34,FIND(CHAR(1),SUBSTITUTE($A34,".",CHAR(1),LEN($A34)-LEN(SUBSTITUTE($A34,".",""))))+1,LEN($A34)))))</f>
         <v/>
       </c>
       <c r="C34" s="26"/>
-      <c r="D34" s="72"/>
+      <c r="D34" s="70"/>
       <c r="E34" s="28"/>
       <c r="F34" s="39" t="str">
         <f aca="false">IF($B34="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B34),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33128,7 +34171,7 @@
         <f aca="true">IF(OR($A34="",$D34=""),"",YEARFRAC($D34,TODAY()))</f>
         <v/>
       </c>
-      <c r="H34" s="73" t="str">
+      <c r="H34" s="71" t="str">
         <f aca="false">IF($G34="","",MAX(0,INT($G34)))</f>
         <v/>
       </c>
@@ -33152,13 +34195,13 @@
       <c r="N34" s="36"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="71"/>
+      <c r="A35" s="69"/>
       <c r="B35" s="37" t="str">
         <f aca="false">IF($A35="","",IF(ISERROR(FIND(".",$A35)),"",LOWER(MID($A35,FIND(CHAR(1),SUBSTITUTE($A35,".",CHAR(1),LEN($A35)-LEN(SUBSTITUTE($A35,".",""))))+1,LEN($A35)))))</f>
         <v/>
       </c>
       <c r="C35" s="26"/>
-      <c r="D35" s="72"/>
+      <c r="D35" s="70"/>
       <c r="E35" s="28"/>
       <c r="F35" s="39" t="str">
         <f aca="false">IF($B35="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B35),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33168,7 +34211,7 @@
         <f aca="true">IF(OR($A35="",$D35=""),"",YEARFRAC($D35,TODAY()))</f>
         <v/>
       </c>
-      <c r="H35" s="73" t="str">
+      <c r="H35" s="71" t="str">
         <f aca="false">IF($G35="","",MAX(0,INT($G35)))</f>
         <v/>
       </c>
@@ -33192,13 +34235,13 @@
       <c r="N35" s="36"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="71"/>
+      <c r="A36" s="69"/>
       <c r="B36" s="37" t="str">
         <f aca="false">IF($A36="","",IF(ISERROR(FIND(".",$A36)),"",LOWER(MID($A36,FIND(CHAR(1),SUBSTITUTE($A36,".",CHAR(1),LEN($A36)-LEN(SUBSTITUTE($A36,".",""))))+1,LEN($A36)))))</f>
         <v/>
       </c>
       <c r="C36" s="26"/>
-      <c r="D36" s="72"/>
+      <c r="D36" s="70"/>
       <c r="E36" s="28"/>
       <c r="F36" s="39" t="str">
         <f aca="false">IF($B36="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B36),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33208,7 +34251,7 @@
         <f aca="true">IF(OR($A36="",$D36=""),"",YEARFRAC($D36,TODAY()))</f>
         <v/>
       </c>
-      <c r="H36" s="73" t="str">
+      <c r="H36" s="71" t="str">
         <f aca="false">IF($G36="","",MAX(0,INT($G36)))</f>
         <v/>
       </c>
@@ -33232,13 +34275,13 @@
       <c r="N36" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="71"/>
+      <c r="A37" s="69"/>
       <c r="B37" s="37" t="str">
         <f aca="false">IF($A37="","",IF(ISERROR(FIND(".",$A37)),"",LOWER(MID($A37,FIND(CHAR(1),SUBSTITUTE($A37,".",CHAR(1),LEN($A37)-LEN(SUBSTITUTE($A37,".",""))))+1,LEN($A37)))))</f>
         <v/>
       </c>
       <c r="C37" s="26"/>
-      <c r="D37" s="72"/>
+      <c r="D37" s="70"/>
       <c r="E37" s="28"/>
       <c r="F37" s="39" t="str">
         <f aca="false">IF($B37="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B37),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33248,7 +34291,7 @@
         <f aca="true">IF(OR($A37="",$D37=""),"",YEARFRAC($D37,TODAY()))</f>
         <v/>
       </c>
-      <c r="H37" s="73" t="str">
+      <c r="H37" s="71" t="str">
         <f aca="false">IF($G37="","",MAX(0,INT($G37)))</f>
         <v/>
       </c>
@@ -33272,13 +34315,13 @@
       <c r="N37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="71"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="37" t="str">
         <f aca="false">IF($A38="","",IF(ISERROR(FIND(".",$A38)),"",LOWER(MID($A38,FIND(CHAR(1),SUBSTITUTE($A38,".",CHAR(1),LEN($A38)-LEN(SUBSTITUTE($A38,".",""))))+1,LEN($A38)))))</f>
         <v/>
       </c>
       <c r="C38" s="26"/>
-      <c r="D38" s="72"/>
+      <c r="D38" s="70"/>
       <c r="E38" s="28"/>
       <c r="F38" s="39" t="str">
         <f aca="false">IF($B38="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B38),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33288,7 +34331,7 @@
         <f aca="true">IF(OR($A38="",$D38=""),"",YEARFRAC($D38,TODAY()))</f>
         <v/>
       </c>
-      <c r="H38" s="73" t="str">
+      <c r="H38" s="71" t="str">
         <f aca="false">IF($G38="","",MAX(0,INT($G38)))</f>
         <v/>
       </c>
@@ -33312,13 +34355,13 @@
       <c r="N38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="71"/>
+      <c r="A39" s="69"/>
       <c r="B39" s="37" t="str">
         <f aca="false">IF($A39="","",IF(ISERROR(FIND(".",$A39)),"",LOWER(MID($A39,FIND(CHAR(1),SUBSTITUTE($A39,".",CHAR(1),LEN($A39)-LEN(SUBSTITUTE($A39,".",""))))+1,LEN($A39)))))</f>
         <v/>
       </c>
       <c r="C39" s="26"/>
-      <c r="D39" s="72"/>
+      <c r="D39" s="70"/>
       <c r="E39" s="28"/>
       <c r="F39" s="39" t="str">
         <f aca="false">IF($B39="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B39),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33328,7 +34371,7 @@
         <f aca="true">IF(OR($A39="",$D39=""),"",YEARFRAC($D39,TODAY()))</f>
         <v/>
       </c>
-      <c r="H39" s="73" t="str">
+      <c r="H39" s="71" t="str">
         <f aca="false">IF($G39="","",MAX(0,INT($G39)))</f>
         <v/>
       </c>
@@ -33352,13 +34395,13 @@
       <c r="N39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="71"/>
+      <c r="A40" s="69"/>
       <c r="B40" s="37" t="str">
         <f aca="false">IF($A40="","",IF(ISERROR(FIND(".",$A40)),"",LOWER(MID($A40,FIND(CHAR(1),SUBSTITUTE($A40,".",CHAR(1),LEN($A40)-LEN(SUBSTITUTE($A40,".",""))))+1,LEN($A40)))))</f>
         <v/>
       </c>
       <c r="C40" s="26"/>
-      <c r="D40" s="72"/>
+      <c r="D40" s="70"/>
       <c r="E40" s="28"/>
       <c r="F40" s="39" t="str">
         <f aca="false">IF($B40="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B40),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33368,7 +34411,7 @@
         <f aca="true">IF(OR($A40="",$D40=""),"",YEARFRAC($D40,TODAY()))</f>
         <v/>
       </c>
-      <c r="H40" s="73" t="str">
+      <c r="H40" s="71" t="str">
         <f aca="false">IF($G40="","",MAX(0,INT($G40)))</f>
         <v/>
       </c>
@@ -33392,13 +34435,13 @@
       <c r="N40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="71"/>
+      <c r="A41" s="69"/>
       <c r="B41" s="37" t="str">
         <f aca="false">IF($A41="","",IF(ISERROR(FIND(".",$A41)),"",LOWER(MID($A41,FIND(CHAR(1),SUBSTITUTE($A41,".",CHAR(1),LEN($A41)-LEN(SUBSTITUTE($A41,".",""))))+1,LEN($A41)))))</f>
         <v/>
       </c>
       <c r="C41" s="26"/>
-      <c r="D41" s="72"/>
+      <c r="D41" s="70"/>
       <c r="E41" s="28"/>
       <c r="F41" s="39" t="str">
         <f aca="false">IF($B41="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B41),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33408,7 +34451,7 @@
         <f aca="true">IF(OR($A41="",$D41=""),"",YEARFRAC($D41,TODAY()))</f>
         <v/>
       </c>
-      <c r="H41" s="73" t="str">
+      <c r="H41" s="71" t="str">
         <f aca="false">IF($G41="","",MAX(0,INT($G41)))</f>
         <v/>
       </c>
@@ -33432,13 +34475,13 @@
       <c r="N41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="71"/>
+      <c r="A42" s="69"/>
       <c r="B42" s="37" t="str">
         <f aca="false">IF($A42="","",IF(ISERROR(FIND(".",$A42)),"",LOWER(MID($A42,FIND(CHAR(1),SUBSTITUTE($A42,".",CHAR(1),LEN($A42)-LEN(SUBSTITUTE($A42,".",""))))+1,LEN($A42)))))</f>
         <v/>
       </c>
       <c r="C42" s="26"/>
-      <c r="D42" s="72"/>
+      <c r="D42" s="70"/>
       <c r="E42" s="28"/>
       <c r="F42" s="39" t="str">
         <f aca="false">IF($B42="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B42),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33448,7 +34491,7 @@
         <f aca="true">IF(OR($A42="",$D42=""),"",YEARFRAC($D42,TODAY()))</f>
         <v/>
       </c>
-      <c r="H42" s="73" t="str">
+      <c r="H42" s="71" t="str">
         <f aca="false">IF($G42="","",MAX(0,INT($G42)))</f>
         <v/>
       </c>
@@ -33472,13 +34515,13 @@
       <c r="N42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="71"/>
+      <c r="A43" s="69"/>
       <c r="B43" s="37" t="str">
         <f aca="false">IF($A43="","",IF(ISERROR(FIND(".",$A43)),"",LOWER(MID($A43,FIND(CHAR(1),SUBSTITUTE($A43,".",CHAR(1),LEN($A43)-LEN(SUBSTITUTE($A43,".",""))))+1,LEN($A43)))))</f>
         <v/>
       </c>
       <c r="C43" s="26"/>
-      <c r="D43" s="72"/>
+      <c r="D43" s="70"/>
       <c r="E43" s="28"/>
       <c r="F43" s="39" t="str">
         <f aca="false">IF($B43="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B43),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33488,7 +34531,7 @@
         <f aca="true">IF(OR($A43="",$D43=""),"",YEARFRAC($D43,TODAY()))</f>
         <v/>
       </c>
-      <c r="H43" s="73" t="str">
+      <c r="H43" s="71" t="str">
         <f aca="false">IF($G43="","",MAX(0,INT($G43)))</f>
         <v/>
       </c>
@@ -33512,13 +34555,13 @@
       <c r="N43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="71"/>
+      <c r="A44" s="69"/>
       <c r="B44" s="37" t="str">
         <f aca="false">IF($A44="","",IF(ISERROR(FIND(".",$A44)),"",LOWER(MID($A44,FIND(CHAR(1),SUBSTITUTE($A44,".",CHAR(1),LEN($A44)-LEN(SUBSTITUTE($A44,".",""))))+1,LEN($A44)))))</f>
         <v/>
       </c>
       <c r="C44" s="26"/>
-      <c r="D44" s="72"/>
+      <c r="D44" s="70"/>
       <c r="E44" s="28"/>
       <c r="F44" s="39" t="str">
         <f aca="false">IF($B44="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B44),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33528,7 +34571,7 @@
         <f aca="true">IF(OR($A44="",$D44=""),"",YEARFRAC($D44,TODAY()))</f>
         <v/>
       </c>
-      <c r="H44" s="73" t="str">
+      <c r="H44" s="71" t="str">
         <f aca="false">IF($G44="","",MAX(0,INT($G44)))</f>
         <v/>
       </c>
@@ -33552,13 +34595,13 @@
       <c r="N44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="71"/>
+      <c r="A45" s="69"/>
       <c r="B45" s="37" t="str">
         <f aca="false">IF($A45="","",IF(ISERROR(FIND(".",$A45)),"",LOWER(MID($A45,FIND(CHAR(1),SUBSTITUTE($A45,".",CHAR(1),LEN($A45)-LEN(SUBSTITUTE($A45,".",""))))+1,LEN($A45)))))</f>
         <v/>
       </c>
       <c r="C45" s="26"/>
-      <c r="D45" s="72"/>
+      <c r="D45" s="70"/>
       <c r="E45" s="28"/>
       <c r="F45" s="39" t="str">
         <f aca="false">IF($B45="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B45),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33568,7 +34611,7 @@
         <f aca="true">IF(OR($A45="",$D45=""),"",YEARFRAC($D45,TODAY()))</f>
         <v/>
       </c>
-      <c r="H45" s="73" t="str">
+      <c r="H45" s="71" t="str">
         <f aca="false">IF($G45="","",MAX(0,INT($G45)))</f>
         <v/>
       </c>
@@ -33592,13 +34635,13 @@
       <c r="N45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="71"/>
+      <c r="A46" s="69"/>
       <c r="B46" s="37" t="str">
         <f aca="false">IF($A46="","",IF(ISERROR(FIND(".",$A46)),"",LOWER(MID($A46,FIND(CHAR(1),SUBSTITUTE($A46,".",CHAR(1),LEN($A46)-LEN(SUBSTITUTE($A46,".",""))))+1,LEN($A46)))))</f>
         <v/>
       </c>
       <c r="C46" s="26"/>
-      <c r="D46" s="72"/>
+      <c r="D46" s="70"/>
       <c r="E46" s="28"/>
       <c r="F46" s="39" t="str">
         <f aca="false">IF($B46="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B46),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33608,7 +34651,7 @@
         <f aca="true">IF(OR($A46="",$D46=""),"",YEARFRAC($D46,TODAY()))</f>
         <v/>
       </c>
-      <c r="H46" s="73" t="str">
+      <c r="H46" s="71" t="str">
         <f aca="false">IF($G46="","",MAX(0,INT($G46)))</f>
         <v/>
       </c>
@@ -33632,13 +34675,13 @@
       <c r="N46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="71"/>
+      <c r="A47" s="69"/>
       <c r="B47" s="37" t="str">
         <f aca="false">IF($A47="","",IF(ISERROR(FIND(".",$A47)),"",LOWER(MID($A47,FIND(CHAR(1),SUBSTITUTE($A47,".",CHAR(1),LEN($A47)-LEN(SUBSTITUTE($A47,".",""))))+1,LEN($A47)))))</f>
         <v/>
       </c>
       <c r="C47" s="26"/>
-      <c r="D47" s="72"/>
+      <c r="D47" s="70"/>
       <c r="E47" s="28"/>
       <c r="F47" s="39" t="str">
         <f aca="false">IF($B47="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B47),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33648,7 +34691,7 @@
         <f aca="true">IF(OR($A47="",$D47=""),"",YEARFRAC($D47,TODAY()))</f>
         <v/>
       </c>
-      <c r="H47" s="73" t="str">
+      <c r="H47" s="71" t="str">
         <f aca="false">IF($G47="","",MAX(0,INT($G47)))</f>
         <v/>
       </c>
@@ -33672,13 +34715,13 @@
       <c r="N47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="71"/>
+      <c r="A48" s="69"/>
       <c r="B48" s="37" t="str">
         <f aca="false">IF($A48="","",IF(ISERROR(FIND(".",$A48)),"",LOWER(MID($A48,FIND(CHAR(1),SUBSTITUTE($A48,".",CHAR(1),LEN($A48)-LEN(SUBSTITUTE($A48,".",""))))+1,LEN($A48)))))</f>
         <v/>
       </c>
       <c r="C48" s="26"/>
-      <c r="D48" s="72"/>
+      <c r="D48" s="70"/>
       <c r="E48" s="28"/>
       <c r="F48" s="39" t="str">
         <f aca="false">IF($B48="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B48),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33688,7 +34731,7 @@
         <f aca="true">IF(OR($A48="",$D48=""),"",YEARFRAC($D48,TODAY()))</f>
         <v/>
       </c>
-      <c r="H48" s="73" t="str">
+      <c r="H48" s="71" t="str">
         <f aca="false">IF($G48="","",MAX(0,INT($G48)))</f>
         <v/>
       </c>
@@ -33712,13 +34755,13 @@
       <c r="N48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="71"/>
+      <c r="A49" s="69"/>
       <c r="B49" s="37" t="str">
         <f aca="false">IF($A49="","",IF(ISERROR(FIND(".",$A49)),"",LOWER(MID($A49,FIND(CHAR(1),SUBSTITUTE($A49,".",CHAR(1),LEN($A49)-LEN(SUBSTITUTE($A49,".",""))))+1,LEN($A49)))))</f>
         <v/>
       </c>
       <c r="C49" s="26"/>
-      <c r="D49" s="72"/>
+      <c r="D49" s="70"/>
       <c r="E49" s="28"/>
       <c r="F49" s="39" t="str">
         <f aca="false">IF($B49="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B49),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33728,7 +34771,7 @@
         <f aca="true">IF(OR($A49="",$D49=""),"",YEARFRAC($D49,TODAY()))</f>
         <v/>
       </c>
-      <c r="H49" s="73" t="str">
+      <c r="H49" s="71" t="str">
         <f aca="false">IF($G49="","",MAX(0,INT($G49)))</f>
         <v/>
       </c>
@@ -33752,13 +34795,13 @@
       <c r="N49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="71"/>
+      <c r="A50" s="69"/>
       <c r="B50" s="37" t="str">
         <f aca="false">IF($A50="","",IF(ISERROR(FIND(".",$A50)),"",LOWER(MID($A50,FIND(CHAR(1),SUBSTITUTE($A50,".",CHAR(1),LEN($A50)-LEN(SUBSTITUTE($A50,".",""))))+1,LEN($A50)))))</f>
         <v/>
       </c>
       <c r="C50" s="26"/>
-      <c r="D50" s="72"/>
+      <c r="D50" s="70"/>
       <c r="E50" s="28"/>
       <c r="F50" s="39" t="str">
         <f aca="false">IF($B50="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B50),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33768,7 +34811,7 @@
         <f aca="true">IF(OR($A50="",$D50=""),"",YEARFRAC($D50,TODAY()))</f>
         <v/>
       </c>
-      <c r="H50" s="73" t="str">
+      <c r="H50" s="71" t="str">
         <f aca="false">IF($G50="","",MAX(0,INT($G50)))</f>
         <v/>
       </c>
@@ -33792,13 +34835,13 @@
       <c r="N50" s="36"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="71"/>
+      <c r="A51" s="69"/>
       <c r="B51" s="37" t="str">
         <f aca="false">IF($A51="","",IF(ISERROR(FIND(".",$A51)),"",LOWER(MID($A51,FIND(CHAR(1),SUBSTITUTE($A51,".",CHAR(1),LEN($A51)-LEN(SUBSTITUTE($A51,".",""))))+1,LEN($A51)))))</f>
         <v/>
       </c>
       <c r="C51" s="26"/>
-      <c r="D51" s="72"/>
+      <c r="D51" s="70"/>
       <c r="E51" s="28"/>
       <c r="F51" s="39" t="str">
         <f aca="false">IF($B51="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B51),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33808,7 +34851,7 @@
         <f aca="true">IF(OR($A51="",$D51=""),"",YEARFRAC($D51,TODAY()))</f>
         <v/>
       </c>
-      <c r="H51" s="73" t="str">
+      <c r="H51" s="71" t="str">
         <f aca="false">IF($G51="","",MAX(0,INT($G51)))</f>
         <v/>
       </c>
@@ -33832,13 +34875,13 @@
       <c r="N51" s="36"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="71"/>
+      <c r="A52" s="69"/>
       <c r="B52" s="37" t="str">
         <f aca="false">IF($A52="","",IF(ISERROR(FIND(".",$A52)),"",LOWER(MID($A52,FIND(CHAR(1),SUBSTITUTE($A52,".",CHAR(1),LEN($A52)-LEN(SUBSTITUTE($A52,".",""))))+1,LEN($A52)))))</f>
         <v/>
       </c>
       <c r="C52" s="26"/>
-      <c r="D52" s="72"/>
+      <c r="D52" s="70"/>
       <c r="E52" s="28"/>
       <c r="F52" s="39" t="str">
         <f aca="false">IF($B52="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B52),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33848,7 +34891,7 @@
         <f aca="true">IF(OR($A52="",$D52=""),"",YEARFRAC($D52,TODAY()))</f>
         <v/>
       </c>
-      <c r="H52" s="73" t="str">
+      <c r="H52" s="71" t="str">
         <f aca="false">IF($G52="","",MAX(0,INT($G52)))</f>
         <v/>
       </c>
@@ -33872,13 +34915,13 @@
       <c r="N52" s="36"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="71"/>
+      <c r="A53" s="69"/>
       <c r="B53" s="37" t="str">
         <f aca="false">IF($A53="","",IF(ISERROR(FIND(".",$A53)),"",LOWER(MID($A53,FIND(CHAR(1),SUBSTITUTE($A53,".",CHAR(1),LEN($A53)-LEN(SUBSTITUTE($A53,".",""))))+1,LEN($A53)))))</f>
         <v/>
       </c>
       <c r="C53" s="26"/>
-      <c r="D53" s="72"/>
+      <c r="D53" s="70"/>
       <c r="E53" s="28"/>
       <c r="F53" s="39" t="str">
         <f aca="false">IF($B53="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B53),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33888,7 +34931,7 @@
         <f aca="true">IF(OR($A53="",$D53=""),"",YEARFRAC($D53,TODAY()))</f>
         <v/>
       </c>
-      <c r="H53" s="73" t="str">
+      <c r="H53" s="71" t="str">
         <f aca="false">IF($G53="","",MAX(0,INT($G53)))</f>
         <v/>
       </c>
@@ -33912,13 +34955,13 @@
       <c r="N53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="71"/>
+      <c r="A54" s="69"/>
       <c r="B54" s="37" t="str">
         <f aca="false">IF($A54="","",IF(ISERROR(FIND(".",$A54)),"",LOWER(MID($A54,FIND(CHAR(1),SUBSTITUTE($A54,".",CHAR(1),LEN($A54)-LEN(SUBSTITUTE($A54,".",""))))+1,LEN($A54)))))</f>
         <v/>
       </c>
       <c r="C54" s="26"/>
-      <c r="D54" s="72"/>
+      <c r="D54" s="70"/>
       <c r="E54" s="28"/>
       <c r="F54" s="39" t="str">
         <f aca="false">IF($B54="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B54),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33928,7 +34971,7 @@
         <f aca="true">IF(OR($A54="",$D54=""),"",YEARFRAC($D54,TODAY()))</f>
         <v/>
       </c>
-      <c r="H54" s="73" t="str">
+      <c r="H54" s="71" t="str">
         <f aca="false">IF($G54="","",MAX(0,INT($G54)))</f>
         <v/>
       </c>
@@ -33952,13 +34995,13 @@
       <c r="N54" s="36"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="71"/>
+      <c r="A55" s="69"/>
       <c r="B55" s="37" t="str">
         <f aca="false">IF($A55="","",IF(ISERROR(FIND(".",$A55)),"",LOWER(MID($A55,FIND(CHAR(1),SUBSTITUTE($A55,".",CHAR(1),LEN($A55)-LEN(SUBSTITUTE($A55,".",""))))+1,LEN($A55)))))</f>
         <v/>
       </c>
       <c r="C55" s="26"/>
-      <c r="D55" s="72"/>
+      <c r="D55" s="70"/>
       <c r="E55" s="28"/>
       <c r="F55" s="39" t="str">
         <f aca="false">IF($B55="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B55),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -33968,7 +35011,7 @@
         <f aca="true">IF(OR($A55="",$D55=""),"",YEARFRAC($D55,TODAY()))</f>
         <v/>
       </c>
-      <c r="H55" s="73" t="str">
+      <c r="H55" s="71" t="str">
         <f aca="false">IF($G55="","",MAX(0,INT($G55)))</f>
         <v/>
       </c>
@@ -33992,13 +35035,13 @@
       <c r="N55" s="36"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="71"/>
+      <c r="A56" s="69"/>
       <c r="B56" s="37" t="str">
         <f aca="false">IF($A56="","",IF(ISERROR(FIND(".",$A56)),"",LOWER(MID($A56,FIND(CHAR(1),SUBSTITUTE($A56,".",CHAR(1),LEN($A56)-LEN(SUBSTITUTE($A56,".",""))))+1,LEN($A56)))))</f>
         <v/>
       </c>
       <c r="C56" s="26"/>
-      <c r="D56" s="72"/>
+      <c r="D56" s="70"/>
       <c r="E56" s="28"/>
       <c r="F56" s="39" t="str">
         <f aca="false">IF($B56="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B56),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34008,7 +35051,7 @@
         <f aca="true">IF(OR($A56="",$D56=""),"",YEARFRAC($D56,TODAY()))</f>
         <v/>
       </c>
-      <c r="H56" s="73" t="str">
+      <c r="H56" s="71" t="str">
         <f aca="false">IF($G56="","",MAX(0,INT($G56)))</f>
         <v/>
       </c>
@@ -34032,13 +35075,13 @@
       <c r="N56" s="36"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="71"/>
+      <c r="A57" s="69"/>
       <c r="B57" s="37" t="str">
         <f aca="false">IF($A57="","",IF(ISERROR(FIND(".",$A57)),"",LOWER(MID($A57,FIND(CHAR(1),SUBSTITUTE($A57,".",CHAR(1),LEN($A57)-LEN(SUBSTITUTE($A57,".",""))))+1,LEN($A57)))))</f>
         <v/>
       </c>
       <c r="C57" s="26"/>
-      <c r="D57" s="72"/>
+      <c r="D57" s="70"/>
       <c r="E57" s="28"/>
       <c r="F57" s="39" t="str">
         <f aca="false">IF($B57="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B57),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34048,7 +35091,7 @@
         <f aca="true">IF(OR($A57="",$D57=""),"",YEARFRAC($D57,TODAY()))</f>
         <v/>
       </c>
-      <c r="H57" s="73" t="str">
+      <c r="H57" s="71" t="str">
         <f aca="false">IF($G57="","",MAX(0,INT($G57)))</f>
         <v/>
       </c>
@@ -34072,13 +35115,13 @@
       <c r="N57" s="36"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="71"/>
+      <c r="A58" s="69"/>
       <c r="B58" s="37" t="str">
         <f aca="false">IF($A58="","",IF(ISERROR(FIND(".",$A58)),"",LOWER(MID($A58,FIND(CHAR(1),SUBSTITUTE($A58,".",CHAR(1),LEN($A58)-LEN(SUBSTITUTE($A58,".",""))))+1,LEN($A58)))))</f>
         <v/>
       </c>
       <c r="C58" s="26"/>
-      <c r="D58" s="72"/>
+      <c r="D58" s="70"/>
       <c r="E58" s="28"/>
       <c r="F58" s="39" t="str">
         <f aca="false">IF($B58="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B58),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34088,7 +35131,7 @@
         <f aca="true">IF(OR($A58="",$D58=""),"",YEARFRAC($D58,TODAY()))</f>
         <v/>
       </c>
-      <c r="H58" s="73" t="str">
+      <c r="H58" s="71" t="str">
         <f aca="false">IF($G58="","",MAX(0,INT($G58)))</f>
         <v/>
       </c>
@@ -34112,13 +35155,13 @@
       <c r="N58" s="36"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="71"/>
+      <c r="A59" s="69"/>
       <c r="B59" s="37" t="str">
         <f aca="false">IF($A59="","",IF(ISERROR(FIND(".",$A59)),"",LOWER(MID($A59,FIND(CHAR(1),SUBSTITUTE($A59,".",CHAR(1),LEN($A59)-LEN(SUBSTITUTE($A59,".",""))))+1,LEN($A59)))))</f>
         <v/>
       </c>
       <c r="C59" s="26"/>
-      <c r="D59" s="72"/>
+      <c r="D59" s="70"/>
       <c r="E59" s="28"/>
       <c r="F59" s="39" t="str">
         <f aca="false">IF($B59="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B59),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34128,7 +35171,7 @@
         <f aca="true">IF(OR($A59="",$D59=""),"",YEARFRAC($D59,TODAY()))</f>
         <v/>
       </c>
-      <c r="H59" s="73" t="str">
+      <c r="H59" s="71" t="str">
         <f aca="false">IF($G59="","",MAX(0,INT($G59)))</f>
         <v/>
       </c>
@@ -34152,13 +35195,13 @@
       <c r="N59" s="36"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="71"/>
+      <c r="A60" s="69"/>
       <c r="B60" s="37" t="str">
         <f aca="false">IF($A60="","",IF(ISERROR(FIND(".",$A60)),"",LOWER(MID($A60,FIND(CHAR(1),SUBSTITUTE($A60,".",CHAR(1),LEN($A60)-LEN(SUBSTITUTE($A60,".",""))))+1,LEN($A60)))))</f>
         <v/>
       </c>
       <c r="C60" s="26"/>
-      <c r="D60" s="72"/>
+      <c r="D60" s="70"/>
       <c r="E60" s="28"/>
       <c r="F60" s="39" t="str">
         <f aca="false">IF($B60="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B60),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34168,7 +35211,7 @@
         <f aca="true">IF(OR($A60="",$D60=""),"",YEARFRAC($D60,TODAY()))</f>
         <v/>
       </c>
-      <c r="H60" s="73" t="str">
+      <c r="H60" s="71" t="str">
         <f aca="false">IF($G60="","",MAX(0,INT($G60)))</f>
         <v/>
       </c>
@@ -34192,13 +35235,13 @@
       <c r="N60" s="36"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="71"/>
+      <c r="A61" s="69"/>
       <c r="B61" s="37" t="str">
         <f aca="false">IF($A61="","",IF(ISERROR(FIND(".",$A61)),"",LOWER(MID($A61,FIND(CHAR(1),SUBSTITUTE($A61,".",CHAR(1),LEN($A61)-LEN(SUBSTITUTE($A61,".",""))))+1,LEN($A61)))))</f>
         <v/>
       </c>
       <c r="C61" s="26"/>
-      <c r="D61" s="72"/>
+      <c r="D61" s="70"/>
       <c r="E61" s="28"/>
       <c r="F61" s="39" t="str">
         <f aca="false">IF($B61="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B61),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34208,7 +35251,7 @@
         <f aca="true">IF(OR($A61="",$D61=""),"",YEARFRAC($D61,TODAY()))</f>
         <v/>
       </c>
-      <c r="H61" s="73" t="str">
+      <c r="H61" s="71" t="str">
         <f aca="false">IF($G61="","",MAX(0,INT($G61)))</f>
         <v/>
       </c>
@@ -34232,13 +35275,13 @@
       <c r="N61" s="36"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="71"/>
+      <c r="A62" s="69"/>
       <c r="B62" s="37" t="str">
         <f aca="false">IF($A62="","",IF(ISERROR(FIND(".",$A62)),"",LOWER(MID($A62,FIND(CHAR(1),SUBSTITUTE($A62,".",CHAR(1),LEN($A62)-LEN(SUBSTITUTE($A62,".",""))))+1,LEN($A62)))))</f>
         <v/>
       </c>
       <c r="C62" s="26"/>
-      <c r="D62" s="72"/>
+      <c r="D62" s="70"/>
       <c r="E62" s="28"/>
       <c r="F62" s="39" t="str">
         <f aca="false">IF($B62="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B62),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34248,7 +35291,7 @@
         <f aca="true">IF(OR($A62="",$D62=""),"",YEARFRAC($D62,TODAY()))</f>
         <v/>
       </c>
-      <c r="H62" s="73" t="str">
+      <c r="H62" s="71" t="str">
         <f aca="false">IF($G62="","",MAX(0,INT($G62)))</f>
         <v/>
       </c>
@@ -34272,13 +35315,13 @@
       <c r="N62" s="36"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="71"/>
+      <c r="A63" s="69"/>
       <c r="B63" s="37" t="str">
         <f aca="false">IF($A63="","",IF(ISERROR(FIND(".",$A63)),"",LOWER(MID($A63,FIND(CHAR(1),SUBSTITUTE($A63,".",CHAR(1),LEN($A63)-LEN(SUBSTITUTE($A63,".",""))))+1,LEN($A63)))))</f>
         <v/>
       </c>
       <c r="C63" s="26"/>
-      <c r="D63" s="72"/>
+      <c r="D63" s="70"/>
       <c r="E63" s="28"/>
       <c r="F63" s="39" t="str">
         <f aca="false">IF($B63="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B63),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34288,7 +35331,7 @@
         <f aca="true">IF(OR($A63="",$D63=""),"",YEARFRAC($D63,TODAY()))</f>
         <v/>
       </c>
-      <c r="H63" s="73" t="str">
+      <c r="H63" s="71" t="str">
         <f aca="false">IF($G63="","",MAX(0,INT($G63)))</f>
         <v/>
       </c>
@@ -34312,13 +35355,13 @@
       <c r="N63" s="36"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="71"/>
+      <c r="A64" s="69"/>
       <c r="B64" s="37" t="str">
         <f aca="false">IF($A64="","",IF(ISERROR(FIND(".",$A64)),"",LOWER(MID($A64,FIND(CHAR(1),SUBSTITUTE($A64,".",CHAR(1),LEN($A64)-LEN(SUBSTITUTE($A64,".",""))))+1,LEN($A64)))))</f>
         <v/>
       </c>
       <c r="C64" s="26"/>
-      <c r="D64" s="72"/>
+      <c r="D64" s="70"/>
       <c r="E64" s="28"/>
       <c r="F64" s="39" t="str">
         <f aca="false">IF($B64="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B64),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34328,7 +35371,7 @@
         <f aca="true">IF(OR($A64="",$D64=""),"",YEARFRAC($D64,TODAY()))</f>
         <v/>
       </c>
-      <c r="H64" s="73" t="str">
+      <c r="H64" s="71" t="str">
         <f aca="false">IF($G64="","",MAX(0,INT($G64)))</f>
         <v/>
       </c>
@@ -34352,13 +35395,13 @@
       <c r="N64" s="36"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="71"/>
+      <c r="A65" s="69"/>
       <c r="B65" s="37" t="str">
         <f aca="false">IF($A65="","",IF(ISERROR(FIND(".",$A65)),"",LOWER(MID($A65,FIND(CHAR(1),SUBSTITUTE($A65,".",CHAR(1),LEN($A65)-LEN(SUBSTITUTE($A65,".",""))))+1,LEN($A65)))))</f>
         <v/>
       </c>
       <c r="C65" s="26"/>
-      <c r="D65" s="72"/>
+      <c r="D65" s="70"/>
       <c r="E65" s="28"/>
       <c r="F65" s="39" t="str">
         <f aca="false">IF($B65="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B65),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34368,7 +35411,7 @@
         <f aca="true">IF(OR($A65="",$D65=""),"",YEARFRAC($D65,TODAY()))</f>
         <v/>
       </c>
-      <c r="H65" s="73" t="str">
+      <c r="H65" s="71" t="str">
         <f aca="false">IF($G65="","",MAX(0,INT($G65)))</f>
         <v/>
       </c>
@@ -34392,13 +35435,13 @@
       <c r="N65" s="36"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="71"/>
+      <c r="A66" s="69"/>
       <c r="B66" s="37" t="str">
         <f aca="false">IF($A66="","",IF(ISERROR(FIND(".",$A66)),"",LOWER(MID($A66,FIND(CHAR(1),SUBSTITUTE($A66,".",CHAR(1),LEN($A66)-LEN(SUBSTITUTE($A66,".",""))))+1,LEN($A66)))))</f>
         <v/>
       </c>
       <c r="C66" s="26"/>
-      <c r="D66" s="72"/>
+      <c r="D66" s="70"/>
       <c r="E66" s="28"/>
       <c r="F66" s="39" t="str">
         <f aca="false">IF($B66="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B66),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34408,7 +35451,7 @@
         <f aca="true">IF(OR($A66="",$D66=""),"",YEARFRAC($D66,TODAY()))</f>
         <v/>
       </c>
-      <c r="H66" s="73" t="str">
+      <c r="H66" s="71" t="str">
         <f aca="false">IF($G66="","",MAX(0,INT($G66)))</f>
         <v/>
       </c>
@@ -34432,13 +35475,13 @@
       <c r="N66" s="36"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="71"/>
+      <c r="A67" s="69"/>
       <c r="B67" s="37" t="str">
         <f aca="false">IF($A67="","",IF(ISERROR(FIND(".",$A67)),"",LOWER(MID($A67,FIND(CHAR(1),SUBSTITUTE($A67,".",CHAR(1),LEN($A67)-LEN(SUBSTITUTE($A67,".",""))))+1,LEN($A67)))))</f>
         <v/>
       </c>
       <c r="C67" s="26"/>
-      <c r="D67" s="72"/>
+      <c r="D67" s="70"/>
       <c r="E67" s="28"/>
       <c r="F67" s="39" t="str">
         <f aca="false">IF($B67="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B67),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34448,7 +35491,7 @@
         <f aca="true">IF(OR($A67="",$D67=""),"",YEARFRAC($D67,TODAY()))</f>
         <v/>
       </c>
-      <c r="H67" s="73" t="str">
+      <c r="H67" s="71" t="str">
         <f aca="false">IF($G67="","",MAX(0,INT($G67)))</f>
         <v/>
       </c>
@@ -34472,13 +35515,13 @@
       <c r="N67" s="36"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="71"/>
+      <c r="A68" s="69"/>
       <c r="B68" s="37" t="str">
         <f aca="false">IF($A68="","",IF(ISERROR(FIND(".",$A68)),"",LOWER(MID($A68,FIND(CHAR(1),SUBSTITUTE($A68,".",CHAR(1),LEN($A68)-LEN(SUBSTITUTE($A68,".",""))))+1,LEN($A68)))))</f>
         <v/>
       </c>
       <c r="C68" s="26"/>
-      <c r="D68" s="72"/>
+      <c r="D68" s="70"/>
       <c r="E68" s="28"/>
       <c r="F68" s="39" t="str">
         <f aca="false">IF($B68="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B68),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34488,7 +35531,7 @@
         <f aca="true">IF(OR($A68="",$D68=""),"",YEARFRAC($D68,TODAY()))</f>
         <v/>
       </c>
-      <c r="H68" s="73" t="str">
+      <c r="H68" s="71" t="str">
         <f aca="false">IF($G68="","",MAX(0,INT($G68)))</f>
         <v/>
       </c>
@@ -34512,13 +35555,13 @@
       <c r="N68" s="36"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="71"/>
+      <c r="A69" s="69"/>
       <c r="B69" s="37" t="str">
         <f aca="false">IF($A69="","",IF(ISERROR(FIND(".",$A69)),"",LOWER(MID($A69,FIND(CHAR(1),SUBSTITUTE($A69,".",CHAR(1),LEN($A69)-LEN(SUBSTITUTE($A69,".",""))))+1,LEN($A69)))))</f>
         <v/>
       </c>
       <c r="C69" s="26"/>
-      <c r="D69" s="72"/>
+      <c r="D69" s="70"/>
       <c r="E69" s="28"/>
       <c r="F69" s="39" t="str">
         <f aca="false">IF($B69="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B69),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34528,7 +35571,7 @@
         <f aca="true">IF(OR($A69="",$D69=""),"",YEARFRAC($D69,TODAY()))</f>
         <v/>
       </c>
-      <c r="H69" s="73" t="str">
+      <c r="H69" s="71" t="str">
         <f aca="false">IF($G69="","",MAX(0,INT($G69)))</f>
         <v/>
       </c>
@@ -34552,13 +35595,13 @@
       <c r="N69" s="36"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="71"/>
+      <c r="A70" s="69"/>
       <c r="B70" s="37" t="str">
         <f aca="false">IF($A70="","",IF(ISERROR(FIND(".",$A70)),"",LOWER(MID($A70,FIND(CHAR(1),SUBSTITUTE($A70,".",CHAR(1),LEN($A70)-LEN(SUBSTITUTE($A70,".",""))))+1,LEN($A70)))))</f>
         <v/>
       </c>
       <c r="C70" s="26"/>
-      <c r="D70" s="72"/>
+      <c r="D70" s="70"/>
       <c r="E70" s="28"/>
       <c r="F70" s="39" t="str">
         <f aca="false">IF($B70="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B70),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34568,7 +35611,7 @@
         <f aca="true">IF(OR($A70="",$D70=""),"",YEARFRAC($D70,TODAY()))</f>
         <v/>
       </c>
-      <c r="H70" s="73" t="str">
+      <c r="H70" s="71" t="str">
         <f aca="false">IF($G70="","",MAX(0,INT($G70)))</f>
         <v/>
       </c>
@@ -34592,13 +35635,13 @@
       <c r="N70" s="36"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="71"/>
+      <c r="A71" s="69"/>
       <c r="B71" s="37" t="str">
         <f aca="false">IF($A71="","",IF(ISERROR(FIND(".",$A71)),"",LOWER(MID($A71,FIND(CHAR(1),SUBSTITUTE($A71,".",CHAR(1),LEN($A71)-LEN(SUBSTITUTE($A71,".",""))))+1,LEN($A71)))))</f>
         <v/>
       </c>
       <c r="C71" s="26"/>
-      <c r="D71" s="72"/>
+      <c r="D71" s="70"/>
       <c r="E71" s="28"/>
       <c r="F71" s="39" t="str">
         <f aca="false">IF($B71="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B71),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34608,7 +35651,7 @@
         <f aca="true">IF(OR($A71="",$D71=""),"",YEARFRAC($D71,TODAY()))</f>
         <v/>
       </c>
-      <c r="H71" s="73" t="str">
+      <c r="H71" s="71" t="str">
         <f aca="false">IF($G71="","",MAX(0,INT($G71)))</f>
         <v/>
       </c>
@@ -34632,13 +35675,13 @@
       <c r="N71" s="36"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="71"/>
+      <c r="A72" s="69"/>
       <c r="B72" s="37" t="str">
         <f aca="false">IF($A72="","",IF(ISERROR(FIND(".",$A72)),"",LOWER(MID($A72,FIND(CHAR(1),SUBSTITUTE($A72,".",CHAR(1),LEN($A72)-LEN(SUBSTITUTE($A72,".",""))))+1,LEN($A72)))))</f>
         <v/>
       </c>
       <c r="C72" s="26"/>
-      <c r="D72" s="72"/>
+      <c r="D72" s="70"/>
       <c r="E72" s="28"/>
       <c r="F72" s="39" t="str">
         <f aca="false">IF($B72="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B72),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34648,7 +35691,7 @@
         <f aca="true">IF(OR($A72="",$D72=""),"",YEARFRAC($D72,TODAY()))</f>
         <v/>
       </c>
-      <c r="H72" s="73" t="str">
+      <c r="H72" s="71" t="str">
         <f aca="false">IF($G72="","",MAX(0,INT($G72)))</f>
         <v/>
       </c>
@@ -34672,13 +35715,13 @@
       <c r="N72" s="36"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="71"/>
+      <c r="A73" s="69"/>
       <c r="B73" s="37" t="str">
         <f aca="false">IF($A73="","",IF(ISERROR(FIND(".",$A73)),"",LOWER(MID($A73,FIND(CHAR(1),SUBSTITUTE($A73,".",CHAR(1),LEN($A73)-LEN(SUBSTITUTE($A73,".",""))))+1,LEN($A73)))))</f>
         <v/>
       </c>
       <c r="C73" s="26"/>
-      <c r="D73" s="72"/>
+      <c r="D73" s="70"/>
       <c r="E73" s="28"/>
       <c r="F73" s="39" t="str">
         <f aca="false">IF($B73="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B73),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34688,7 +35731,7 @@
         <f aca="true">IF(OR($A73="",$D73=""),"",YEARFRAC($D73,TODAY()))</f>
         <v/>
       </c>
-      <c r="H73" s="73" t="str">
+      <c r="H73" s="71" t="str">
         <f aca="false">IF($G73="","",MAX(0,INT($G73)))</f>
         <v/>
       </c>
@@ -34712,13 +35755,13 @@
       <c r="N73" s="36"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="71"/>
+      <c r="A74" s="69"/>
       <c r="B74" s="37" t="str">
         <f aca="false">IF($A74="","",IF(ISERROR(FIND(".",$A74)),"",LOWER(MID($A74,FIND(CHAR(1),SUBSTITUTE($A74,".",CHAR(1),LEN($A74)-LEN(SUBSTITUTE($A74,".",""))))+1,LEN($A74)))))</f>
         <v/>
       </c>
       <c r="C74" s="26"/>
-      <c r="D74" s="72"/>
+      <c r="D74" s="70"/>
       <c r="E74" s="28"/>
       <c r="F74" s="39" t="str">
         <f aca="false">IF($B74="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B74),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34728,7 +35771,7 @@
         <f aca="true">IF(OR($A74="",$D74=""),"",YEARFRAC($D74,TODAY()))</f>
         <v/>
       </c>
-      <c r="H74" s="73" t="str">
+      <c r="H74" s="71" t="str">
         <f aca="false">IF($G74="","",MAX(0,INT($G74)))</f>
         <v/>
       </c>
@@ -34752,13 +35795,13 @@
       <c r="N74" s="36"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="71"/>
+      <c r="A75" s="69"/>
       <c r="B75" s="37" t="str">
         <f aca="false">IF($A75="","",IF(ISERROR(FIND(".",$A75)),"",LOWER(MID($A75,FIND(CHAR(1),SUBSTITUTE($A75,".",CHAR(1),LEN($A75)-LEN(SUBSTITUTE($A75,".",""))))+1,LEN($A75)))))</f>
         <v/>
       </c>
       <c r="C75" s="26"/>
-      <c r="D75" s="72"/>
+      <c r="D75" s="70"/>
       <c r="E75" s="28"/>
       <c r="F75" s="39" t="str">
         <f aca="false">IF($B75="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B75),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34768,7 +35811,7 @@
         <f aca="true">IF(OR($A75="",$D75=""),"",YEARFRAC($D75,TODAY()))</f>
         <v/>
       </c>
-      <c r="H75" s="73" t="str">
+      <c r="H75" s="71" t="str">
         <f aca="false">IF($G75="","",MAX(0,INT($G75)))</f>
         <v/>
       </c>
@@ -34792,13 +35835,13 @@
       <c r="N75" s="36"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="71"/>
+      <c r="A76" s="69"/>
       <c r="B76" s="37" t="str">
         <f aca="false">IF($A76="","",IF(ISERROR(FIND(".",$A76)),"",LOWER(MID($A76,FIND(CHAR(1),SUBSTITUTE($A76,".",CHAR(1),LEN($A76)-LEN(SUBSTITUTE($A76,".",""))))+1,LEN($A76)))))</f>
         <v/>
       </c>
       <c r="C76" s="26"/>
-      <c r="D76" s="72"/>
+      <c r="D76" s="70"/>
       <c r="E76" s="28"/>
       <c r="F76" s="39" t="str">
         <f aca="false">IF($B76="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B76),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34808,7 +35851,7 @@
         <f aca="true">IF(OR($A76="",$D76=""),"",YEARFRAC($D76,TODAY()))</f>
         <v/>
       </c>
-      <c r="H76" s="73" t="str">
+      <c r="H76" s="71" t="str">
         <f aca="false">IF($G76="","",MAX(0,INT($G76)))</f>
         <v/>
       </c>
@@ -34832,13 +35875,13 @@
       <c r="N76" s="36"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="71"/>
+      <c r="A77" s="69"/>
       <c r="B77" s="37" t="str">
         <f aca="false">IF($A77="","",IF(ISERROR(FIND(".",$A77)),"",LOWER(MID($A77,FIND(CHAR(1),SUBSTITUTE($A77,".",CHAR(1),LEN($A77)-LEN(SUBSTITUTE($A77,".",""))))+1,LEN($A77)))))</f>
         <v/>
       </c>
       <c r="C77" s="26"/>
-      <c r="D77" s="72"/>
+      <c r="D77" s="70"/>
       <c r="E77" s="28"/>
       <c r="F77" s="39" t="str">
         <f aca="false">IF($B77="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B77),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34848,7 +35891,7 @@
         <f aca="true">IF(OR($A77="",$D77=""),"",YEARFRAC($D77,TODAY()))</f>
         <v/>
       </c>
-      <c r="H77" s="73" t="str">
+      <c r="H77" s="71" t="str">
         <f aca="false">IF($G77="","",MAX(0,INT($G77)))</f>
         <v/>
       </c>
@@ -34872,13 +35915,13 @@
       <c r="N77" s="36"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="71"/>
+      <c r="A78" s="69"/>
       <c r="B78" s="37" t="str">
         <f aca="false">IF($A78="","",IF(ISERROR(FIND(".",$A78)),"",LOWER(MID($A78,FIND(CHAR(1),SUBSTITUTE($A78,".",CHAR(1),LEN($A78)-LEN(SUBSTITUTE($A78,".",""))))+1,LEN($A78)))))</f>
         <v/>
       </c>
       <c r="C78" s="26"/>
-      <c r="D78" s="72"/>
+      <c r="D78" s="70"/>
       <c r="E78" s="28"/>
       <c r="F78" s="39" t="str">
         <f aca="false">IF($B78="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B78),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34888,7 +35931,7 @@
         <f aca="true">IF(OR($A78="",$D78=""),"",YEARFRAC($D78,TODAY()))</f>
         <v/>
       </c>
-      <c r="H78" s="73" t="str">
+      <c r="H78" s="71" t="str">
         <f aca="false">IF($G78="","",MAX(0,INT($G78)))</f>
         <v/>
       </c>
@@ -34912,13 +35955,13 @@
       <c r="N78" s="36"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="71"/>
+      <c r="A79" s="69"/>
       <c r="B79" s="37" t="str">
         <f aca="false">IF($A79="","",IF(ISERROR(FIND(".",$A79)),"",LOWER(MID($A79,FIND(CHAR(1),SUBSTITUTE($A79,".",CHAR(1),LEN($A79)-LEN(SUBSTITUTE($A79,".",""))))+1,LEN($A79)))))</f>
         <v/>
       </c>
       <c r="C79" s="26"/>
-      <c r="D79" s="72"/>
+      <c r="D79" s="70"/>
       <c r="E79" s="28"/>
       <c r="F79" s="39" t="str">
         <f aca="false">IF($B79="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B79),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34928,7 +35971,7 @@
         <f aca="true">IF(OR($A79="",$D79=""),"",YEARFRAC($D79,TODAY()))</f>
         <v/>
       </c>
-      <c r="H79" s="73" t="str">
+      <c r="H79" s="71" t="str">
         <f aca="false">IF($G79="","",MAX(0,INT($G79)))</f>
         <v/>
       </c>
@@ -34952,13 +35995,13 @@
       <c r="N79" s="36"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="71"/>
+      <c r="A80" s="69"/>
       <c r="B80" s="37" t="str">
         <f aca="false">IF($A80="","",IF(ISERROR(FIND(".",$A80)),"",LOWER(MID($A80,FIND(CHAR(1),SUBSTITUTE($A80,".",CHAR(1),LEN($A80)-LEN(SUBSTITUTE($A80,".",""))))+1,LEN($A80)))))</f>
         <v/>
       </c>
       <c r="C80" s="26"/>
-      <c r="D80" s="72"/>
+      <c r="D80" s="70"/>
       <c r="E80" s="28"/>
       <c r="F80" s="39" t="str">
         <f aca="false">IF($B80="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B80),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -34968,7 +36011,7 @@
         <f aca="true">IF(OR($A80="",$D80=""),"",YEARFRAC($D80,TODAY()))</f>
         <v/>
       </c>
-      <c r="H80" s="73" t="str">
+      <c r="H80" s="71" t="str">
         <f aca="false">IF($G80="","",MAX(0,INT($G80)))</f>
         <v/>
       </c>
@@ -34992,13 +36035,13 @@
       <c r="N80" s="36"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="71"/>
+      <c r="A81" s="69"/>
       <c r="B81" s="37" t="str">
         <f aca="false">IF($A81="","",IF(ISERROR(FIND(".",$A81)),"",LOWER(MID($A81,FIND(CHAR(1),SUBSTITUTE($A81,".",CHAR(1),LEN($A81)-LEN(SUBSTITUTE($A81,".",""))))+1,LEN($A81)))))</f>
         <v/>
       </c>
       <c r="C81" s="26"/>
-      <c r="D81" s="72"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="28"/>
       <c r="F81" s="39" t="str">
         <f aca="false">IF($B81="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B81),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35008,7 +36051,7 @@
         <f aca="true">IF(OR($A81="",$D81=""),"",YEARFRAC($D81,TODAY()))</f>
         <v/>
       </c>
-      <c r="H81" s="73" t="str">
+      <c r="H81" s="71" t="str">
         <f aca="false">IF($G81="","",MAX(0,INT($G81)))</f>
         <v/>
       </c>
@@ -35032,13 +36075,13 @@
       <c r="N81" s="36"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="71"/>
+      <c r="A82" s="69"/>
       <c r="B82" s="37" t="str">
         <f aca="false">IF($A82="","",IF(ISERROR(FIND(".",$A82)),"",LOWER(MID($A82,FIND(CHAR(1),SUBSTITUTE($A82,".",CHAR(1),LEN($A82)-LEN(SUBSTITUTE($A82,".",""))))+1,LEN($A82)))))</f>
         <v/>
       </c>
       <c r="C82" s="26"/>
-      <c r="D82" s="72"/>
+      <c r="D82" s="70"/>
       <c r="E82" s="28"/>
       <c r="F82" s="39" t="str">
         <f aca="false">IF($B82="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B82),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35048,7 +36091,7 @@
         <f aca="true">IF(OR($A82="",$D82=""),"",YEARFRAC($D82,TODAY()))</f>
         <v/>
       </c>
-      <c r="H82" s="73" t="str">
+      <c r="H82" s="71" t="str">
         <f aca="false">IF($G82="","",MAX(0,INT($G82)))</f>
         <v/>
       </c>
@@ -35072,13 +36115,13 @@
       <c r="N82" s="36"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="71"/>
+      <c r="A83" s="69"/>
       <c r="B83" s="37" t="str">
         <f aca="false">IF($A83="","",IF(ISERROR(FIND(".",$A83)),"",LOWER(MID($A83,FIND(CHAR(1),SUBSTITUTE($A83,".",CHAR(1),LEN($A83)-LEN(SUBSTITUTE($A83,".",""))))+1,LEN($A83)))))</f>
         <v/>
       </c>
       <c r="C83" s="26"/>
-      <c r="D83" s="72"/>
+      <c r="D83" s="70"/>
       <c r="E83" s="28"/>
       <c r="F83" s="39" t="str">
         <f aca="false">IF($B83="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B83),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35088,7 +36131,7 @@
         <f aca="true">IF(OR($A83="",$D83=""),"",YEARFRAC($D83,TODAY()))</f>
         <v/>
       </c>
-      <c r="H83" s="73" t="str">
+      <c r="H83" s="71" t="str">
         <f aca="false">IF($G83="","",MAX(0,INT($G83)))</f>
         <v/>
       </c>
@@ -35112,13 +36155,13 @@
       <c r="N83" s="36"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="71"/>
+      <c r="A84" s="69"/>
       <c r="B84" s="37" t="str">
         <f aca="false">IF($A84="","",IF(ISERROR(FIND(".",$A84)),"",LOWER(MID($A84,FIND(CHAR(1),SUBSTITUTE($A84,".",CHAR(1),LEN($A84)-LEN(SUBSTITUTE($A84,".",""))))+1,LEN($A84)))))</f>
         <v/>
       </c>
       <c r="C84" s="26"/>
-      <c r="D84" s="72"/>
+      <c r="D84" s="70"/>
       <c r="E84" s="28"/>
       <c r="F84" s="39" t="str">
         <f aca="false">IF($B84="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B84),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35128,7 +36171,7 @@
         <f aca="true">IF(OR($A84="",$D84=""),"",YEARFRAC($D84,TODAY()))</f>
         <v/>
       </c>
-      <c r="H84" s="73" t="str">
+      <c r="H84" s="71" t="str">
         <f aca="false">IF($G84="","",MAX(0,INT($G84)))</f>
         <v/>
       </c>
@@ -35152,13 +36195,13 @@
       <c r="N84" s="36"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="71"/>
+      <c r="A85" s="69"/>
       <c r="B85" s="37" t="str">
         <f aca="false">IF($A85="","",IF(ISERROR(FIND(".",$A85)),"",LOWER(MID($A85,FIND(CHAR(1),SUBSTITUTE($A85,".",CHAR(1),LEN($A85)-LEN(SUBSTITUTE($A85,".",""))))+1,LEN($A85)))))</f>
         <v/>
       </c>
       <c r="C85" s="26"/>
-      <c r="D85" s="72"/>
+      <c r="D85" s="70"/>
       <c r="E85" s="28"/>
       <c r="F85" s="39" t="str">
         <f aca="false">IF($B85="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B85),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35168,7 +36211,7 @@
         <f aca="true">IF(OR($A85="",$D85=""),"",YEARFRAC($D85,TODAY()))</f>
         <v/>
       </c>
-      <c r="H85" s="73" t="str">
+      <c r="H85" s="71" t="str">
         <f aca="false">IF($G85="","",MAX(0,INT($G85)))</f>
         <v/>
       </c>
@@ -35192,13 +36235,13 @@
       <c r="N85" s="36"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="71"/>
+      <c r="A86" s="69"/>
       <c r="B86" s="37" t="str">
         <f aca="false">IF($A86="","",IF(ISERROR(FIND(".",$A86)),"",LOWER(MID($A86,FIND(CHAR(1),SUBSTITUTE($A86,".",CHAR(1),LEN($A86)-LEN(SUBSTITUTE($A86,".",""))))+1,LEN($A86)))))</f>
         <v/>
       </c>
       <c r="C86" s="26"/>
-      <c r="D86" s="72"/>
+      <c r="D86" s="70"/>
       <c r="E86" s="28"/>
       <c r="F86" s="39" t="str">
         <f aca="false">IF($B86="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B86),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35208,7 +36251,7 @@
         <f aca="true">IF(OR($A86="",$D86=""),"",YEARFRAC($D86,TODAY()))</f>
         <v/>
       </c>
-      <c r="H86" s="73" t="str">
+      <c r="H86" s="71" t="str">
         <f aca="false">IF($G86="","",MAX(0,INT($G86)))</f>
         <v/>
       </c>
@@ -35232,13 +36275,13 @@
       <c r="N86" s="36"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="71"/>
+      <c r="A87" s="69"/>
       <c r="B87" s="37" t="str">
         <f aca="false">IF($A87="","",IF(ISERROR(FIND(".",$A87)),"",LOWER(MID($A87,FIND(CHAR(1),SUBSTITUTE($A87,".",CHAR(1),LEN($A87)-LEN(SUBSTITUTE($A87,".",""))))+1,LEN($A87)))))</f>
         <v/>
       </c>
       <c r="C87" s="26"/>
-      <c r="D87" s="72"/>
+      <c r="D87" s="70"/>
       <c r="E87" s="28"/>
       <c r="F87" s="39" t="str">
         <f aca="false">IF($B87="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B87),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35248,7 +36291,7 @@
         <f aca="true">IF(OR($A87="",$D87=""),"",YEARFRAC($D87,TODAY()))</f>
         <v/>
       </c>
-      <c r="H87" s="73" t="str">
+      <c r="H87" s="71" t="str">
         <f aca="false">IF($G87="","",MAX(0,INT($G87)))</f>
         <v/>
       </c>
@@ -35272,13 +36315,13 @@
       <c r="N87" s="36"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="71"/>
+      <c r="A88" s="69"/>
       <c r="B88" s="37" t="str">
         <f aca="false">IF($A88="","",IF(ISERROR(FIND(".",$A88)),"",LOWER(MID($A88,FIND(CHAR(1),SUBSTITUTE($A88,".",CHAR(1),LEN($A88)-LEN(SUBSTITUTE($A88,".",""))))+1,LEN($A88)))))</f>
         <v/>
       </c>
       <c r="C88" s="26"/>
-      <c r="D88" s="72"/>
+      <c r="D88" s="70"/>
       <c r="E88" s="28"/>
       <c r="F88" s="39" t="str">
         <f aca="false">IF($B88="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B88),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35288,7 +36331,7 @@
         <f aca="true">IF(OR($A88="",$D88=""),"",YEARFRAC($D88,TODAY()))</f>
         <v/>
       </c>
-      <c r="H88" s="73" t="str">
+      <c r="H88" s="71" t="str">
         <f aca="false">IF($G88="","",MAX(0,INT($G88)))</f>
         <v/>
       </c>
@@ -35312,13 +36355,13 @@
       <c r="N88" s="36"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="71"/>
+      <c r="A89" s="69"/>
       <c r="B89" s="37" t="str">
         <f aca="false">IF($A89="","",IF(ISERROR(FIND(".",$A89)),"",LOWER(MID($A89,FIND(CHAR(1),SUBSTITUTE($A89,".",CHAR(1),LEN($A89)-LEN(SUBSTITUTE($A89,".",""))))+1,LEN($A89)))))</f>
         <v/>
       </c>
       <c r="C89" s="26"/>
-      <c r="D89" s="72"/>
+      <c r="D89" s="70"/>
       <c r="E89" s="28"/>
       <c r="F89" s="39" t="str">
         <f aca="false">IF($B89="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B89),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35328,7 +36371,7 @@
         <f aca="true">IF(OR($A89="",$D89=""),"",YEARFRAC($D89,TODAY()))</f>
         <v/>
       </c>
-      <c r="H89" s="73" t="str">
+      <c r="H89" s="71" t="str">
         <f aca="false">IF($G89="","",MAX(0,INT($G89)))</f>
         <v/>
       </c>
@@ -35352,13 +36395,13 @@
       <c r="N89" s="36"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="71"/>
+      <c r="A90" s="69"/>
       <c r="B90" s="37" t="str">
         <f aca="false">IF($A90="","",IF(ISERROR(FIND(".",$A90)),"",LOWER(MID($A90,FIND(CHAR(1),SUBSTITUTE($A90,".",CHAR(1),LEN($A90)-LEN(SUBSTITUTE($A90,".",""))))+1,LEN($A90)))))</f>
         <v/>
       </c>
       <c r="C90" s="26"/>
-      <c r="D90" s="72"/>
+      <c r="D90" s="70"/>
       <c r="E90" s="28"/>
       <c r="F90" s="39" t="str">
         <f aca="false">IF($B90="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B90),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35368,7 +36411,7 @@
         <f aca="true">IF(OR($A90="",$D90=""),"",YEARFRAC($D90,TODAY()))</f>
         <v/>
       </c>
-      <c r="H90" s="73" t="str">
+      <c r="H90" s="71" t="str">
         <f aca="false">IF($G90="","",MAX(0,INT($G90)))</f>
         <v/>
       </c>
@@ -35392,13 +36435,13 @@
       <c r="N90" s="36"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="71"/>
+      <c r="A91" s="69"/>
       <c r="B91" s="37" t="str">
         <f aca="false">IF($A91="","",IF(ISERROR(FIND(".",$A91)),"",LOWER(MID($A91,FIND(CHAR(1),SUBSTITUTE($A91,".",CHAR(1),LEN($A91)-LEN(SUBSTITUTE($A91,".",""))))+1,LEN($A91)))))</f>
         <v/>
       </c>
       <c r="C91" s="26"/>
-      <c r="D91" s="72"/>
+      <c r="D91" s="70"/>
       <c r="E91" s="28"/>
       <c r="F91" s="39" t="str">
         <f aca="false">IF($B91="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B91),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35408,7 +36451,7 @@
         <f aca="true">IF(OR($A91="",$D91=""),"",YEARFRAC($D91,TODAY()))</f>
         <v/>
       </c>
-      <c r="H91" s="73" t="str">
+      <c r="H91" s="71" t="str">
         <f aca="false">IF($G91="","",MAX(0,INT($G91)))</f>
         <v/>
       </c>
@@ -35432,13 +36475,13 @@
       <c r="N91" s="36"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="71"/>
+      <c r="A92" s="69"/>
       <c r="B92" s="37" t="str">
         <f aca="false">IF($A92="","",IF(ISERROR(FIND(".",$A92)),"",LOWER(MID($A92,FIND(CHAR(1),SUBSTITUTE($A92,".",CHAR(1),LEN($A92)-LEN(SUBSTITUTE($A92,".",""))))+1,LEN($A92)))))</f>
         <v/>
       </c>
       <c r="C92" s="26"/>
-      <c r="D92" s="72"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="28"/>
       <c r="F92" s="39" t="str">
         <f aca="false">IF($B92="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B92),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35448,7 +36491,7 @@
         <f aca="true">IF(OR($A92="",$D92=""),"",YEARFRAC($D92,TODAY()))</f>
         <v/>
       </c>
-      <c r="H92" s="73" t="str">
+      <c r="H92" s="71" t="str">
         <f aca="false">IF($G92="","",MAX(0,INT($G92)))</f>
         <v/>
       </c>
@@ -35472,13 +36515,13 @@
       <c r="N92" s="36"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="71"/>
+      <c r="A93" s="69"/>
       <c r="B93" s="37" t="str">
         <f aca="false">IF($A93="","",IF(ISERROR(FIND(".",$A93)),"",LOWER(MID($A93,FIND(CHAR(1),SUBSTITUTE($A93,".",CHAR(1),LEN($A93)-LEN(SUBSTITUTE($A93,".",""))))+1,LEN($A93)))))</f>
         <v/>
       </c>
       <c r="C93" s="26"/>
-      <c r="D93" s="72"/>
+      <c r="D93" s="70"/>
       <c r="E93" s="28"/>
       <c r="F93" s="39" t="str">
         <f aca="false">IF($B93="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B93),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35488,7 +36531,7 @@
         <f aca="true">IF(OR($A93="",$D93=""),"",YEARFRAC($D93,TODAY()))</f>
         <v/>
       </c>
-      <c r="H93" s="73" t="str">
+      <c r="H93" s="71" t="str">
         <f aca="false">IF($G93="","",MAX(0,INT($G93)))</f>
         <v/>
       </c>
@@ -35512,13 +36555,13 @@
       <c r="N93" s="36"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="71"/>
+      <c r="A94" s="69"/>
       <c r="B94" s="37" t="str">
         <f aca="false">IF($A94="","",IF(ISERROR(FIND(".",$A94)),"",LOWER(MID($A94,FIND(CHAR(1),SUBSTITUTE($A94,".",CHAR(1),LEN($A94)-LEN(SUBSTITUTE($A94,".",""))))+1,LEN($A94)))))</f>
         <v/>
       </c>
       <c r="C94" s="26"/>
-      <c r="D94" s="72"/>
+      <c r="D94" s="70"/>
       <c r="E94" s="28"/>
       <c r="F94" s="39" t="str">
         <f aca="false">IF($B94="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B94),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35528,7 +36571,7 @@
         <f aca="true">IF(OR($A94="",$D94=""),"",YEARFRAC($D94,TODAY()))</f>
         <v/>
       </c>
-      <c r="H94" s="73" t="str">
+      <c r="H94" s="71" t="str">
         <f aca="false">IF($G94="","",MAX(0,INT($G94)))</f>
         <v/>
       </c>
@@ -35552,13 +36595,13 @@
       <c r="N94" s="36"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="71"/>
+      <c r="A95" s="69"/>
       <c r="B95" s="37" t="str">
         <f aca="false">IF($A95="","",IF(ISERROR(FIND(".",$A95)),"",LOWER(MID($A95,FIND(CHAR(1),SUBSTITUTE($A95,".",CHAR(1),LEN($A95)-LEN(SUBSTITUTE($A95,".",""))))+1,LEN($A95)))))</f>
         <v/>
       </c>
       <c r="C95" s="26"/>
-      <c r="D95" s="72"/>
+      <c r="D95" s="70"/>
       <c r="E95" s="28"/>
       <c r="F95" s="39" t="str">
         <f aca="false">IF($B95="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B95),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35568,7 +36611,7 @@
         <f aca="true">IF(OR($A95="",$D95=""),"",YEARFRAC($D95,TODAY()))</f>
         <v/>
       </c>
-      <c r="H95" s="73" t="str">
+      <c r="H95" s="71" t="str">
         <f aca="false">IF($G95="","",MAX(0,INT($G95)))</f>
         <v/>
       </c>
@@ -35592,13 +36635,13 @@
       <c r="N95" s="36"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="71"/>
+      <c r="A96" s="69"/>
       <c r="B96" s="37" t="str">
         <f aca="false">IF($A96="","",IF(ISERROR(FIND(".",$A96)),"",LOWER(MID($A96,FIND(CHAR(1),SUBSTITUTE($A96,".",CHAR(1),LEN($A96)-LEN(SUBSTITUTE($A96,".",""))))+1,LEN($A96)))))</f>
         <v/>
       </c>
       <c r="C96" s="26"/>
-      <c r="D96" s="72"/>
+      <c r="D96" s="70"/>
       <c r="E96" s="28"/>
       <c r="F96" s="39" t="str">
         <f aca="false">IF($B96="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B96),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35608,7 +36651,7 @@
         <f aca="true">IF(OR($A96="",$D96=""),"",YEARFRAC($D96,TODAY()))</f>
         <v/>
       </c>
-      <c r="H96" s="73" t="str">
+      <c r="H96" s="71" t="str">
         <f aca="false">IF($G96="","",MAX(0,INT($G96)))</f>
         <v/>
       </c>
@@ -35632,13 +36675,13 @@
       <c r="N96" s="36"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="71"/>
+      <c r="A97" s="69"/>
       <c r="B97" s="37" t="str">
         <f aca="false">IF($A97="","",IF(ISERROR(FIND(".",$A97)),"",LOWER(MID($A97,FIND(CHAR(1),SUBSTITUTE($A97,".",CHAR(1),LEN($A97)-LEN(SUBSTITUTE($A97,".",""))))+1,LEN($A97)))))</f>
         <v/>
       </c>
       <c r="C97" s="26"/>
-      <c r="D97" s="72"/>
+      <c r="D97" s="70"/>
       <c r="E97" s="28"/>
       <c r="F97" s="39" t="str">
         <f aca="false">IF($B97="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B97),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35648,7 +36691,7 @@
         <f aca="true">IF(OR($A97="",$D97=""),"",YEARFRAC($D97,TODAY()))</f>
         <v/>
       </c>
-      <c r="H97" s="73" t="str">
+      <c r="H97" s="71" t="str">
         <f aca="false">IF($G97="","",MAX(0,INT($G97)))</f>
         <v/>
       </c>
@@ -35672,13 +36715,13 @@
       <c r="N97" s="36"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="71"/>
+      <c r="A98" s="69"/>
       <c r="B98" s="37" t="str">
         <f aca="false">IF($A98="","",IF(ISERROR(FIND(".",$A98)),"",LOWER(MID($A98,FIND(CHAR(1),SUBSTITUTE($A98,".",CHAR(1),LEN($A98)-LEN(SUBSTITUTE($A98,".",""))))+1,LEN($A98)))))</f>
         <v/>
       </c>
       <c r="C98" s="26"/>
-      <c r="D98" s="72"/>
+      <c r="D98" s="70"/>
       <c r="E98" s="28"/>
       <c r="F98" s="39" t="str">
         <f aca="false">IF($B98="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B98),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35688,7 +36731,7 @@
         <f aca="true">IF(OR($A98="",$D98=""),"",YEARFRAC($D98,TODAY()))</f>
         <v/>
       </c>
-      <c r="H98" s="73" t="str">
+      <c r="H98" s="71" t="str">
         <f aca="false">IF($G98="","",MAX(0,INT($G98)))</f>
         <v/>
       </c>
@@ -35712,13 +36755,13 @@
       <c r="N98" s="36"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="71"/>
+      <c r="A99" s="69"/>
       <c r="B99" s="37" t="str">
         <f aca="false">IF($A99="","",IF(ISERROR(FIND(".",$A99)),"",LOWER(MID($A99,FIND(CHAR(1),SUBSTITUTE($A99,".",CHAR(1),LEN($A99)-LEN(SUBSTITUTE($A99,".",""))))+1,LEN($A99)))))</f>
         <v/>
       </c>
       <c r="C99" s="26"/>
-      <c r="D99" s="72"/>
+      <c r="D99" s="70"/>
       <c r="E99" s="28"/>
       <c r="F99" s="39" t="str">
         <f aca="false">IF($B99="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B99),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35728,7 +36771,7 @@
         <f aca="true">IF(OR($A99="",$D99=""),"",YEARFRAC($D99,TODAY()))</f>
         <v/>
       </c>
-      <c r="H99" s="73" t="str">
+      <c r="H99" s="71" t="str">
         <f aca="false">IF($G99="","",MAX(0,INT($G99)))</f>
         <v/>
       </c>
@@ -35752,13 +36795,13 @@
       <c r="N99" s="36"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="71"/>
+      <c r="A100" s="69"/>
       <c r="B100" s="37" t="str">
         <f aca="false">IF($A100="","",IF(ISERROR(FIND(".",$A100)),"",LOWER(MID($A100,FIND(CHAR(1),SUBSTITUTE($A100,".",CHAR(1),LEN($A100)-LEN(SUBSTITUTE($A100,".",""))))+1,LEN($A100)))))</f>
         <v/>
       </c>
       <c r="C100" s="26"/>
-      <c r="D100" s="72"/>
+      <c r="D100" s="70"/>
       <c r="E100" s="28"/>
       <c r="F100" s="39" t="str">
         <f aca="false">IF($B100="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B100),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35768,7 +36811,7 @@
         <f aca="true">IF(OR($A100="",$D100=""),"",YEARFRAC($D100,TODAY()))</f>
         <v/>
       </c>
-      <c r="H100" s="73" t="str">
+      <c r="H100" s="71" t="str">
         <f aca="false">IF($G100="","",MAX(0,INT($G100)))</f>
         <v/>
       </c>
@@ -35792,13 +36835,13 @@
       <c r="N100" s="36"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="71"/>
+      <c r="A101" s="69"/>
       <c r="B101" s="37" t="str">
         <f aca="false">IF($A101="","",IF(ISERROR(FIND(".",$A101)),"",LOWER(MID($A101,FIND(CHAR(1),SUBSTITUTE($A101,".",CHAR(1),LEN($A101)-LEN(SUBSTITUTE($A101,".",""))))+1,LEN($A101)))))</f>
         <v/>
       </c>
       <c r="C101" s="26"/>
-      <c r="D101" s="72"/>
+      <c r="D101" s="70"/>
       <c r="E101" s="28"/>
       <c r="F101" s="39" t="str">
         <f aca="false">IF($B101="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B101),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35808,7 +36851,7 @@
         <f aca="true">IF(OR($A101="",$D101=""),"",YEARFRAC($D101,TODAY()))</f>
         <v/>
       </c>
-      <c r="H101" s="73" t="str">
+      <c r="H101" s="71" t="str">
         <f aca="false">IF($G101="","",MAX(0,INT($G101)))</f>
         <v/>
       </c>
@@ -35832,13 +36875,13 @@
       <c r="N101" s="36"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="71"/>
+      <c r="A102" s="69"/>
       <c r="B102" s="37" t="str">
         <f aca="false">IF($A102="","",IF(ISERROR(FIND(".",$A102)),"",LOWER(MID($A102,FIND(CHAR(1),SUBSTITUTE($A102,".",CHAR(1),LEN($A102)-LEN(SUBSTITUTE($A102,".",""))))+1,LEN($A102)))))</f>
         <v/>
       </c>
       <c r="C102" s="26"/>
-      <c r="D102" s="72"/>
+      <c r="D102" s="70"/>
       <c r="E102" s="28"/>
       <c r="F102" s="39" t="str">
         <f aca="false">IF($B102="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B102),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35848,7 +36891,7 @@
         <f aca="true">IF(OR($A102="",$D102=""),"",YEARFRAC($D102,TODAY()))</f>
         <v/>
       </c>
-      <c r="H102" s="73" t="str">
+      <c r="H102" s="71" t="str">
         <f aca="false">IF($G102="","",MAX(0,INT($G102)))</f>
         <v/>
       </c>
@@ -35872,13 +36915,13 @@
       <c r="N102" s="36"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="71"/>
+      <c r="A103" s="69"/>
       <c r="B103" s="37" t="str">
         <f aca="false">IF($A103="","",IF(ISERROR(FIND(".",$A103)),"",LOWER(MID($A103,FIND(CHAR(1),SUBSTITUTE($A103,".",CHAR(1),LEN($A103)-LEN(SUBSTITUTE($A103,".",""))))+1,LEN($A103)))))</f>
         <v/>
       </c>
       <c r="C103" s="26"/>
-      <c r="D103" s="72"/>
+      <c r="D103" s="70"/>
       <c r="E103" s="28"/>
       <c r="F103" s="39" t="str">
         <f aca="false">IF($B103="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B103),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35888,7 +36931,7 @@
         <f aca="true">IF(OR($A103="",$D103=""),"",YEARFRAC($D103,TODAY()))</f>
         <v/>
       </c>
-      <c r="H103" s="73" t="str">
+      <c r="H103" s="71" t="str">
         <f aca="false">IF($G103="","",MAX(0,INT($G103)))</f>
         <v/>
       </c>
@@ -35912,13 +36955,13 @@
       <c r="N103" s="36"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="71"/>
+      <c r="A104" s="69"/>
       <c r="B104" s="37" t="str">
         <f aca="false">IF($A104="","",IF(ISERROR(FIND(".",$A104)),"",LOWER(MID($A104,FIND(CHAR(1),SUBSTITUTE($A104,".",CHAR(1),LEN($A104)-LEN(SUBSTITUTE($A104,".",""))))+1,LEN($A104)))))</f>
         <v/>
       </c>
       <c r="C104" s="26"/>
-      <c r="D104" s="72"/>
+      <c r="D104" s="70"/>
       <c r="E104" s="28"/>
       <c r="F104" s="39" t="str">
         <f aca="false">IF($B104="","",IFERROR(INDEX(Rubric!$C$14:$C$23,MATCH(LOWER($B104),Rubric!$A$14:$A$23,0)),INDEX(Rubric!$C$14:$C$23,MATCH("other",Rubric!$A$14:$A$23,0))))</f>
@@ -35928,7 +36971,7 @@
         <f aca="true">IF(OR($A104="",$D104=""),"",YEARFRAC($D104,TODAY()))</f>
         <v/>
       </c>
-      <c r="H104" s="73" t="str">
+      <c r="H104" s="71" t="str">
         <f aca="false">IF($G104="","",MAX(0,INT($G104)))</f>
         <v/>
       </c>
@@ -36043,19 +37086,19 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="66" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="69" t="n">
+      <c r="B5" s="67" t="n">
         <v>46162</v>
       </c>
-      <c r="C5" s="65" t="n">
+      <c r="C5" s="63" t="n">
         <v>11500</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="62" t="s">
         <v>648</v>
       </c>
-      <c r="E5" s="74" t="n">
+      <c r="E5" s="72" t="n">
         <v>0.2</v>
       </c>
       <c r="F5" s="33" t="n">
@@ -36066,7 +37109,7 @@
         <f aca="false">IF($F5="","",$C5-$F5)</f>
         <v>9200</v>
       </c>
-      <c r="H5" s="65" t="n">
+      <c r="H5" s="63" t="n">
         <v>2433</v>
       </c>
       <c r="I5" s="33" t="n">
@@ -36077,16 +37120,16 @@
         <f aca="false">IF(OR($I5="",$H5="",$H5=0),"",$I5/$H5)</f>
         <v>2.78133990957665</v>
       </c>
-      <c r="K5" s="67" t="s">
+      <c r="K5" s="65" t="s">
         <v>636</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71"/>
-      <c r="B6" s="72"/>
+      <c r="A6" s="69"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="28"/>
       <c r="D6" s="26"/>
-      <c r="E6" s="75" t="str">
+      <c r="E6" s="73" t="str">
         <f aca="false">IF($A6="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36110,11 +37153,11 @@
       <c r="K6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71"/>
-      <c r="B7" s="72"/>
+      <c r="A7" s="69"/>
+      <c r="B7" s="70"/>
       <c r="C7" s="28"/>
       <c r="D7" s="26"/>
-      <c r="E7" s="75" t="str">
+      <c r="E7" s="73" t="str">
         <f aca="false">IF($A7="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36138,11 +37181,11 @@
       <c r="K7" s="36"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
+      <c r="A8" s="69"/>
+      <c r="B8" s="70"/>
       <c r="C8" s="28"/>
       <c r="D8" s="26"/>
-      <c r="E8" s="75" t="str">
+      <c r="E8" s="73" t="str">
         <f aca="false">IF($A8="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36166,11 +37209,11 @@
       <c r="K8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71"/>
-      <c r="B9" s="72"/>
+      <c r="A9" s="69"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="28"/>
       <c r="D9" s="26"/>
-      <c r="E9" s="75" t="str">
+      <c r="E9" s="73" t="str">
         <f aca="false">IF($A9="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36194,11 +37237,11 @@
       <c r="K9" s="36"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71"/>
-      <c r="B10" s="72"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="70"/>
       <c r="C10" s="28"/>
       <c r="D10" s="26"/>
-      <c r="E10" s="75" t="str">
+      <c r="E10" s="73" t="str">
         <f aca="false">IF($A10="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36222,11 +37265,11 @@
       <c r="K10" s="36"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="70"/>
       <c r="C11" s="28"/>
       <c r="D11" s="26"/>
-      <c r="E11" s="75" t="str">
+      <c r="E11" s="73" t="str">
         <f aca="false">IF($A11="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36250,11 +37293,11 @@
       <c r="K11" s="36"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72"/>
+      <c r="A12" s="69"/>
+      <c r="B12" s="70"/>
       <c r="C12" s="28"/>
       <c r="D12" s="26"/>
-      <c r="E12" s="75" t="str">
+      <c r="E12" s="73" t="str">
         <f aca="false">IF($A12="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36278,11 +37321,11 @@
       <c r="K12" s="36"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71"/>
-      <c r="B13" s="72"/>
+      <c r="A13" s="69"/>
+      <c r="B13" s="70"/>
       <c r="C13" s="28"/>
       <c r="D13" s="26"/>
-      <c r="E13" s="75" t="str">
+      <c r="E13" s="73" t="str">
         <f aca="false">IF($A13="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36306,11 +37349,11 @@
       <c r="K13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="70"/>
       <c r="C14" s="28"/>
       <c r="D14" s="26"/>
-      <c r="E14" s="75" t="str">
+      <c r="E14" s="73" t="str">
         <f aca="false">IF($A14="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36334,11 +37377,11 @@
       <c r="K14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71"/>
-      <c r="B15" s="72"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="70"/>
       <c r="C15" s="28"/>
       <c r="D15" s="26"/>
-      <c r="E15" s="75" t="str">
+      <c r="E15" s="73" t="str">
         <f aca="false">IF($A15="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36362,11 +37405,11 @@
       <c r="K15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71"/>
-      <c r="B16" s="72"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="28"/>
       <c r="D16" s="26"/>
-      <c r="E16" s="75" t="str">
+      <c r="E16" s="73" t="str">
         <f aca="false">IF($A16="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36390,11 +37433,11 @@
       <c r="K16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71"/>
-      <c r="B17" s="72"/>
+      <c r="A17" s="69"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="28"/>
       <c r="D17" s="26"/>
-      <c r="E17" s="75" t="str">
+      <c r="E17" s="73" t="str">
         <f aca="false">IF($A17="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36418,11 +37461,11 @@
       <c r="K17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="71"/>
-      <c r="B18" s="72"/>
+      <c r="A18" s="69"/>
+      <c r="B18" s="70"/>
       <c r="C18" s="28"/>
       <c r="D18" s="26"/>
-      <c r="E18" s="75" t="str">
+      <c r="E18" s="73" t="str">
         <f aca="false">IF($A18="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36446,11 +37489,11 @@
       <c r="K18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71"/>
-      <c r="B19" s="72"/>
+      <c r="A19" s="69"/>
+      <c r="B19" s="70"/>
       <c r="C19" s="28"/>
       <c r="D19" s="26"/>
-      <c r="E19" s="75" t="str">
+      <c r="E19" s="73" t="str">
         <f aca="false">IF($A19="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36474,11 +37517,11 @@
       <c r="K19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="71"/>
-      <c r="B20" s="72"/>
+      <c r="A20" s="69"/>
+      <c r="B20" s="70"/>
       <c r="C20" s="28"/>
       <c r="D20" s="26"/>
-      <c r="E20" s="75" t="str">
+      <c r="E20" s="73" t="str">
         <f aca="false">IF($A20="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36502,11 +37545,11 @@
       <c r="K20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71"/>
-      <c r="B21" s="72"/>
+      <c r="A21" s="69"/>
+      <c r="B21" s="70"/>
       <c r="C21" s="28"/>
       <c r="D21" s="26"/>
-      <c r="E21" s="75" t="str">
+      <c r="E21" s="73" t="str">
         <f aca="false">IF($A21="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36530,11 +37573,11 @@
       <c r="K21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71"/>
-      <c r="B22" s="72"/>
+      <c r="A22" s="69"/>
+      <c r="B22" s="70"/>
       <c r="C22" s="28"/>
       <c r="D22" s="26"/>
-      <c r="E22" s="75" t="str">
+      <c r="E22" s="73" t="str">
         <f aca="false">IF($A22="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36558,11 +37601,11 @@
       <c r="K22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71"/>
-      <c r="B23" s="72"/>
+      <c r="A23" s="69"/>
+      <c r="B23" s="70"/>
       <c r="C23" s="28"/>
       <c r="D23" s="26"/>
-      <c r="E23" s="75" t="str">
+      <c r="E23" s="73" t="str">
         <f aca="false">IF($A23="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36586,11 +37629,11 @@
       <c r="K23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71"/>
-      <c r="B24" s="72"/>
+      <c r="A24" s="69"/>
+      <c r="B24" s="70"/>
       <c r="C24" s="28"/>
       <c r="D24" s="26"/>
-      <c r="E24" s="75" t="str">
+      <c r="E24" s="73" t="str">
         <f aca="false">IF($A24="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36614,11 +37657,11 @@
       <c r="K24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71"/>
-      <c r="B25" s="72"/>
+      <c r="A25" s="69"/>
+      <c r="B25" s="70"/>
       <c r="C25" s="28"/>
       <c r="D25" s="26"/>
-      <c r="E25" s="75" t="str">
+      <c r="E25" s="73" t="str">
         <f aca="false">IF($A25="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36642,11 +37685,11 @@
       <c r="K25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="71"/>
-      <c r="B26" s="72"/>
+      <c r="A26" s="69"/>
+      <c r="B26" s="70"/>
       <c r="C26" s="28"/>
       <c r="D26" s="26"/>
-      <c r="E26" s="75" t="str">
+      <c r="E26" s="73" t="str">
         <f aca="false">IF($A26="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36670,11 +37713,11 @@
       <c r="K26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="71"/>
-      <c r="B27" s="72"/>
+      <c r="A27" s="69"/>
+      <c r="B27" s="70"/>
       <c r="C27" s="28"/>
       <c r="D27" s="26"/>
-      <c r="E27" s="75" t="str">
+      <c r="E27" s="73" t="str">
         <f aca="false">IF($A27="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36698,11 +37741,11 @@
       <c r="K27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="71"/>
-      <c r="B28" s="72"/>
+      <c r="A28" s="69"/>
+      <c r="B28" s="70"/>
       <c r="C28" s="28"/>
       <c r="D28" s="26"/>
-      <c r="E28" s="75" t="str">
+      <c r="E28" s="73" t="str">
         <f aca="false">IF($A28="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36726,11 +37769,11 @@
       <c r="K28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="71"/>
-      <c r="B29" s="72"/>
+      <c r="A29" s="69"/>
+      <c r="B29" s="70"/>
       <c r="C29" s="28"/>
       <c r="D29" s="26"/>
-      <c r="E29" s="75" t="str">
+      <c r="E29" s="73" t="str">
         <f aca="false">IF($A29="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36754,11 +37797,11 @@
       <c r="K29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="71"/>
-      <c r="B30" s="72"/>
+      <c r="A30" s="69"/>
+      <c r="B30" s="70"/>
       <c r="C30" s="28"/>
       <c r="D30" s="26"/>
-      <c r="E30" s="75" t="str">
+      <c r="E30" s="73" t="str">
         <f aca="false">IF($A30="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36782,11 +37825,11 @@
       <c r="K30" s="36"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="71"/>
-      <c r="B31" s="72"/>
+      <c r="A31" s="69"/>
+      <c r="B31" s="70"/>
       <c r="C31" s="28"/>
       <c r="D31" s="26"/>
-      <c r="E31" s="75" t="str">
+      <c r="E31" s="73" t="str">
         <f aca="false">IF($A31="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36810,11 +37853,11 @@
       <c r="K31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
+      <c r="A32" s="69"/>
+      <c r="B32" s="70"/>
       <c r="C32" s="28"/>
       <c r="D32" s="26"/>
-      <c r="E32" s="75" t="str">
+      <c r="E32" s="73" t="str">
         <f aca="false">IF($A32="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36838,11 +37881,11 @@
       <c r="K32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="71"/>
-      <c r="B33" s="72"/>
+      <c r="A33" s="69"/>
+      <c r="B33" s="70"/>
       <c r="C33" s="28"/>
       <c r="D33" s="26"/>
-      <c r="E33" s="75" t="str">
+      <c r="E33" s="73" t="str">
         <f aca="false">IF($A33="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36866,11 +37909,11 @@
       <c r="K33" s="36"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="71"/>
-      <c r="B34" s="72"/>
+      <c r="A34" s="69"/>
+      <c r="B34" s="70"/>
       <c r="C34" s="28"/>
       <c r="D34" s="26"/>
-      <c r="E34" s="75" t="str">
+      <c r="E34" s="73" t="str">
         <f aca="false">IF($A34="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36894,11 +37937,11 @@
       <c r="K34" s="36"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="71"/>
-      <c r="B35" s="72"/>
+      <c r="A35" s="69"/>
+      <c r="B35" s="70"/>
       <c r="C35" s="28"/>
       <c r="D35" s="26"/>
-      <c r="E35" s="75" t="str">
+      <c r="E35" s="73" t="str">
         <f aca="false">IF($A35="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36922,11 +37965,11 @@
       <c r="K35" s="36"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="71"/>
-      <c r="B36" s="72"/>
+      <c r="A36" s="69"/>
+      <c r="B36" s="70"/>
       <c r="C36" s="28"/>
       <c r="D36" s="26"/>
-      <c r="E36" s="75" t="str">
+      <c r="E36" s="73" t="str">
         <f aca="false">IF($A36="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36950,11 +37993,11 @@
       <c r="K36" s="36"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="71"/>
-      <c r="B37" s="72"/>
+      <c r="A37" s="69"/>
+      <c r="B37" s="70"/>
       <c r="C37" s="28"/>
       <c r="D37" s="26"/>
-      <c r="E37" s="75" t="str">
+      <c r="E37" s="73" t="str">
         <f aca="false">IF($A37="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -36978,11 +38021,11 @@
       <c r="K37" s="36"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="71"/>
-      <c r="B38" s="72"/>
+      <c r="A38" s="69"/>
+      <c r="B38" s="70"/>
       <c r="C38" s="28"/>
       <c r="D38" s="26"/>
-      <c r="E38" s="75" t="str">
+      <c r="E38" s="73" t="str">
         <f aca="false">IF($A38="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37006,11 +38049,11 @@
       <c r="K38" s="36"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="71"/>
-      <c r="B39" s="72"/>
+      <c r="A39" s="69"/>
+      <c r="B39" s="70"/>
       <c r="C39" s="28"/>
       <c r="D39" s="26"/>
-      <c r="E39" s="75" t="str">
+      <c r="E39" s="73" t="str">
         <f aca="false">IF($A39="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37034,11 +38077,11 @@
       <c r="K39" s="36"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="71"/>
-      <c r="B40" s="72"/>
+      <c r="A40" s="69"/>
+      <c r="B40" s="70"/>
       <c r="C40" s="28"/>
       <c r="D40" s="26"/>
-      <c r="E40" s="75" t="str">
+      <c r="E40" s="73" t="str">
         <f aca="false">IF($A40="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37062,11 +38105,11 @@
       <c r="K40" s="36"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="71"/>
-      <c r="B41" s="72"/>
+      <c r="A41" s="69"/>
+      <c r="B41" s="70"/>
       <c r="C41" s="28"/>
       <c r="D41" s="26"/>
-      <c r="E41" s="75" t="str">
+      <c r="E41" s="73" t="str">
         <f aca="false">IF($A41="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37090,11 +38133,11 @@
       <c r="K41" s="36"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="71"/>
-      <c r="B42" s="72"/>
+      <c r="A42" s="69"/>
+      <c r="B42" s="70"/>
       <c r="C42" s="28"/>
       <c r="D42" s="26"/>
-      <c r="E42" s="75" t="str">
+      <c r="E42" s="73" t="str">
         <f aca="false">IF($A42="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37118,11 +38161,11 @@
       <c r="K42" s="36"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="71"/>
-      <c r="B43" s="72"/>
+      <c r="A43" s="69"/>
+      <c r="B43" s="70"/>
       <c r="C43" s="28"/>
       <c r="D43" s="26"/>
-      <c r="E43" s="75" t="str">
+      <c r="E43" s="73" t="str">
         <f aca="false">IF($A43="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37146,11 +38189,11 @@
       <c r="K43" s="36"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="71"/>
-      <c r="B44" s="72"/>
+      <c r="A44" s="69"/>
+      <c r="B44" s="70"/>
       <c r="C44" s="28"/>
       <c r="D44" s="26"/>
-      <c r="E44" s="75" t="str">
+      <c r="E44" s="73" t="str">
         <f aca="false">IF($A44="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37174,11 +38217,11 @@
       <c r="K44" s="36"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="71"/>
-      <c r="B45" s="72"/>
+      <c r="A45" s="69"/>
+      <c r="B45" s="70"/>
       <c r="C45" s="28"/>
       <c r="D45" s="26"/>
-      <c r="E45" s="75" t="str">
+      <c r="E45" s="73" t="str">
         <f aca="false">IF($A45="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37202,11 +38245,11 @@
       <c r="K45" s="36"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="71"/>
-      <c r="B46" s="72"/>
+      <c r="A46" s="69"/>
+      <c r="B46" s="70"/>
       <c r="C46" s="28"/>
       <c r="D46" s="26"/>
-      <c r="E46" s="75" t="str">
+      <c r="E46" s="73" t="str">
         <f aca="false">IF($A46="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37230,11 +38273,11 @@
       <c r="K46" s="36"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="71"/>
-      <c r="B47" s="72"/>
+      <c r="A47" s="69"/>
+      <c r="B47" s="70"/>
       <c r="C47" s="28"/>
       <c r="D47" s="26"/>
-      <c r="E47" s="75" t="str">
+      <c r="E47" s="73" t="str">
         <f aca="false">IF($A47="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37258,11 +38301,11 @@
       <c r="K47" s="36"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="71"/>
-      <c r="B48" s="72"/>
+      <c r="A48" s="69"/>
+      <c r="B48" s="70"/>
       <c r="C48" s="28"/>
       <c r="D48" s="26"/>
-      <c r="E48" s="75" t="str">
+      <c r="E48" s="73" t="str">
         <f aca="false">IF($A48="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37286,11 +38329,11 @@
       <c r="K48" s="36"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="71"/>
-      <c r="B49" s="72"/>
+      <c r="A49" s="69"/>
+      <c r="B49" s="70"/>
       <c r="C49" s="28"/>
       <c r="D49" s="26"/>
-      <c r="E49" s="75" t="str">
+      <c r="E49" s="73" t="str">
         <f aca="false">IF($A49="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37314,11 +38357,11 @@
       <c r="K49" s="36"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="71"/>
-      <c r="B50" s="72"/>
+      <c r="A50" s="69"/>
+      <c r="B50" s="70"/>
       <c r="C50" s="28"/>
       <c r="D50" s="26"/>
-      <c r="E50" s="75" t="str">
+      <c r="E50" s="73" t="str">
         <f aca="false">IF($A50="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37342,11 +38385,11 @@
       <c r="K50" s="36"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="71"/>
-      <c r="B51" s="72"/>
+      <c r="A51" s="69"/>
+      <c r="B51" s="70"/>
       <c r="C51" s="28"/>
       <c r="D51" s="26"/>
-      <c r="E51" s="75" t="str">
+      <c r="E51" s="73" t="str">
         <f aca="false">IF($A51="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37370,11 +38413,11 @@
       <c r="K51" s="36"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="71"/>
-      <c r="B52" s="72"/>
+      <c r="A52" s="69"/>
+      <c r="B52" s="70"/>
       <c r="C52" s="28"/>
       <c r="D52" s="26"/>
-      <c r="E52" s="75" t="str">
+      <c r="E52" s="73" t="str">
         <f aca="false">IF($A52="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37398,11 +38441,11 @@
       <c r="K52" s="36"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="71"/>
-      <c r="B53" s="72"/>
+      <c r="A53" s="69"/>
+      <c r="B53" s="70"/>
       <c r="C53" s="28"/>
       <c r="D53" s="26"/>
-      <c r="E53" s="75" t="str">
+      <c r="E53" s="73" t="str">
         <f aca="false">IF($A53="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37426,11 +38469,11 @@
       <c r="K53" s="36"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="71"/>
-      <c r="B54" s="72"/>
+      <c r="A54" s="69"/>
+      <c r="B54" s="70"/>
       <c r="C54" s="28"/>
       <c r="D54" s="26"/>
-      <c r="E54" s="75" t="str">
+      <c r="E54" s="73" t="str">
         <f aca="false">IF($A54="","",Assumptions!$B$4)</f>
         <v/>
       </c>
@@ -37490,22 +38533,22 @@
       <c r="D1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="48" t="s">
         <v>650</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>651</v>
       </c>
-      <c r="B4" s="76" t="n">
+      <c r="B4" s="74" t="n">
         <f aca="false">COUNTIF(Portfolio!$C$5:$C$104,"Active")</f>
         <v>1</v>
       </c>
-      <c r="D4" s="77" t="s">
+      <c r="D4" s="75" t="s">
         <v>652</v>
       </c>
     </row>
@@ -37513,11 +38556,11 @@
       <c r="A5" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="B5" s="78" t="n">
+      <c r="B5" s="76" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$E$5:$E$104)</f>
         <v>2400</v>
       </c>
-      <c r="D5" s="77" t="s">
+      <c r="D5" s="75" t="s">
         <v>654</v>
       </c>
     </row>
@@ -37525,11 +38568,11 @@
       <c r="A6" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="B6" s="78" t="n">
+      <c r="B6" s="76" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$I$5:$I$104)</f>
         <v>22</v>
       </c>
-      <c r="D6" s="77" t="s">
+      <c r="D6" s="75" t="s">
         <v>656</v>
       </c>
     </row>
@@ -37537,11 +38580,11 @@
       <c r="A7" s="9" t="s">
         <v>657</v>
       </c>
-      <c r="B7" s="78" t="n">
+      <c r="B7" s="76" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$J$5:$J$104)</f>
         <v>2422</v>
       </c>
-      <c r="D7" s="77" t="s">
+      <c r="D7" s="75" t="s">
         <v>658</v>
       </c>
     </row>
@@ -37549,31 +38592,31 @@
       <c r="A8" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="B8" s="78" t="n">
+      <c r="B8" s="76" t="n">
         <f aca="false">SUMIF(Portfolio!$C$5:$C$104,"Active",Portfolio!$F$5:$F$104)</f>
         <v>11</v>
       </c>
-      <c r="D8" s="77" t="s">
+      <c r="D8" s="75" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="s">
+      <c r="A10" s="48" t="s">
         <v>661</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="B11" s="76" t="n">
+      <c r="B11" s="74" t="n">
         <f aca="false">COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="D11" s="77" t="s">
+      <c r="D11" s="75" t="s">
         <v>663</v>
       </c>
     </row>
@@ -37581,11 +38624,11 @@
       <c r="A12" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="B12" s="78" t="n">
+      <c r="B12" s="76" t="n">
         <f aca="false">SUM('Sales Log'!$C$5:$C$54)</f>
         <v>11500</v>
       </c>
-      <c r="D12" s="77" t="s">
+      <c r="D12" s="75" t="s">
         <v>665</v>
       </c>
     </row>
@@ -37593,11 +38636,11 @@
       <c r="A13" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="B13" s="78" t="n">
+      <c r="B13" s="76" t="n">
         <f aca="false">SUM('Sales Log'!$G$5:$G$54)</f>
         <v>9200</v>
       </c>
-      <c r="D13" s="77" t="s">
+      <c r="D13" s="75" t="s">
         <v>667</v>
       </c>
     </row>
@@ -37605,11 +38648,11 @@
       <c r="A14" s="9" t="s">
         <v>668</v>
       </c>
-      <c r="B14" s="78" t="n">
+      <c r="B14" s="76" t="n">
         <f aca="false">SUM('Sales Log'!$I$5:$I$54)</f>
         <v>6767</v>
       </c>
-      <c r="D14" s="77" t="s">
+      <c r="D14" s="75" t="s">
         <v>669</v>
       </c>
     </row>
@@ -37617,31 +38660,31 @@
       <c r="A15" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="B15" s="79" t="n">
+      <c r="B15" s="77" t="n">
         <f aca="false">IF($B$8=0,"n/a",SUM('Sales Log'!$I$5:$I$54)/$B$8)</f>
         <v>615.181818181818</v>
       </c>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="75" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="50" t="s">
+      <c r="A17" s="48" t="s">
         <v>672</v>
       </c>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
         <v>673</v>
       </c>
-      <c r="B18" s="80" t="n">
+      <c r="B18" s="78" t="n">
         <f aca="false">IF(($B$4+COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;"))=0,"n/a",COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;")/($B$4+COUNTIF('Sales Log'!$A$5:$A$54,"&lt;&gt;")))</f>
         <v>0.5</v>
       </c>
-      <c r="D18" s="77" t="s">
+      <c r="D18" s="75" t="s">
         <v>674</v>
       </c>
     </row>
@@ -37649,11 +38692,11 @@
       <c r="A19" s="9" t="s">
         <v>675</v>
       </c>
-      <c r="B19" s="80" t="n">
+      <c r="B19" s="78" t="n">
         <f aca="false">Assumptions!$B$6</f>
         <v>0.02</v>
       </c>
-      <c r="D19" s="77" t="s">
+      <c r="D19" s="75" t="s">
         <v>676</v>
       </c>
     </row>
@@ -37661,31 +38704,31 @@
       <c r="A20" s="9" t="s">
         <v>677</v>
       </c>
-      <c r="B20" s="81" t="n">
+      <c r="B20" s="79" t="n">
         <f aca="false">$B$4*Assumptions!$B$6</f>
         <v>0.02</v>
       </c>
-      <c r="D20" s="77" t="s">
+      <c r="D20" s="75" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="s">
+      <c r="A22" s="48" t="s">
         <v>679</v>
       </c>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
         <v>680</v>
       </c>
-      <c r="B23" s="76" t="n">
+      <c r="B23" s="74" t="n">
         <f aca="false">COUNTIF(Candidates!$A$5:$A$204,"&lt;&gt;")</f>
         <v>200</v>
       </c>
-      <c r="D23" s="77" t="s">
+      <c r="D23" s="75" t="s">
         <v>681</v>
       </c>
     </row>
@@ -37693,11 +38736,11 @@
       <c r="A24" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="B24" s="76" t="n">
+      <c r="B24" s="74" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"BUY")</f>
         <v>0</v>
       </c>
-      <c r="D24" s="77" t="s">
+      <c r="D24" s="75" t="s">
         <v>683</v>
       </c>
     </row>
@@ -37705,11 +38748,11 @@
       <c r="A25" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="B25" s="76" t="n">
+      <c r="B25" s="74" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"MARGINAL")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="77" t="s">
+      <c r="D25" s="75" t="s">
         <v>685</v>
       </c>
     </row>
@@ -37717,11 +38760,11 @@
       <c r="A26" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="B26" s="76" t="n">
+      <c r="B26" s="74" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"NEEDS VALUATION")+COUNTIF(Candidates!$V$5:$V$204,"NEEDS PRICE")</f>
         <v>190</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="75" t="s">
         <v>687</v>
       </c>
     </row>
@@ -37729,11 +38772,11 @@
       <c r="A27" s="9" t="s">
         <v>688</v>
       </c>
-      <c r="B27" s="76" t="n">
+      <c r="B27" s="74" t="n">
         <f aca="false">COUNTIF(Candidates!$V$5:$V$204,"PASS")+COUNTIF(Candidates!$V$5:$V$204,"REJECT")</f>
         <v>10</v>
       </c>
-      <c r="D27" s="77" t="s">
+      <c r="D27" s="75" t="s">
         <v>689</v>
       </c>
     </row>
@@ -37776,7 +38819,7 @@
       <c r="E1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="80" t="s">
         <v>691</v>
       </c>
     </row>
@@ -38087,54 +39130,54 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="50" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="83" t="s">
+      <c r="A25" s="81" t="s">
         <v>756</v>
       </c>
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="83" t="s">
+      <c r="A26" s="81" t="s">
         <v>757</v>
       </c>
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="83" t="s">
+      <c r="A27" s="81" t="s">
         <v>758</v>
       </c>
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="81" t="s">
         <v>759</v>
       </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="83" t="s">
+      <c r="A29" s="81" t="s">
         <v>760</v>
       </c>
-      <c r="B29" s="83"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/domain-investing/domain-portfolio-tracker.xlsx
+++ b/domain-investing/domain-portfolio-tracker.xlsx
@@ -197,7 +197,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Total cost basis grossed up for commission: basis / (1 - commission rate). List below this and the sale loses money after GoDaddy takes its cut.</t>
+          <t xml:space="preserve">Total cost basis grossed up for commission, whichever is higher: basis / (1 - commission rate), or basis + the $15 minimum commission. The second binds below a ~$75 sale price. List under this and the sale loses money after GoDaddy takes its cut.</t>
         </r>
       </text>
     </comment>
@@ -5921,7 +5921,7 @@
         <v>55</v>
       </c>
       <c r="S5" s="32" t="str">
-        <f aca="false">IF(OR($J5="",$Q5="",$Q5=0),"",($J5+$R5)/($Q5*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J5="",$Q5="",$Q5=0),"",MAX(($J5+$R5)/($Q5*(1-Assumptions!$B$4)),($J5+$R5)/$Q5+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T5" s="33" t="str">
@@ -6001,7 +6001,7 @@
         <v>55</v>
       </c>
       <c r="S6" s="42" t="str">
-        <f aca="false">IF(OR($J6="",$Q6="",$Q6=0),"",($J6+$R6)/($Q6*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J6="",$Q6="",$Q6=0),"",MAX(($J6+$R6)/($Q6*(1-Assumptions!$B$4)),($J6+$R6)/$Q6+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T6" s="43" t="str">
@@ -6081,7 +6081,7 @@
         <v>55</v>
       </c>
       <c r="S7" s="42" t="str">
-        <f aca="false">IF(OR($J7="",$Q7="",$Q7=0),"",($J7+$R7)/($Q7*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J7="",$Q7="",$Q7=0),"",MAX(($J7+$R7)/($Q7*(1-Assumptions!$B$4)),($J7+$R7)/$Q7+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T7" s="43" t="str">
@@ -6161,7 +6161,7 @@
         <v>55</v>
       </c>
       <c r="S8" s="42" t="str">
-        <f aca="false">IF(OR($J8="",$Q8="",$Q8=0),"",($J8+$R8)/($Q8*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J8="",$Q8="",$Q8=0),"",MAX(($J8+$R8)/($Q8*(1-Assumptions!$B$4)),($J8+$R8)/$Q8+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T8" s="43" t="str">
@@ -6241,7 +6241,7 @@
         <v>55</v>
       </c>
       <c r="S9" s="42" t="str">
-        <f aca="false">IF(OR($J9="",$Q9="",$Q9=0),"",($J9+$R9)/($Q9*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J9="",$Q9="",$Q9=0),"",MAX(($J9+$R9)/($Q9*(1-Assumptions!$B$4)),($J9+$R9)/$Q9+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T9" s="43" t="str">
@@ -6321,7 +6321,7 @@
         <v>55</v>
       </c>
       <c r="S10" s="42" t="str">
-        <f aca="false">IF(OR($J10="",$Q10="",$Q10=0),"",($J10+$R10)/($Q10*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J10="",$Q10="",$Q10=0),"",MAX(($J10+$R10)/($Q10*(1-Assumptions!$B$4)),($J10+$R10)/$Q10+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T10" s="43" t="str">
@@ -6401,7 +6401,7 @@
         <v>55</v>
       </c>
       <c r="S11" s="42" t="str">
-        <f aca="false">IF(OR($J11="",$Q11="",$Q11=0),"",($J11+$R11)/($Q11*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J11="",$Q11="",$Q11=0),"",MAX(($J11+$R11)/($Q11*(1-Assumptions!$B$4)),($J11+$R11)/$Q11+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T11" s="43" t="str">
@@ -6481,7 +6481,7 @@
         <v>55</v>
       </c>
       <c r="S12" s="42" t="str">
-        <f aca="false">IF(OR($J12="",$Q12="",$Q12=0),"",($J12+$R12)/($Q12*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J12="",$Q12="",$Q12=0),"",MAX(($J12+$R12)/($Q12*(1-Assumptions!$B$4)),($J12+$R12)/$Q12+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T12" s="43" t="str">
@@ -6561,7 +6561,7 @@
         <v>55</v>
       </c>
       <c r="S13" s="42" t="str">
-        <f aca="false">IF(OR($J13="",$Q13="",$Q13=0),"",($J13+$R13)/($Q13*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J13="",$Q13="",$Q13=0),"",MAX(($J13+$R13)/($Q13*(1-Assumptions!$B$4)),($J13+$R13)/$Q13+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T13" s="43" t="str">
@@ -6641,7 +6641,7 @@
         <v>55</v>
       </c>
       <c r="S14" s="42" t="str">
-        <f aca="false">IF(OR($J14="",$Q14="",$Q14=0),"",($J14+$R14)/($Q14*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J14="",$Q14="",$Q14=0),"",MAX(($J14+$R14)/($Q14*(1-Assumptions!$B$4)),($J14+$R14)/$Q14+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T14" s="43" t="str">
@@ -6721,7 +6721,7 @@
         <v>55</v>
       </c>
       <c r="S15" s="42" t="str">
-        <f aca="false">IF(OR($J15="",$Q15="",$Q15=0),"",($J15+$R15)/($Q15*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J15="",$Q15="",$Q15=0),"",MAX(($J15+$R15)/($Q15*(1-Assumptions!$B$4)),($J15+$R15)/$Q15+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T15" s="43" t="str">
@@ -6801,7 +6801,7 @@
         <v>55</v>
       </c>
       <c r="S16" s="42" t="str">
-        <f aca="false">IF(OR($J16="",$Q16="",$Q16=0),"",($J16+$R16)/($Q16*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J16="",$Q16="",$Q16=0),"",MAX(($J16+$R16)/($Q16*(1-Assumptions!$B$4)),($J16+$R16)/$Q16+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T16" s="43" t="str">
@@ -6881,7 +6881,7 @@
         <v>55</v>
       </c>
       <c r="S17" s="42" t="str">
-        <f aca="false">IF(OR($J17="",$Q17="",$Q17=0),"",($J17+$R17)/($Q17*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J17="",$Q17="",$Q17=0),"",MAX(($J17+$R17)/($Q17*(1-Assumptions!$B$4)),($J17+$R17)/$Q17+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T17" s="43" t="str">
@@ -6963,7 +6963,7 @@
         <v>55</v>
       </c>
       <c r="S18" s="42" t="n">
-        <f aca="false">IF(OR($J18="",$Q18="",$Q18=0),"",($J18+$R18)/($Q18*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J18="",$Q18="",$Q18=0),"",MAX(($J18+$R18)/($Q18*(1-Assumptions!$B$4)),($J18+$R18)/$Q18+Assumptions!$B$5))</f>
         <v>100273.028679492</v>
       </c>
       <c r="T18" s="43" t="str">
@@ -7045,7 +7045,7 @@
         <v>55</v>
       </c>
       <c r="S19" s="42" t="n">
-        <f aca="false">IF(OR($J19="",$Q19="",$Q19=0),"",($J19+$R19)/($Q19*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J19="",$Q19="",$Q19=0),"",MAX(($J19+$R19)/($Q19*(1-Assumptions!$B$4)),($J19+$R19)/$Q19+Assumptions!$B$5))</f>
         <v>6583280.96482983</v>
       </c>
       <c r="T19" s="43" t="str">
@@ -7127,7 +7127,7 @@
         <v>55</v>
       </c>
       <c r="S20" s="42" t="n">
-        <f aca="false">IF(OR($J20="",$Q20="",$Q20=0),"",($J20+$R20)/($Q20*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J20="",$Q20="",$Q20=0),"",MAX(($J20+$R20)/($Q20*(1-Assumptions!$B$4)),($J20+$R20)/$Q20+Assumptions!$B$5))</f>
         <v>102159.594178624</v>
       </c>
       <c r="T20" s="43" t="str">
@@ -7207,7 +7207,7 @@
         <v>55</v>
       </c>
       <c r="S21" s="42" t="str">
-        <f aca="false">IF(OR($J21="",$Q21="",$Q21=0),"",($J21+$R21)/($Q21*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J21="",$Q21="",$Q21=0),"",MAX(($J21+$R21)/($Q21*(1-Assumptions!$B$4)),($J21+$R21)/$Q21+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T21" s="43" t="str">
@@ -7287,7 +7287,7 @@
         <v>55</v>
       </c>
       <c r="S22" s="42" t="str">
-        <f aca="false">IF(OR($J22="",$Q22="",$Q22=0),"",($J22+$R22)/($Q22*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J22="",$Q22="",$Q22=0),"",MAX(($J22+$R22)/($Q22*(1-Assumptions!$B$4)),($J22+$R22)/$Q22+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T22" s="43" t="str">
@@ -7367,7 +7367,7 @@
         <v>55</v>
       </c>
       <c r="S23" s="42" t="str">
-        <f aca="false">IF(OR($J23="",$Q23="",$Q23=0),"",($J23+$R23)/($Q23*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J23="",$Q23="",$Q23=0),"",MAX(($J23+$R23)/($Q23*(1-Assumptions!$B$4)),($J23+$R23)/$Q23+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T23" s="43" t="str">
@@ -7453,7 +7453,7 @@
         <v>55</v>
       </c>
       <c r="S24" s="42" t="n">
-        <f aca="false">IF(OR($J24="",$Q24="",$Q24=0),"",($J24+$R24)/($Q24*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J24="",$Q24="",$Q24=0),"",MAX(($J24+$R24)/($Q24*(1-Assumptions!$B$4)),($J24+$R24)/$Q24+Assumptions!$B$5))</f>
         <v>1801.25121618271</v>
       </c>
       <c r="T24" s="43" t="n">
@@ -7535,7 +7535,7 @@
         <v>55</v>
       </c>
       <c r="S25" s="42" t="n">
-        <f aca="false">IF(OR($J25="",$Q25="",$Q25=0),"",($J25+$R25)/($Q25*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J25="",$Q25="",$Q25=0),"",MAX(($J25+$R25)/($Q25*(1-Assumptions!$B$4)),($J25+$R25)/$Q25+Assumptions!$B$5))</f>
         <v>65661.7157021084</v>
       </c>
       <c r="T25" s="43" t="str">
@@ -7615,7 +7615,7 @@
         <v>55</v>
       </c>
       <c r="S26" s="42" t="str">
-        <f aca="false">IF(OR($J26="",$Q26="",$Q26=0),"",($J26+$R26)/($Q26*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J26="",$Q26="",$Q26=0),"",MAX(($J26+$R26)/($Q26*(1-Assumptions!$B$4)),($J26+$R26)/$Q26+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T26" s="43" t="str">
@@ -7697,7 +7697,7 @@
         <v>55</v>
       </c>
       <c r="S27" s="42" t="n">
-        <f aca="false">IF(OR($J27="",$Q27="",$Q27=0),"",($J27+$R27)/($Q27*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J27="",$Q27="",$Q27=0),"",MAX(($J27+$R27)/($Q27*(1-Assumptions!$B$4)),($J27+$R27)/$Q27+Assumptions!$B$5))</f>
         <v>1720.26892472924</v>
       </c>
       <c r="T27" s="43" t="str">
@@ -7777,7 +7777,7 @@
         <v>55</v>
       </c>
       <c r="S28" s="42" t="str">
-        <f aca="false">IF(OR($J28="",$Q28="",$Q28=0),"",($J28+$R28)/($Q28*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J28="",$Q28="",$Q28=0),"",MAX(($J28+$R28)/($Q28*(1-Assumptions!$B$4)),($J28+$R28)/$Q28+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T28" s="43" t="str">
@@ -7859,7 +7859,7 @@
         <v>55</v>
       </c>
       <c r="S29" s="42" t="n">
-        <f aca="false">IF(OR($J29="",$Q29="",$Q29=0),"",($J29+$R29)/($Q29*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J29="",$Q29="",$Q29=0),"",MAX(($J29+$R29)/($Q29*(1-Assumptions!$B$4)),($J29+$R29)/$Q29+Assumptions!$B$5))</f>
         <v>415895.25036248</v>
       </c>
       <c r="T29" s="43" t="str">
@@ -7939,7 +7939,7 @@
         <v>55</v>
       </c>
       <c r="S30" s="42" t="str">
-        <f aca="false">IF(OR($J30="",$Q30="",$Q30=0),"",($J30+$R30)/($Q30*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J30="",$Q30="",$Q30=0),"",MAX(($J30+$R30)/($Q30*(1-Assumptions!$B$4)),($J30+$R30)/$Q30+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T30" s="43" t="str">
@@ -8021,7 +8021,7 @@
         <v>55</v>
       </c>
       <c r="S31" s="42" t="n">
-        <f aca="false">IF(OR($J31="",$Q31="",$Q31=0),"",($J31+$R31)/($Q31*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J31="",$Q31="",$Q31=0),"",MAX(($J31+$R31)/($Q31*(1-Assumptions!$B$4)),($J31+$R31)/$Q31+Assumptions!$B$5))</f>
         <v>1855.95305458221</v>
       </c>
       <c r="T31" s="43" t="str">
@@ -8103,7 +8103,7 @@
         <v>55</v>
       </c>
       <c r="S32" s="42" t="n">
-        <f aca="false">IF(OR($J32="",$Q32="",$Q32=0),"",($J32+$R32)/($Q32*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J32="",$Q32="",$Q32=0),"",MAX(($J32+$R32)/($Q32*(1-Assumptions!$B$4)),($J32+$R32)/$Q32+Assumptions!$B$5))</f>
         <v>1769.98415008371</v>
       </c>
       <c r="T32" s="43" t="str">
@@ -8183,7 +8183,7 @@
         <v>55</v>
       </c>
       <c r="S33" s="42" t="str">
-        <f aca="false">IF(OR($J33="",$Q33="",$Q33=0),"",($J33+$R33)/($Q33*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J33="",$Q33="",$Q33=0),"",MAX(($J33+$R33)/($Q33*(1-Assumptions!$B$4)),($J33+$R33)/$Q33+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T33" s="43" t="str">
@@ -8263,7 +8263,7 @@
         <v>55</v>
       </c>
       <c r="S34" s="42" t="str">
-        <f aca="false">IF(OR($J34="",$Q34="",$Q34=0),"",($J34+$R34)/($Q34*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J34="",$Q34="",$Q34=0),"",MAX(($J34+$R34)/($Q34*(1-Assumptions!$B$4)),($J34+$R34)/$Q34+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T34" s="43" t="str">
@@ -8343,7 +8343,7 @@
         <v>55</v>
       </c>
       <c r="S35" s="42" t="str">
-        <f aca="false">IF(OR($J35="",$Q35="",$Q35=0),"",($J35+$R35)/($Q35*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J35="",$Q35="",$Q35=0),"",MAX(($J35+$R35)/($Q35*(1-Assumptions!$B$4)),($J35+$R35)/$Q35+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T35" s="43" t="str">
@@ -8425,7 +8425,7 @@
         <v>55</v>
       </c>
       <c r="S36" s="42" t="n">
-        <f aca="false">IF(OR($J36="",$Q36="",$Q36=0),"",($J36+$R36)/($Q36*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J36="",$Q36="",$Q36=0),"",MAX(($J36+$R36)/($Q36*(1-Assumptions!$B$4)),($J36+$R36)/$Q36+Assumptions!$B$5))</f>
         <v>123137.136470521</v>
       </c>
       <c r="T36" s="43" t="str">
@@ -8505,7 +8505,7 @@
         <v>55</v>
       </c>
       <c r="S37" s="42" t="str">
-        <f aca="false">IF(OR($J37="",$Q37="",$Q37=0),"",($J37+$R37)/($Q37*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J37="",$Q37="",$Q37=0),"",MAX(($J37+$R37)/($Q37*(1-Assumptions!$B$4)),($J37+$R37)/$Q37+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T37" s="43" t="str">
@@ -8587,7 +8587,7 @@
         <v>55</v>
       </c>
       <c r="S38" s="42" t="n">
-        <f aca="false">IF(OR($J38="",$Q38="",$Q38=0),"",($J38+$R38)/($Q38*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J38="",$Q38="",$Q38=0),"",MAX(($J38+$R38)/($Q38*(1-Assumptions!$B$4)),($J38+$R38)/$Q38+Assumptions!$B$5))</f>
         <v>89748.8450244064</v>
       </c>
       <c r="T38" s="43" t="str">
@@ -8667,7 +8667,7 @@
         <v>55</v>
       </c>
       <c r="S39" s="42" t="str">
-        <f aca="false">IF(OR($J39="",$Q39="",$Q39=0),"",($J39+$R39)/($Q39*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J39="",$Q39="",$Q39=0),"",MAX(($J39+$R39)/($Q39*(1-Assumptions!$B$4)),($J39+$R39)/$Q39+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T39" s="43" t="str">
@@ -8749,7 +8749,7 @@
         <v>55</v>
       </c>
       <c r="S40" s="42" t="n">
-        <f aca="false">IF(OR($J40="",$Q40="",$Q40=0),"",($J40+$R40)/($Q40*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J40="",$Q40="",$Q40=0),"",MAX(($J40+$R40)/($Q40*(1-Assumptions!$B$4)),($J40+$R40)/$Q40+Assumptions!$B$5))</f>
         <v>9057388.23384047</v>
       </c>
       <c r="T40" s="43" t="str">
@@ -8829,7 +8829,7 @@
         <v>55</v>
       </c>
       <c r="S41" s="42" t="str">
-        <f aca="false">IF(OR($J41="",$Q41="",$Q41=0),"",($J41+$R41)/($Q41*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J41="",$Q41="",$Q41=0),"",MAX(($J41+$R41)/($Q41*(1-Assumptions!$B$4)),($J41+$R41)/$Q41+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T41" s="43" t="str">
@@ -8909,7 +8909,7 @@
         <v>55</v>
       </c>
       <c r="S42" s="42" t="str">
-        <f aca="false">IF(OR($J42="",$Q42="",$Q42=0),"",($J42+$R42)/($Q42*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J42="",$Q42="",$Q42=0),"",MAX(($J42+$R42)/($Q42*(1-Assumptions!$B$4)),($J42+$R42)/$Q42+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T42" s="43" t="str">
@@ -8991,7 +8991,7 @@
         <v>55</v>
       </c>
       <c r="S43" s="42" t="n">
-        <f aca="false">IF(OR($J43="",$Q43="",$Q43=0),"",($J43+$R43)/($Q43*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J43="",$Q43="",$Q43=0),"",MAX(($J43+$R43)/($Q43*(1-Assumptions!$B$4)),($J43+$R43)/$Q43+Assumptions!$B$5))</f>
         <v>57107.418921708</v>
       </c>
       <c r="T43" s="43" t="str">
@@ -9073,7 +9073,7 @@
         <v>55</v>
       </c>
       <c r="S44" s="42" t="n">
-        <f aca="false">IF(OR($J44="",$Q44="",$Q44=0),"",($J44+$R44)/($Q44*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J44="",$Q44="",$Q44=0),"",MAX(($J44+$R44)/($Q44*(1-Assumptions!$B$4)),($J44+$R44)/$Q44+Assumptions!$B$5))</f>
         <v>1729.98201166764</v>
       </c>
       <c r="T44" s="43" t="str">
@@ -9155,7 +9155,7 @@
         <v>55</v>
       </c>
       <c r="S45" s="42" t="n">
-        <f aca="false">IF(OR($J45="",$Q45="",$Q45=0),"",($J45+$R45)/($Q45*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J45="",$Q45="",$Q45=0),"",MAX(($J45+$R45)/($Q45*(1-Assumptions!$B$4)),($J45+$R45)/$Q45+Assumptions!$B$5))</f>
         <v>77468.7011557863</v>
       </c>
       <c r="T45" s="43" t="str">
@@ -9237,7 +9237,7 @@
         <v>55</v>
       </c>
       <c r="S46" s="42" t="n">
-        <f aca="false">IF(OR($J46="",$Q46="",$Q46=0),"",($J46+$R46)/($Q46*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J46="",$Q46="",$Q46=0),"",MAX(($J46+$R46)/($Q46*(1-Assumptions!$B$4)),($J46+$R46)/$Q46+Assumptions!$B$5))</f>
         <v>358225.669533705</v>
       </c>
       <c r="T46" s="43" t="str">
@@ -9317,7 +9317,7 @@
         <v>55</v>
       </c>
       <c r="S47" s="42" t="str">
-        <f aca="false">IF(OR($J47="",$Q47="",$Q47=0),"",($J47+$R47)/($Q47*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J47="",$Q47="",$Q47=0),"",MAX(($J47+$R47)/($Q47*(1-Assumptions!$B$4)),($J47+$R47)/$Q47+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T47" s="43" t="str">
@@ -9399,7 +9399,7 @@
         <v>55</v>
       </c>
       <c r="S48" s="42" t="n">
-        <f aca="false">IF(OR($J48="",$Q48="",$Q48=0),"",($J48+$R48)/($Q48*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J48="",$Q48="",$Q48=0),"",MAX(($J48+$R48)/($Q48*(1-Assumptions!$B$4)),($J48+$R48)/$Q48+Assumptions!$B$5))</f>
         <v>170136.043520338</v>
       </c>
       <c r="T48" s="43" t="str">
@@ -9479,7 +9479,7 @@
         <v>55</v>
       </c>
       <c r="S49" s="42" t="str">
-        <f aca="false">IF(OR($J49="",$Q49="",$Q49=0),"",($J49+$R49)/($Q49*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J49="",$Q49="",$Q49=0),"",MAX(($J49+$R49)/($Q49*(1-Assumptions!$B$4)),($J49+$R49)/$Q49+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T49" s="43" t="str">
@@ -9559,7 +9559,7 @@
         <v>55</v>
       </c>
       <c r="S50" s="42" t="str">
-        <f aca="false">IF(OR($J50="",$Q50="",$Q50=0),"",($J50+$R50)/($Q50*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J50="",$Q50="",$Q50=0),"",MAX(($J50+$R50)/($Q50*(1-Assumptions!$B$4)),($J50+$R50)/$Q50+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T50" s="43" t="str">
@@ -9639,7 +9639,7 @@
         <v>55</v>
       </c>
       <c r="S51" s="42" t="str">
-        <f aca="false">IF(OR($J51="",$Q51="",$Q51=0),"",($J51+$R51)/($Q51*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J51="",$Q51="",$Q51=0),"",MAX(($J51+$R51)/($Q51*(1-Assumptions!$B$4)),($J51+$R51)/$Q51+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T51" s="43" t="str">
@@ -9719,7 +9719,7 @@
         <v>55</v>
       </c>
       <c r="S52" s="42" t="str">
-        <f aca="false">IF(OR($J52="",$Q52="",$Q52=0),"",($J52+$R52)/($Q52*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J52="",$Q52="",$Q52=0),"",MAX(($J52+$R52)/($Q52*(1-Assumptions!$B$4)),($J52+$R52)/$Q52+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T52" s="43" t="str">
@@ -9801,7 +9801,7 @@
         <v>55</v>
       </c>
       <c r="S53" s="42" t="n">
-        <f aca="false">IF(OR($J53="",$Q53="",$Q53=0),"",($J53+$R53)/($Q53*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J53="",$Q53="",$Q53=0),"",MAX(($J53+$R53)/($Q53*(1-Assumptions!$B$4)),($J53+$R53)/$Q53+Assumptions!$B$5))</f>
         <v>1720.26892472924</v>
       </c>
       <c r="T53" s="43" t="str">
@@ -9881,7 +9881,7 @@
         <v>55</v>
       </c>
       <c r="S54" s="42" t="str">
-        <f aca="false">IF(OR($J54="",$Q54="",$Q54=0),"",($J54+$R54)/($Q54*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J54="",$Q54="",$Q54=0),"",MAX(($J54+$R54)/($Q54*(1-Assumptions!$B$4)),($J54+$R54)/$Q54+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T54" s="43" t="str">
@@ -9961,7 +9961,7 @@
         <v>55</v>
       </c>
       <c r="S55" s="42" t="str">
-        <f aca="false">IF(OR($J55="",$Q55="",$Q55=0),"",($J55+$R55)/($Q55*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J55="",$Q55="",$Q55=0),"",MAX(($J55+$R55)/($Q55*(1-Assumptions!$B$4)),($J55+$R55)/$Q55+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T55" s="43" t="str">
@@ -10041,7 +10041,7 @@
         <v>55</v>
       </c>
       <c r="S56" s="42" t="str">
-        <f aca="false">IF(OR($J56="",$Q56="",$Q56=0),"",($J56+$R56)/($Q56*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J56="",$Q56="",$Q56=0),"",MAX(($J56+$R56)/($Q56*(1-Assumptions!$B$4)),($J56+$R56)/$Q56+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T56" s="43" t="str">
@@ -10123,7 +10123,7 @@
         <v>55</v>
       </c>
       <c r="S57" s="42" t="n">
-        <f aca="false">IF(OR($J57="",$Q57="",$Q57=0),"",($J57+$R57)/($Q57*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J57="",$Q57="",$Q57=0),"",MAX(($J57+$R57)/($Q57*(1-Assumptions!$B$4)),($J57+$R57)/$Q57+Assumptions!$B$5))</f>
         <v>1268891.08742377</v>
       </c>
       <c r="T57" s="43" t="str">
@@ -10205,7 +10205,7 @@
         <v>55</v>
       </c>
       <c r="S58" s="42" t="n">
-        <f aca="false">IF(OR($J58="",$Q58="",$Q58=0),"",($J58+$R58)/($Q58*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J58="",$Q58="",$Q58=0),"",MAX(($J58+$R58)/($Q58*(1-Assumptions!$B$4)),($J58+$R58)/$Q58+Assumptions!$B$5))</f>
         <v>64387.0218945527</v>
       </c>
       <c r="T58" s="43" t="str">
@@ -10285,7 +10285,7 @@
         <v>55</v>
       </c>
       <c r="S59" s="42" t="str">
-        <f aca="false">IF(OR($J59="",$Q59="",$Q59=0),"",($J59+$R59)/($Q59*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J59="",$Q59="",$Q59=0),"",MAX(($J59+$R59)/($Q59*(1-Assumptions!$B$4)),($J59+$R59)/$Q59+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T59" s="43" t="str">
@@ -10365,7 +10365,7 @@
         <v>55</v>
       </c>
       <c r="S60" s="42" t="str">
-        <f aca="false">IF(OR($J60="",$Q60="",$Q60=0),"",($J60+$R60)/($Q60*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J60="",$Q60="",$Q60=0),"",MAX(($J60+$R60)/($Q60*(1-Assumptions!$B$4)),($J60+$R60)/$Q60+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T60" s="43" t="str">
@@ -10445,7 +10445,7 @@
         <v>55</v>
       </c>
       <c r="S61" s="42" t="str">
-        <f aca="false">IF(OR($J61="",$Q61="",$Q61=0),"",($J61+$R61)/($Q61*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J61="",$Q61="",$Q61=0),"",MAX(($J61+$R61)/($Q61*(1-Assumptions!$B$4)),($J61+$R61)/$Q61+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T61" s="43" t="str">
@@ -10527,7 +10527,7 @@
         <v>55</v>
       </c>
       <c r="S62" s="42" t="n">
-        <f aca="false">IF(OR($J62="",$Q62="",$Q62=0),"",($J62+$R62)/($Q62*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J62="",$Q62="",$Q62=0),"",MAX(($J62+$R62)/($Q62*(1-Assumptions!$B$4)),($J62+$R62)/$Q62+Assumptions!$B$5))</f>
         <v>300795.212153692</v>
       </c>
       <c r="T62" s="43" t="str">
@@ -10607,7 +10607,7 @@
         <v>55</v>
       </c>
       <c r="S63" s="42" t="str">
-        <f aca="false">IF(OR($J63="",$Q63="",$Q63=0),"",($J63+$R63)/($Q63*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J63="",$Q63="",$Q63=0),"",MAX(($J63+$R63)/($Q63*(1-Assumptions!$B$4)),($J63+$R63)/$Q63+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T63" s="43" t="str">
@@ -10689,7 +10689,7 @@
         <v>55</v>
       </c>
       <c r="S64" s="42" t="n">
-        <f aca="false">IF(OR($J64="",$Q64="",$Q64=0),"",($J64+$R64)/($Q64*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J64="",$Q64="",$Q64=0),"",MAX(($J64+$R64)/($Q64*(1-Assumptions!$B$4)),($J64+$R64)/$Q64+Assumptions!$B$5))</f>
         <v>52566.5209803163</v>
       </c>
       <c r="T64" s="43" t="str">
@@ -10769,7 +10769,7 @@
         <v>55</v>
       </c>
       <c r="S65" s="42" t="str">
-        <f aca="false">IF(OR($J65="",$Q65="",$Q65=0),"",($J65+$R65)/($Q65*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J65="",$Q65="",$Q65=0),"",MAX(($J65+$R65)/($Q65*(1-Assumptions!$B$4)),($J65+$R65)/$Q65+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T65" s="43" t="str">
@@ -10849,7 +10849,7 @@
         <v>55</v>
       </c>
       <c r="S66" s="42" t="str">
-        <f aca="false">IF(OR($J66="",$Q66="",$Q66=0),"",($J66+$R66)/($Q66*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J66="",$Q66="",$Q66=0),"",MAX(($J66+$R66)/($Q66*(1-Assumptions!$B$4)),($J66+$R66)/$Q66+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T66" s="43" t="str">
@@ -10929,7 +10929,7 @@
         <v>55</v>
       </c>
       <c r="S67" s="42" t="str">
-        <f aca="false">IF(OR($J67="",$Q67="",$Q67=0),"",($J67+$R67)/($Q67*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J67="",$Q67="",$Q67=0),"",MAX(($J67+$R67)/($Q67*(1-Assumptions!$B$4)),($J67+$R67)/$Q67+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T67" s="43" t="str">
@@ -11009,7 +11009,7 @@
         <v>55</v>
       </c>
       <c r="S68" s="42" t="str">
-        <f aca="false">IF(OR($J68="",$Q68="",$Q68=0),"",($J68+$R68)/($Q68*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J68="",$Q68="",$Q68=0),"",MAX(($J68+$R68)/($Q68*(1-Assumptions!$B$4)),($J68+$R68)/$Q68+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T68" s="43" t="str">
@@ -11091,7 +11091,7 @@
         <v>55</v>
       </c>
       <c r="S69" s="42" t="n">
-        <f aca="false">IF(OR($J69="",$Q69="",$Q69=0),"",($J69+$R69)/($Q69*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J69="",$Q69="",$Q69=0),"",MAX(($J69+$R69)/($Q69*(1-Assumptions!$B$4)),($J69+$R69)/$Q69+Assumptions!$B$5))</f>
         <v>1060178.2233457</v>
       </c>
       <c r="T69" s="43" t="str">
@@ -11171,7 +11171,7 @@
         <v>55</v>
       </c>
       <c r="S70" s="42" t="str">
-        <f aca="false">IF(OR($J70="",$Q70="",$Q70=0),"",($J70+$R70)/($Q70*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J70="",$Q70="",$Q70=0),"",MAX(($J70+$R70)/($Q70*(1-Assumptions!$B$4)),($J70+$R70)/$Q70+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T70" s="43" t="str">
@@ -11251,7 +11251,7 @@
         <v>55</v>
       </c>
       <c r="S71" s="42" t="str">
-        <f aca="false">IF(OR($J71="",$Q71="",$Q71=0),"",($J71+$R71)/($Q71*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J71="",$Q71="",$Q71=0),"",MAX(($J71+$R71)/($Q71*(1-Assumptions!$B$4)),($J71+$R71)/$Q71+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T71" s="43" t="str">
@@ -11333,7 +11333,7 @@
         <v>55</v>
       </c>
       <c r="S72" s="42" t="n">
-        <f aca="false">IF(OR($J72="",$Q72="",$Q72=0),"",($J72+$R72)/($Q72*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J72="",$Q72="",$Q72=0),"",MAX(($J72+$R72)/($Q72*(1-Assumptions!$B$4)),($J72+$R72)/$Q72+Assumptions!$B$5))</f>
         <v>2084.5608285367</v>
       </c>
       <c r="T72" s="43" t="str">
@@ -11413,7 +11413,7 @@
         <v>55</v>
       </c>
       <c r="S73" s="42" t="str">
-        <f aca="false">IF(OR($J73="",$Q73="",$Q73=0),"",($J73+$R73)/($Q73*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J73="",$Q73="",$Q73=0),"",MAX(($J73+$R73)/($Q73*(1-Assumptions!$B$4)),($J73+$R73)/$Q73+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T73" s="43" t="str">
@@ -11493,7 +11493,7 @@
         <v>55</v>
       </c>
       <c r="S74" s="42" t="str">
-        <f aca="false">IF(OR($J74="",$Q74="",$Q74=0),"",($J74+$R74)/($Q74*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J74="",$Q74="",$Q74=0),"",MAX(($J74+$R74)/($Q74*(1-Assumptions!$B$4)),($J74+$R74)/$Q74+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T74" s="43" t="str">
@@ -11573,7 +11573,7 @@
         <v>55</v>
       </c>
       <c r="S75" s="42" t="str">
-        <f aca="false">IF(OR($J75="",$Q75="",$Q75=0),"",($J75+$R75)/($Q75*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J75="",$Q75="",$Q75=0),"",MAX(($J75+$R75)/($Q75*(1-Assumptions!$B$4)),($J75+$R75)/$Q75+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T75" s="43" t="str">
@@ -11653,7 +11653,7 @@
         <v>55</v>
       </c>
       <c r="S76" s="42" t="str">
-        <f aca="false">IF(OR($J76="",$Q76="",$Q76=0),"",($J76+$R76)/($Q76*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J76="",$Q76="",$Q76=0),"",MAX(($J76+$R76)/($Q76*(1-Assumptions!$B$4)),($J76+$R76)/$Q76+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T76" s="43" t="str">
@@ -11735,7 +11735,7 @@
         <v>55</v>
       </c>
       <c r="S77" s="42" t="n">
-        <f aca="false">IF(OR($J77="",$Q77="",$Q77=0),"",($J77+$R77)/($Q77*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J77="",$Q77="",$Q77=0),"",MAX(($J77+$R77)/($Q77*(1-Assumptions!$B$4)),($J77+$R77)/$Q77+Assumptions!$B$5))</f>
         <v>76167.8161143359</v>
       </c>
       <c r="T77" s="43" t="str">
@@ -11815,7 +11815,7 @@
         <v>55</v>
       </c>
       <c r="S78" s="42" t="str">
-        <f aca="false">IF(OR($J78="",$Q78="",$Q78=0),"",($J78+$R78)/($Q78*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J78="",$Q78="",$Q78=0),"",MAX(($J78+$R78)/($Q78*(1-Assumptions!$B$4)),($J78+$R78)/$Q78+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T78" s="43" t="str">
@@ -11895,7 +11895,7 @@
         <v>55</v>
       </c>
       <c r="S79" s="42" t="str">
-        <f aca="false">IF(OR($J79="",$Q79="",$Q79=0),"",($J79+$R79)/($Q79*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J79="",$Q79="",$Q79=0),"",MAX(($J79+$R79)/($Q79*(1-Assumptions!$B$4)),($J79+$R79)/$Q79+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T79" s="43" t="str">
@@ -11975,7 +11975,7 @@
         <v>55</v>
       </c>
       <c r="S80" s="42" t="str">
-        <f aca="false">IF(OR($J80="",$Q80="",$Q80=0),"",($J80+$R80)/($Q80*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J80="",$Q80="",$Q80=0),"",MAX(($J80+$R80)/($Q80*(1-Assumptions!$B$4)),($J80+$R80)/$Q80+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T80" s="43" t="str">
@@ -12055,7 +12055,7 @@
         <v>55</v>
       </c>
       <c r="S81" s="42" t="str">
-        <f aca="false">IF(OR($J81="",$Q81="",$Q81=0),"",($J81+$R81)/($Q81*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J81="",$Q81="",$Q81=0),"",MAX(($J81+$R81)/($Q81*(1-Assumptions!$B$4)),($J81+$R81)/$Q81+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T81" s="43" t="str">
@@ -12135,7 +12135,7 @@
         <v>55</v>
       </c>
       <c r="S82" s="42" t="str">
-        <f aca="false">IF(OR($J82="",$Q82="",$Q82=0),"",($J82+$R82)/($Q82*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J82="",$Q82="",$Q82=0),"",MAX(($J82+$R82)/($Q82*(1-Assumptions!$B$4)),($J82+$R82)/$Q82+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T82" s="43" t="str">
@@ -12215,7 +12215,7 @@
         <v>55</v>
       </c>
       <c r="S83" s="42" t="str">
-        <f aca="false">IF(OR($J83="",$Q83="",$Q83=0),"",($J83+$R83)/($Q83*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J83="",$Q83="",$Q83=0),"",MAX(($J83+$R83)/($Q83*(1-Assumptions!$B$4)),($J83+$R83)/$Q83+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T83" s="43" t="str">
@@ -12295,7 +12295,7 @@
         <v>55</v>
       </c>
       <c r="S84" s="42" t="str">
-        <f aca="false">IF(OR($J84="",$Q84="",$Q84=0),"",($J84+$R84)/($Q84*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J84="",$Q84="",$Q84=0),"",MAX(($J84+$R84)/($Q84*(1-Assumptions!$B$4)),($J84+$R84)/$Q84+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T84" s="43" t="str">
@@ -12375,7 +12375,7 @@
         <v>55</v>
       </c>
       <c r="S85" s="42" t="str">
-        <f aca="false">IF(OR($J85="",$Q85="",$Q85=0),"",($J85+$R85)/($Q85*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J85="",$Q85="",$Q85=0),"",MAX(($J85+$R85)/($Q85*(1-Assumptions!$B$4)),($J85+$R85)/$Q85+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T85" s="43" t="str">
@@ -12455,7 +12455,7 @@
         <v>55</v>
       </c>
       <c r="S86" s="42" t="str">
-        <f aca="false">IF(OR($J86="",$Q86="",$Q86=0),"",($J86+$R86)/($Q86*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J86="",$Q86="",$Q86=0),"",MAX(($J86+$R86)/($Q86*(1-Assumptions!$B$4)),($J86+$R86)/$Q86+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T86" s="43" t="str">
@@ -12535,7 +12535,7 @@
         <v>55</v>
       </c>
       <c r="S87" s="42" t="str">
-        <f aca="false">IF(OR($J87="",$Q87="",$Q87=0),"",($J87+$R87)/($Q87*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J87="",$Q87="",$Q87=0),"",MAX(($J87+$R87)/($Q87*(1-Assumptions!$B$4)),($J87+$R87)/$Q87+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T87" s="43" t="str">
@@ -12615,7 +12615,7 @@
         <v>55</v>
       </c>
       <c r="S88" s="42" t="str">
-        <f aca="false">IF(OR($J88="",$Q88="",$Q88=0),"",($J88+$R88)/($Q88*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J88="",$Q88="",$Q88=0),"",MAX(($J88+$R88)/($Q88*(1-Assumptions!$B$4)),($J88+$R88)/$Q88+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T88" s="43" t="str">
@@ -12695,7 +12695,7 @@
         <v>55</v>
       </c>
       <c r="S89" s="42" t="str">
-        <f aca="false">IF(OR($J89="",$Q89="",$Q89=0),"",($J89+$R89)/($Q89*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J89="",$Q89="",$Q89=0),"",MAX(($J89+$R89)/($Q89*(1-Assumptions!$B$4)),($J89+$R89)/$Q89+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T89" s="43" t="str">
@@ -12775,7 +12775,7 @@
         <v>55</v>
       </c>
       <c r="S90" s="42" t="str">
-        <f aca="false">IF(OR($J90="",$Q90="",$Q90=0),"",($J90+$R90)/($Q90*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J90="",$Q90="",$Q90=0),"",MAX(($J90+$R90)/($Q90*(1-Assumptions!$B$4)),($J90+$R90)/$Q90+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T90" s="43" t="str">
@@ -12855,7 +12855,7 @@
         <v>55</v>
       </c>
       <c r="S91" s="42" t="str">
-        <f aca="false">IF(OR($J91="",$Q91="",$Q91=0),"",($J91+$R91)/($Q91*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J91="",$Q91="",$Q91=0),"",MAX(($J91+$R91)/($Q91*(1-Assumptions!$B$4)),($J91+$R91)/$Q91+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T91" s="43" t="str">
@@ -12935,7 +12935,7 @@
         <v>55</v>
       </c>
       <c r="S92" s="42" t="str">
-        <f aca="false">IF(OR($J92="",$Q92="",$Q92=0),"",($J92+$R92)/($Q92*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J92="",$Q92="",$Q92=0),"",MAX(($J92+$R92)/($Q92*(1-Assumptions!$B$4)),($J92+$R92)/$Q92+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T92" s="43" t="str">
@@ -13015,7 +13015,7 @@
         <v>55</v>
       </c>
       <c r="S93" s="42" t="str">
-        <f aca="false">IF(OR($J93="",$Q93="",$Q93=0),"",($J93+$R93)/($Q93*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J93="",$Q93="",$Q93=0),"",MAX(($J93+$R93)/($Q93*(1-Assumptions!$B$4)),($J93+$R93)/$Q93+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T93" s="43" t="str">
@@ -13095,7 +13095,7 @@
         <v>55</v>
       </c>
       <c r="S94" s="42" t="str">
-        <f aca="false">IF(OR($J94="",$Q94="",$Q94=0),"",($J94+$R94)/($Q94*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J94="",$Q94="",$Q94=0),"",MAX(($J94+$R94)/($Q94*(1-Assumptions!$B$4)),($J94+$R94)/$Q94+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T94" s="43" t="str">
@@ -13175,7 +13175,7 @@
         <v>55</v>
       </c>
       <c r="S95" s="42" t="str">
-        <f aca="false">IF(OR($J95="",$Q95="",$Q95=0),"",($J95+$R95)/($Q95*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J95="",$Q95="",$Q95=0),"",MAX(($J95+$R95)/($Q95*(1-Assumptions!$B$4)),($J95+$R95)/$Q95+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T95" s="43" t="str">
@@ -13257,7 +13257,7 @@
         <v>55</v>
       </c>
       <c r="S96" s="42" t="n">
-        <f aca="false">IF(OR($J96="",$Q96="",$Q96=0),"",($J96+$R96)/($Q96*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J96="",$Q96="",$Q96=0),"",MAX(($J96+$R96)/($Q96*(1-Assumptions!$B$4)),($J96+$R96)/$Q96+Assumptions!$B$5))</f>
         <v>322994.451770482</v>
       </c>
       <c r="T96" s="43" t="str">
@@ -13337,7 +13337,7 @@
         <v>55</v>
       </c>
       <c r="S97" s="42" t="str">
-        <f aca="false">IF(OR($J97="",$Q97="",$Q97=0),"",($J97+$R97)/($Q97*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J97="",$Q97="",$Q97=0),"",MAX(($J97+$R97)/($Q97*(1-Assumptions!$B$4)),($J97+$R97)/$Q97+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T97" s="43" t="str">
@@ -13417,7 +13417,7 @@
         <v>55</v>
       </c>
       <c r="S98" s="42" t="str">
-        <f aca="false">IF(OR($J98="",$Q98="",$Q98=0),"",($J98+$R98)/($Q98*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J98="",$Q98="",$Q98=0),"",MAX(($J98+$R98)/($Q98*(1-Assumptions!$B$4)),($J98+$R98)/$Q98+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T98" s="43" t="str">
@@ -13497,7 +13497,7 @@
         <v>55</v>
       </c>
       <c r="S99" s="42" t="str">
-        <f aca="false">IF(OR($J99="",$Q99="",$Q99=0),"",($J99+$R99)/($Q99*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J99="",$Q99="",$Q99=0),"",MAX(($J99+$R99)/($Q99*(1-Assumptions!$B$4)),($J99+$R99)/$Q99+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T99" s="43" t="str">
@@ -13577,7 +13577,7 @@
         <v>55</v>
       </c>
       <c r="S100" s="42" t="str">
-        <f aca="false">IF(OR($J100="",$Q100="",$Q100=0),"",($J100+$R100)/($Q100*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J100="",$Q100="",$Q100=0),"",MAX(($J100+$R100)/($Q100*(1-Assumptions!$B$4)),($J100+$R100)/$Q100+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T100" s="43" t="str">
@@ -13657,7 +13657,7 @@
         <v>55</v>
       </c>
       <c r="S101" s="42" t="str">
-        <f aca="false">IF(OR($J101="",$Q101="",$Q101=0),"",($J101+$R101)/($Q101*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J101="",$Q101="",$Q101=0),"",MAX(($J101+$R101)/($Q101*(1-Assumptions!$B$4)),($J101+$R101)/$Q101+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T101" s="43" t="str">
@@ -13739,7 +13739,7 @@
         <v>55</v>
       </c>
       <c r="S102" s="42" t="n">
-        <f aca="false">IF(OR($J102="",$Q102="",$Q102=0),"",($J102+$R102)/($Q102*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J102="",$Q102="",$Q102=0),"",MAX(($J102+$R102)/($Q102*(1-Assumptions!$B$4)),($J102+$R102)/$Q102+Assumptions!$B$5))</f>
         <v>5208421.62078571</v>
       </c>
       <c r="T102" s="43" t="str">
@@ -13819,7 +13819,7 @@
         <v>55</v>
       </c>
       <c r="S103" s="42" t="str">
-        <f aca="false">IF(OR($J103="",$Q103="",$Q103=0),"",($J103+$R103)/($Q103*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J103="",$Q103="",$Q103=0),"",MAX(($J103+$R103)/($Q103*(1-Assumptions!$B$4)),($J103+$R103)/$Q103+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T103" s="43" t="str">
@@ -13899,7 +13899,7 @@
         <v>55</v>
       </c>
       <c r="S104" s="42" t="str">
-        <f aca="false">IF(OR($J104="",$Q104="",$Q104=0),"",($J104+$R104)/($Q104*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J104="",$Q104="",$Q104=0),"",MAX(($J104+$R104)/($Q104*(1-Assumptions!$B$4)),($J104+$R104)/$Q104+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T104" s="43" t="str">
@@ -13979,7 +13979,7 @@
         <v>55</v>
       </c>
       <c r="S105" s="42" t="str">
-        <f aca="false">IF(OR($J105="",$Q105="",$Q105=0),"",($J105+$R105)/($Q105*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J105="",$Q105="",$Q105=0),"",MAX(($J105+$R105)/($Q105*(1-Assumptions!$B$4)),($J105+$R105)/$Q105+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T105" s="43" t="str">
@@ -14059,7 +14059,7 @@
         <v>55</v>
       </c>
       <c r="S106" s="42" t="str">
-        <f aca="false">IF(OR($J106="",$Q106="",$Q106=0),"",($J106+$R106)/($Q106*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J106="",$Q106="",$Q106=0),"",MAX(($J106+$R106)/($Q106*(1-Assumptions!$B$4)),($J106+$R106)/$Q106+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T106" s="43" t="str">
@@ -14139,7 +14139,7 @@
         <v>55</v>
       </c>
       <c r="S107" s="42" t="str">
-        <f aca="false">IF(OR($J107="",$Q107="",$Q107=0),"",($J107+$R107)/($Q107*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J107="",$Q107="",$Q107=0),"",MAX(($J107+$R107)/($Q107*(1-Assumptions!$B$4)),($J107+$R107)/$Q107+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T107" s="43" t="str">
@@ -14219,7 +14219,7 @@
         <v>55</v>
       </c>
       <c r="S108" s="42" t="str">
-        <f aca="false">IF(OR($J108="",$Q108="",$Q108=0),"",($J108+$R108)/($Q108*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J108="",$Q108="",$Q108=0),"",MAX(($J108+$R108)/($Q108*(1-Assumptions!$B$4)),($J108+$R108)/$Q108+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T108" s="43" t="str">
@@ -14299,7 +14299,7 @@
         <v>55</v>
       </c>
       <c r="S109" s="42" t="str">
-        <f aca="false">IF(OR($J109="",$Q109="",$Q109=0),"",($J109+$R109)/($Q109*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J109="",$Q109="",$Q109=0),"",MAX(($J109+$R109)/($Q109*(1-Assumptions!$B$4)),($J109+$R109)/$Q109+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T109" s="43" t="str">
@@ -14381,7 +14381,7 @@
         <v>55</v>
       </c>
       <c r="S110" s="42" t="n">
-        <f aca="false">IF(OR($J110="",$Q110="",$Q110=0),"",($J110+$R110)/($Q110*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J110="",$Q110="",$Q110=0),"",MAX(($J110+$R110)/($Q110*(1-Assumptions!$B$4)),($J110+$R110)/$Q110+Assumptions!$B$5))</f>
         <v>64239.24840168</v>
       </c>
       <c r="T110" s="43" t="str">
@@ -14461,7 +14461,7 @@
         <v>55</v>
       </c>
       <c r="S111" s="42" t="str">
-        <f aca="false">IF(OR($J111="",$Q111="",$Q111=0),"",($J111+$R111)/($Q111*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J111="",$Q111="",$Q111=0),"",MAX(($J111+$R111)/($Q111*(1-Assumptions!$B$4)),($J111+$R111)/$Q111+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T111" s="43" t="str">
@@ -14541,7 +14541,7 @@
         <v>55</v>
       </c>
       <c r="S112" s="42" t="str">
-        <f aca="false">IF(OR($J112="",$Q112="",$Q112=0),"",($J112+$R112)/($Q112*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J112="",$Q112="",$Q112=0),"",MAX(($J112+$R112)/($Q112*(1-Assumptions!$B$4)),($J112+$R112)/$Q112+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T112" s="43" t="str">
@@ -14621,7 +14621,7 @@
         <v>55</v>
       </c>
       <c r="S113" s="42" t="str">
-        <f aca="false">IF(OR($J113="",$Q113="",$Q113=0),"",($J113+$R113)/($Q113*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J113="",$Q113="",$Q113=0),"",MAX(($J113+$R113)/($Q113*(1-Assumptions!$B$4)),($J113+$R113)/$Q113+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T113" s="43" t="str">
@@ -14701,7 +14701,7 @@
         <v>55</v>
       </c>
       <c r="S114" s="42" t="str">
-        <f aca="false">IF(OR($J114="",$Q114="",$Q114=0),"",($J114+$R114)/($Q114*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J114="",$Q114="",$Q114=0),"",MAX(($J114+$R114)/($Q114*(1-Assumptions!$B$4)),($J114+$R114)/$Q114+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T114" s="43" t="str">
@@ -14781,7 +14781,7 @@
         <v>55</v>
       </c>
       <c r="S115" s="42" t="str">
-        <f aca="false">IF(OR($J115="",$Q115="",$Q115=0),"",($J115+$R115)/($Q115*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J115="",$Q115="",$Q115=0),"",MAX(($J115+$R115)/($Q115*(1-Assumptions!$B$4)),($J115+$R115)/$Q115+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T115" s="43" t="str">
@@ -14861,7 +14861,7 @@
         <v>55</v>
       </c>
       <c r="S116" s="42" t="str">
-        <f aca="false">IF(OR($J116="",$Q116="",$Q116=0),"",($J116+$R116)/($Q116*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J116="",$Q116="",$Q116=0),"",MAX(($J116+$R116)/($Q116*(1-Assumptions!$B$4)),($J116+$R116)/$Q116+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T116" s="43" t="str">
@@ -14941,7 +14941,7 @@
         <v>55</v>
       </c>
       <c r="S117" s="42" t="str">
-        <f aca="false">IF(OR($J117="",$Q117="",$Q117=0),"",($J117+$R117)/($Q117*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J117="",$Q117="",$Q117=0),"",MAX(($J117+$R117)/($Q117*(1-Assumptions!$B$4)),($J117+$R117)/$Q117+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T117" s="43" t="str">
@@ -15021,7 +15021,7 @@
         <v>55</v>
       </c>
       <c r="S118" s="42" t="str">
-        <f aca="false">IF(OR($J118="",$Q118="",$Q118=0),"",($J118+$R118)/($Q118*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J118="",$Q118="",$Q118=0),"",MAX(($J118+$R118)/($Q118*(1-Assumptions!$B$4)),($J118+$R118)/$Q118+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T118" s="43" t="str">
@@ -15101,7 +15101,7 @@
         <v>55</v>
       </c>
       <c r="S119" s="42" t="str">
-        <f aca="false">IF(OR($J119="",$Q119="",$Q119=0),"",($J119+$R119)/($Q119*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J119="",$Q119="",$Q119=0),"",MAX(($J119+$R119)/($Q119*(1-Assumptions!$B$4)),($J119+$R119)/$Q119+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T119" s="43" t="str">
@@ -15181,7 +15181,7 @@
         <v>55</v>
       </c>
       <c r="S120" s="42" t="str">
-        <f aca="false">IF(OR($J120="",$Q120="",$Q120=0),"",($J120+$R120)/($Q120*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J120="",$Q120="",$Q120=0),"",MAX(($J120+$R120)/($Q120*(1-Assumptions!$B$4)),($J120+$R120)/$Q120+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T120" s="43" t="str">
@@ -15261,7 +15261,7 @@
         <v>55</v>
       </c>
       <c r="S121" s="42" t="str">
-        <f aca="false">IF(OR($J121="",$Q121="",$Q121=0),"",($J121+$R121)/($Q121*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J121="",$Q121="",$Q121=0),"",MAX(($J121+$R121)/($Q121*(1-Assumptions!$B$4)),($J121+$R121)/$Q121+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T121" s="43" t="str">
@@ -15341,7 +15341,7 @@
         <v>55</v>
       </c>
       <c r="S122" s="42" t="str">
-        <f aca="false">IF(OR($J122="",$Q122="",$Q122=0),"",($J122+$R122)/($Q122*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J122="",$Q122="",$Q122=0),"",MAX(($J122+$R122)/($Q122*(1-Assumptions!$B$4)),($J122+$R122)/$Q122+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T122" s="43" t="str">
@@ -15421,7 +15421,7 @@
         <v>55</v>
       </c>
       <c r="S123" s="42" t="str">
-        <f aca="false">IF(OR($J123="",$Q123="",$Q123=0),"",($J123+$R123)/($Q123*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J123="",$Q123="",$Q123=0),"",MAX(($J123+$R123)/($Q123*(1-Assumptions!$B$4)),($J123+$R123)/$Q123+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T123" s="43" t="str">
@@ -15501,7 +15501,7 @@
         <v>55</v>
       </c>
       <c r="S124" s="42" t="str">
-        <f aca="false">IF(OR($J124="",$Q124="",$Q124=0),"",($J124+$R124)/($Q124*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J124="",$Q124="",$Q124=0),"",MAX(($J124+$R124)/($Q124*(1-Assumptions!$B$4)),($J124+$R124)/$Q124+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T124" s="43" t="str">
@@ -15581,7 +15581,7 @@
         <v>55</v>
       </c>
       <c r="S125" s="42" t="str">
-        <f aca="false">IF(OR($J125="",$Q125="",$Q125=0),"",($J125+$R125)/($Q125*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J125="",$Q125="",$Q125=0),"",MAX(($J125+$R125)/($Q125*(1-Assumptions!$B$4)),($J125+$R125)/$Q125+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T125" s="43" t="str">
@@ -15661,7 +15661,7 @@
         <v>55</v>
       </c>
       <c r="S126" s="42" t="str">
-        <f aca="false">IF(OR($J126="",$Q126="",$Q126=0),"",($J126+$R126)/($Q126*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J126="",$Q126="",$Q126=0),"",MAX(($J126+$R126)/($Q126*(1-Assumptions!$B$4)),($J126+$R126)/$Q126+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T126" s="43" t="str">
@@ -15741,7 +15741,7 @@
         <v>55</v>
       </c>
       <c r="S127" s="42" t="str">
-        <f aca="false">IF(OR($J127="",$Q127="",$Q127=0),"",($J127+$R127)/($Q127*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J127="",$Q127="",$Q127=0),"",MAX(($J127+$R127)/($Q127*(1-Assumptions!$B$4)),($J127+$R127)/$Q127+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T127" s="43" t="str">
@@ -15821,7 +15821,7 @@
         <v>55</v>
       </c>
       <c r="S128" s="42" t="str">
-        <f aca="false">IF(OR($J128="",$Q128="",$Q128=0),"",($J128+$R128)/($Q128*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J128="",$Q128="",$Q128=0),"",MAX(($J128+$R128)/($Q128*(1-Assumptions!$B$4)),($J128+$R128)/$Q128+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T128" s="43" t="str">
@@ -15901,7 +15901,7 @@
         <v>55</v>
       </c>
       <c r="S129" s="42" t="str">
-        <f aca="false">IF(OR($J129="",$Q129="",$Q129=0),"",($J129+$R129)/($Q129*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J129="",$Q129="",$Q129=0),"",MAX(($J129+$R129)/($Q129*(1-Assumptions!$B$4)),($J129+$R129)/$Q129+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T129" s="43" t="str">
@@ -15981,7 +15981,7 @@
         <v>55</v>
       </c>
       <c r="S130" s="42" t="str">
-        <f aca="false">IF(OR($J130="",$Q130="",$Q130=0),"",($J130+$R130)/($Q130*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J130="",$Q130="",$Q130=0),"",MAX(($J130+$R130)/($Q130*(1-Assumptions!$B$4)),($J130+$R130)/$Q130+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T130" s="43" t="str">
@@ -16061,7 +16061,7 @@
         <v>55</v>
       </c>
       <c r="S131" s="42" t="str">
-        <f aca="false">IF(OR($J131="",$Q131="",$Q131=0),"",($J131+$R131)/($Q131*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J131="",$Q131="",$Q131=0),"",MAX(($J131+$R131)/($Q131*(1-Assumptions!$B$4)),($J131+$R131)/$Q131+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T131" s="43" t="str">
@@ -16141,7 +16141,7 @@
         <v>55</v>
       </c>
       <c r="S132" s="42" t="str">
-        <f aca="false">IF(OR($J132="",$Q132="",$Q132=0),"",($J132+$R132)/($Q132*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J132="",$Q132="",$Q132=0),"",MAX(($J132+$R132)/($Q132*(1-Assumptions!$B$4)),($J132+$R132)/$Q132+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T132" s="43" t="str">
@@ -16221,7 +16221,7 @@
         <v>55</v>
       </c>
       <c r="S133" s="42" t="str">
-        <f aca="false">IF(OR($J133="",$Q133="",$Q133=0),"",($J133+$R133)/($Q133*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J133="",$Q133="",$Q133=0),"",MAX(($J133+$R133)/($Q133*(1-Assumptions!$B$4)),($J133+$R133)/$Q133+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T133" s="43" t="str">
@@ -16301,7 +16301,7 @@
         <v>55</v>
       </c>
       <c r="S134" s="42" t="str">
-        <f aca="false">IF(OR($J134="",$Q134="",$Q134=0),"",($J134+$R134)/($Q134*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J134="",$Q134="",$Q134=0),"",MAX(($J134+$R134)/($Q134*(1-Assumptions!$B$4)),($J134+$R134)/$Q134+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T134" s="43" t="str">
@@ -16381,7 +16381,7 @@
         <v>55</v>
       </c>
       <c r="S135" s="42" t="str">
-        <f aca="false">IF(OR($J135="",$Q135="",$Q135=0),"",($J135+$R135)/($Q135*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J135="",$Q135="",$Q135=0),"",MAX(($J135+$R135)/($Q135*(1-Assumptions!$B$4)),($J135+$R135)/$Q135+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T135" s="43" t="str">
@@ -16461,7 +16461,7 @@
         <v>55</v>
       </c>
       <c r="S136" s="42" t="str">
-        <f aca="false">IF(OR($J136="",$Q136="",$Q136=0),"",($J136+$R136)/($Q136*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J136="",$Q136="",$Q136=0),"",MAX(($J136+$R136)/($Q136*(1-Assumptions!$B$4)),($J136+$R136)/$Q136+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T136" s="43" t="str">
@@ -16541,7 +16541,7 @@
         <v>55</v>
       </c>
       <c r="S137" s="42" t="str">
-        <f aca="false">IF(OR($J137="",$Q137="",$Q137=0),"",($J137+$R137)/($Q137*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J137="",$Q137="",$Q137=0),"",MAX(($J137+$R137)/($Q137*(1-Assumptions!$B$4)),($J137+$R137)/$Q137+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T137" s="43" t="str">
@@ -16621,7 +16621,7 @@
         <v>55</v>
       </c>
       <c r="S138" s="42" t="str">
-        <f aca="false">IF(OR($J138="",$Q138="",$Q138=0),"",($J138+$R138)/($Q138*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J138="",$Q138="",$Q138=0),"",MAX(($J138+$R138)/($Q138*(1-Assumptions!$B$4)),($J138+$R138)/$Q138+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T138" s="43" t="str">
@@ -16701,7 +16701,7 @@
         <v>55</v>
       </c>
       <c r="S139" s="42" t="str">
-        <f aca="false">IF(OR($J139="",$Q139="",$Q139=0),"",($J139+$R139)/($Q139*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J139="",$Q139="",$Q139=0),"",MAX(($J139+$R139)/($Q139*(1-Assumptions!$B$4)),($J139+$R139)/$Q139+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T139" s="43" t="str">
@@ -16781,7 +16781,7 @@
         <v>55</v>
       </c>
       <c r="S140" s="42" t="str">
-        <f aca="false">IF(OR($J140="",$Q140="",$Q140=0),"",($J140+$R140)/($Q140*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J140="",$Q140="",$Q140=0),"",MAX(($J140+$R140)/($Q140*(1-Assumptions!$B$4)),($J140+$R140)/$Q140+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T140" s="43" t="str">
@@ -16861,7 +16861,7 @@
         <v>55</v>
       </c>
       <c r="S141" s="42" t="str">
-        <f aca="false">IF(OR($J141="",$Q141="",$Q141=0),"",($J141+$R141)/($Q141*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J141="",$Q141="",$Q141=0),"",MAX(($J141+$R141)/($Q141*(1-Assumptions!$B$4)),($J141+$R141)/$Q141+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T141" s="43" t="str">
@@ -16941,7 +16941,7 @@
         <v>55</v>
       </c>
       <c r="S142" s="42" t="str">
-        <f aca="false">IF(OR($J142="",$Q142="",$Q142=0),"",($J142+$R142)/($Q142*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J142="",$Q142="",$Q142=0),"",MAX(($J142+$R142)/($Q142*(1-Assumptions!$B$4)),($J142+$R142)/$Q142+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T142" s="43" t="str">
@@ -17021,7 +17021,7 @@
         <v>55</v>
       </c>
       <c r="S143" s="42" t="str">
-        <f aca="false">IF(OR($J143="",$Q143="",$Q143=0),"",($J143+$R143)/($Q143*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J143="",$Q143="",$Q143=0),"",MAX(($J143+$R143)/($Q143*(1-Assumptions!$B$4)),($J143+$R143)/$Q143+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T143" s="43" t="str">
@@ -17101,7 +17101,7 @@
         <v>55</v>
       </c>
       <c r="S144" s="42" t="str">
-        <f aca="false">IF(OR($J144="",$Q144="",$Q144=0),"",($J144+$R144)/($Q144*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J144="",$Q144="",$Q144=0),"",MAX(($J144+$R144)/($Q144*(1-Assumptions!$B$4)),($J144+$R144)/$Q144+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T144" s="43" t="str">
@@ -17181,7 +17181,7 @@
         <v>55</v>
       </c>
       <c r="S145" s="42" t="str">
-        <f aca="false">IF(OR($J145="",$Q145="",$Q145=0),"",($J145+$R145)/($Q145*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J145="",$Q145="",$Q145=0),"",MAX(($J145+$R145)/($Q145*(1-Assumptions!$B$4)),($J145+$R145)/$Q145+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T145" s="43" t="str">
@@ -17261,7 +17261,7 @@
         <v>55</v>
       </c>
       <c r="S146" s="42" t="str">
-        <f aca="false">IF(OR($J146="",$Q146="",$Q146=0),"",($J146+$R146)/($Q146*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J146="",$Q146="",$Q146=0),"",MAX(($J146+$R146)/($Q146*(1-Assumptions!$B$4)),($J146+$R146)/$Q146+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T146" s="43" t="str">
@@ -17341,7 +17341,7 @@
         <v>55</v>
       </c>
       <c r="S147" s="42" t="str">
-        <f aca="false">IF(OR($J147="",$Q147="",$Q147=0),"",($J147+$R147)/($Q147*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J147="",$Q147="",$Q147=0),"",MAX(($J147+$R147)/($Q147*(1-Assumptions!$B$4)),($J147+$R147)/$Q147+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T147" s="43" t="str">
@@ -17421,7 +17421,7 @@
         <v>55</v>
       </c>
       <c r="S148" s="42" t="str">
-        <f aca="false">IF(OR($J148="",$Q148="",$Q148=0),"",($J148+$R148)/($Q148*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J148="",$Q148="",$Q148=0),"",MAX(($J148+$R148)/($Q148*(1-Assumptions!$B$4)),($J148+$R148)/$Q148+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T148" s="43" t="str">
@@ -17501,7 +17501,7 @@
         <v>55</v>
       </c>
       <c r="S149" s="42" t="str">
-        <f aca="false">IF(OR($J149="",$Q149="",$Q149=0),"",($J149+$R149)/($Q149*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J149="",$Q149="",$Q149=0),"",MAX(($J149+$R149)/($Q149*(1-Assumptions!$B$4)),($J149+$R149)/$Q149+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T149" s="43" t="str">
@@ -17581,7 +17581,7 @@
         <v>55</v>
       </c>
       <c r="S150" s="42" t="str">
-        <f aca="false">IF(OR($J150="",$Q150="",$Q150=0),"",($J150+$R150)/($Q150*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J150="",$Q150="",$Q150=0),"",MAX(($J150+$R150)/($Q150*(1-Assumptions!$B$4)),($J150+$R150)/$Q150+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T150" s="43" t="str">
@@ -17661,7 +17661,7 @@
         <v>55</v>
       </c>
       <c r="S151" s="42" t="str">
-        <f aca="false">IF(OR($J151="",$Q151="",$Q151=0),"",($J151+$R151)/($Q151*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J151="",$Q151="",$Q151=0),"",MAX(($J151+$R151)/($Q151*(1-Assumptions!$B$4)),($J151+$R151)/$Q151+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T151" s="43" t="str">
@@ -17741,7 +17741,7 @@
         <v>55</v>
       </c>
       <c r="S152" s="42" t="str">
-        <f aca="false">IF(OR($J152="",$Q152="",$Q152=0),"",($J152+$R152)/($Q152*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J152="",$Q152="",$Q152=0),"",MAX(($J152+$R152)/($Q152*(1-Assumptions!$B$4)),($J152+$R152)/$Q152+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T152" s="43" t="str">
@@ -17821,7 +17821,7 @@
         <v>55</v>
       </c>
       <c r="S153" s="42" t="str">
-        <f aca="false">IF(OR($J153="",$Q153="",$Q153=0),"",($J153+$R153)/($Q153*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J153="",$Q153="",$Q153=0),"",MAX(($J153+$R153)/($Q153*(1-Assumptions!$B$4)),($J153+$R153)/$Q153+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T153" s="43" t="str">
@@ -17901,7 +17901,7 @@
         <v>55</v>
       </c>
       <c r="S154" s="42" t="str">
-        <f aca="false">IF(OR($J154="",$Q154="",$Q154=0),"",($J154+$R154)/($Q154*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J154="",$Q154="",$Q154=0),"",MAX(($J154+$R154)/($Q154*(1-Assumptions!$B$4)),($J154+$R154)/$Q154+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T154" s="43" t="str">
@@ -17981,7 +17981,7 @@
         <v>55</v>
       </c>
       <c r="S155" s="42" t="str">
-        <f aca="false">IF(OR($J155="",$Q155="",$Q155=0),"",($J155+$R155)/($Q155*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J155="",$Q155="",$Q155=0),"",MAX(($J155+$R155)/($Q155*(1-Assumptions!$B$4)),($J155+$R155)/$Q155+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T155" s="43" t="str">
@@ -18061,7 +18061,7 @@
         <v>55</v>
       </c>
       <c r="S156" s="42" t="str">
-        <f aca="false">IF(OR($J156="",$Q156="",$Q156=0),"",($J156+$R156)/($Q156*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J156="",$Q156="",$Q156=0),"",MAX(($J156+$R156)/($Q156*(1-Assumptions!$B$4)),($J156+$R156)/$Q156+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T156" s="43" t="str">
@@ -18141,7 +18141,7 @@
         <v>55</v>
       </c>
       <c r="S157" s="42" t="str">
-        <f aca="false">IF(OR($J157="",$Q157="",$Q157=0),"",($J157+$R157)/($Q157*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J157="",$Q157="",$Q157=0),"",MAX(($J157+$R157)/($Q157*(1-Assumptions!$B$4)),($J157+$R157)/$Q157+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T157" s="43" t="str">
@@ -18221,7 +18221,7 @@
         <v>55</v>
       </c>
       <c r="S158" s="42" t="str">
-        <f aca="false">IF(OR($J158="",$Q158="",$Q158=0),"",($J158+$R158)/($Q158*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J158="",$Q158="",$Q158=0),"",MAX(($J158+$R158)/($Q158*(1-Assumptions!$B$4)),($J158+$R158)/$Q158+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T158" s="43" t="str">
@@ -18301,7 +18301,7 @@
         <v>55</v>
       </c>
       <c r="S159" s="42" t="str">
-        <f aca="false">IF(OR($J159="",$Q159="",$Q159=0),"",($J159+$R159)/($Q159*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J159="",$Q159="",$Q159=0),"",MAX(($J159+$R159)/($Q159*(1-Assumptions!$B$4)),($J159+$R159)/$Q159+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T159" s="43" t="str">
@@ -18381,7 +18381,7 @@
         <v>55</v>
       </c>
       <c r="S160" s="42" t="str">
-        <f aca="false">IF(OR($J160="",$Q160="",$Q160=0),"",($J160+$R160)/($Q160*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J160="",$Q160="",$Q160=0),"",MAX(($J160+$R160)/($Q160*(1-Assumptions!$B$4)),($J160+$R160)/$Q160+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T160" s="43" t="str">
@@ -18461,7 +18461,7 @@
         <v>55</v>
       </c>
       <c r="S161" s="42" t="str">
-        <f aca="false">IF(OR($J161="",$Q161="",$Q161=0),"",($J161+$R161)/($Q161*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J161="",$Q161="",$Q161=0),"",MAX(($J161+$R161)/($Q161*(1-Assumptions!$B$4)),($J161+$R161)/$Q161+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T161" s="43" t="str">
@@ -18541,7 +18541,7 @@
         <v>55</v>
       </c>
       <c r="S162" s="42" t="str">
-        <f aca="false">IF(OR($J162="",$Q162="",$Q162=0),"",($J162+$R162)/($Q162*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J162="",$Q162="",$Q162=0),"",MAX(($J162+$R162)/($Q162*(1-Assumptions!$B$4)),($J162+$R162)/$Q162+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T162" s="43" t="str">
@@ -18621,7 +18621,7 @@
         <v>55</v>
       </c>
       <c r="S163" s="42" t="str">
-        <f aca="false">IF(OR($J163="",$Q163="",$Q163=0),"",($J163+$R163)/($Q163*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J163="",$Q163="",$Q163=0),"",MAX(($J163+$R163)/($Q163*(1-Assumptions!$B$4)),($J163+$R163)/$Q163+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T163" s="43" t="str">
@@ -18701,7 +18701,7 @@
         <v>55</v>
       </c>
       <c r="S164" s="42" t="str">
-        <f aca="false">IF(OR($J164="",$Q164="",$Q164=0),"",($J164+$R164)/($Q164*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J164="",$Q164="",$Q164=0),"",MAX(($J164+$R164)/($Q164*(1-Assumptions!$B$4)),($J164+$R164)/$Q164+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T164" s="43" t="str">
@@ -18781,7 +18781,7 @@
         <v>55</v>
       </c>
       <c r="S165" s="42" t="str">
-        <f aca="false">IF(OR($J165="",$Q165="",$Q165=0),"",($J165+$R165)/($Q165*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J165="",$Q165="",$Q165=0),"",MAX(($J165+$R165)/($Q165*(1-Assumptions!$B$4)),($J165+$R165)/$Q165+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T165" s="43" t="str">
@@ -18861,7 +18861,7 @@
         <v>55</v>
       </c>
       <c r="S166" s="42" t="str">
-        <f aca="false">IF(OR($J166="",$Q166="",$Q166=0),"",($J166+$R166)/($Q166*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J166="",$Q166="",$Q166=0),"",MAX(($J166+$R166)/($Q166*(1-Assumptions!$B$4)),($J166+$R166)/$Q166+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T166" s="43" t="str">
@@ -18941,7 +18941,7 @@
         <v>55</v>
       </c>
       <c r="S167" s="42" t="str">
-        <f aca="false">IF(OR($J167="",$Q167="",$Q167=0),"",($J167+$R167)/($Q167*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J167="",$Q167="",$Q167=0),"",MAX(($J167+$R167)/($Q167*(1-Assumptions!$B$4)),($J167+$R167)/$Q167+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T167" s="43" t="str">
@@ -19021,7 +19021,7 @@
         <v>55</v>
       </c>
       <c r="S168" s="42" t="str">
-        <f aca="false">IF(OR($J168="",$Q168="",$Q168=0),"",($J168+$R168)/($Q168*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J168="",$Q168="",$Q168=0),"",MAX(($J168+$R168)/($Q168*(1-Assumptions!$B$4)),($J168+$R168)/$Q168+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T168" s="43" t="str">
@@ -19101,7 +19101,7 @@
         <v>55</v>
       </c>
       <c r="S169" s="42" t="str">
-        <f aca="false">IF(OR($J169="",$Q169="",$Q169=0),"",($J169+$R169)/($Q169*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J169="",$Q169="",$Q169=0),"",MAX(($J169+$R169)/($Q169*(1-Assumptions!$B$4)),($J169+$R169)/$Q169+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T169" s="43" t="str">
@@ -19181,7 +19181,7 @@
         <v>55</v>
       </c>
       <c r="S170" s="42" t="str">
-        <f aca="false">IF(OR($J170="",$Q170="",$Q170=0),"",($J170+$R170)/($Q170*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J170="",$Q170="",$Q170=0),"",MAX(($J170+$R170)/($Q170*(1-Assumptions!$B$4)),($J170+$R170)/$Q170+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T170" s="43" t="str">
@@ -19261,7 +19261,7 @@
         <v>55</v>
       </c>
       <c r="S171" s="42" t="str">
-        <f aca="false">IF(OR($J171="",$Q171="",$Q171=0),"",($J171+$R171)/($Q171*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J171="",$Q171="",$Q171=0),"",MAX(($J171+$R171)/($Q171*(1-Assumptions!$B$4)),($J171+$R171)/$Q171+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T171" s="43" t="str">
@@ -19341,7 +19341,7 @@
         <v>55</v>
       </c>
       <c r="S172" s="42" t="str">
-        <f aca="false">IF(OR($J172="",$Q172="",$Q172=0),"",($J172+$R172)/($Q172*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J172="",$Q172="",$Q172=0),"",MAX(($J172+$R172)/($Q172*(1-Assumptions!$B$4)),($J172+$R172)/$Q172+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T172" s="43" t="str">
@@ -19421,7 +19421,7 @@
         <v>55</v>
       </c>
       <c r="S173" s="42" t="str">
-        <f aca="false">IF(OR($J173="",$Q173="",$Q173=0),"",($J173+$R173)/($Q173*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J173="",$Q173="",$Q173=0),"",MAX(($J173+$R173)/($Q173*(1-Assumptions!$B$4)),($J173+$R173)/$Q173+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T173" s="43" t="str">
@@ -19501,7 +19501,7 @@
         <v>55</v>
       </c>
       <c r="S174" s="42" t="str">
-        <f aca="false">IF(OR($J174="",$Q174="",$Q174=0),"",($J174+$R174)/($Q174*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J174="",$Q174="",$Q174=0),"",MAX(($J174+$R174)/($Q174*(1-Assumptions!$B$4)),($J174+$R174)/$Q174+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T174" s="43" t="str">
@@ -19581,7 +19581,7 @@
         <v>55</v>
       </c>
       <c r="S175" s="42" t="str">
-        <f aca="false">IF(OR($J175="",$Q175="",$Q175=0),"",($J175+$R175)/($Q175*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J175="",$Q175="",$Q175=0),"",MAX(($J175+$R175)/($Q175*(1-Assumptions!$B$4)),($J175+$R175)/$Q175+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T175" s="43" t="str">
@@ -19661,7 +19661,7 @@
         <v>55</v>
       </c>
       <c r="S176" s="42" t="str">
-        <f aca="false">IF(OR($J176="",$Q176="",$Q176=0),"",($J176+$R176)/($Q176*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J176="",$Q176="",$Q176=0),"",MAX(($J176+$R176)/($Q176*(1-Assumptions!$B$4)),($J176+$R176)/$Q176+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T176" s="43" t="str">
@@ -19741,7 +19741,7 @@
         <v>55</v>
       </c>
       <c r="S177" s="42" t="str">
-        <f aca="false">IF(OR($J177="",$Q177="",$Q177=0),"",($J177+$R177)/($Q177*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J177="",$Q177="",$Q177=0),"",MAX(($J177+$R177)/($Q177*(1-Assumptions!$B$4)),($J177+$R177)/$Q177+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T177" s="43" t="str">
@@ -19821,7 +19821,7 @@
         <v>55</v>
       </c>
       <c r="S178" s="42" t="str">
-        <f aca="false">IF(OR($J178="",$Q178="",$Q178=0),"",($J178+$R178)/($Q178*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J178="",$Q178="",$Q178=0),"",MAX(($J178+$R178)/($Q178*(1-Assumptions!$B$4)),($J178+$R178)/$Q178+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T178" s="43" t="str">
@@ -19901,7 +19901,7 @@
         <v>55</v>
       </c>
       <c r="S179" s="42" t="str">
-        <f aca="false">IF(OR($J179="",$Q179="",$Q179=0),"",($J179+$R179)/($Q179*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J179="",$Q179="",$Q179=0),"",MAX(($J179+$R179)/($Q179*(1-Assumptions!$B$4)),($J179+$R179)/$Q179+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T179" s="43" t="str">
@@ -19981,7 +19981,7 @@
         <v>55</v>
       </c>
       <c r="S180" s="42" t="str">
-        <f aca="false">IF(OR($J180="",$Q180="",$Q180=0),"",($J180+$R180)/($Q180*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J180="",$Q180="",$Q180=0),"",MAX(($J180+$R180)/($Q180*(1-Assumptions!$B$4)),($J180+$R180)/$Q180+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T180" s="43" t="str">
@@ -20061,7 +20061,7 @@
         <v>55</v>
       </c>
       <c r="S181" s="42" t="str">
-        <f aca="false">IF(OR($J181="",$Q181="",$Q181=0),"",($J181+$R181)/($Q181*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J181="",$Q181="",$Q181=0),"",MAX(($J181+$R181)/($Q181*(1-Assumptions!$B$4)),($J181+$R181)/$Q181+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T181" s="43" t="str">
@@ -20141,7 +20141,7 @@
         <v>55</v>
       </c>
       <c r="S182" s="42" t="str">
-        <f aca="false">IF(OR($J182="",$Q182="",$Q182=0),"",($J182+$R182)/($Q182*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J182="",$Q182="",$Q182=0),"",MAX(($J182+$R182)/($Q182*(1-Assumptions!$B$4)),($J182+$R182)/$Q182+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T182" s="43" t="str">
@@ -20221,7 +20221,7 @@
         <v>55</v>
       </c>
       <c r="S183" s="42" t="str">
-        <f aca="false">IF(OR($J183="",$Q183="",$Q183=0),"",($J183+$R183)/($Q183*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J183="",$Q183="",$Q183=0),"",MAX(($J183+$R183)/($Q183*(1-Assumptions!$B$4)),($J183+$R183)/$Q183+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T183" s="43" t="str">
@@ -20301,7 +20301,7 @@
         <v>55</v>
       </c>
       <c r="S184" s="42" t="str">
-        <f aca="false">IF(OR($J184="",$Q184="",$Q184=0),"",($J184+$R184)/($Q184*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J184="",$Q184="",$Q184=0),"",MAX(($J184+$R184)/($Q184*(1-Assumptions!$B$4)),($J184+$R184)/$Q184+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T184" s="43" t="str">
@@ -20381,7 +20381,7 @@
         <v>55</v>
       </c>
       <c r="S185" s="42" t="str">
-        <f aca="false">IF(OR($J185="",$Q185="",$Q185=0),"",($J185+$R185)/($Q185*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J185="",$Q185="",$Q185=0),"",MAX(($J185+$R185)/($Q185*(1-Assumptions!$B$4)),($J185+$R185)/$Q185+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T185" s="43" t="str">
@@ -20461,7 +20461,7 @@
         <v>55</v>
       </c>
       <c r="S186" s="42" t="str">
-        <f aca="false">IF(OR($J186="",$Q186="",$Q186=0),"",($J186+$R186)/($Q186*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J186="",$Q186="",$Q186=0),"",MAX(($J186+$R186)/($Q186*(1-Assumptions!$B$4)),($J186+$R186)/$Q186+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T186" s="43" t="str">
@@ -20541,7 +20541,7 @@
         <v>55</v>
       </c>
       <c r="S187" s="42" t="str">
-        <f aca="false">IF(OR($J187="",$Q187="",$Q187=0),"",($J187+$R187)/($Q187*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J187="",$Q187="",$Q187=0),"",MAX(($J187+$R187)/($Q187*(1-Assumptions!$B$4)),($J187+$R187)/$Q187+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T187" s="43" t="str">
@@ -20621,7 +20621,7 @@
         <v>55</v>
       </c>
       <c r="S188" s="42" t="str">
-        <f aca="false">IF(OR($J188="",$Q188="",$Q188=0),"",($J188+$R188)/($Q188*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J188="",$Q188="",$Q188=0),"",MAX(($J188+$R188)/($Q188*(1-Assumptions!$B$4)),($J188+$R188)/$Q188+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T188" s="43" t="str">
@@ -20701,7 +20701,7 @@
         <v>55</v>
       </c>
       <c r="S189" s="42" t="str">
-        <f aca="false">IF(OR($J189="",$Q189="",$Q189=0),"",($J189+$R189)/($Q189*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J189="",$Q189="",$Q189=0),"",MAX(($J189+$R189)/($Q189*(1-Assumptions!$B$4)),($J189+$R189)/$Q189+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T189" s="43" t="str">
@@ -20781,7 +20781,7 @@
         <v>55</v>
       </c>
       <c r="S190" s="42" t="str">
-        <f aca="false">IF(OR($J190="",$Q190="",$Q190=0),"",($J190+$R190)/($Q190*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J190="",$Q190="",$Q190=0),"",MAX(($J190+$R190)/($Q190*(1-Assumptions!$B$4)),($J190+$R190)/$Q190+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T190" s="43" t="str">
@@ -20861,7 +20861,7 @@
         <v>55</v>
       </c>
       <c r="S191" s="42" t="str">
-        <f aca="false">IF(OR($J191="",$Q191="",$Q191=0),"",($J191+$R191)/($Q191*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J191="",$Q191="",$Q191=0),"",MAX(($J191+$R191)/($Q191*(1-Assumptions!$B$4)),($J191+$R191)/$Q191+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T191" s="43" t="str">
@@ -20941,7 +20941,7 @@
         <v>55</v>
       </c>
       <c r="S192" s="42" t="str">
-        <f aca="false">IF(OR($J192="",$Q192="",$Q192=0),"",($J192+$R192)/($Q192*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J192="",$Q192="",$Q192=0),"",MAX(($J192+$R192)/($Q192*(1-Assumptions!$B$4)),($J192+$R192)/$Q192+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T192" s="43" t="str">
@@ -21021,7 +21021,7 @@
         <v>55</v>
       </c>
       <c r="S193" s="42" t="str">
-        <f aca="false">IF(OR($J193="",$Q193="",$Q193=0),"",($J193+$R193)/($Q193*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J193="",$Q193="",$Q193=0),"",MAX(($J193+$R193)/($Q193*(1-Assumptions!$B$4)),($J193+$R193)/$Q193+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T193" s="43" t="str">
@@ -21101,7 +21101,7 @@
         <v>55</v>
       </c>
       <c r="S194" s="42" t="str">
-        <f aca="false">IF(OR($J194="",$Q194="",$Q194=0),"",($J194+$R194)/($Q194*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J194="",$Q194="",$Q194=0),"",MAX(($J194+$R194)/($Q194*(1-Assumptions!$B$4)),($J194+$R194)/$Q194+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T194" s="43" t="str">
@@ -21181,7 +21181,7 @@
         <v>55</v>
       </c>
       <c r="S195" s="42" t="str">
-        <f aca="false">IF(OR($J195="",$Q195="",$Q195=0),"",($J195+$R195)/($Q195*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J195="",$Q195="",$Q195=0),"",MAX(($J195+$R195)/($Q195*(1-Assumptions!$B$4)),($J195+$R195)/$Q195+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T195" s="43" t="str">
@@ -21261,7 +21261,7 @@
         <v>55</v>
       </c>
       <c r="S196" s="42" t="str">
-        <f aca="false">IF(OR($J196="",$Q196="",$Q196=0),"",($J196+$R196)/($Q196*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J196="",$Q196="",$Q196=0),"",MAX(($J196+$R196)/($Q196*(1-Assumptions!$B$4)),($J196+$R196)/$Q196+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T196" s="43" t="str">
@@ -21341,7 +21341,7 @@
         <v>55</v>
       </c>
       <c r="S197" s="42" t="str">
-        <f aca="false">IF(OR($J197="",$Q197="",$Q197=0),"",($J197+$R197)/($Q197*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J197="",$Q197="",$Q197=0),"",MAX(($J197+$R197)/($Q197*(1-Assumptions!$B$4)),($J197+$R197)/$Q197+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T197" s="43" t="str">
@@ -21421,7 +21421,7 @@
         <v>55</v>
       </c>
       <c r="S198" s="42" t="str">
-        <f aca="false">IF(OR($J198="",$Q198="",$Q198=0),"",($J198+$R198)/($Q198*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J198="",$Q198="",$Q198=0),"",MAX(($J198+$R198)/($Q198*(1-Assumptions!$B$4)),($J198+$R198)/$Q198+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T198" s="43" t="str">
@@ -21501,7 +21501,7 @@
         <v>55</v>
       </c>
       <c r="S199" s="42" t="str">
-        <f aca="false">IF(OR($J199="",$Q199="",$Q199=0),"",($J199+$R199)/($Q199*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J199="",$Q199="",$Q199=0),"",MAX(($J199+$R199)/($Q199*(1-Assumptions!$B$4)),($J199+$R199)/$Q199+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T199" s="43" t="str">
@@ -21581,7 +21581,7 @@
         <v>55</v>
       </c>
       <c r="S200" s="42" t="str">
-        <f aca="false">IF(OR($J200="",$Q200="",$Q200=0),"",($J200+$R200)/($Q200*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J200="",$Q200="",$Q200=0),"",MAX(($J200+$R200)/($Q200*(1-Assumptions!$B$4)),($J200+$R200)/$Q200+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T200" s="43" t="str">
@@ -21661,7 +21661,7 @@
         <v>55</v>
       </c>
       <c r="S201" s="42" t="str">
-        <f aca="false">IF(OR($J201="",$Q201="",$Q201=0),"",($J201+$R201)/($Q201*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J201="",$Q201="",$Q201=0),"",MAX(($J201+$R201)/($Q201*(1-Assumptions!$B$4)),($J201+$R201)/$Q201+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T201" s="43" t="str">
@@ -21741,7 +21741,7 @@
         <v>55</v>
       </c>
       <c r="S202" s="42" t="str">
-        <f aca="false">IF(OR($J202="",$Q202="",$Q202=0),"",($J202+$R202)/($Q202*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J202="",$Q202="",$Q202=0),"",MAX(($J202+$R202)/($Q202*(1-Assumptions!$B$4)),($J202+$R202)/$Q202+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T202" s="43" t="str">
@@ -21821,7 +21821,7 @@
         <v>55</v>
       </c>
       <c r="S203" s="42" t="str">
-        <f aca="false">IF(OR($J203="",$Q203="",$Q203=0),"",($J203+$R203)/($Q203*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J203="",$Q203="",$Q203=0),"",MAX(($J203+$R203)/($Q203*(1-Assumptions!$B$4)),($J203+$R203)/$Q203+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T203" s="43" t="str">
@@ -21901,7 +21901,7 @@
         <v>55</v>
       </c>
       <c r="S204" s="42" t="str">
-        <f aca="false">IF(OR($J204="",$Q204="",$Q204=0),"",($J204+$R204)/($Q204*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J204="",$Q204="",$Q204=0),"",MAX(($J204+$R204)/($Q204*(1-Assumptions!$B$4)),($J204+$R204)/$Q204+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T204" s="43" t="str">
@@ -21981,7 +21981,7 @@
         <v>55</v>
       </c>
       <c r="S205" s="42" t="str">
-        <f aca="false">IF(OR($J205="",$Q205="",$Q205=0),"",($J205+$R205)/($Q205*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J205="",$Q205="",$Q205=0),"",MAX(($J205+$R205)/($Q205*(1-Assumptions!$B$4)),($J205+$R205)/$Q205+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T205" s="43" t="str">
@@ -22061,7 +22061,7 @@
         <v>55</v>
       </c>
       <c r="S206" s="42" t="str">
-        <f aca="false">IF(OR($J206="",$Q206="",$Q206=0),"",($J206+$R206)/($Q206*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J206="",$Q206="",$Q206=0),"",MAX(($J206+$R206)/($Q206*(1-Assumptions!$B$4)),($J206+$R206)/$Q206+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T206" s="43" t="str">
@@ -22141,7 +22141,7 @@
         <v>55</v>
       </c>
       <c r="S207" s="42" t="str">
-        <f aca="false">IF(OR($J207="",$Q207="",$Q207=0),"",($J207+$R207)/($Q207*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J207="",$Q207="",$Q207=0),"",MAX(($J207+$R207)/($Q207*(1-Assumptions!$B$4)),($J207+$R207)/$Q207+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T207" s="43" t="str">
@@ -22221,7 +22221,7 @@
         <v>55</v>
       </c>
       <c r="S208" s="42" t="str">
-        <f aca="false">IF(OR($J208="",$Q208="",$Q208=0),"",($J208+$R208)/($Q208*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J208="",$Q208="",$Q208=0),"",MAX(($J208+$R208)/($Q208*(1-Assumptions!$B$4)),($J208+$R208)/$Q208+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T208" s="43" t="str">
@@ -22301,7 +22301,7 @@
         <v>55</v>
       </c>
       <c r="S209" s="42" t="str">
-        <f aca="false">IF(OR($J209="",$Q209="",$Q209=0),"",($J209+$R209)/($Q209*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J209="",$Q209="",$Q209=0),"",MAX(($J209+$R209)/($Q209*(1-Assumptions!$B$4)),($J209+$R209)/$Q209+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T209" s="43" t="str">
@@ -22381,7 +22381,7 @@
         <v>55</v>
       </c>
       <c r="S210" s="42" t="str">
-        <f aca="false">IF(OR($J210="",$Q210="",$Q210=0),"",($J210+$R210)/($Q210*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J210="",$Q210="",$Q210=0),"",MAX(($J210+$R210)/($Q210*(1-Assumptions!$B$4)),($J210+$R210)/$Q210+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T210" s="43" t="str">
@@ -22461,7 +22461,7 @@
         <v>55</v>
       </c>
       <c r="S211" s="42" t="str">
-        <f aca="false">IF(OR($J211="",$Q211="",$Q211=0),"",($J211+$R211)/($Q211*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J211="",$Q211="",$Q211=0),"",MAX(($J211+$R211)/($Q211*(1-Assumptions!$B$4)),($J211+$R211)/$Q211+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T211" s="43" t="str">
@@ -22541,7 +22541,7 @@
         <v>55</v>
       </c>
       <c r="S212" s="42" t="str">
-        <f aca="false">IF(OR($J212="",$Q212="",$Q212=0),"",($J212+$R212)/($Q212*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J212="",$Q212="",$Q212=0),"",MAX(($J212+$R212)/($Q212*(1-Assumptions!$B$4)),($J212+$R212)/$Q212+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T212" s="43" t="str">
@@ -22621,7 +22621,7 @@
         <v>55</v>
       </c>
       <c r="S213" s="42" t="str">
-        <f aca="false">IF(OR($J213="",$Q213="",$Q213=0),"",($J213+$R213)/($Q213*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J213="",$Q213="",$Q213=0),"",MAX(($J213+$R213)/($Q213*(1-Assumptions!$B$4)),($J213+$R213)/$Q213+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T213" s="43" t="str">
@@ -22701,7 +22701,7 @@
         <v>55</v>
       </c>
       <c r="S214" s="42" t="str">
-        <f aca="false">IF(OR($J214="",$Q214="",$Q214=0),"",($J214+$R214)/($Q214*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J214="",$Q214="",$Q214=0),"",MAX(($J214+$R214)/($Q214*(1-Assumptions!$B$4)),($J214+$R214)/$Q214+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T214" s="43" t="str">
@@ -22781,7 +22781,7 @@
         <v>55</v>
       </c>
       <c r="S215" s="42" t="str">
-        <f aca="false">IF(OR($J215="",$Q215="",$Q215=0),"",($J215+$R215)/($Q215*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J215="",$Q215="",$Q215=0),"",MAX(($J215+$R215)/($Q215*(1-Assumptions!$B$4)),($J215+$R215)/$Q215+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T215" s="43" t="str">
@@ -22861,7 +22861,7 @@
         <v>55</v>
       </c>
       <c r="S216" s="42" t="str">
-        <f aca="false">IF(OR($J216="",$Q216="",$Q216=0),"",($J216+$R216)/($Q216*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J216="",$Q216="",$Q216=0),"",MAX(($J216+$R216)/($Q216*(1-Assumptions!$B$4)),($J216+$R216)/$Q216+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T216" s="43" t="str">
@@ -22941,7 +22941,7 @@
         <v>55</v>
       </c>
       <c r="S217" s="42" t="str">
-        <f aca="false">IF(OR($J217="",$Q217="",$Q217=0),"",($J217+$R217)/($Q217*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J217="",$Q217="",$Q217=0),"",MAX(($J217+$R217)/($Q217*(1-Assumptions!$B$4)),($J217+$R217)/$Q217+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T217" s="43" t="str">
@@ -23021,7 +23021,7 @@
         <v>55</v>
       </c>
       <c r="S218" s="42" t="str">
-        <f aca="false">IF(OR($J218="",$Q218="",$Q218=0),"",($J218+$R218)/($Q218*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J218="",$Q218="",$Q218=0),"",MAX(($J218+$R218)/($Q218*(1-Assumptions!$B$4)),($J218+$R218)/$Q218+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T218" s="43" t="str">
@@ -23101,7 +23101,7 @@
         <v>55</v>
       </c>
       <c r="S219" s="42" t="str">
-        <f aca="false">IF(OR($J219="",$Q219="",$Q219=0),"",($J219+$R219)/($Q219*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J219="",$Q219="",$Q219=0),"",MAX(($J219+$R219)/($Q219*(1-Assumptions!$B$4)),($J219+$R219)/$Q219+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T219" s="43" t="str">
@@ -23181,7 +23181,7 @@
         <v>55</v>
       </c>
       <c r="S220" s="42" t="str">
-        <f aca="false">IF(OR($J220="",$Q220="",$Q220=0),"",($J220+$R220)/($Q220*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J220="",$Q220="",$Q220=0),"",MAX(($J220+$R220)/($Q220*(1-Assumptions!$B$4)),($J220+$R220)/$Q220+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T220" s="43" t="str">
@@ -23261,7 +23261,7 @@
         <v>55</v>
       </c>
       <c r="S221" s="42" t="str">
-        <f aca="false">IF(OR($J221="",$Q221="",$Q221=0),"",($J221+$R221)/($Q221*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J221="",$Q221="",$Q221=0),"",MAX(($J221+$R221)/($Q221*(1-Assumptions!$B$4)),($J221+$R221)/$Q221+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T221" s="43" t="str">
@@ -23341,7 +23341,7 @@
         <v>55</v>
       </c>
       <c r="S222" s="42" t="str">
-        <f aca="false">IF(OR($J222="",$Q222="",$Q222=0),"",($J222+$R222)/($Q222*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J222="",$Q222="",$Q222=0),"",MAX(($J222+$R222)/($Q222*(1-Assumptions!$B$4)),($J222+$R222)/$Q222+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T222" s="43" t="str">
@@ -23421,7 +23421,7 @@
         <v>55</v>
       </c>
       <c r="S223" s="42" t="str">
-        <f aca="false">IF(OR($J223="",$Q223="",$Q223=0),"",($J223+$R223)/($Q223*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J223="",$Q223="",$Q223=0),"",MAX(($J223+$R223)/($Q223*(1-Assumptions!$B$4)),($J223+$R223)/$Q223+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T223" s="43" t="str">
@@ -23501,7 +23501,7 @@
         <v>55</v>
       </c>
       <c r="S224" s="42" t="str">
-        <f aca="false">IF(OR($J224="",$Q224="",$Q224=0),"",($J224+$R224)/($Q224*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J224="",$Q224="",$Q224=0),"",MAX(($J224+$R224)/($Q224*(1-Assumptions!$B$4)),($J224+$R224)/$Q224+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T224" s="43" t="str">
@@ -23581,7 +23581,7 @@
         <v>55</v>
       </c>
       <c r="S225" s="42" t="str">
-        <f aca="false">IF(OR($J225="",$Q225="",$Q225=0),"",($J225+$R225)/($Q225*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J225="",$Q225="",$Q225=0),"",MAX(($J225+$R225)/($Q225*(1-Assumptions!$B$4)),($J225+$R225)/$Q225+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T225" s="43" t="str">
@@ -23661,7 +23661,7 @@
         <v>55</v>
       </c>
       <c r="S226" s="42" t="str">
-        <f aca="false">IF(OR($J226="",$Q226="",$Q226=0),"",($J226+$R226)/($Q226*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J226="",$Q226="",$Q226=0),"",MAX(($J226+$R226)/($Q226*(1-Assumptions!$B$4)),($J226+$R226)/$Q226+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T226" s="43" t="str">
@@ -23741,7 +23741,7 @@
         <v>55</v>
       </c>
       <c r="S227" s="42" t="str">
-        <f aca="false">IF(OR($J227="",$Q227="",$Q227=0),"",($J227+$R227)/($Q227*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J227="",$Q227="",$Q227=0),"",MAX(($J227+$R227)/($Q227*(1-Assumptions!$B$4)),($J227+$R227)/$Q227+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T227" s="43" t="str">
@@ -23821,7 +23821,7 @@
         <v>55</v>
       </c>
       <c r="S228" s="42" t="str">
-        <f aca="false">IF(OR($J228="",$Q228="",$Q228=0),"",($J228+$R228)/($Q228*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J228="",$Q228="",$Q228=0),"",MAX(($J228+$R228)/($Q228*(1-Assumptions!$B$4)),($J228+$R228)/$Q228+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T228" s="43" t="str">
@@ -23901,7 +23901,7 @@
         <v>55</v>
       </c>
       <c r="S229" s="42" t="str">
-        <f aca="false">IF(OR($J229="",$Q229="",$Q229=0),"",($J229+$R229)/($Q229*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J229="",$Q229="",$Q229=0),"",MAX(($J229+$R229)/($Q229*(1-Assumptions!$B$4)),($J229+$R229)/$Q229+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T229" s="43" t="str">
@@ -23981,7 +23981,7 @@
         <v>55</v>
       </c>
       <c r="S230" s="42" t="str">
-        <f aca="false">IF(OR($J230="",$Q230="",$Q230=0),"",($J230+$R230)/($Q230*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J230="",$Q230="",$Q230=0),"",MAX(($J230+$R230)/($Q230*(1-Assumptions!$B$4)),($J230+$R230)/$Q230+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T230" s="43" t="str">
@@ -24061,7 +24061,7 @@
         <v>55</v>
       </c>
       <c r="S231" s="42" t="str">
-        <f aca="false">IF(OR($J231="",$Q231="",$Q231=0),"",($J231+$R231)/($Q231*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J231="",$Q231="",$Q231=0),"",MAX(($J231+$R231)/($Q231*(1-Assumptions!$B$4)),($J231+$R231)/$Q231+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T231" s="43" t="str">
@@ -24141,7 +24141,7 @@
         <v>55</v>
       </c>
       <c r="S232" s="42" t="str">
-        <f aca="false">IF(OR($J232="",$Q232="",$Q232=0),"",($J232+$R232)/($Q232*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J232="",$Q232="",$Q232=0),"",MAX(($J232+$R232)/($Q232*(1-Assumptions!$B$4)),($J232+$R232)/$Q232+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T232" s="43" t="str">
@@ -24221,7 +24221,7 @@
         <v>55</v>
       </c>
       <c r="S233" s="42" t="str">
-        <f aca="false">IF(OR($J233="",$Q233="",$Q233=0),"",($J233+$R233)/($Q233*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J233="",$Q233="",$Q233=0),"",MAX(($J233+$R233)/($Q233*(1-Assumptions!$B$4)),($J233+$R233)/$Q233+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T233" s="43" t="str">
@@ -24301,7 +24301,7 @@
         <v>55</v>
       </c>
       <c r="S234" s="42" t="str">
-        <f aca="false">IF(OR($J234="",$Q234="",$Q234=0),"",($J234+$R234)/($Q234*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J234="",$Q234="",$Q234=0),"",MAX(($J234+$R234)/($Q234*(1-Assumptions!$B$4)),($J234+$R234)/$Q234+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T234" s="43" t="str">
@@ -24381,7 +24381,7 @@
         <v>55</v>
       </c>
       <c r="S235" s="42" t="str">
-        <f aca="false">IF(OR($J235="",$Q235="",$Q235=0),"",($J235+$R235)/($Q235*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J235="",$Q235="",$Q235=0),"",MAX(($J235+$R235)/($Q235*(1-Assumptions!$B$4)),($J235+$R235)/$Q235+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T235" s="43" t="str">
@@ -24461,7 +24461,7 @@
         <v>55</v>
       </c>
       <c r="S236" s="42" t="str">
-        <f aca="false">IF(OR($J236="",$Q236="",$Q236=0),"",($J236+$R236)/($Q236*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J236="",$Q236="",$Q236=0),"",MAX(($J236+$R236)/($Q236*(1-Assumptions!$B$4)),($J236+$R236)/$Q236+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T236" s="43" t="str">
@@ -24541,7 +24541,7 @@
         <v>55</v>
       </c>
       <c r="S237" s="42" t="str">
-        <f aca="false">IF(OR($J237="",$Q237="",$Q237=0),"",($J237+$R237)/($Q237*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J237="",$Q237="",$Q237=0),"",MAX(($J237+$R237)/($Q237*(1-Assumptions!$B$4)),($J237+$R237)/$Q237+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T237" s="43" t="str">
@@ -24621,7 +24621,7 @@
         <v>55</v>
       </c>
       <c r="S238" s="42" t="str">
-        <f aca="false">IF(OR($J238="",$Q238="",$Q238=0),"",($J238+$R238)/($Q238*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J238="",$Q238="",$Q238=0),"",MAX(($J238+$R238)/($Q238*(1-Assumptions!$B$4)),($J238+$R238)/$Q238+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T238" s="43" t="str">
@@ -24701,7 +24701,7 @@
         <v>55</v>
       </c>
       <c r="S239" s="42" t="str">
-        <f aca="false">IF(OR($J239="",$Q239="",$Q239=0),"",($J239+$R239)/($Q239*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J239="",$Q239="",$Q239=0),"",MAX(($J239+$R239)/($Q239*(1-Assumptions!$B$4)),($J239+$R239)/$Q239+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T239" s="43" t="str">
@@ -24781,7 +24781,7 @@
         <v>55</v>
       </c>
       <c r="S240" s="42" t="str">
-        <f aca="false">IF(OR($J240="",$Q240="",$Q240=0),"",($J240+$R240)/($Q240*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J240="",$Q240="",$Q240=0),"",MAX(($J240+$R240)/($Q240*(1-Assumptions!$B$4)),($J240+$R240)/$Q240+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T240" s="43" t="str">
@@ -24861,7 +24861,7 @@
         <v>55</v>
       </c>
       <c r="S241" s="42" t="str">
-        <f aca="false">IF(OR($J241="",$Q241="",$Q241=0),"",($J241+$R241)/($Q241*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J241="",$Q241="",$Q241=0),"",MAX(($J241+$R241)/($Q241*(1-Assumptions!$B$4)),($J241+$R241)/$Q241+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T241" s="43" t="str">
@@ -24941,7 +24941,7 @@
         <v>55</v>
       </c>
       <c r="S242" s="42" t="str">
-        <f aca="false">IF(OR($J242="",$Q242="",$Q242=0),"",($J242+$R242)/($Q242*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J242="",$Q242="",$Q242=0),"",MAX(($J242+$R242)/($Q242*(1-Assumptions!$B$4)),($J242+$R242)/$Q242+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T242" s="43" t="str">
@@ -25021,7 +25021,7 @@
         <v>55</v>
       </c>
       <c r="S243" s="42" t="str">
-        <f aca="false">IF(OR($J243="",$Q243="",$Q243=0),"",($J243+$R243)/($Q243*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J243="",$Q243="",$Q243=0),"",MAX(($J243+$R243)/($Q243*(1-Assumptions!$B$4)),($J243+$R243)/$Q243+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T243" s="43" t="str">
@@ -25101,7 +25101,7 @@
         <v>55</v>
       </c>
       <c r="S244" s="42" t="str">
-        <f aca="false">IF(OR($J244="",$Q244="",$Q244=0),"",($J244+$R244)/($Q244*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J244="",$Q244="",$Q244=0),"",MAX(($J244+$R244)/($Q244*(1-Assumptions!$B$4)),($J244+$R244)/$Q244+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T244" s="43" t="str">
@@ -25181,7 +25181,7 @@
         <v>55</v>
       </c>
       <c r="S245" s="42" t="str">
-        <f aca="false">IF(OR($J245="",$Q245="",$Q245=0),"",($J245+$R245)/($Q245*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J245="",$Q245="",$Q245=0),"",MAX(($J245+$R245)/($Q245*(1-Assumptions!$B$4)),($J245+$R245)/$Q245+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T245" s="43" t="str">
@@ -25261,7 +25261,7 @@
         <v>55</v>
       </c>
       <c r="S246" s="42" t="str">
-        <f aca="false">IF(OR($J246="",$Q246="",$Q246=0),"",($J246+$R246)/($Q246*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J246="",$Q246="",$Q246=0),"",MAX(($J246+$R246)/($Q246*(1-Assumptions!$B$4)),($J246+$R246)/$Q246+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T246" s="43" t="str">
@@ -25341,7 +25341,7 @@
         <v>55</v>
       </c>
       <c r="S247" s="42" t="str">
-        <f aca="false">IF(OR($J247="",$Q247="",$Q247=0),"",($J247+$R247)/($Q247*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J247="",$Q247="",$Q247=0),"",MAX(($J247+$R247)/($Q247*(1-Assumptions!$B$4)),($J247+$R247)/$Q247+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T247" s="43" t="str">
@@ -25421,7 +25421,7 @@
         <v>55</v>
       </c>
       <c r="S248" s="42" t="str">
-        <f aca="false">IF(OR($J248="",$Q248="",$Q248=0),"",($J248+$R248)/($Q248*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J248="",$Q248="",$Q248=0),"",MAX(($J248+$R248)/($Q248*(1-Assumptions!$B$4)),($J248+$R248)/$Q248+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T248" s="43" t="str">
@@ -25501,7 +25501,7 @@
         <v>55</v>
       </c>
       <c r="S249" s="42" t="str">
-        <f aca="false">IF(OR($J249="",$Q249="",$Q249=0),"",($J249+$R249)/($Q249*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J249="",$Q249="",$Q249=0),"",MAX(($J249+$R249)/($Q249*(1-Assumptions!$B$4)),($J249+$R249)/$Q249+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T249" s="43" t="str">
@@ -25581,7 +25581,7 @@
         <v>55</v>
       </c>
       <c r="S250" s="42" t="str">
-        <f aca="false">IF(OR($J250="",$Q250="",$Q250=0),"",($J250+$R250)/($Q250*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J250="",$Q250="",$Q250=0),"",MAX(($J250+$R250)/($Q250*(1-Assumptions!$B$4)),($J250+$R250)/$Q250+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T250" s="43" t="str">
@@ -25661,7 +25661,7 @@
         <v>55</v>
       </c>
       <c r="S251" s="42" t="str">
-        <f aca="false">IF(OR($J251="",$Q251="",$Q251=0),"",($J251+$R251)/($Q251*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J251="",$Q251="",$Q251=0),"",MAX(($J251+$R251)/($Q251*(1-Assumptions!$B$4)),($J251+$R251)/$Q251+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T251" s="43" t="str">
@@ -25741,7 +25741,7 @@
         <v>55</v>
       </c>
       <c r="S252" s="42" t="str">
-        <f aca="false">IF(OR($J252="",$Q252="",$Q252=0),"",($J252+$R252)/($Q252*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J252="",$Q252="",$Q252=0),"",MAX(($J252+$R252)/($Q252*(1-Assumptions!$B$4)),($J252+$R252)/$Q252+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T252" s="43" t="str">
@@ -25821,7 +25821,7 @@
         <v>55</v>
       </c>
       <c r="S253" s="42" t="str">
-        <f aca="false">IF(OR($J253="",$Q253="",$Q253=0),"",($J253+$R253)/($Q253*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J253="",$Q253="",$Q253=0),"",MAX(($J253+$R253)/($Q253*(1-Assumptions!$B$4)),($J253+$R253)/$Q253+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T253" s="43" t="str">
@@ -25901,7 +25901,7 @@
         <v>55</v>
       </c>
       <c r="S254" s="42" t="str">
-        <f aca="false">IF(OR($J254="",$Q254="",$Q254=0),"",($J254+$R254)/($Q254*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J254="",$Q254="",$Q254=0),"",MAX(($J254+$R254)/($Q254*(1-Assumptions!$B$4)),($J254+$R254)/$Q254+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T254" s="43" t="str">
@@ -25981,7 +25981,7 @@
         <v>55</v>
       </c>
       <c r="S255" s="42" t="str">
-        <f aca="false">IF(OR($J255="",$Q255="",$Q255=0),"",($J255+$R255)/($Q255*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J255="",$Q255="",$Q255=0),"",MAX(($J255+$R255)/($Q255*(1-Assumptions!$B$4)),($J255+$R255)/$Q255+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T255" s="43" t="str">
@@ -26061,7 +26061,7 @@
         <v>55</v>
       </c>
       <c r="S256" s="42" t="str">
-        <f aca="false">IF(OR($J256="",$Q256="",$Q256=0),"",($J256+$R256)/($Q256*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J256="",$Q256="",$Q256=0),"",MAX(($J256+$R256)/($Q256*(1-Assumptions!$B$4)),($J256+$R256)/$Q256+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T256" s="43" t="str">
@@ -26141,7 +26141,7 @@
         <v>55</v>
       </c>
       <c r="S257" s="42" t="str">
-        <f aca="false">IF(OR($J257="",$Q257="",$Q257=0),"",($J257+$R257)/($Q257*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J257="",$Q257="",$Q257=0),"",MAX(($J257+$R257)/($Q257*(1-Assumptions!$B$4)),($J257+$R257)/$Q257+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T257" s="43" t="str">
@@ -26221,7 +26221,7 @@
         <v>55</v>
       </c>
       <c r="S258" s="42" t="str">
-        <f aca="false">IF(OR($J258="",$Q258="",$Q258=0),"",($J258+$R258)/($Q258*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J258="",$Q258="",$Q258=0),"",MAX(($J258+$R258)/($Q258*(1-Assumptions!$B$4)),($J258+$R258)/$Q258+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T258" s="43" t="str">
@@ -26301,7 +26301,7 @@
         <v>55</v>
       </c>
       <c r="S259" s="42" t="str">
-        <f aca="false">IF(OR($J259="",$Q259="",$Q259=0),"",($J259+$R259)/($Q259*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J259="",$Q259="",$Q259=0),"",MAX(($J259+$R259)/($Q259*(1-Assumptions!$B$4)),($J259+$R259)/$Q259+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T259" s="43" t="str">
@@ -26381,7 +26381,7 @@
         <v>55</v>
       </c>
       <c r="S260" s="42" t="str">
-        <f aca="false">IF(OR($J260="",$Q260="",$Q260=0),"",($J260+$R260)/($Q260*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J260="",$Q260="",$Q260=0),"",MAX(($J260+$R260)/($Q260*(1-Assumptions!$B$4)),($J260+$R260)/$Q260+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T260" s="43" t="str">
@@ -26461,7 +26461,7 @@
         <v>55</v>
       </c>
       <c r="S261" s="42" t="str">
-        <f aca="false">IF(OR($J261="",$Q261="",$Q261=0),"",($J261+$R261)/($Q261*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J261="",$Q261="",$Q261=0),"",MAX(($J261+$R261)/($Q261*(1-Assumptions!$B$4)),($J261+$R261)/$Q261+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T261" s="43" t="str">
@@ -26527,7 +26527,7 @@
         <v/>
       </c>
       <c r="S262" s="42" t="str">
-        <f aca="false">IF(OR($J262="",$Q262="",$Q262=0),"",($J262+$R262)/($Q262*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J262="",$Q262="",$Q262=0),"",MAX(($J262+$R262)/($Q262*(1-Assumptions!$B$4)),($J262+$R262)/$Q262+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T262" s="43" t="str">
@@ -26589,7 +26589,7 @@
         <v/>
       </c>
       <c r="S263" s="42" t="str">
-        <f aca="false">IF(OR($J263="",$Q263="",$Q263=0),"",($J263+$R263)/($Q263*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J263="",$Q263="",$Q263=0),"",MAX(($J263+$R263)/($Q263*(1-Assumptions!$B$4)),($J263+$R263)/$Q263+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T263" s="43" t="str">
@@ -26651,7 +26651,7 @@
         <v/>
       </c>
       <c r="S264" s="42" t="str">
-        <f aca="false">IF(OR($J264="",$Q264="",$Q264=0),"",($J264+$R264)/($Q264*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J264="",$Q264="",$Q264=0),"",MAX(($J264+$R264)/($Q264*(1-Assumptions!$B$4)),($J264+$R264)/$Q264+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T264" s="43" t="str">
@@ -26713,7 +26713,7 @@
         <v/>
       </c>
       <c r="S265" s="42" t="str">
-        <f aca="false">IF(OR($J265="",$Q265="",$Q265=0),"",($J265+$R265)/($Q265*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J265="",$Q265="",$Q265=0),"",MAX(($J265+$R265)/($Q265*(1-Assumptions!$B$4)),($J265+$R265)/$Q265+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T265" s="43" t="str">
@@ -26775,7 +26775,7 @@
         <v/>
       </c>
       <c r="S266" s="42" t="str">
-        <f aca="false">IF(OR($J266="",$Q266="",$Q266=0),"",($J266+$R266)/($Q266*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J266="",$Q266="",$Q266=0),"",MAX(($J266+$R266)/($Q266*(1-Assumptions!$B$4)),($J266+$R266)/$Q266+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T266" s="43" t="str">
@@ -26837,7 +26837,7 @@
         <v/>
       </c>
       <c r="S267" s="42" t="str">
-        <f aca="false">IF(OR($J267="",$Q267="",$Q267=0),"",($J267+$R267)/($Q267*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J267="",$Q267="",$Q267=0),"",MAX(($J267+$R267)/($Q267*(1-Assumptions!$B$4)),($J267+$R267)/$Q267+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T267" s="43" t="str">
@@ -26899,7 +26899,7 @@
         <v/>
       </c>
       <c r="S268" s="42" t="str">
-        <f aca="false">IF(OR($J268="",$Q268="",$Q268=0),"",($J268+$R268)/($Q268*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J268="",$Q268="",$Q268=0),"",MAX(($J268+$R268)/($Q268*(1-Assumptions!$B$4)),($J268+$R268)/$Q268+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T268" s="43" t="str">
@@ -26961,7 +26961,7 @@
         <v/>
       </c>
       <c r="S269" s="42" t="str">
-        <f aca="false">IF(OR($J269="",$Q269="",$Q269=0),"",($J269+$R269)/($Q269*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J269="",$Q269="",$Q269=0),"",MAX(($J269+$R269)/($Q269*(1-Assumptions!$B$4)),($J269+$R269)/$Q269+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T269" s="43" t="str">
@@ -27023,7 +27023,7 @@
         <v/>
       </c>
       <c r="S270" s="42" t="str">
-        <f aca="false">IF(OR($J270="",$Q270="",$Q270=0),"",($J270+$R270)/($Q270*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J270="",$Q270="",$Q270=0),"",MAX(($J270+$R270)/($Q270*(1-Assumptions!$B$4)),($J270+$R270)/$Q270+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T270" s="43" t="str">
@@ -27085,7 +27085,7 @@
         <v/>
       </c>
       <c r="S271" s="42" t="str">
-        <f aca="false">IF(OR($J271="",$Q271="",$Q271=0),"",($J271+$R271)/($Q271*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J271="",$Q271="",$Q271=0),"",MAX(($J271+$R271)/($Q271*(1-Assumptions!$B$4)),($J271+$R271)/$Q271+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T271" s="43" t="str">
@@ -27147,7 +27147,7 @@
         <v/>
       </c>
       <c r="S272" s="42" t="str">
-        <f aca="false">IF(OR($J272="",$Q272="",$Q272=0),"",($J272+$R272)/($Q272*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J272="",$Q272="",$Q272=0),"",MAX(($J272+$R272)/($Q272*(1-Assumptions!$B$4)),($J272+$R272)/$Q272+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T272" s="43" t="str">
@@ -27209,7 +27209,7 @@
         <v/>
       </c>
       <c r="S273" s="42" t="str">
-        <f aca="false">IF(OR($J273="",$Q273="",$Q273=0),"",($J273+$R273)/($Q273*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J273="",$Q273="",$Q273=0),"",MAX(($J273+$R273)/($Q273*(1-Assumptions!$B$4)),($J273+$R273)/$Q273+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T273" s="43" t="str">
@@ -27271,7 +27271,7 @@
         <v/>
       </c>
       <c r="S274" s="42" t="str">
-        <f aca="false">IF(OR($J274="",$Q274="",$Q274=0),"",($J274+$R274)/($Q274*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J274="",$Q274="",$Q274=0),"",MAX(($J274+$R274)/($Q274*(1-Assumptions!$B$4)),($J274+$R274)/$Q274+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T274" s="43" t="str">
@@ -27333,7 +27333,7 @@
         <v/>
       </c>
       <c r="S275" s="42" t="str">
-        <f aca="false">IF(OR($J275="",$Q275="",$Q275=0),"",($J275+$R275)/($Q275*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J275="",$Q275="",$Q275=0),"",MAX(($J275+$R275)/($Q275*(1-Assumptions!$B$4)),($J275+$R275)/$Q275+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T275" s="43" t="str">
@@ -27395,7 +27395,7 @@
         <v/>
       </c>
       <c r="S276" s="42" t="str">
-        <f aca="false">IF(OR($J276="",$Q276="",$Q276=0),"",($J276+$R276)/($Q276*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J276="",$Q276="",$Q276=0),"",MAX(($J276+$R276)/($Q276*(1-Assumptions!$B$4)),($J276+$R276)/$Q276+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T276" s="43" t="str">
@@ -27457,7 +27457,7 @@
         <v/>
       </c>
       <c r="S277" s="42" t="str">
-        <f aca="false">IF(OR($J277="",$Q277="",$Q277=0),"",($J277+$R277)/($Q277*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J277="",$Q277="",$Q277=0),"",MAX(($J277+$R277)/($Q277*(1-Assumptions!$B$4)),($J277+$R277)/$Q277+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T277" s="43" t="str">
@@ -27519,7 +27519,7 @@
         <v/>
       </c>
       <c r="S278" s="42" t="str">
-        <f aca="false">IF(OR($J278="",$Q278="",$Q278=0),"",($J278+$R278)/($Q278*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J278="",$Q278="",$Q278=0),"",MAX(($J278+$R278)/($Q278*(1-Assumptions!$B$4)),($J278+$R278)/$Q278+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T278" s="43" t="str">
@@ -27581,7 +27581,7 @@
         <v/>
       </c>
       <c r="S279" s="42" t="str">
-        <f aca="false">IF(OR($J279="",$Q279="",$Q279=0),"",($J279+$R279)/($Q279*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J279="",$Q279="",$Q279=0),"",MAX(($J279+$R279)/($Q279*(1-Assumptions!$B$4)),($J279+$R279)/$Q279+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T279" s="43" t="str">
@@ -27643,7 +27643,7 @@
         <v/>
       </c>
       <c r="S280" s="42" t="str">
-        <f aca="false">IF(OR($J280="",$Q280="",$Q280=0),"",($J280+$R280)/($Q280*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J280="",$Q280="",$Q280=0),"",MAX(($J280+$R280)/($Q280*(1-Assumptions!$B$4)),($J280+$R280)/$Q280+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T280" s="43" t="str">
@@ -27705,7 +27705,7 @@
         <v/>
       </c>
       <c r="S281" s="42" t="str">
-        <f aca="false">IF(OR($J281="",$Q281="",$Q281=0),"",($J281+$R281)/($Q281*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J281="",$Q281="",$Q281=0),"",MAX(($J281+$R281)/($Q281*(1-Assumptions!$B$4)),($J281+$R281)/$Q281+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T281" s="43" t="str">
@@ -27767,7 +27767,7 @@
         <v/>
       </c>
       <c r="S282" s="42" t="str">
-        <f aca="false">IF(OR($J282="",$Q282="",$Q282=0),"",($J282+$R282)/($Q282*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J282="",$Q282="",$Q282=0),"",MAX(($J282+$R282)/($Q282*(1-Assumptions!$B$4)),($J282+$R282)/$Q282+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T282" s="43" t="str">
@@ -27829,7 +27829,7 @@
         <v/>
       </c>
       <c r="S283" s="42" t="str">
-        <f aca="false">IF(OR($J283="",$Q283="",$Q283=0),"",($J283+$R283)/($Q283*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J283="",$Q283="",$Q283=0),"",MAX(($J283+$R283)/($Q283*(1-Assumptions!$B$4)),($J283+$R283)/$Q283+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T283" s="43" t="str">
@@ -27891,7 +27891,7 @@
         <v/>
       </c>
       <c r="S284" s="42" t="str">
-        <f aca="false">IF(OR($J284="",$Q284="",$Q284=0),"",($J284+$R284)/($Q284*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J284="",$Q284="",$Q284=0),"",MAX(($J284+$R284)/($Q284*(1-Assumptions!$B$4)),($J284+$R284)/$Q284+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T284" s="43" t="str">
@@ -27953,7 +27953,7 @@
         <v/>
       </c>
       <c r="S285" s="42" t="str">
-        <f aca="false">IF(OR($J285="",$Q285="",$Q285=0),"",($J285+$R285)/($Q285*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J285="",$Q285="",$Q285=0),"",MAX(($J285+$R285)/($Q285*(1-Assumptions!$B$4)),($J285+$R285)/$Q285+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T285" s="43" t="str">
@@ -28015,7 +28015,7 @@
         <v/>
       </c>
       <c r="S286" s="42" t="str">
-        <f aca="false">IF(OR($J286="",$Q286="",$Q286=0),"",($J286+$R286)/($Q286*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J286="",$Q286="",$Q286=0),"",MAX(($J286+$R286)/($Q286*(1-Assumptions!$B$4)),($J286+$R286)/$Q286+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T286" s="43" t="str">
@@ -28077,7 +28077,7 @@
         <v/>
       </c>
       <c r="S287" s="42" t="str">
-        <f aca="false">IF(OR($J287="",$Q287="",$Q287=0),"",($J287+$R287)/($Q287*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J287="",$Q287="",$Q287=0),"",MAX(($J287+$R287)/($Q287*(1-Assumptions!$B$4)),($J287+$R287)/$Q287+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T287" s="43" t="str">
@@ -28139,7 +28139,7 @@
         <v/>
       </c>
       <c r="S288" s="42" t="str">
-        <f aca="false">IF(OR($J288="",$Q288="",$Q288=0),"",($J288+$R288)/($Q288*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J288="",$Q288="",$Q288=0),"",MAX(($J288+$R288)/($Q288*(1-Assumptions!$B$4)),($J288+$R288)/$Q288+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T288" s="43" t="str">
@@ -28201,7 +28201,7 @@
         <v/>
       </c>
       <c r="S289" s="42" t="str">
-        <f aca="false">IF(OR($J289="",$Q289="",$Q289=0),"",($J289+$R289)/($Q289*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J289="",$Q289="",$Q289=0),"",MAX(($J289+$R289)/($Q289*(1-Assumptions!$B$4)),($J289+$R289)/$Q289+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T289" s="43" t="str">
@@ -28263,7 +28263,7 @@
         <v/>
       </c>
       <c r="S290" s="42" t="str">
-        <f aca="false">IF(OR($J290="",$Q290="",$Q290=0),"",($J290+$R290)/($Q290*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J290="",$Q290="",$Q290=0),"",MAX(($J290+$R290)/($Q290*(1-Assumptions!$B$4)),($J290+$R290)/$Q290+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T290" s="43" t="str">
@@ -28325,7 +28325,7 @@
         <v/>
       </c>
       <c r="S291" s="42" t="str">
-        <f aca="false">IF(OR($J291="",$Q291="",$Q291=0),"",($J291+$R291)/($Q291*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J291="",$Q291="",$Q291=0),"",MAX(($J291+$R291)/($Q291*(1-Assumptions!$B$4)),($J291+$R291)/$Q291+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T291" s="43" t="str">
@@ -28387,7 +28387,7 @@
         <v/>
       </c>
       <c r="S292" s="42" t="str">
-        <f aca="false">IF(OR($J292="",$Q292="",$Q292=0),"",($J292+$R292)/($Q292*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J292="",$Q292="",$Q292=0),"",MAX(($J292+$R292)/($Q292*(1-Assumptions!$B$4)),($J292+$R292)/$Q292+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T292" s="43" t="str">
@@ -28449,7 +28449,7 @@
         <v/>
       </c>
       <c r="S293" s="42" t="str">
-        <f aca="false">IF(OR($J293="",$Q293="",$Q293=0),"",($J293+$R293)/($Q293*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J293="",$Q293="",$Q293=0),"",MAX(($J293+$R293)/($Q293*(1-Assumptions!$B$4)),($J293+$R293)/$Q293+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T293" s="43" t="str">
@@ -28511,7 +28511,7 @@
         <v/>
       </c>
       <c r="S294" s="42" t="str">
-        <f aca="false">IF(OR($J294="",$Q294="",$Q294=0),"",($J294+$R294)/($Q294*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J294="",$Q294="",$Q294=0),"",MAX(($J294+$R294)/($Q294*(1-Assumptions!$B$4)),($J294+$R294)/$Q294+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T294" s="43" t="str">
@@ -28573,7 +28573,7 @@
         <v/>
       </c>
       <c r="S295" s="42" t="str">
-        <f aca="false">IF(OR($J295="",$Q295="",$Q295=0),"",($J295+$R295)/($Q295*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J295="",$Q295="",$Q295=0),"",MAX(($J295+$R295)/($Q295*(1-Assumptions!$B$4)),($J295+$R295)/$Q295+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T295" s="43" t="str">
@@ -28635,7 +28635,7 @@
         <v/>
       </c>
       <c r="S296" s="42" t="str">
-        <f aca="false">IF(OR($J296="",$Q296="",$Q296=0),"",($J296+$R296)/($Q296*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J296="",$Q296="",$Q296=0),"",MAX(($J296+$R296)/($Q296*(1-Assumptions!$B$4)),($J296+$R296)/$Q296+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T296" s="43" t="str">
@@ -28697,7 +28697,7 @@
         <v/>
       </c>
       <c r="S297" s="42" t="str">
-        <f aca="false">IF(OR($J297="",$Q297="",$Q297=0),"",($J297+$R297)/($Q297*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J297="",$Q297="",$Q297=0),"",MAX(($J297+$R297)/($Q297*(1-Assumptions!$B$4)),($J297+$R297)/$Q297+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T297" s="43" t="str">
@@ -28759,7 +28759,7 @@
         <v/>
       </c>
       <c r="S298" s="42" t="str">
-        <f aca="false">IF(OR($J298="",$Q298="",$Q298=0),"",($J298+$R298)/($Q298*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J298="",$Q298="",$Q298=0),"",MAX(($J298+$R298)/($Q298*(1-Assumptions!$B$4)),($J298+$R298)/$Q298+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T298" s="43" t="str">
@@ -28821,7 +28821,7 @@
         <v/>
       </c>
       <c r="S299" s="42" t="str">
-        <f aca="false">IF(OR($J299="",$Q299="",$Q299=0),"",($J299+$R299)/($Q299*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J299="",$Q299="",$Q299=0),"",MAX(($J299+$R299)/($Q299*(1-Assumptions!$B$4)),($J299+$R299)/$Q299+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T299" s="43" t="str">
@@ -28883,7 +28883,7 @@
         <v/>
       </c>
       <c r="S300" s="42" t="str">
-        <f aca="false">IF(OR($J300="",$Q300="",$Q300=0),"",($J300+$R300)/($Q300*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J300="",$Q300="",$Q300=0),"",MAX(($J300+$R300)/($Q300*(1-Assumptions!$B$4)),($J300+$R300)/$Q300+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T300" s="43" t="str">
@@ -28945,7 +28945,7 @@
         <v/>
       </c>
       <c r="S301" s="42" t="str">
-        <f aca="false">IF(OR($J301="",$Q301="",$Q301=0),"",($J301+$R301)/($Q301*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J301="",$Q301="",$Q301=0),"",MAX(($J301+$R301)/($Q301*(1-Assumptions!$B$4)),($J301+$R301)/$Q301+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T301" s="43" t="str">
@@ -29007,7 +29007,7 @@
         <v/>
       </c>
       <c r="S302" s="42" t="str">
-        <f aca="false">IF(OR($J302="",$Q302="",$Q302=0),"",($J302+$R302)/($Q302*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J302="",$Q302="",$Q302=0),"",MAX(($J302+$R302)/($Q302*(1-Assumptions!$B$4)),($J302+$R302)/$Q302+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T302" s="43" t="str">
@@ -29069,7 +29069,7 @@
         <v/>
       </c>
       <c r="S303" s="42" t="str">
-        <f aca="false">IF(OR($J303="",$Q303="",$Q303=0),"",($J303+$R303)/($Q303*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J303="",$Q303="",$Q303=0),"",MAX(($J303+$R303)/($Q303*(1-Assumptions!$B$4)),($J303+$R303)/$Q303+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T303" s="43" t="str">
@@ -29131,7 +29131,7 @@
         <v/>
       </c>
       <c r="S304" s="42" t="str">
-        <f aca="false">IF(OR($J304="",$Q304="",$Q304=0),"",($J304+$R304)/($Q304*(1-Assumptions!$B$4)))</f>
+        <f aca="false">IF(OR($J304="",$Q304="",$Q304=0),"",MAX(($J304+$R304)/($Q304*(1-Assumptions!$B$4)),($J304+$R304)/$Q304+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="T304" s="43" t="str">
@@ -40667,7 +40667,7 @@
         <v>2422</v>
       </c>
       <c r="K5" s="32" t="n">
-        <f aca="false">IF(OR($J5="",$J5=0),"",$J5/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J5="",$J5=0),"",MAX($J5/(1-Assumptions!$B$4),$J5+Assumptions!$B$5))</f>
         <v>3027.5</v>
       </c>
       <c r="L5" s="32" t="n">
@@ -40711,7 +40711,7 @@
         <v/>
       </c>
       <c r="K6" s="42" t="str">
-        <f aca="false">IF(OR($J6="",$J6=0),"",$J6/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J6="",$J6=0),"",MAX($J6/(1-Assumptions!$B$4),$J6+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L6" s="42" t="str">
@@ -40751,7 +40751,7 @@
         <v/>
       </c>
       <c r="K7" s="42" t="str">
-        <f aca="false">IF(OR($J7="",$J7=0),"",$J7/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J7="",$J7=0),"",MAX($J7/(1-Assumptions!$B$4),$J7+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L7" s="42" t="str">
@@ -40791,7 +40791,7 @@
         <v/>
       </c>
       <c r="K8" s="42" t="str">
-        <f aca="false">IF(OR($J8="",$J8=0),"",$J8/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J8="",$J8=0),"",MAX($J8/(1-Assumptions!$B$4),$J8+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L8" s="42" t="str">
@@ -40831,7 +40831,7 @@
         <v/>
       </c>
       <c r="K9" s="42" t="str">
-        <f aca="false">IF(OR($J9="",$J9=0),"",$J9/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J9="",$J9=0),"",MAX($J9/(1-Assumptions!$B$4),$J9+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L9" s="42" t="str">
@@ -40871,7 +40871,7 @@
         <v/>
       </c>
       <c r="K10" s="42" t="str">
-        <f aca="false">IF(OR($J10="",$J10=0),"",$J10/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J10="",$J10=0),"",MAX($J10/(1-Assumptions!$B$4),$J10+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L10" s="42" t="str">
@@ -40911,7 +40911,7 @@
         <v/>
       </c>
       <c r="K11" s="42" t="str">
-        <f aca="false">IF(OR($J11="",$J11=0),"",$J11/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J11="",$J11=0),"",MAX($J11/(1-Assumptions!$B$4),$J11+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L11" s="42" t="str">
@@ -40951,7 +40951,7 @@
         <v/>
       </c>
       <c r="K12" s="42" t="str">
-        <f aca="false">IF(OR($J12="",$J12=0),"",$J12/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J12="",$J12=0),"",MAX($J12/(1-Assumptions!$B$4),$J12+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L12" s="42" t="str">
@@ -40991,7 +40991,7 @@
         <v/>
       </c>
       <c r="K13" s="42" t="str">
-        <f aca="false">IF(OR($J13="",$J13=0),"",$J13/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J13="",$J13=0),"",MAX($J13/(1-Assumptions!$B$4),$J13+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L13" s="42" t="str">
@@ -41031,7 +41031,7 @@
         <v/>
       </c>
       <c r="K14" s="42" t="str">
-        <f aca="false">IF(OR($J14="",$J14=0),"",$J14/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J14="",$J14=0),"",MAX($J14/(1-Assumptions!$B$4),$J14+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L14" s="42" t="str">
@@ -41071,7 +41071,7 @@
         <v/>
       </c>
       <c r="K15" s="42" t="str">
-        <f aca="false">IF(OR($J15="",$J15=0),"",$J15/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J15="",$J15=0),"",MAX($J15/(1-Assumptions!$B$4),$J15+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L15" s="42" t="str">
@@ -41111,7 +41111,7 @@
         <v/>
       </c>
       <c r="K16" s="42" t="str">
-        <f aca="false">IF(OR($J16="",$J16=0),"",$J16/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J16="",$J16=0),"",MAX($J16/(1-Assumptions!$B$4),$J16+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L16" s="42" t="str">
@@ -41151,7 +41151,7 @@
         <v/>
       </c>
       <c r="K17" s="42" t="str">
-        <f aca="false">IF(OR($J17="",$J17=0),"",$J17/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J17="",$J17=0),"",MAX($J17/(1-Assumptions!$B$4),$J17+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L17" s="42" t="str">
@@ -41191,7 +41191,7 @@
         <v/>
       </c>
       <c r="K18" s="42" t="str">
-        <f aca="false">IF(OR($J18="",$J18=0),"",$J18/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J18="",$J18=0),"",MAX($J18/(1-Assumptions!$B$4),$J18+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L18" s="42" t="str">
@@ -41231,7 +41231,7 @@
         <v/>
       </c>
       <c r="K19" s="42" t="str">
-        <f aca="false">IF(OR($J19="",$J19=0),"",$J19/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J19="",$J19=0),"",MAX($J19/(1-Assumptions!$B$4),$J19+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L19" s="42" t="str">
@@ -41271,7 +41271,7 @@
         <v/>
       </c>
       <c r="K20" s="42" t="str">
-        <f aca="false">IF(OR($J20="",$J20=0),"",$J20/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J20="",$J20=0),"",MAX($J20/(1-Assumptions!$B$4),$J20+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L20" s="42" t="str">
@@ -41311,7 +41311,7 @@
         <v/>
       </c>
       <c r="K21" s="42" t="str">
-        <f aca="false">IF(OR($J21="",$J21=0),"",$J21/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J21="",$J21=0),"",MAX($J21/(1-Assumptions!$B$4),$J21+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L21" s="42" t="str">
@@ -41351,7 +41351,7 @@
         <v/>
       </c>
       <c r="K22" s="42" t="str">
-        <f aca="false">IF(OR($J22="",$J22=0),"",$J22/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J22="",$J22=0),"",MAX($J22/(1-Assumptions!$B$4),$J22+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L22" s="42" t="str">
@@ -41391,7 +41391,7 @@
         <v/>
       </c>
       <c r="K23" s="42" t="str">
-        <f aca="false">IF(OR($J23="",$J23=0),"",$J23/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J23="",$J23=0),"",MAX($J23/(1-Assumptions!$B$4),$J23+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L23" s="42" t="str">
@@ -41431,7 +41431,7 @@
         <v/>
       </c>
       <c r="K24" s="42" t="str">
-        <f aca="false">IF(OR($J24="",$J24=0),"",$J24/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J24="",$J24=0),"",MAX($J24/(1-Assumptions!$B$4),$J24+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L24" s="42" t="str">
@@ -41471,7 +41471,7 @@
         <v/>
       </c>
       <c r="K25" s="42" t="str">
-        <f aca="false">IF(OR($J25="",$J25=0),"",$J25/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J25="",$J25=0),"",MAX($J25/(1-Assumptions!$B$4),$J25+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L25" s="42" t="str">
@@ -41511,7 +41511,7 @@
         <v/>
       </c>
       <c r="K26" s="42" t="str">
-        <f aca="false">IF(OR($J26="",$J26=0),"",$J26/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J26="",$J26=0),"",MAX($J26/(1-Assumptions!$B$4),$J26+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L26" s="42" t="str">
@@ -41551,7 +41551,7 @@
         <v/>
       </c>
       <c r="K27" s="42" t="str">
-        <f aca="false">IF(OR($J27="",$J27=0),"",$J27/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J27="",$J27=0),"",MAX($J27/(1-Assumptions!$B$4),$J27+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L27" s="42" t="str">
@@ -41591,7 +41591,7 @@
         <v/>
       </c>
       <c r="K28" s="42" t="str">
-        <f aca="false">IF(OR($J28="",$J28=0),"",$J28/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J28="",$J28=0),"",MAX($J28/(1-Assumptions!$B$4),$J28+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L28" s="42" t="str">
@@ -41631,7 +41631,7 @@
         <v/>
       </c>
       <c r="K29" s="42" t="str">
-        <f aca="false">IF(OR($J29="",$J29=0),"",$J29/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J29="",$J29=0),"",MAX($J29/(1-Assumptions!$B$4),$J29+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L29" s="42" t="str">
@@ -41671,7 +41671,7 @@
         <v/>
       </c>
       <c r="K30" s="42" t="str">
-        <f aca="false">IF(OR($J30="",$J30=0),"",$J30/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J30="",$J30=0),"",MAX($J30/(1-Assumptions!$B$4),$J30+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L30" s="42" t="str">
@@ -41711,7 +41711,7 @@
         <v/>
       </c>
       <c r="K31" s="42" t="str">
-        <f aca="false">IF(OR($J31="",$J31=0),"",$J31/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J31="",$J31=0),"",MAX($J31/(1-Assumptions!$B$4),$J31+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L31" s="42" t="str">
@@ -41751,7 +41751,7 @@
         <v/>
       </c>
       <c r="K32" s="42" t="str">
-        <f aca="false">IF(OR($J32="",$J32=0),"",$J32/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J32="",$J32=0),"",MAX($J32/(1-Assumptions!$B$4),$J32+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L32" s="42" t="str">
@@ -41791,7 +41791,7 @@
         <v/>
       </c>
       <c r="K33" s="42" t="str">
-        <f aca="false">IF(OR($J33="",$J33=0),"",$J33/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J33="",$J33=0),"",MAX($J33/(1-Assumptions!$B$4),$J33+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L33" s="42" t="str">
@@ -41831,7 +41831,7 @@
         <v/>
       </c>
       <c r="K34" s="42" t="str">
-        <f aca="false">IF(OR($J34="",$J34=0),"",$J34/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J34="",$J34=0),"",MAX($J34/(1-Assumptions!$B$4),$J34+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L34" s="42" t="str">
@@ -41871,7 +41871,7 @@
         <v/>
       </c>
       <c r="K35" s="42" t="str">
-        <f aca="false">IF(OR($J35="",$J35=0),"",$J35/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J35="",$J35=0),"",MAX($J35/(1-Assumptions!$B$4),$J35+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L35" s="42" t="str">
@@ -41911,7 +41911,7 @@
         <v/>
       </c>
       <c r="K36" s="42" t="str">
-        <f aca="false">IF(OR($J36="",$J36=0),"",$J36/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J36="",$J36=0),"",MAX($J36/(1-Assumptions!$B$4),$J36+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L36" s="42" t="str">
@@ -41951,7 +41951,7 @@
         <v/>
       </c>
       <c r="K37" s="42" t="str">
-        <f aca="false">IF(OR($J37="",$J37=0),"",$J37/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J37="",$J37=0),"",MAX($J37/(1-Assumptions!$B$4),$J37+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L37" s="42" t="str">
@@ -41991,7 +41991,7 @@
         <v/>
       </c>
       <c r="K38" s="42" t="str">
-        <f aca="false">IF(OR($J38="",$J38=0),"",$J38/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J38="",$J38=0),"",MAX($J38/(1-Assumptions!$B$4),$J38+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L38" s="42" t="str">
@@ -42031,7 +42031,7 @@
         <v/>
       </c>
       <c r="K39" s="42" t="str">
-        <f aca="false">IF(OR($J39="",$J39=0),"",$J39/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J39="",$J39=0),"",MAX($J39/(1-Assumptions!$B$4),$J39+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L39" s="42" t="str">
@@ -42071,7 +42071,7 @@
         <v/>
       </c>
       <c r="K40" s="42" t="str">
-        <f aca="false">IF(OR($J40="",$J40=0),"",$J40/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J40="",$J40=0),"",MAX($J40/(1-Assumptions!$B$4),$J40+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L40" s="42" t="str">
@@ -42111,7 +42111,7 @@
         <v/>
       </c>
       <c r="K41" s="42" t="str">
-        <f aca="false">IF(OR($J41="",$J41=0),"",$J41/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J41="",$J41=0),"",MAX($J41/(1-Assumptions!$B$4),$J41+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L41" s="42" t="str">
@@ -42151,7 +42151,7 @@
         <v/>
       </c>
       <c r="K42" s="42" t="str">
-        <f aca="false">IF(OR($J42="",$J42=0),"",$J42/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J42="",$J42=0),"",MAX($J42/(1-Assumptions!$B$4),$J42+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L42" s="42" t="str">
@@ -42191,7 +42191,7 @@
         <v/>
       </c>
       <c r="K43" s="42" t="str">
-        <f aca="false">IF(OR($J43="",$J43=0),"",$J43/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J43="",$J43=0),"",MAX($J43/(1-Assumptions!$B$4),$J43+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L43" s="42" t="str">
@@ -42231,7 +42231,7 @@
         <v/>
       </c>
       <c r="K44" s="42" t="str">
-        <f aca="false">IF(OR($J44="",$J44=0),"",$J44/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J44="",$J44=0),"",MAX($J44/(1-Assumptions!$B$4),$J44+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L44" s="42" t="str">
@@ -42271,7 +42271,7 @@
         <v/>
       </c>
       <c r="K45" s="42" t="str">
-        <f aca="false">IF(OR($J45="",$J45=0),"",$J45/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J45="",$J45=0),"",MAX($J45/(1-Assumptions!$B$4),$J45+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L45" s="42" t="str">
@@ -42311,7 +42311,7 @@
         <v/>
       </c>
       <c r="K46" s="42" t="str">
-        <f aca="false">IF(OR($J46="",$J46=0),"",$J46/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J46="",$J46=0),"",MAX($J46/(1-Assumptions!$B$4),$J46+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L46" s="42" t="str">
@@ -42351,7 +42351,7 @@
         <v/>
       </c>
       <c r="K47" s="42" t="str">
-        <f aca="false">IF(OR($J47="",$J47=0),"",$J47/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J47="",$J47=0),"",MAX($J47/(1-Assumptions!$B$4),$J47+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L47" s="42" t="str">
@@ -42391,7 +42391,7 @@
         <v/>
       </c>
       <c r="K48" s="42" t="str">
-        <f aca="false">IF(OR($J48="",$J48=0),"",$J48/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J48="",$J48=0),"",MAX($J48/(1-Assumptions!$B$4),$J48+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L48" s="42" t="str">
@@ -42431,7 +42431,7 @@
         <v/>
       </c>
       <c r="K49" s="42" t="str">
-        <f aca="false">IF(OR($J49="",$J49=0),"",$J49/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J49="",$J49=0),"",MAX($J49/(1-Assumptions!$B$4),$J49+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L49" s="42" t="str">
@@ -42471,7 +42471,7 @@
         <v/>
       </c>
       <c r="K50" s="42" t="str">
-        <f aca="false">IF(OR($J50="",$J50=0),"",$J50/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J50="",$J50=0),"",MAX($J50/(1-Assumptions!$B$4),$J50+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L50" s="42" t="str">
@@ -42511,7 +42511,7 @@
         <v/>
       </c>
       <c r="K51" s="42" t="str">
-        <f aca="false">IF(OR($J51="",$J51=0),"",$J51/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J51="",$J51=0),"",MAX($J51/(1-Assumptions!$B$4),$J51+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L51" s="42" t="str">
@@ -42551,7 +42551,7 @@
         <v/>
       </c>
       <c r="K52" s="42" t="str">
-        <f aca="false">IF(OR($J52="",$J52=0),"",$J52/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J52="",$J52=0),"",MAX($J52/(1-Assumptions!$B$4),$J52+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L52" s="42" t="str">
@@ -42591,7 +42591,7 @@
         <v/>
       </c>
       <c r="K53" s="42" t="str">
-        <f aca="false">IF(OR($J53="",$J53=0),"",$J53/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J53="",$J53=0),"",MAX($J53/(1-Assumptions!$B$4),$J53+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L53" s="42" t="str">
@@ -42631,7 +42631,7 @@
         <v/>
       </c>
       <c r="K54" s="42" t="str">
-        <f aca="false">IF(OR($J54="",$J54=0),"",$J54/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J54="",$J54=0),"",MAX($J54/(1-Assumptions!$B$4),$J54+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L54" s="42" t="str">
@@ -42671,7 +42671,7 @@
         <v/>
       </c>
       <c r="K55" s="42" t="str">
-        <f aca="false">IF(OR($J55="",$J55=0),"",$J55/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J55="",$J55=0),"",MAX($J55/(1-Assumptions!$B$4),$J55+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L55" s="42" t="str">
@@ -42711,7 +42711,7 @@
         <v/>
       </c>
       <c r="K56" s="42" t="str">
-        <f aca="false">IF(OR($J56="",$J56=0),"",$J56/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J56="",$J56=0),"",MAX($J56/(1-Assumptions!$B$4),$J56+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L56" s="42" t="str">
@@ -42751,7 +42751,7 @@
         <v/>
       </c>
       <c r="K57" s="42" t="str">
-        <f aca="false">IF(OR($J57="",$J57=0),"",$J57/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J57="",$J57=0),"",MAX($J57/(1-Assumptions!$B$4),$J57+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L57" s="42" t="str">
@@ -42791,7 +42791,7 @@
         <v/>
       </c>
       <c r="K58" s="42" t="str">
-        <f aca="false">IF(OR($J58="",$J58=0),"",$J58/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J58="",$J58=0),"",MAX($J58/(1-Assumptions!$B$4),$J58+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L58" s="42" t="str">
@@ -42831,7 +42831,7 @@
         <v/>
       </c>
       <c r="K59" s="42" t="str">
-        <f aca="false">IF(OR($J59="",$J59=0),"",$J59/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J59="",$J59=0),"",MAX($J59/(1-Assumptions!$B$4),$J59+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L59" s="42" t="str">
@@ -42871,7 +42871,7 @@
         <v/>
       </c>
       <c r="K60" s="42" t="str">
-        <f aca="false">IF(OR($J60="",$J60=0),"",$J60/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J60="",$J60=0),"",MAX($J60/(1-Assumptions!$B$4),$J60+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L60" s="42" t="str">
@@ -42911,7 +42911,7 @@
         <v/>
       </c>
       <c r="K61" s="42" t="str">
-        <f aca="false">IF(OR($J61="",$J61=0),"",$J61/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J61="",$J61=0),"",MAX($J61/(1-Assumptions!$B$4),$J61+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L61" s="42" t="str">
@@ -42951,7 +42951,7 @@
         <v/>
       </c>
       <c r="K62" s="42" t="str">
-        <f aca="false">IF(OR($J62="",$J62=0),"",$J62/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J62="",$J62=0),"",MAX($J62/(1-Assumptions!$B$4),$J62+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L62" s="42" t="str">
@@ -42991,7 +42991,7 @@
         <v/>
       </c>
       <c r="K63" s="42" t="str">
-        <f aca="false">IF(OR($J63="",$J63=0),"",$J63/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J63="",$J63=0),"",MAX($J63/(1-Assumptions!$B$4),$J63+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L63" s="42" t="str">
@@ -43031,7 +43031,7 @@
         <v/>
       </c>
       <c r="K64" s="42" t="str">
-        <f aca="false">IF(OR($J64="",$J64=0),"",$J64/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J64="",$J64=0),"",MAX($J64/(1-Assumptions!$B$4),$J64+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L64" s="42" t="str">
@@ -43071,7 +43071,7 @@
         <v/>
       </c>
       <c r="K65" s="42" t="str">
-        <f aca="false">IF(OR($J65="",$J65=0),"",$J65/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J65="",$J65=0),"",MAX($J65/(1-Assumptions!$B$4),$J65+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L65" s="42" t="str">
@@ -43111,7 +43111,7 @@
         <v/>
       </c>
       <c r="K66" s="42" t="str">
-        <f aca="false">IF(OR($J66="",$J66=0),"",$J66/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J66="",$J66=0),"",MAX($J66/(1-Assumptions!$B$4),$J66+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L66" s="42" t="str">
@@ -43151,7 +43151,7 @@
         <v/>
       </c>
       <c r="K67" s="42" t="str">
-        <f aca="false">IF(OR($J67="",$J67=0),"",$J67/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J67="",$J67=0),"",MAX($J67/(1-Assumptions!$B$4),$J67+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L67" s="42" t="str">
@@ -43191,7 +43191,7 @@
         <v/>
       </c>
       <c r="K68" s="42" t="str">
-        <f aca="false">IF(OR($J68="",$J68=0),"",$J68/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J68="",$J68=0),"",MAX($J68/(1-Assumptions!$B$4),$J68+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L68" s="42" t="str">
@@ -43231,7 +43231,7 @@
         <v/>
       </c>
       <c r="K69" s="42" t="str">
-        <f aca="false">IF(OR($J69="",$J69=0),"",$J69/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J69="",$J69=0),"",MAX($J69/(1-Assumptions!$B$4),$J69+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L69" s="42" t="str">
@@ -43271,7 +43271,7 @@
         <v/>
       </c>
       <c r="K70" s="42" t="str">
-        <f aca="false">IF(OR($J70="",$J70=0),"",$J70/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J70="",$J70=0),"",MAX($J70/(1-Assumptions!$B$4),$J70+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L70" s="42" t="str">
@@ -43311,7 +43311,7 @@
         <v/>
       </c>
       <c r="K71" s="42" t="str">
-        <f aca="false">IF(OR($J71="",$J71=0),"",$J71/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J71="",$J71=0),"",MAX($J71/(1-Assumptions!$B$4),$J71+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L71" s="42" t="str">
@@ -43351,7 +43351,7 @@
         <v/>
       </c>
       <c r="K72" s="42" t="str">
-        <f aca="false">IF(OR($J72="",$J72=0),"",$J72/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J72="",$J72=0),"",MAX($J72/(1-Assumptions!$B$4),$J72+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L72" s="42" t="str">
@@ -43391,7 +43391,7 @@
         <v/>
       </c>
       <c r="K73" s="42" t="str">
-        <f aca="false">IF(OR($J73="",$J73=0),"",$J73/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J73="",$J73=0),"",MAX($J73/(1-Assumptions!$B$4),$J73+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L73" s="42" t="str">
@@ -43431,7 +43431,7 @@
         <v/>
       </c>
       <c r="K74" s="42" t="str">
-        <f aca="false">IF(OR($J74="",$J74=0),"",$J74/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J74="",$J74=0),"",MAX($J74/(1-Assumptions!$B$4),$J74+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L74" s="42" t="str">
@@ -43471,7 +43471,7 @@
         <v/>
       </c>
       <c r="K75" s="42" t="str">
-        <f aca="false">IF(OR($J75="",$J75=0),"",$J75/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J75="",$J75=0),"",MAX($J75/(1-Assumptions!$B$4),$J75+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L75" s="42" t="str">
@@ -43511,7 +43511,7 @@
         <v/>
       </c>
       <c r="K76" s="42" t="str">
-        <f aca="false">IF(OR($J76="",$J76=0),"",$J76/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J76="",$J76=0),"",MAX($J76/(1-Assumptions!$B$4),$J76+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L76" s="42" t="str">
@@ -43551,7 +43551,7 @@
         <v/>
       </c>
       <c r="K77" s="42" t="str">
-        <f aca="false">IF(OR($J77="",$J77=0),"",$J77/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J77="",$J77=0),"",MAX($J77/(1-Assumptions!$B$4),$J77+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L77" s="42" t="str">
@@ -43591,7 +43591,7 @@
         <v/>
       </c>
       <c r="K78" s="42" t="str">
-        <f aca="false">IF(OR($J78="",$J78=0),"",$J78/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J78="",$J78=0),"",MAX($J78/(1-Assumptions!$B$4),$J78+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L78" s="42" t="str">
@@ -43631,7 +43631,7 @@
         <v/>
       </c>
       <c r="K79" s="42" t="str">
-        <f aca="false">IF(OR($J79="",$J79=0),"",$J79/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J79="",$J79=0),"",MAX($J79/(1-Assumptions!$B$4),$J79+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L79" s="42" t="str">
@@ -43671,7 +43671,7 @@
         <v/>
       </c>
       <c r="K80" s="42" t="str">
-        <f aca="false">IF(OR($J80="",$J80=0),"",$J80/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J80="",$J80=0),"",MAX($J80/(1-Assumptions!$B$4),$J80+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L80" s="42" t="str">
@@ -43711,7 +43711,7 @@
         <v/>
       </c>
       <c r="K81" s="42" t="str">
-        <f aca="false">IF(OR($J81="",$J81=0),"",$J81/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J81="",$J81=0),"",MAX($J81/(1-Assumptions!$B$4),$J81+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L81" s="42" t="str">
@@ -43751,7 +43751,7 @@
         <v/>
       </c>
       <c r="K82" s="42" t="str">
-        <f aca="false">IF(OR($J82="",$J82=0),"",$J82/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J82="",$J82=0),"",MAX($J82/(1-Assumptions!$B$4),$J82+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L82" s="42" t="str">
@@ -43791,7 +43791,7 @@
         <v/>
       </c>
       <c r="K83" s="42" t="str">
-        <f aca="false">IF(OR($J83="",$J83=0),"",$J83/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J83="",$J83=0),"",MAX($J83/(1-Assumptions!$B$4),$J83+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L83" s="42" t="str">
@@ -43831,7 +43831,7 @@
         <v/>
       </c>
       <c r="K84" s="42" t="str">
-        <f aca="false">IF(OR($J84="",$J84=0),"",$J84/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J84="",$J84=0),"",MAX($J84/(1-Assumptions!$B$4),$J84+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L84" s="42" t="str">
@@ -43871,7 +43871,7 @@
         <v/>
       </c>
       <c r="K85" s="42" t="str">
-        <f aca="false">IF(OR($J85="",$J85=0),"",$J85/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J85="",$J85=0),"",MAX($J85/(1-Assumptions!$B$4),$J85+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L85" s="42" t="str">
@@ -43911,7 +43911,7 @@
         <v/>
       </c>
       <c r="K86" s="42" t="str">
-        <f aca="false">IF(OR($J86="",$J86=0),"",$J86/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J86="",$J86=0),"",MAX($J86/(1-Assumptions!$B$4),$J86+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L86" s="42" t="str">
@@ -43951,7 +43951,7 @@
         <v/>
       </c>
       <c r="K87" s="42" t="str">
-        <f aca="false">IF(OR($J87="",$J87=0),"",$J87/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J87="",$J87=0),"",MAX($J87/(1-Assumptions!$B$4),$J87+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L87" s="42" t="str">
@@ -43991,7 +43991,7 @@
         <v/>
       </c>
       <c r="K88" s="42" t="str">
-        <f aca="false">IF(OR($J88="",$J88=0),"",$J88/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J88="",$J88=0),"",MAX($J88/(1-Assumptions!$B$4),$J88+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L88" s="42" t="str">
@@ -44031,7 +44031,7 @@
         <v/>
       </c>
       <c r="K89" s="42" t="str">
-        <f aca="false">IF(OR($J89="",$J89=0),"",$J89/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J89="",$J89=0),"",MAX($J89/(1-Assumptions!$B$4),$J89+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L89" s="42" t="str">
@@ -44071,7 +44071,7 @@
         <v/>
       </c>
       <c r="K90" s="42" t="str">
-        <f aca="false">IF(OR($J90="",$J90=0),"",$J90/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J90="",$J90=0),"",MAX($J90/(1-Assumptions!$B$4),$J90+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L90" s="42" t="str">
@@ -44111,7 +44111,7 @@
         <v/>
       </c>
       <c r="K91" s="42" t="str">
-        <f aca="false">IF(OR($J91="",$J91=0),"",$J91/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J91="",$J91=0),"",MAX($J91/(1-Assumptions!$B$4),$J91+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L91" s="42" t="str">
@@ -44151,7 +44151,7 @@
         <v/>
       </c>
       <c r="K92" s="42" t="str">
-        <f aca="false">IF(OR($J92="",$J92=0),"",$J92/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J92="",$J92=0),"",MAX($J92/(1-Assumptions!$B$4),$J92+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L92" s="42" t="str">
@@ -44191,7 +44191,7 @@
         <v/>
       </c>
       <c r="K93" s="42" t="str">
-        <f aca="false">IF(OR($J93="",$J93=0),"",$J93/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J93="",$J93=0),"",MAX($J93/(1-Assumptions!$B$4),$J93+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L93" s="42" t="str">
@@ -44231,7 +44231,7 @@
         <v/>
       </c>
       <c r="K94" s="42" t="str">
-        <f aca="false">IF(OR($J94="",$J94=0),"",$J94/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J94="",$J94=0),"",MAX($J94/(1-Assumptions!$B$4),$J94+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L94" s="42" t="str">
@@ -44271,7 +44271,7 @@
         <v/>
       </c>
       <c r="K95" s="42" t="str">
-        <f aca="false">IF(OR($J95="",$J95=0),"",$J95/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J95="",$J95=0),"",MAX($J95/(1-Assumptions!$B$4),$J95+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L95" s="42" t="str">
@@ -44311,7 +44311,7 @@
         <v/>
       </c>
       <c r="K96" s="42" t="str">
-        <f aca="false">IF(OR($J96="",$J96=0),"",$J96/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J96="",$J96=0),"",MAX($J96/(1-Assumptions!$B$4),$J96+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L96" s="42" t="str">
@@ -44351,7 +44351,7 @@
         <v/>
       </c>
       <c r="K97" s="42" t="str">
-        <f aca="false">IF(OR($J97="",$J97=0),"",$J97/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J97="",$J97=0),"",MAX($J97/(1-Assumptions!$B$4),$J97+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L97" s="42" t="str">
@@ -44391,7 +44391,7 @@
         <v/>
       </c>
       <c r="K98" s="42" t="str">
-        <f aca="false">IF(OR($J98="",$J98=0),"",$J98/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J98="",$J98=0),"",MAX($J98/(1-Assumptions!$B$4),$J98+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L98" s="42" t="str">
@@ -44431,7 +44431,7 @@
         <v/>
       </c>
       <c r="K99" s="42" t="str">
-        <f aca="false">IF(OR($J99="",$J99=0),"",$J99/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J99="",$J99=0),"",MAX($J99/(1-Assumptions!$B$4),$J99+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L99" s="42" t="str">
@@ -44471,7 +44471,7 @@
         <v/>
       </c>
       <c r="K100" s="42" t="str">
-        <f aca="false">IF(OR($J100="",$J100=0),"",$J100/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J100="",$J100=0),"",MAX($J100/(1-Assumptions!$B$4),$J100+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L100" s="42" t="str">
@@ -44511,7 +44511,7 @@
         <v/>
       </c>
       <c r="K101" s="42" t="str">
-        <f aca="false">IF(OR($J101="",$J101=0),"",$J101/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J101="",$J101=0),"",MAX($J101/(1-Assumptions!$B$4),$J101+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L101" s="42" t="str">
@@ -44551,7 +44551,7 @@
         <v/>
       </c>
       <c r="K102" s="42" t="str">
-        <f aca="false">IF(OR($J102="",$J102=0),"",$J102/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J102="",$J102=0),"",MAX($J102/(1-Assumptions!$B$4),$J102+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L102" s="42" t="str">
@@ -44591,7 +44591,7 @@
         <v/>
       </c>
       <c r="K103" s="42" t="str">
-        <f aca="false">IF(OR($J103="",$J103=0),"",$J103/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J103="",$J103=0),"",MAX($J103/(1-Assumptions!$B$4),$J103+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L103" s="42" t="str">
@@ -44631,7 +44631,7 @@
         <v/>
       </c>
       <c r="K104" s="42" t="str">
-        <f aca="false">IF(OR($J104="",$J104=0),"",$J104/(1-Assumptions!$B$4))</f>
+        <f aca="false">IF(OR($J104="",$J104=0),"",MAX($J104/(1-Assumptions!$B$4),$J104+Assumptions!$B$5))</f>
         <v/>
       </c>
       <c r="L104" s="42" t="str">
